--- a/Results/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.29143996540681</v>
+        <v>21.29143996540591</v>
       </c>
       <c r="C2" t="n">
-        <v>16.17579206403443</v>
+        <v>16.17579206403444</v>
       </c>
       <c r="D2" t="n">
-        <v>38.80103637525647</v>
+        <v>38.80103637525619</v>
       </c>
       <c r="E2" t="n">
-        <v>18.45789882856387</v>
+        <v>18.45789882856366</v>
       </c>
       <c r="F2" t="n">
-        <v>12.01150050606018</v>
+        <v>12.01150050606007</v>
       </c>
       <c r="G2" t="n">
-        <v>27.87386109729521</v>
+        <v>27.87386109729492</v>
       </c>
       <c r="H2" t="n">
-        <v>52.26061188267928</v>
+        <v>52.26061188267933</v>
       </c>
       <c r="I2" t="n">
-        <v>20.67334297961307</v>
+        <v>20.67334297961293</v>
       </c>
       <c r="J2" t="n">
-        <v>32.2091988789413</v>
+        <v>32.20919887894134</v>
       </c>
       <c r="K2" t="n">
-        <v>30.6819386080664</v>
+        <v>30.68193860806652</v>
       </c>
       <c r="L2" t="n">
-        <v>46.5705574769482</v>
+        <v>46.57055747694821</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.0004743712132</v>
+        <v>24.00047437121385</v>
       </c>
       <c r="C3" t="n">
         <v>18.78775569419621</v>
       </c>
       <c r="D3" t="n">
-        <v>44.14013734451093</v>
+        <v>44.14013734451088</v>
       </c>
       <c r="E3" t="n">
-        <v>21.07371698946794</v>
+        <v>21.07371698946796</v>
       </c>
       <c r="F3" t="n">
-        <v>14.62731866696421</v>
+        <v>14.62731866696431</v>
       </c>
       <c r="G3" t="n">
-        <v>31.57162221731599</v>
+        <v>31.57162221731574</v>
       </c>
       <c r="H3" t="n">
-        <v>59.62777470433638</v>
+        <v>59.62777470433645</v>
       </c>
       <c r="I3" t="n">
-        <v>23.28011104934948</v>
+        <v>23.28011104934949</v>
       </c>
       <c r="J3" t="n">
-        <v>35.54560423089676</v>
+        <v>35.54560423089646</v>
       </c>
       <c r="K3" t="n">
-        <v>33.65783883892551</v>
+        <v>33.65783883892499</v>
       </c>
       <c r="L3" t="n">
-        <v>53.07598446174638</v>
+        <v>53.07598446174642</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.43102667924992</v>
+        <v>14.04976533365169</v>
       </c>
       <c r="C4" t="n">
-        <v>41.08598618163295</v>
+        <v>13.33304862022393</v>
       </c>
       <c r="D4" t="n">
-        <v>53.8397398003686</v>
+        <v>24.45847845477068</v>
       </c>
       <c r="E4" t="n">
-        <v>41.23005107086426</v>
+        <v>13.35841075584037</v>
       </c>
       <c r="F4" t="n">
-        <v>41.23005107086428</v>
+        <v>13.35841075584038</v>
       </c>
       <c r="G4" t="n">
-        <v>47.16948121606591</v>
+        <v>17.93202097655913</v>
       </c>
       <c r="H4" t="n">
-        <v>61.83572824725544</v>
+        <v>32.45446690165758</v>
       </c>
       <c r="I4" t="n">
-        <v>41.95326396065999</v>
+        <v>13.48462719554327</v>
       </c>
       <c r="J4" t="n">
-        <v>45.91390079724128</v>
+        <v>16.53263945164335</v>
       </c>
       <c r="K4" t="n">
-        <v>44.48717098121935</v>
+        <v>15.10590963562127</v>
       </c>
       <c r="L4" t="n">
-        <v>58.45528564228541</v>
+        <v>29.07402429668762</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>415.8585612261326</v>
+        <v>79.59701105872118</v>
       </c>
       <c r="C5" t="n">
-        <v>382.6103668125886</v>
+        <v>73.441339285569</v>
       </c>
       <c r="D5" t="n">
-        <v>1508.640351499781</v>
+        <v>280.5033847264604</v>
       </c>
       <c r="E5" t="n">
-        <v>382.6103749621616</v>
+        <v>73.44134743514331</v>
       </c>
       <c r="F5" t="n">
-        <v>382.6103749621616</v>
+        <v>73.44134743514331</v>
       </c>
       <c r="G5" t="n">
-        <v>848.4644866977796</v>
+        <v>158.9599411771654</v>
       </c>
       <c r="H5" t="n">
-        <v>2634.181301509836</v>
+        <v>485.1872853426917</v>
       </c>
       <c r="I5" t="n">
-        <v>382.6090775978296</v>
+        <v>73.44005007081046</v>
       </c>
       <c r="J5" t="n">
-        <v>714.5401609890994</v>
+        <v>134.2108606077579</v>
       </c>
       <c r="K5" t="n">
-        <v>532.3763603412168</v>
+        <v>100.9744064976917</v>
       </c>
       <c r="L5" t="n">
-        <v>2309.770627294221</v>
+        <v>81.02394192100328</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>240.5974174919005</v>
+        <v>34.15619584384044</v>
       </c>
       <c r="C6" t="n">
-        <v>155.3301526761007</v>
+        <v>33.44002181429862</v>
       </c>
       <c r="D6" t="n">
-        <v>169.705562605023</v>
+        <v>44.85085231063151</v>
       </c>
       <c r="E6" t="n">
-        <v>144.3077909128541</v>
+        <v>31.50009286972811</v>
       </c>
       <c r="F6" t="n">
-        <v>156.1782102240956</v>
+        <v>33.58928665718595</v>
       </c>
       <c r="G6" t="n">
-        <v>244.3358720287163</v>
+        <v>52.63330557155307</v>
       </c>
       <c r="H6" t="n">
-        <v>257.6891366386135</v>
+        <v>66.92466659175624</v>
       </c>
       <c r="I6" t="n">
-        <v>239.1196547733101</v>
+        <v>33.59105770573191</v>
       </c>
       <c r="J6" t="n">
-        <v>166.3346455756709</v>
+        <v>37.72669041780554</v>
       </c>
       <c r="K6" t="n">
-        <v>158.429266115753</v>
+        <v>35.15971827063555</v>
       </c>
       <c r="L6" t="n">
-        <v>173.3122857745039</v>
+        <v>49.28885621042186</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72.60622357438123</v>
+        <v>19.1845999593715</v>
       </c>
       <c r="C7" t="n">
-        <v>71.12975007055027</v>
+        <v>18.62075103602145</v>
       </c>
       <c r="D7" t="n">
-        <v>83.0143730637644</v>
+        <v>29.59321388130522</v>
       </c>
       <c r="E7" t="n">
-        <v>71.11569122991364</v>
+        <v>18.61828339533193</v>
       </c>
       <c r="F7" t="n">
-        <v>71.11569122991364</v>
+        <v>18.61828339533193</v>
       </c>
       <c r="G7" t="n">
-        <v>76.34467811119772</v>
+        <v>23.06685560227872</v>
       </c>
       <c r="H7" t="n">
-        <v>91.01092514238729</v>
+        <v>37.5893015273771</v>
       </c>
       <c r="I7" t="n">
-        <v>71.12846085579172</v>
+        <v>18.6194618212628</v>
       </c>
       <c r="J7" t="n">
-        <v>75.08909769237306</v>
+        <v>21.66747407736298</v>
       </c>
       <c r="K7" t="n">
-        <v>73.66236787635086</v>
+        <v>20.24074426134078</v>
       </c>
       <c r="L7" t="n">
-        <v>87.63048253741715</v>
+        <v>34.20885892240713</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>152.679269168937</v>
+        <v>33.2774559076496</v>
       </c>
       <c r="C8" t="n">
-        <v>223.4238974714739</v>
+        <v>45.42452083334489</v>
       </c>
       <c r="D8" t="n">
-        <v>250.2828888746099</v>
+        <v>59.0324725044944</v>
       </c>
       <c r="E8" t="n">
-        <v>203.6722172876796</v>
+        <v>41.94823185508292</v>
       </c>
       <c r="F8" t="n">
-        <v>153.4840008879306</v>
+        <v>33.11510581659033</v>
       </c>
       <c r="G8" t="n">
-        <v>228.6374082352611</v>
+        <v>49.87037595887624</v>
       </c>
       <c r="H8" t="n">
-        <v>243.3036552664547</v>
+        <v>64.39282188397533</v>
       </c>
       <c r="I8" t="n">
-        <v>223.4211909798553</v>
+        <v>45.42298217786025</v>
       </c>
       <c r="J8" t="n">
-        <v>227.396021058802</v>
+        <v>48.47349244460318</v>
       </c>
       <c r="K8" t="n">
-        <v>152.3938957527144</v>
+        <v>34.09749309249641</v>
       </c>
       <c r="L8" t="n">
-        <v>315.3627120689992</v>
+        <v>74.28973110278321</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150.5251517104529</v>
+        <v>32.89833123701089</v>
       </c>
       <c r="C9" t="n">
-        <v>179.8868267744674</v>
+        <v>37.76199643219208</v>
       </c>
       <c r="D9" t="n">
-        <v>191.7720073098242</v>
+        <v>48.7345574048925</v>
       </c>
       <c r="E9" t="n">
-        <v>215.4733527966624</v>
+        <v>44.02523169340945</v>
       </c>
       <c r="F9" t="n">
-        <v>179.8867979676687</v>
+        <v>37.76199807744466</v>
       </c>
       <c r="G9" t="n">
-        <v>185.1017548151149</v>
+        <v>42.20810099844925</v>
       </c>
       <c r="H9" t="n">
-        <v>199.7680018463047</v>
+        <v>56.73054692354771</v>
       </c>
       <c r="I9" t="n">
-        <v>179.8855375597092</v>
+        <v>37.76070721743343</v>
       </c>
       <c r="J9" t="n">
-        <v>183.8461743962903</v>
+        <v>40.80871947353363</v>
       </c>
       <c r="K9" t="n">
-        <v>143.5887125216059</v>
+        <v>36.23726621096191</v>
       </c>
       <c r="L9" t="n">
-        <v>196.3875592413343</v>
+        <v>53.35010431857782</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.5872273141355</v>
+        <v>18.58722731413548</v>
       </c>
       <c r="C2" t="n">
-        <v>13.44610160398871</v>
+        <v>13.44610160398867</v>
       </c>
       <c r="D2" t="n">
-        <v>18.18703022697146</v>
+        <v>18.18703022697144</v>
       </c>
       <c r="E2" t="n">
-        <v>15.67023305514282</v>
+        <v>15.6702330551428</v>
       </c>
       <c r="F2" t="n">
-        <v>9.394969158606436</v>
+        <v>9.394969158606408</v>
       </c>
       <c r="G2" t="n">
-        <v>18.29472252636476</v>
+        <v>18.29472252636475</v>
       </c>
       <c r="H2" t="n">
-        <v>18.00953833950603</v>
+        <v>18.00953833950601</v>
       </c>
       <c r="I2" t="n">
-        <v>18.00977035452519</v>
+        <v>18.00977035452516</v>
       </c>
       <c r="J2" t="n">
-        <v>26.44318031336618</v>
+        <v>26.44318031336615</v>
       </c>
       <c r="K2" t="n">
-        <v>24.55128744449825</v>
+        <v>24.55128744449823</v>
       </c>
       <c r="L2" t="n">
-        <v>17.05257780189188</v>
+        <v>17.05257780189185</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.85282365467646</v>
+        <v>20.85282365467644</v>
       </c>
       <c r="C3" t="n">
-        <v>15.62119794535911</v>
+        <v>15.62119794535907</v>
       </c>
       <c r="D3" t="n">
-        <v>20.39251410386097</v>
+        <v>20.39251410386094</v>
       </c>
       <c r="E3" t="n">
-        <v>17.84891108131567</v>
+        <v>17.84891108131562</v>
       </c>
       <c r="F3" t="n">
-        <v>11.57364718477927</v>
+        <v>11.57364718477922</v>
       </c>
       <c r="G3" t="n">
-        <v>20.51638255655592</v>
+        <v>20.51638255655585</v>
       </c>
       <c r="H3" t="n">
-        <v>20.19375713820116</v>
+        <v>20.19375713820114</v>
       </c>
       <c r="I3" t="n">
-        <v>20.18441920390731</v>
+        <v>20.18441920390727</v>
       </c>
       <c r="J3" t="n">
-        <v>28.92304209766643</v>
+        <v>28.92304209766635</v>
       </c>
       <c r="K3" t="n">
-        <v>26.59994291337844</v>
+        <v>26.59994291337842</v>
       </c>
       <c r="L3" t="n">
-        <v>19.08783038828221</v>
+        <v>19.0878303882822</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.54208486382624</v>
+        <v>12.09397264279853</v>
       </c>
       <c r="C4" t="n">
-        <v>37.68295556505873</v>
+        <v>11.4833144445997</v>
       </c>
       <c r="D4" t="n">
-        <v>39.30418465329632</v>
+        <v>11.85607243226859</v>
       </c>
       <c r="E4" t="n">
-        <v>37.78152485547188</v>
+        <v>11.50066907907136</v>
       </c>
       <c r="F4" t="n">
-        <v>37.7815248554719</v>
+        <v>11.50066907907137</v>
       </c>
       <c r="G4" t="n">
-        <v>39.20874068312189</v>
+        <v>11.89202554482187</v>
       </c>
       <c r="H4" t="n">
-        <v>39.19917440253909</v>
+        <v>11.75106218151137</v>
       </c>
       <c r="I4" t="n">
-        <v>38.18618553260379</v>
+        <v>11.57160327155938</v>
       </c>
       <c r="J4" t="n">
-        <v>40.3900586629899</v>
+        <v>12.94194644196215</v>
       </c>
       <c r="K4" t="n">
-        <v>38.68352283017072</v>
+        <v>11.23541060914301</v>
       </c>
       <c r="L4" t="n">
-        <v>38.63089521431806</v>
+        <v>11.18278299329034</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>256.1572778420096</v>
+        <v>50.21824640037843</v>
       </c>
       <c r="C5" t="n">
-        <v>229.372957583386</v>
+        <v>45.22075461701538</v>
       </c>
       <c r="D5" t="n">
-        <v>238.0148271742036</v>
+        <v>46.82914532644302</v>
       </c>
       <c r="E5" t="n">
-        <v>229.372965398256</v>
+        <v>45.2207624318867</v>
       </c>
       <c r="F5" t="n">
-        <v>229.3729653982558</v>
+        <v>45.2207624318867</v>
       </c>
       <c r="G5" t="n">
-        <v>246.4051531216134</v>
+        <v>48.35859393639851</v>
       </c>
       <c r="H5" t="n">
-        <v>250.425195400153</v>
+        <v>48.92684167565049</v>
       </c>
       <c r="I5" t="n">
-        <v>229.3726182061437</v>
+        <v>45.22041523977191</v>
       </c>
       <c r="J5" t="n">
-        <v>350.9207902823953</v>
+        <v>67.59535491083224</v>
       </c>
       <c r="K5" t="n">
-        <v>182.3531280076089</v>
+        <v>36.52126098335805</v>
       </c>
       <c r="L5" t="n">
-        <v>190.1111427497665</v>
+        <v>39.06091064793512</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207.1111714004283</v>
+        <v>41.58613171343413</v>
       </c>
       <c r="C6" t="n">
-        <v>136.4558066662524</v>
+        <v>28.86733614421266</v>
       </c>
       <c r="D6" t="n">
-        <v>137.7531339891408</v>
+        <v>41.06372966580038</v>
       </c>
       <c r="E6" t="n">
-        <v>126.9029062713899</v>
+        <v>27.18603212328016</v>
       </c>
       <c r="F6" t="n">
-        <v>136.6928298562685</v>
+        <v>28.90905866488243</v>
       </c>
       <c r="G6" t="n">
-        <v>206.7778272197242</v>
+        <v>29.22467647269804</v>
       </c>
       <c r="H6" t="n">
-        <v>205.2257444215223</v>
+        <v>40.97173834651712</v>
       </c>
       <c r="I6" t="n">
-        <v>136.6671572473474</v>
+        <v>28.90425419943554</v>
       </c>
       <c r="J6" t="n">
-        <v>206.1602923779381</v>
+        <v>42.11750741770222</v>
       </c>
       <c r="K6" t="n">
-        <v>137.0266296315504</v>
+        <v>28.54379731239833</v>
       </c>
       <c r="L6" t="n">
-        <v>137.1324306702654</v>
+        <v>28.51905313959865</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.07458459660874</v>
+        <v>16.05969257427956</v>
       </c>
       <c r="C7" t="n">
-        <v>60.71902464262891</v>
+        <v>15.53766258028313</v>
       </c>
       <c r="D7" t="n">
-        <v>61.83622069053887</v>
+        <v>15.82171075333504</v>
       </c>
       <c r="E7" t="n">
-        <v>60.70852040973404</v>
+        <v>15.53582027475663</v>
       </c>
       <c r="F7" t="n">
-        <v>60.70852040973408</v>
+        <v>15.53582027475663</v>
       </c>
       <c r="G7" t="n">
-        <v>61.74124041590441</v>
+        <v>15.8577454763029</v>
       </c>
       <c r="H7" t="n">
-        <v>61.73167413532155</v>
+        <v>15.71678211299239</v>
       </c>
       <c r="I7" t="n">
-        <v>60.71868526538631</v>
+        <v>15.53732320304042</v>
       </c>
       <c r="J7" t="n">
-        <v>62.92255839577236</v>
+        <v>16.90766637344316</v>
       </c>
       <c r="K7" t="n">
-        <v>61.21602256295321</v>
+        <v>15.20113054062402</v>
       </c>
       <c r="L7" t="n">
-        <v>61.16339494710044</v>
+        <v>15.14850292477136</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>129.4469972564935</v>
+        <v>27.91723713816788</v>
       </c>
       <c r="C8" t="n">
-        <v>187.109264401042</v>
+        <v>37.78234465722865</v>
       </c>
       <c r="D8" t="n">
-        <v>200.4621145458601</v>
+        <v>40.2198679396676</v>
       </c>
       <c r="E8" t="n">
-        <v>170.9686920225313</v>
+        <v>34.94161037345661</v>
       </c>
       <c r="F8" t="n">
-        <v>129.956158074121</v>
+        <v>27.72340443764901</v>
       </c>
       <c r="G8" t="n">
-        <v>188.1293759795312</v>
+        <v>38.10205721496807</v>
       </c>
       <c r="H8" t="n">
-        <v>188.1198096989495</v>
+        <v>37.96109385165772</v>
       </c>
       <c r="I8" t="n">
-        <v>187.1068208290133</v>
+        <v>37.78163494170558</v>
       </c>
       <c r="J8" t="n">
-        <v>189.3222922452173</v>
+        <v>39.15401941040127</v>
       </c>
       <c r="K8" t="n">
-        <v>127.4921878707164</v>
+        <v>26.86573557158445</v>
       </c>
       <c r="L8" t="n">
-        <v>249.1983879031044</v>
+        <v>48.2426615057038</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106.299344052228</v>
+        <v>23.84325019629254</v>
       </c>
       <c r="C9" t="n">
-        <v>124.2289798513662</v>
+        <v>26.71541463645305</v>
       </c>
       <c r="D9" t="n">
-        <v>125.3466461634294</v>
+        <v>26.99954557599548</v>
       </c>
       <c r="E9" t="n">
-        <v>146.4836944561679</v>
+        <v>30.63225082512734</v>
       </c>
       <c r="F9" t="n">
-        <v>124.2289827583365</v>
+        <v>26.71542158753275</v>
       </c>
       <c r="G9" t="n">
-        <v>125.2511956246416</v>
+        <v>27.03549753247285</v>
       </c>
       <c r="H9" t="n">
-        <v>125.2416293440589</v>
+        <v>26.89453416916233</v>
       </c>
       <c r="I9" t="n">
-        <v>124.2286404741237</v>
+        <v>26.71507525921032</v>
       </c>
       <c r="J9" t="n">
-        <v>126.4325136045096</v>
+        <v>28.08541842961311</v>
       </c>
       <c r="K9" t="n">
-        <v>113.5520623762674</v>
+        <v>24.41227349785573</v>
       </c>
       <c r="L9" t="n">
-        <v>124.673350155838</v>
+        <v>26.3262549809413</v>
       </c>
     </row>
   </sheetData>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.6007174926388</v>
+        <v>18.60071749263891</v>
       </c>
       <c r="C2" t="n">
-        <v>8.336032983377589</v>
+        <v>8.336032983377592</v>
       </c>
       <c r="D2" t="n">
-        <v>29.83938582192927</v>
+        <v>29.83938582192935</v>
       </c>
       <c r="E2" t="n">
         <v>10.52541051764368</v>
@@ -1322,22 +1322,22 @@
         <v>10.52541051764368</v>
       </c>
       <c r="G2" t="n">
-        <v>23.48208940578911</v>
+        <v>23.48208940578883</v>
       </c>
       <c r="H2" t="n">
-        <v>34.51773430698236</v>
+        <v>34.51773430698231</v>
       </c>
       <c r="I2" t="n">
-        <v>19.51783561043906</v>
+        <v>19.51783561043902</v>
       </c>
       <c r="J2" t="n">
-        <v>22.8707493067523</v>
+        <v>22.87074930675237</v>
       </c>
       <c r="K2" t="n">
-        <v>32.21533046484309</v>
+        <v>32.21533046484323</v>
       </c>
       <c r="L2" t="n">
-        <v>23.50624009397492</v>
+        <v>23.50624009397491</v>
       </c>
     </row>
     <row r="3">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.4528574778334</v>
+        <v>20.45285747783327</v>
       </c>
       <c r="C3" t="n">
-        <v>10.17081049564687</v>
+        <v>10.1708104956469</v>
       </c>
       <c r="D3" t="n">
-        <v>33.37965413964841</v>
+        <v>33.37965413964835</v>
       </c>
       <c r="E3" t="n">
         <v>12.51503441521323</v>
@@ -1362,22 +1362,22 @@
         <v>12.51503441521323</v>
       </c>
       <c r="G3" t="n">
-        <v>26.06744635110183</v>
+        <v>26.06744635110174</v>
       </c>
       <c r="H3" t="n">
-        <v>38.76719099820507</v>
+        <v>38.76719099820504</v>
       </c>
       <c r="I3" t="n">
-        <v>21.50055032396862</v>
+        <v>21.50055032396858</v>
       </c>
       <c r="J3" t="n">
-        <v>25.59438705794502</v>
+        <v>25.59438705794508</v>
       </c>
       <c r="K3" t="n">
-        <v>34.43943813623311</v>
+        <v>34.43943813623305</v>
       </c>
       <c r="L3" t="n">
-        <v>26.09541948601872</v>
+        <v>26.09541948601869</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.18406099738974</v>
+        <v>11.72587477958608</v>
       </c>
       <c r="C4" t="n">
-        <v>39.00312628160499</v>
+        <v>11.47176050868657</v>
       </c>
       <c r="D4" t="n">
-        <v>46.86497309637893</v>
+        <v>18.40678687857539</v>
       </c>
       <c r="E4" t="n">
-        <v>39.11836826368825</v>
+        <v>11.98665482707024</v>
       </c>
       <c r="F4" t="n">
-        <v>39.11836826368828</v>
+        <v>11.98665482707023</v>
       </c>
       <c r="G4" t="n">
-        <v>42.92190644963726</v>
+        <v>14.59879303847948</v>
       </c>
       <c r="H4" t="n">
-        <v>49.6439732408549</v>
+        <v>21.18578702305129</v>
       </c>
       <c r="I4" t="n">
-        <v>39.68909001622336</v>
+        <v>12.08639915951015</v>
       </c>
       <c r="J4" t="n">
-        <v>43.63308786159276</v>
+        <v>15.17490164378918</v>
       </c>
       <c r="K4" t="n">
-        <v>41.65615489407833</v>
+        <v>13.19796867627477</v>
       </c>
       <c r="L4" t="n">
-        <v>43.10118323272987</v>
+        <v>14.64299701492615</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>159.4533171796072</v>
+        <v>32.71726375391178</v>
       </c>
       <c r="C5" t="n">
-        <v>198.2990742384902</v>
+        <v>39.50784719718195</v>
       </c>
       <c r="D5" t="n">
-        <v>847.5523941794228</v>
+        <v>159.3277722255966</v>
       </c>
       <c r="E5" t="n">
-        <v>253.4178195906948</v>
+        <v>49.70335805625165</v>
       </c>
       <c r="F5" t="n">
-        <v>253.4178195906948</v>
+        <v>49.70335805625165</v>
       </c>
       <c r="G5" t="n">
-        <v>492.8287132643666</v>
+        <v>93.78239060881165</v>
       </c>
       <c r="H5" t="n">
-        <v>1257.119177945805</v>
+        <v>233.7014218995842</v>
       </c>
       <c r="I5" t="n">
-        <v>253.4169668049409</v>
+        <v>49.7025052704978</v>
       </c>
       <c r="J5" t="n">
-        <v>559.1971767766726</v>
+        <v>105.9141808011634</v>
       </c>
       <c r="K5" t="n">
-        <v>343.6600280463483</v>
+        <v>66.35065006306127</v>
       </c>
       <c r="L5" t="n">
-        <v>548.3977895298461</v>
+        <v>103.5751992413303</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>218.668840368978</v>
+        <v>30.05777580995465</v>
       </c>
       <c r="C6" t="n">
-        <v>143.4751818021216</v>
+        <v>29.85884218066518</v>
       </c>
       <c r="D6" t="n">
-        <v>151.8473250017288</v>
+        <v>36.88366696021675</v>
       </c>
       <c r="E6" t="n">
-        <v>133.1872511687207</v>
+        <v>28.54277812864488</v>
       </c>
       <c r="F6" t="n">
-        <v>143.8318424482199</v>
+        <v>30.41622618368531</v>
       </c>
       <c r="G6" t="n">
-        <v>221.4066858212255</v>
+        <v>46.01211403766266</v>
       </c>
       <c r="H6" t="n">
-        <v>227.9197264922918</v>
+        <v>52.56231942528726</v>
       </c>
       <c r="I6" t="n">
-        <v>218.1738693878112</v>
+        <v>43.49972015869326</v>
       </c>
       <c r="J6" t="n">
-        <v>220.726840182357</v>
+        <v>46.34340188335386</v>
       </c>
       <c r="K6" t="n">
-        <v>145.6631776344593</v>
+        <v>31.50320457939222</v>
       </c>
       <c r="L6" t="n">
-        <v>147.3642566362868</v>
+        <v>32.99329783451907</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.18067827571932</v>
+        <v>16.30127939577978</v>
       </c>
       <c r="C7" t="n">
-        <v>66.01579245515298</v>
+        <v>16.22598972946975</v>
       </c>
       <c r="D7" t="n">
-        <v>72.86119185250728</v>
+        <v>22.98212135486205</v>
       </c>
       <c r="E7" t="n">
-        <v>65.6884523991251</v>
+        <v>16.66298960956792</v>
       </c>
       <c r="F7" t="n">
-        <v>65.6884523991251</v>
+        <v>16.66298960956792</v>
       </c>
       <c r="G7" t="n">
-        <v>68.9185237279669</v>
+        <v>19.17419765467323</v>
       </c>
       <c r="H7" t="n">
-        <v>75.64059051918446</v>
+        <v>25.761191639245</v>
       </c>
       <c r="I7" t="n">
-        <v>65.68570729455281</v>
+        <v>16.66180377570385</v>
       </c>
       <c r="J7" t="n">
-        <v>69.62970513992235</v>
+        <v>19.75030625998289</v>
       </c>
       <c r="K7" t="n">
-        <v>67.65277217240789</v>
+        <v>17.77337329246846</v>
       </c>
       <c r="L7" t="n">
-        <v>69.09780051105935</v>
+        <v>19.21840163111984</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>139.5107146560758</v>
+        <v>29.20736572878957</v>
       </c>
       <c r="C8" t="n">
-        <v>205.018005305502</v>
+        <v>40.69037905861174</v>
       </c>
       <c r="D8" t="n">
-        <v>225.4629917273022</v>
+        <v>49.84003798729351</v>
       </c>
       <c r="E8" t="n">
-        <v>186.7304814351753</v>
+        <v>37.96638660447805</v>
       </c>
       <c r="F8" t="n">
-        <v>141.0991874797083</v>
+        <v>29.93527891183326</v>
       </c>
       <c r="G8" t="n">
-        <v>207.9055255751292</v>
+        <v>43.63590984722499</v>
       </c>
       <c r="H8" t="n">
-        <v>214.6275923664118</v>
+        <v>50.22290383180868</v>
       </c>
       <c r="I8" t="n">
-        <v>204.6727091417146</v>
+        <v>41.12351596825602</v>
       </c>
       <c r="J8" t="n">
-        <v>208.6296104668153</v>
+        <v>44.21428946495536</v>
       </c>
       <c r="K8" t="n">
-        <v>139.7631967103744</v>
+        <v>30.46480794238059</v>
       </c>
       <c r="L8" t="n">
-        <v>276.6689929392633</v>
+        <v>55.75093130052847</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123.96052893066</v>
+        <v>26.47053305594626</v>
       </c>
       <c r="C9" t="n">
-        <v>148.0725848935625</v>
+        <v>30.66798512037435</v>
       </c>
       <c r="D9" t="n">
-        <v>154.9183860031834</v>
+        <v>37.42418744712514</v>
       </c>
       <c r="E9" t="n">
-        <v>175.7584099524113</v>
+        <v>36.03530203397548</v>
       </c>
       <c r="F9" t="n">
-        <v>147.7433353076049</v>
+        <v>31.10464892320664</v>
       </c>
       <c r="G9" t="n">
-        <v>150.9753161663765</v>
+        <v>33.61619304557777</v>
       </c>
       <c r="H9" t="n">
-        <v>157.6973829575939</v>
+        <v>40.20318703014947</v>
       </c>
       <c r="I9" t="n">
-        <v>147.7424997329623</v>
+        <v>31.10379916660839</v>
       </c>
       <c r="J9" t="n">
-        <v>151.6864975783317</v>
+        <v>34.19230165088746</v>
       </c>
       <c r="K9" t="n">
-        <v>119.1405606598651</v>
+        <v>29.7397255803776</v>
       </c>
       <c r="L9" t="n">
-        <v>151.1545929494687</v>
+        <v>33.66039702202433</v>
       </c>
     </row>
   </sheetData>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.72284784328006</v>
+        <v>17.72284784328007</v>
       </c>
       <c r="C2" t="n">
-        <v>8.324267555784393</v>
+        <v>8.324267555784314</v>
       </c>
       <c r="D2" t="n">
         <v>25.85481656597785</v>
@@ -1718,22 +1718,22 @@
         <v>9.52737691951393</v>
       </c>
       <c r="G2" t="n">
-        <v>20.76660139709418</v>
+        <v>20.76660139709417</v>
       </c>
       <c r="H2" t="n">
-        <v>26.27619415264348</v>
+        <v>26.27619415264349</v>
       </c>
       <c r="I2" t="n">
         <v>18.25281560243128</v>
       </c>
       <c r="J2" t="n">
-        <v>20.08317382516201</v>
+        <v>20.083173825162</v>
       </c>
       <c r="K2" t="n">
         <v>30.15195944438054</v>
       </c>
       <c r="L2" t="n">
-        <v>18.88100899519132</v>
+        <v>18.88100899519133</v>
       </c>
     </row>
     <row r="3">
@@ -1746,10 +1746,10 @@
         <v>19.48186441621316</v>
       </c>
       <c r="C3" t="n">
-        <v>10.15307303997922</v>
+        <v>10.15307303997902</v>
       </c>
       <c r="D3" t="n">
-        <v>28.83531297956167</v>
+        <v>28.8353129795617</v>
       </c>
       <c r="E3" t="n">
         <v>11.36576595290528</v>
@@ -1758,22 +1758,22 @@
         <v>11.36576595290528</v>
       </c>
       <c r="G3" t="n">
-        <v>22.98281151474858</v>
+        <v>22.98281151474855</v>
       </c>
       <c r="H3" t="n">
         <v>29.32619144349348</v>
       </c>
       <c r="I3" t="n">
-        <v>20.08610491311127</v>
+        <v>20.08610491311126</v>
       </c>
       <c r="J3" t="n">
-        <v>22.38919185074761</v>
+        <v>22.3891918507476</v>
       </c>
       <c r="K3" t="n">
-        <v>32.0677717688104</v>
+        <v>32.06777176881042</v>
       </c>
       <c r="L3" t="n">
-        <v>20.81426316824233</v>
+        <v>20.81426316824234</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.51229915556307</v>
+        <v>11.3050510665231</v>
       </c>
       <c r="C4" t="n">
-        <v>38.74769562586116</v>
+        <v>11.40895877774336</v>
       </c>
       <c r="D4" t="n">
-        <v>44.34640998046212</v>
+        <v>16.13916189142221</v>
       </c>
       <c r="E4" t="n">
-        <v>38.42833237391801</v>
+        <v>11.37311050800347</v>
       </c>
       <c r="F4" t="n">
-        <v>38.42833237391801</v>
+        <v>11.37311050800347</v>
       </c>
       <c r="G4" t="n">
-        <v>41.16073761256745</v>
+        <v>13.0861074257915</v>
       </c>
       <c r="H4" t="n">
-        <v>44.59609616919847</v>
+        <v>16.38884808015845</v>
       </c>
       <c r="I4" t="n">
-        <v>38.80666688882518</v>
+        <v>11.4391586420468</v>
       </c>
       <c r="J4" t="n">
-        <v>41.67710413678512</v>
+        <v>13.4698560477452</v>
       </c>
       <c r="K4" t="n">
-        <v>40.13283173775047</v>
+        <v>11.92558364871039</v>
       </c>
       <c r="L4" t="n">
-        <v>40.20212361147323</v>
+        <v>11.99487552243334</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>124.831282188139</v>
+        <v>26.32119199888997</v>
       </c>
       <c r="C5" t="n">
-        <v>194.2984372413683</v>
+        <v>38.78588915372676</v>
       </c>
       <c r="D5" t="n">
-        <v>608.008509395592</v>
+        <v>115.343690850935</v>
       </c>
       <c r="E5" t="n">
-        <v>192.9856602244256</v>
+        <v>38.5752000622954</v>
       </c>
       <c r="F5" t="n">
-        <v>192.9856602244256</v>
+        <v>38.5752000622954</v>
       </c>
       <c r="G5" t="n">
-        <v>337.3245700440267</v>
+        <v>65.21094165128351</v>
       </c>
       <c r="H5" t="n">
-        <v>706.7876395231592</v>
+        <v>132.9345590789405</v>
       </c>
       <c r="I5" t="n">
-        <v>192.9850064134804</v>
+        <v>38.57454625135011</v>
       </c>
       <c r="J5" t="n">
-        <v>378.7537664362273</v>
+        <v>72.79534829098561</v>
       </c>
       <c r="K5" t="n">
-        <v>221.4764794778578</v>
+        <v>43.84206547802657</v>
       </c>
       <c r="L5" t="n">
-        <v>253.531099176003</v>
+        <v>49.54077501834423</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207.7645459173879</v>
+        <v>40.91744633614647</v>
       </c>
       <c r="C6" t="n">
-        <v>137.5832179319034</v>
+        <v>28.80401060934994</v>
       </c>
       <c r="D6" t="n">
-        <v>143.2835203535129</v>
+        <v>45.57164704939011</v>
       </c>
       <c r="E6" t="n">
-        <v>127.1970577449268</v>
+        <v>26.9964060886446</v>
       </c>
       <c r="F6" t="n">
-        <v>137.1635527700973</v>
+        <v>28.75050920356977</v>
       </c>
       <c r="G6" t="n">
-        <v>139.5196340936761</v>
+        <v>30.39727311266437</v>
       </c>
       <c r="H6" t="n">
-        <v>213.1961342424146</v>
+        <v>46.062454620255</v>
       </c>
       <c r="I6" t="n">
-        <v>137.1655633699343</v>
+        <v>28.75032432891961</v>
       </c>
       <c r="J6" t="n">
-        <v>145.2884228668811</v>
+        <v>31.70544804543063</v>
       </c>
       <c r="K6" t="n">
-        <v>138.3205841758972</v>
+        <v>29.20662798418511</v>
       </c>
       <c r="L6" t="n">
-        <v>138.5883774510982</v>
+        <v>29.31085610437884</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63.66456385886686</v>
+        <v>15.5558496312712</v>
       </c>
       <c r="C7" t="n">
-        <v>63.85049781575417</v>
+        <v>15.82705193922467</v>
       </c>
       <c r="D7" t="n">
-        <v>68.49832264303068</v>
+        <v>20.38989849700122</v>
       </c>
       <c r="E7" t="n">
-        <v>63.00198914266791</v>
+        <v>15.6980740758682</v>
       </c>
       <c r="F7" t="n">
-        <v>63.00198914266791</v>
+        <v>15.6980740758682</v>
       </c>
       <c r="G7" t="n">
-        <v>65.3130023158713</v>
+        <v>17.33690599053959</v>
       </c>
       <c r="H7" t="n">
-        <v>68.74836087250239</v>
+        <v>20.63964664490658</v>
       </c>
       <c r="I7" t="n">
-        <v>62.95893159212913</v>
+        <v>15.68995720679491</v>
       </c>
       <c r="J7" t="n">
-        <v>65.82936884008896</v>
+        <v>17.72065461249326</v>
       </c>
       <c r="K7" t="n">
-        <v>64.28509644105443</v>
+        <v>16.1763822134585</v>
       </c>
       <c r="L7" t="n">
-        <v>64.35438831477718</v>
+        <v>16.24567408718147</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>132.9960807369158</v>
+        <v>27.75819653568812</v>
       </c>
       <c r="C8" t="n">
-        <v>195.0045626934618</v>
+        <v>38.91016723267639</v>
       </c>
       <c r="D8" t="n">
-        <v>212.4078967559533</v>
+        <v>45.71798340363269</v>
       </c>
       <c r="E8" t="n">
-        <v>177.2145511375898</v>
+        <v>35.79948487805284</v>
       </c>
       <c r="F8" t="n">
-        <v>134.2746032434995</v>
+        <v>28.24205408964368</v>
       </c>
       <c r="G8" t="n">
-        <v>196.4139338652502</v>
+        <v>40.41066981820276</v>
       </c>
       <c r="H8" t="n">
-        <v>199.8492924220732</v>
+        <v>43.71341047260336</v>
       </c>
       <c r="I8" t="n">
-        <v>194.0598631415083</v>
+        <v>38.76372103445804</v>
       </c>
       <c r="J8" t="n">
-        <v>196.942439853261</v>
+        <v>40.79655498577239</v>
       </c>
       <c r="K8" t="n">
-        <v>132.469214728593</v>
+        <v>28.17678696703982</v>
       </c>
       <c r="L8" t="n">
-        <v>259.9786385672287</v>
+        <v>50.67554194505111</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111.6332111324244</v>
+        <v>23.99833150567086</v>
       </c>
       <c r="C9" t="n">
-        <v>132.796487211179</v>
+        <v>27.96154600706733</v>
       </c>
       <c r="D9" t="n">
-        <v>137.4446693818736</v>
+        <v>32.52445545728516</v>
       </c>
       <c r="E9" t="n">
-        <v>156.1129744254436</v>
+        <v>32.08560739683914</v>
       </c>
       <c r="F9" t="n">
-        <v>131.9055642515182</v>
+        <v>27.82510322931427</v>
       </c>
       <c r="G9" t="n">
-        <v>134.2589917112958</v>
+        <v>29.4714000583823</v>
       </c>
       <c r="H9" t="n">
-        <v>137.6943502679268</v>
+        <v>32.77414071274933</v>
       </c>
       <c r="I9" t="n">
-        <v>131.9049209875538</v>
+        <v>27.82445127463762</v>
       </c>
       <c r="J9" t="n">
-        <v>134.7753582355137</v>
+        <v>29.85514868033597</v>
       </c>
       <c r="K9" t="n">
-        <v>121.0767336569857</v>
+        <v>26.17171030930165</v>
       </c>
       <c r="L9" t="n">
-        <v>133.3003777102018</v>
+        <v>28.38016815502416</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.98517481409517</v>
+        <v>16.98517481409519</v>
       </c>
       <c r="C2" t="n">
-        <v>8.029713388121261</v>
+        <v>8.029713388121269</v>
       </c>
       <c r="D2" t="n">
         <v>22.64072405464076</v>
       </c>
       <c r="E2" t="n">
-        <v>8.579122774852067</v>
+        <v>8.579122774852076</v>
       </c>
       <c r="F2" t="n">
-        <v>8.579122774852067</v>
+        <v>8.579122774852076</v>
       </c>
       <c r="G2" t="n">
-        <v>18.75078992425735</v>
+        <v>18.75078992425761</v>
       </c>
       <c r="H2" t="n">
-        <v>21.54151547180613</v>
+        <v>21.54151547180616</v>
       </c>
       <c r="I2" t="n">
-        <v>17.02280209279179</v>
+        <v>17.02280209279177</v>
       </c>
       <c r="J2" t="n">
-        <v>17.45845906799618</v>
+        <v>17.45845906799615</v>
       </c>
       <c r="K2" t="n">
-        <v>29.06255167525441</v>
+        <v>29.06255167525436</v>
       </c>
       <c r="L2" t="n">
-        <v>17.14216547405777</v>
+        <v>17.14216547405779</v>
       </c>
     </row>
     <row r="3">
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.67922425196311</v>
+        <v>18.67922425196308</v>
       </c>
       <c r="C3" t="n">
-        <v>9.81443953617006</v>
+        <v>9.814439536170084</v>
       </c>
       <c r="D3" t="n">
-        <v>25.18427742208631</v>
+        <v>25.18427742208624</v>
       </c>
       <c r="E3" t="n">
         <v>10.27861293605892</v>
@@ -2154,19 +2154,19 @@
         <v>10.27861293605892</v>
       </c>
       <c r="G3" t="n">
-        <v>20.71004737471788</v>
+        <v>20.71004737471809</v>
       </c>
       <c r="H3" t="n">
-        <v>23.92598070181289</v>
+        <v>23.92598070181288</v>
       </c>
       <c r="I3" t="n">
-        <v>18.717834357198</v>
+        <v>18.71783435719787</v>
       </c>
       <c r="J3" t="n">
-        <v>19.37554597342297</v>
+        <v>19.375545973423</v>
       </c>
       <c r="K3" t="n">
-        <v>30.80970180529486</v>
+        <v>30.80970180529492</v>
       </c>
       <c r="L3" t="n">
         <v>18.86002982555307</v>
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.09028748034805</v>
+        <v>11.0158989056911</v>
       </c>
       <c r="C4" t="n">
-        <v>38.44502943686898</v>
+        <v>11.20917811074971</v>
       </c>
       <c r="D4" t="n">
-        <v>42.45227185790245</v>
+        <v>14.37788328324551</v>
       </c>
       <c r="E4" t="n">
-        <v>37.76525389265547</v>
+        <v>10.80043546854777</v>
       </c>
       <c r="F4" t="n">
-        <v>37.76525389265548</v>
+        <v>10.80043546854776</v>
       </c>
       <c r="G4" t="n">
-        <v>39.98055776821414</v>
+        <v>12.03744317135448</v>
       </c>
       <c r="H4" t="n">
-        <v>41.79865760231469</v>
+        <v>13.72426902765769</v>
       </c>
       <c r="I4" t="n">
-        <v>38.1026342885136</v>
+        <v>10.85936467844287</v>
       </c>
       <c r="J4" t="n">
-        <v>39.972977313125</v>
+        <v>11.89858873846805</v>
       </c>
       <c r="K4" t="n">
-        <v>39.30043800620856</v>
+        <v>11.2260494315516</v>
       </c>
       <c r="L4" t="n">
-        <v>39.18482766394387</v>
+        <v>11.11043908928693</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105.4379484050636</v>
+        <v>22.69308716516695</v>
       </c>
       <c r="C5" t="n">
-        <v>182.7752503532623</v>
+        <v>36.61129685439098</v>
       </c>
       <c r="D5" t="n">
-        <v>453.8743386289425</v>
+        <v>86.78816664258619</v>
       </c>
       <c r="E5" t="n">
-        <v>146.7927049407086</v>
+        <v>29.98926674902826</v>
       </c>
       <c r="F5" t="n">
-        <v>146.7927049407086</v>
+        <v>29.98926674902826</v>
       </c>
       <c r="G5" t="n">
-        <v>246.0018067381786</v>
+        <v>48.29718279359213</v>
       </c>
       <c r="H5" t="n">
-        <v>438.2572348370928</v>
+        <v>83.50097824288615</v>
       </c>
       <c r="I5" t="n">
-        <v>146.7921591404054</v>
+        <v>29.98872094872043</v>
       </c>
       <c r="J5" t="n">
-        <v>234.8802113705786</v>
+        <v>46.20226174670166</v>
       </c>
       <c r="K5" t="n">
-        <v>164.6768042826298</v>
+        <v>33.29228977663358</v>
       </c>
       <c r="L5" t="n">
-        <v>168.595583847658</v>
+        <v>33.88673205420495</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>206.7645924532448</v>
+        <v>28.28112348576042</v>
       </c>
       <c r="C6" t="n">
-        <v>137.1023924044272</v>
+        <v>28.57287389895061</v>
       </c>
       <c r="D6" t="n">
-        <v>140.9638117107915</v>
+        <v>31.71591420340515</v>
       </c>
       <c r="E6" t="n">
-        <v>126.2984550587833</v>
+        <v>26.38227878935442</v>
       </c>
       <c r="F6" t="n">
-        <v>136.1973348310215</v>
+        <v>28.12448161982802</v>
       </c>
       <c r="G6" t="n">
-        <v>138.0784252319796</v>
+        <v>41.54812068667779</v>
       </c>
       <c r="H6" t="n">
-        <v>209.8012377137747</v>
+        <v>43.292722967055</v>
       </c>
       <c r="I6" t="n">
-        <v>136.200501752279</v>
+        <v>40.37004219376604</v>
       </c>
       <c r="J6" t="n">
-        <v>143.2652213928652</v>
+        <v>41.18407780374984</v>
       </c>
       <c r="K6" t="n">
-        <v>137.2487996536808</v>
+        <v>28.46496098809582</v>
       </c>
       <c r="L6" t="n">
-        <v>137.2905722427529</v>
+        <v>28.37705004159637</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.86941729733336</v>
+        <v>15.20102573080296</v>
       </c>
       <c r="C7" t="n">
-        <v>63.14153420025917</v>
+        <v>15.55576292555399</v>
       </c>
       <c r="D7" t="n">
-        <v>66.23104540544423</v>
+        <v>18.56294740493566</v>
       </c>
       <c r="E7" t="n">
-        <v>61.93309317230725</v>
+        <v>15.0539751587182</v>
       </c>
       <c r="F7" t="n">
-        <v>61.93309317230725</v>
+        <v>15.0539751587182</v>
       </c>
       <c r="G7" t="n">
-        <v>63.75968758519929</v>
+        <v>16.22256999646645</v>
       </c>
       <c r="H7" t="n">
-        <v>65.57778741929994</v>
+        <v>17.90939585276956</v>
       </c>
       <c r="I7" t="n">
-        <v>61.88176410549902</v>
+        <v>15.04449150355475</v>
       </c>
       <c r="J7" t="n">
-        <v>63.75210713011023</v>
+        <v>16.0837155635799</v>
       </c>
       <c r="K7" t="n">
-        <v>63.07956782319388</v>
+        <v>15.41117625666348</v>
       </c>
       <c r="L7" t="n">
-        <v>62.96395748092925</v>
+        <v>15.2955659143988</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>132.0029193396746</v>
+        <v>27.36852202432418</v>
       </c>
       <c r="C8" t="n">
-        <v>193.6934494176169</v>
+        <v>38.53289987924268</v>
       </c>
       <c r="D8" t="n">
-        <v>209.4450656125253</v>
+        <v>43.76861482480239</v>
       </c>
       <c r="E8" t="n">
-        <v>175.6469651830755</v>
+        <v>35.06761652416746</v>
       </c>
       <c r="F8" t="n">
-        <v>132.9912515124815</v>
+        <v>27.56021095882257</v>
       </c>
       <c r="G8" t="n">
-        <v>194.250511190603</v>
+        <v>39.18895482657152</v>
       </c>
       <c r="H8" t="n">
-        <v>196.068611024897</v>
+        <v>40.87578068290894</v>
       </c>
       <c r="I8" t="n">
-        <v>192.3725877109028</v>
+        <v>38.01087633366001</v>
       </c>
       <c r="J8" t="n">
-        <v>194.2549892110133</v>
+        <v>39.05222268536166</v>
       </c>
       <c r="K8" t="n">
-        <v>131.073326116031</v>
+        <v>27.37807765135893</v>
       </c>
       <c r="L8" t="n">
-        <v>257.5476340791027</v>
+        <v>49.54229281010795</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105.9898045910803</v>
+        <v>22.79021385337964</v>
       </c>
       <c r="C9" t="n">
-        <v>125.7738491895099</v>
+        <v>26.57905030393125</v>
       </c>
       <c r="D9" t="n">
-        <v>128.8637224993106</v>
+        <v>29.58629851372504</v>
       </c>
       <c r="E9" t="n">
-        <v>147.030971397064</v>
+        <v>30.03120164511976</v>
       </c>
       <c r="F9" t="n">
-        <v>124.5146172040141</v>
+        <v>26.06832332861625</v>
       </c>
       <c r="G9" t="n">
-        <v>126.3920025744503</v>
+        <v>27.24585737484368</v>
       </c>
       <c r="H9" t="n">
-        <v>128.2101024085506</v>
+        <v>28.93268323114685</v>
       </c>
       <c r="I9" t="n">
-        <v>124.5140790947495</v>
+        <v>26.06777888193209</v>
       </c>
       <c r="J9" t="n">
-        <v>126.384422119361</v>
+        <v>27.10700294195712</v>
       </c>
       <c r="K9" t="n">
-        <v>113.9479277974469</v>
+        <v>22.110319421267</v>
       </c>
       <c r="L9" t="n">
-        <v>125.5962724701798</v>
+        <v>26.31885329277609</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.97186291997793</v>
+        <v>17.97186291997789</v>
       </c>
       <c r="C2" t="n">
-        <v>7.664720051496462</v>
+        <v>7.664720051496458</v>
       </c>
       <c r="D2" t="n">
-        <v>24.31837226992444</v>
+        <v>24.31837226992446</v>
       </c>
       <c r="E2" t="n">
-        <v>9.509096257822286</v>
+        <v>9.509096257822272</v>
       </c>
       <c r="F2" t="n">
-        <v>9.509096257822289</v>
+        <v>9.509096257822272</v>
       </c>
       <c r="G2" t="n">
-        <v>21.19324064554286</v>
+        <v>21.19324064554285</v>
       </c>
       <c r="H2" t="n">
-        <v>30.84583756123579</v>
+        <v>30.84583756123577</v>
       </c>
       <c r="I2" t="n">
-        <v>18.64858893764061</v>
+        <v>18.64858893764058</v>
       </c>
       <c r="J2" t="n">
-        <v>22.34592878951411</v>
+        <v>22.3459287895141</v>
       </c>
       <c r="K2" t="n">
-        <v>30.76102369418665</v>
+        <v>30.76102369418658</v>
       </c>
       <c r="L2" t="n">
-        <v>23.34723166038437</v>
+        <v>23.34723166038436</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.70347665515533</v>
+        <v>19.70347665515531</v>
       </c>
       <c r="C3" t="n">
-        <v>9.393599051010323</v>
+        <v>9.393599051010316</v>
       </c>
       <c r="D3" t="n">
-        <v>27.00327708304507</v>
+        <v>27.00327708304508</v>
       </c>
       <c r="E3" t="n">
         <v>11.34213135961316</v>
       </c>
       <c r="F3" t="n">
-        <v>11.34213135961315</v>
+        <v>11.34213135961316</v>
       </c>
       <c r="G3" t="n">
-        <v>23.40872834594051</v>
+        <v>23.4087283459405</v>
       </c>
       <c r="H3" t="n">
-        <v>34.51759348307142</v>
+        <v>34.51759348307138</v>
       </c>
       <c r="I3" t="n">
-        <v>20.47710802319743</v>
+        <v>20.47710802319741</v>
       </c>
       <c r="J3" t="n">
-        <v>24.99014739361276</v>
+        <v>24.99014739361275</v>
       </c>
       <c r="K3" t="n">
-        <v>32.76983266273076</v>
+        <v>32.76983266273072</v>
       </c>
       <c r="L3" t="n">
-        <v>25.88631980209493</v>
+        <v>25.88631980209491</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.21499803191951</v>
+        <v>11.17760790678828</v>
       </c>
       <c r="C4" t="n">
-        <v>38.16244797797068</v>
+        <v>10.99349461954628</v>
       </c>
       <c r="D4" t="n">
-        <v>42.98772891604935</v>
+        <v>14.95033879091813</v>
       </c>
       <c r="E4" t="n">
-        <v>38.32042231704816</v>
+        <v>11.35090277010214</v>
       </c>
       <c r="F4" t="n">
-        <v>38.32042231704813</v>
+        <v>11.35090277010214</v>
       </c>
       <c r="G4" t="n">
-        <v>40.96943063982624</v>
+        <v>13.0643254324849</v>
       </c>
       <c r="H4" t="n">
-        <v>46.86626015286126</v>
+        <v>18.82887002773</v>
       </c>
       <c r="I4" t="n">
-        <v>38.59887180217748</v>
+        <v>11.39936881310691</v>
       </c>
       <c r="J4" t="n">
-        <v>42.82670976787215</v>
+        <v>14.78931964274087</v>
       </c>
       <c r="K4" t="n">
-        <v>40.31202184977859</v>
+        <v>12.27463172464735</v>
       </c>
       <c r="L4" t="n">
-        <v>42.41083272474528</v>
+        <v>14.37344259961406</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>121.6997645354423</v>
+        <v>25.6949267327447</v>
       </c>
       <c r="C5" t="n">
-        <v>166.3344078564106</v>
+        <v>33.55175943591739</v>
       </c>
       <c r="D5" t="n">
-        <v>528.8670207884654</v>
+        <v>100.4650936970931</v>
       </c>
       <c r="E5" t="n">
-        <v>202.3966355323726</v>
+        <v>40.22831613952408</v>
       </c>
       <c r="F5" t="n">
-        <v>202.3966355323726</v>
+        <v>40.22831613952408</v>
       </c>
       <c r="G5" t="n">
-        <v>356.5004048309111</v>
+        <v>68.5977765892018</v>
       </c>
       <c r="H5" t="n">
-        <v>1017.001686589877</v>
+        <v>189.5727041554517</v>
       </c>
       <c r="I5" t="n">
-        <v>202.3959788987417</v>
+        <v>40.22765950589324</v>
       </c>
       <c r="J5" t="n">
-        <v>537.1975542218565</v>
+        <v>101.7985877951732</v>
       </c>
       <c r="K5" t="n">
-        <v>270.2944153817559</v>
+        <v>52.75153276694692</v>
       </c>
       <c r="L5" t="n">
-        <v>537.297398116987</v>
+        <v>101.473477636688</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>216.7509465274274</v>
+        <v>29.46692935897445</v>
       </c>
       <c r="C6" t="n">
-        <v>142.4766632088523</v>
+        <v>29.35279640069959</v>
       </c>
       <c r="D6" t="n">
-        <v>147.2942892639854</v>
+        <v>33.30829331268077</v>
       </c>
       <c r="E6" t="n">
-        <v>132.0127958913135</v>
+        <v>27.84076042982094</v>
       </c>
       <c r="F6" t="n">
-        <v>142.5217032529491</v>
+        <v>29.6903281154467</v>
       </c>
       <c r="G6" t="n">
-        <v>144.886030363058</v>
+        <v>31.35364688467114</v>
       </c>
       <c r="H6" t="n">
-        <v>224.0813767147705</v>
+        <v>50.01873037362041</v>
       </c>
       <c r="I6" t="n">
-        <v>216.1348202976855</v>
+        <v>29.68869026529313</v>
       </c>
       <c r="J6" t="n">
-        <v>218.9406730988407</v>
+        <v>45.78537702103599</v>
       </c>
       <c r="K6" t="n">
-        <v>144.1280585051748</v>
+        <v>30.54625407699038</v>
       </c>
       <c r="L6" t="n">
-        <v>146.4398984087728</v>
+        <v>32.68255806079313</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64.4991362912491</v>
+        <v>15.62761621631744</v>
       </c>
       <c r="C7" t="n">
-        <v>64.39693313563308</v>
+        <v>15.61076398227569</v>
       </c>
       <c r="D7" t="n">
-        <v>68.27147632546425</v>
+        <v>19.40027831086265</v>
       </c>
       <c r="E7" t="n">
-        <v>63.95397602289719</v>
+        <v>15.86240819788552</v>
       </c>
       <c r="F7" t="n">
-        <v>63.95397602289719</v>
+        <v>15.86240819788552</v>
       </c>
       <c r="G7" t="n">
-        <v>66.25356889915589</v>
+        <v>17.51433374201406</v>
       </c>
       <c r="H7" t="n">
-        <v>72.15039841219091</v>
+        <v>23.27887833725916</v>
       </c>
       <c r="I7" t="n">
-        <v>63.88301006150706</v>
+        <v>15.84937712263607</v>
       </c>
       <c r="J7" t="n">
-        <v>68.11084802720177</v>
+        <v>19.23932795227005</v>
       </c>
       <c r="K7" t="n">
-        <v>65.59616010910821</v>
+        <v>16.7246400341765</v>
       </c>
       <c r="L7" t="n">
-        <v>67.69497098407494</v>
+        <v>18.82345090914323</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>137.3196710466536</v>
+        <v>28.44403026382151</v>
       </c>
       <c r="C8" t="n">
-        <v>202.0288902516114</v>
+        <v>39.83398830343178</v>
       </c>
       <c r="D8" t="n">
-        <v>219.245822741571</v>
+        <v>45.97176313611698</v>
       </c>
       <c r="E8" t="n">
-        <v>183.8036917051278</v>
+        <v>36.95595804366043</v>
       </c>
       <c r="F8" t="n">
-        <v>138.7982509738959</v>
+        <v>29.03500051788419</v>
       </c>
       <c r="G8" t="n">
-        <v>203.8051254186581</v>
+        <v>41.72340755826698</v>
       </c>
       <c r="H8" t="n">
-        <v>209.7019549317436</v>
+        <v>47.48795215352101</v>
       </c>
       <c r="I8" t="n">
-        <v>201.4345665810092</v>
+        <v>40.058450938889</v>
       </c>
       <c r="J8" t="n">
-        <v>205.6751260518261</v>
+        <v>43.45064075341238</v>
       </c>
       <c r="K8" t="n">
-        <v>137.2142829017963</v>
+        <v>29.32942957738923</v>
       </c>
       <c r="L8" t="n">
-        <v>272.8634924608427</v>
+        <v>54.93311049339032</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119.5074243890783</v>
+        <v>25.30907486907538</v>
       </c>
       <c r="C9" t="n">
-        <v>142.6535596313656</v>
+        <v>29.38393017089331</v>
       </c>
       <c r="D9" t="n">
-        <v>146.5284955216443</v>
+        <v>33.17351361475862</v>
       </c>
       <c r="E9" t="n">
-        <v>168.9683659050037</v>
+        <v>34.34494071698674</v>
       </c>
       <c r="F9" t="n">
-        <v>142.1402783704592</v>
+        <v>29.62319733649217</v>
       </c>
       <c r="G9" t="n">
-        <v>144.5101953948886</v>
+        <v>31.28749993063168</v>
       </c>
       <c r="H9" t="n">
-        <v>150.4070249079235</v>
+        <v>37.05204452587679</v>
       </c>
       <c r="I9" t="n">
-        <v>142.1396365572397</v>
+        <v>29.6225433112537</v>
       </c>
       <c r="J9" t="n">
-        <v>146.3674745229345</v>
+        <v>33.01249414088765</v>
       </c>
       <c r="K9" t="n">
-        <v>114.5789782685483</v>
+        <v>25.34561598352429</v>
       </c>
       <c r="L9" t="n">
-        <v>145.9515974798077</v>
+        <v>32.59661709776081</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.43248609858519</v>
+        <v>17.43248609858527</v>
       </c>
       <c r="C2" t="n">
-        <v>7.559886111600802</v>
+        <v>7.559886111600817</v>
       </c>
       <c r="D2" t="n">
-        <v>17.67912876207928</v>
+        <v>17.67912876207943</v>
       </c>
       <c r="E2" t="n">
-        <v>8.944542262518077</v>
+        <v>8.944542262518056</v>
       </c>
       <c r="F2" t="n">
-        <v>8.944542262518077</v>
+        <v>8.944542262518056</v>
       </c>
       <c r="G2" t="n">
-        <v>17.71101695590134</v>
+        <v>17.71101695590133</v>
       </c>
       <c r="H2" t="n">
-        <v>18.38367099040049</v>
+        <v>18.3836709904005</v>
       </c>
       <c r="I2" t="n">
-        <v>17.85829861722597</v>
+        <v>17.85829861722607</v>
       </c>
       <c r="J2" t="n">
-        <v>17.77106920602606</v>
+        <v>17.77106920602612</v>
       </c>
       <c r="K2" t="n">
         <v>28.56767056241978</v>
       </c>
       <c r="L2" t="n">
-        <v>17.90690032277334</v>
+        <v>17.90690032277328</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.10589334895255</v>
+        <v>19.10589334895252</v>
       </c>
       <c r="C3" t="n">
-        <v>9.259858839394514</v>
+        <v>9.259858839394523</v>
       </c>
       <c r="D3" t="n">
-        <v>19.3895835038446</v>
+        <v>19.38958350384462</v>
       </c>
       <c r="E3" t="n">
         <v>10.68175609630934</v>
       </c>
       <c r="F3" t="n">
-        <v>10.68175609630933</v>
+        <v>10.68175609630934</v>
       </c>
       <c r="G3" t="n">
-        <v>19.4262615323594</v>
+        <v>19.42626153235946</v>
       </c>
       <c r="H3" t="n">
-        <v>20.20612242676109</v>
+        <v>20.20612242676112</v>
       </c>
       <c r="I3" t="n">
-        <v>19.59301646828457</v>
+        <v>19.59301646828468</v>
       </c>
       <c r="J3" t="n">
-        <v>19.72868419059964</v>
+        <v>19.72868419059967</v>
       </c>
       <c r="K3" t="n">
-        <v>30.24720334433244</v>
+        <v>30.24720334433256</v>
       </c>
       <c r="L3" t="n">
-        <v>19.6516995990224</v>
+        <v>19.65169959902234</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.63012247901582</v>
+        <v>10.92042500953844</v>
       </c>
       <c r="C4" t="n">
-        <v>37.81583954023267</v>
+        <v>10.87380154404424</v>
       </c>
       <c r="D4" t="n">
-        <v>38.77674109132685</v>
+        <v>11.06704362184949</v>
       </c>
       <c r="E4" t="n">
-        <v>37.77827396184939</v>
+        <v>10.97857615579879</v>
       </c>
       <c r="F4" t="n">
-        <v>37.77827396184944</v>
+        <v>10.97857615579879</v>
       </c>
       <c r="G4" t="n">
-        <v>38.64066540267794</v>
+        <v>11.05871419312323</v>
       </c>
       <c r="H4" t="n">
-        <v>39.19586082961181</v>
+        <v>11.48616336013444</v>
       </c>
       <c r="I4" t="n">
-        <v>37.90081786747406</v>
+        <v>10.99990694035014</v>
       </c>
       <c r="J4" t="n">
-        <v>39.75489886805097</v>
+        <v>12.04520139857359</v>
       </c>
       <c r="K4" t="n">
-        <v>38.6543647934333</v>
+        <v>10.94466732395597</v>
       </c>
       <c r="L4" t="n">
-        <v>38.91287346626527</v>
+        <v>11.20317599678788</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.3099509788232</v>
+        <v>23.18407475905267</v>
       </c>
       <c r="C5" t="n">
-        <v>161.435488160836</v>
+        <v>32.63085958337757</v>
       </c>
       <c r="D5" t="n">
-        <v>161.0718842672454</v>
+        <v>32.59098870418148</v>
       </c>
       <c r="E5" t="n">
-        <v>170.9691962229326</v>
+        <v>34.42017834672859</v>
       </c>
       <c r="F5" t="n">
-        <v>170.9691962229326</v>
+        <v>34.42017834672859</v>
       </c>
       <c r="G5" t="n">
-        <v>165.1018386310542</v>
+        <v>33.31588056071493</v>
       </c>
       <c r="H5" t="n">
-        <v>218.3457140939735</v>
+        <v>43.01653736381152</v>
       </c>
       <c r="I5" t="n">
-        <v>170.9689086710861</v>
+        <v>34.41989079488157</v>
       </c>
       <c r="J5" t="n">
-        <v>261.1333128736966</v>
+        <v>51.00780205244429</v>
       </c>
       <c r="K5" t="n">
-        <v>150.2098921977637</v>
+        <v>30.57844004073051</v>
       </c>
       <c r="L5" t="n">
-        <v>191.7093907914077</v>
+        <v>38.09536290029484</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>136.6992124951433</v>
+        <v>28.18058475885094</v>
       </c>
       <c r="C6" t="n">
-        <v>136.4388887485329</v>
+        <v>28.23145811065088</v>
       </c>
       <c r="D6" t="n">
-        <v>204.6703783477079</v>
+        <v>28.31274727131364</v>
       </c>
       <c r="E6" t="n">
-        <v>126.2516429967693</v>
+        <v>26.54988902156996</v>
       </c>
       <c r="F6" t="n">
-        <v>135.9973431997156</v>
+        <v>28.26513224799422</v>
       </c>
       <c r="G6" t="n">
-        <v>136.7097554188054</v>
+        <v>40.45973893374633</v>
       </c>
       <c r="H6" t="n">
-        <v>206.3650966143395</v>
+        <v>40.90794869882151</v>
       </c>
       <c r="I6" t="n">
-        <v>135.9699078836016</v>
+        <v>40.40093168097327</v>
       </c>
       <c r="J6" t="n">
-        <v>143.0083165108428</v>
+        <v>30.21780280523482</v>
       </c>
       <c r="K6" t="n">
-        <v>136.637138413138</v>
+        <v>28.18963538758034</v>
       </c>
       <c r="L6" t="n">
-        <v>136.9958717199664</v>
+        <v>28.46578359589996</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.73250506247041</v>
+        <v>14.98644432219432</v>
       </c>
       <c r="C7" t="n">
-        <v>61.75365974406191</v>
+        <v>15.08685787708934</v>
       </c>
       <c r="D7" t="n">
-        <v>61.87877353639482</v>
+        <v>15.13300131014965</v>
       </c>
       <c r="E7" t="n">
-        <v>61.09374439837127</v>
+        <v>15.08209893039129</v>
       </c>
       <c r="F7" t="n">
-        <v>61.09374439837127</v>
+        <v>15.08209893039129</v>
       </c>
       <c r="G7" t="n">
-        <v>61.74304798613259</v>
+        <v>15.12473350577909</v>
       </c>
       <c r="H7" t="n">
-        <v>62.29824341306639</v>
+        <v>15.5521826727903</v>
       </c>
       <c r="I7" t="n">
-        <v>61.00320045092869</v>
+        <v>15.065926253006</v>
       </c>
       <c r="J7" t="n">
-        <v>62.85728145150558</v>
+        <v>16.11122071122946</v>
       </c>
       <c r="K7" t="n">
-        <v>61.7567473768879</v>
+        <v>15.01068663661183</v>
       </c>
       <c r="L7" t="n">
-        <v>62.01525604971985</v>
+        <v>15.26919530944375</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>130.2634415781338</v>
+        <v>27.04788908359488</v>
       </c>
       <c r="C8" t="n">
-        <v>190.7524178310697</v>
+        <v>37.79063917737989</v>
       </c>
       <c r="D8" t="n">
-        <v>203.2972404651633</v>
+        <v>40.02265135474568</v>
       </c>
       <c r="E8" t="n">
-        <v>173.4812802196428</v>
+        <v>34.862305127754</v>
       </c>
       <c r="F8" t="n">
-        <v>131.5020870115429</v>
+        <v>27.47396716316288</v>
       </c>
       <c r="G8" t="n">
-        <v>190.6432121536002</v>
+        <v>37.81116227632462</v>
       </c>
       <c r="H8" t="n">
-        <v>191.1984075806998</v>
+        <v>38.23861144336499</v>
       </c>
       <c r="I8" t="n">
-        <v>189.9033646183964</v>
+        <v>37.75235502355154</v>
       </c>
       <c r="J8" t="n">
-        <v>191.7693099058594</v>
+        <v>38.79973759625565</v>
       </c>
       <c r="K8" t="n">
-        <v>129.1662944947932</v>
+        <v>26.87476686507641</v>
       </c>
       <c r="L8" t="n">
-        <v>253.9761264966019</v>
+        <v>49.05430832502689</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106.7759643560827</v>
+        <v>22.91409311491329</v>
       </c>
       <c r="C9" t="n">
-        <v>126.577453202033</v>
+        <v>26.49584546387149</v>
       </c>
       <c r="D9" t="n">
-        <v>126.7029229891619</v>
+        <v>26.54205155201554</v>
       </c>
       <c r="E9" t="n">
-        <v>148.6533670490888</v>
+        <v>30.4925924334142</v>
       </c>
       <c r="F9" t="n">
-        <v>125.8272767242756</v>
+        <v>26.47520055801575</v>
       </c>
       <c r="G9" t="n">
-        <v>126.5668414441037</v>
+        <v>26.53372109256124</v>
       </c>
       <c r="H9" t="n">
-        <v>127.1220368710375</v>
+        <v>26.96117025957248</v>
       </c>
       <c r="I9" t="n">
-        <v>125.8269939088998</v>
+        <v>26.47491383978814</v>
       </c>
       <c r="J9" t="n">
-        <v>127.6810749094767</v>
+        <v>27.52020829801162</v>
       </c>
       <c r="K9" t="n">
-        <v>115.1197399998542</v>
+        <v>22.0360469977512</v>
       </c>
       <c r="L9" t="n">
-        <v>126.839049507691</v>
+        <v>26.67818289622591</v>
       </c>
     </row>
   </sheetData>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.96223545333389</v>
+        <v>16.96223545333388</v>
       </c>
       <c r="C2" t="n">
-        <v>7.265124000711547</v>
+        <v>7.265124000711545</v>
       </c>
       <c r="D2" t="n">
-        <v>17.4248216024425</v>
+        <v>17.42482160244249</v>
       </c>
       <c r="E2" t="n">
-        <v>8.50964966739593</v>
+        <v>8.509649667395923</v>
       </c>
       <c r="F2" t="n">
-        <v>8.50964966739593</v>
+        <v>8.509649667395923</v>
       </c>
       <c r="G2" t="n">
-        <v>17.20966768896326</v>
+        <v>17.20966768896324</v>
       </c>
       <c r="H2" t="n">
-        <v>17.53891035908641</v>
+        <v>17.53891035908639</v>
       </c>
       <c r="I2" t="n">
         <v>17.28315403267037</v>
       </c>
       <c r="J2" t="n">
-        <v>16.25857710159267</v>
+        <v>16.25857710159265</v>
       </c>
       <c r="K2" t="n">
-        <v>28.31327281772032</v>
+        <v>28.3132728177203</v>
       </c>
       <c r="L2" t="n">
         <v>17.05507538134657</v>
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.59625566185692</v>
+        <v>18.59625566185691</v>
       </c>
       <c r="C3" t="n">
-        <v>8.92991592730073</v>
+        <v>8.929915927300719</v>
       </c>
       <c r="D3" t="n">
-        <v>19.12832555776394</v>
+        <v>19.12832555776392</v>
       </c>
       <c r="E3" t="n">
-        <v>10.19172038779358</v>
+        <v>10.19172038779356</v>
       </c>
       <c r="F3" t="n">
-        <v>10.19172038779358</v>
+        <v>10.19172038779356</v>
       </c>
       <c r="G3" t="n">
-        <v>18.8808539882639</v>
+        <v>18.88085398826389</v>
       </c>
       <c r="H3" t="n">
-        <v>19.26542833298711</v>
+        <v>19.2654283329871</v>
       </c>
       <c r="I3" t="n">
-        <v>18.96278859666501</v>
+        <v>18.96278859666499</v>
       </c>
       <c r="J3" t="n">
-        <v>17.99688536759029</v>
+        <v>17.99688536759028</v>
       </c>
       <c r="K3" t="n">
-        <v>29.94909392185425</v>
+        <v>29.94909392185423</v>
       </c>
       <c r="L3" t="n">
-        <v>18.70318167614129</v>
+        <v>18.70318167614126</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.60485839920159</v>
+        <v>10.76128574145095</v>
       </c>
       <c r="C4" t="n">
-        <v>37.80536111575281</v>
+        <v>10.73140975659138</v>
       </c>
       <c r="D4" t="n">
-        <v>38.87984626340878</v>
+        <v>11.03627360565813</v>
       </c>
       <c r="E4" t="n">
-        <v>37.63974257429039</v>
+        <v>10.74812049821019</v>
       </c>
       <c r="F4" t="n">
-        <v>37.63974257429041</v>
+        <v>10.7481204982102</v>
       </c>
       <c r="G4" t="n">
-        <v>38.59649781151043</v>
+        <v>10.88101477326443</v>
       </c>
       <c r="H4" t="n">
-        <v>38.9480476939232</v>
+        <v>11.1044750361726</v>
       </c>
       <c r="I4" t="n">
-        <v>37.81068330001452</v>
+        <v>10.77796075958916</v>
       </c>
       <c r="J4" t="n">
-        <v>39.01758729637027</v>
+        <v>11.17401463861965</v>
       </c>
       <c r="K4" t="n">
-        <v>38.61198559743888</v>
+        <v>10.76841293968822</v>
       </c>
       <c r="L4" t="n">
-        <v>38.66085082593194</v>
+        <v>10.8172781681813</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>91.73930228897922</v>
+        <v>20.11294781537884</v>
       </c>
       <c r="C5" t="n">
-        <v>146.566282273204</v>
+        <v>29.87333177658044</v>
       </c>
       <c r="D5" t="n">
-        <v>156.8104572986185</v>
+        <v>31.79206103538762</v>
       </c>
       <c r="E5" t="n">
-        <v>148.9558636154977</v>
+        <v>30.33975769530326</v>
       </c>
       <c r="F5" t="n">
-        <v>148.9558636154977</v>
+        <v>30.33975769530326</v>
       </c>
       <c r="G5" t="n">
-        <v>146.8107468314439</v>
+        <v>29.92672249757113</v>
       </c>
       <c r="H5" t="n">
-        <v>176.9905774640674</v>
+        <v>35.39996014407034</v>
       </c>
       <c r="I5" t="n">
-        <v>148.9555659138165</v>
+        <v>30.33945999362205</v>
       </c>
       <c r="J5" t="n">
-        <v>175.3377183497159</v>
+        <v>35.16635757400358</v>
       </c>
       <c r="K5" t="n">
-        <v>132.5051338462555</v>
+        <v>27.29360694193645</v>
       </c>
       <c r="L5" t="n">
-        <v>149.0788703275886</v>
+        <v>30.25084949516999</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>205.7413193177644</v>
+        <v>40.17730270372422</v>
       </c>
       <c r="C6" t="n">
-        <v>136.4306548453143</v>
+        <v>28.08946135893774</v>
       </c>
       <c r="D6" t="n">
-        <v>136.8823772330142</v>
+        <v>28.28471896284614</v>
       </c>
       <c r="E6" t="n">
-        <v>126.133933179245</v>
+        <v>26.32309796028757</v>
       </c>
       <c r="F6" t="n">
-        <v>135.8981993181276</v>
+        <v>28.04160879141894</v>
       </c>
       <c r="G6" t="n">
-        <v>205.7329587300729</v>
+        <v>40.29703173553717</v>
       </c>
       <c r="H6" t="n">
-        <v>206.2916510300684</v>
+        <v>40.55694906374291</v>
       </c>
       <c r="I6" t="n">
-        <v>135.875306163108</v>
+        <v>28.03733428997176</v>
       </c>
       <c r="J6" t="n">
-        <v>204.8434002025996</v>
+        <v>40.35935755197219</v>
       </c>
       <c r="K6" t="n">
-        <v>136.5924505655364</v>
+        <v>28.01297468063352</v>
       </c>
       <c r="L6" t="n">
-        <v>136.7324560562053</v>
+        <v>28.077880595181</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.52546141121269</v>
+        <v>14.79531184970612</v>
       </c>
       <c r="C7" t="n">
-        <v>61.56346311373313</v>
+        <v>14.9128356855784</v>
       </c>
       <c r="D7" t="n">
-        <v>61.80008808892984</v>
+        <v>15.0702361450914</v>
       </c>
       <c r="E7" t="n">
-        <v>60.81312110985395</v>
+        <v>14.82663509836952</v>
       </c>
       <c r="F7" t="n">
-        <v>60.81312110985395</v>
+        <v>14.82663509836952</v>
       </c>
       <c r="G7" t="n">
-        <v>61.51710082352157</v>
+        <v>14.91504088151918</v>
       </c>
       <c r="H7" t="n">
-        <v>61.86865070593431</v>
+        <v>15.13850114442775</v>
       </c>
       <c r="I7" t="n">
-        <v>60.73128631202562</v>
+        <v>14.8119868678442</v>
       </c>
       <c r="J7" t="n">
-        <v>61.93819030838137</v>
+        <v>15.20804074687481</v>
       </c>
       <c r="K7" t="n">
-        <v>61.53258860944999</v>
+        <v>14.80243904794338</v>
       </c>
       <c r="L7" t="n">
-        <v>61.58145383794309</v>
+        <v>14.85130427643646</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>130.0712864176492</v>
+        <v>26.85937698546856</v>
       </c>
       <c r="C8" t="n">
-        <v>190.5016097552988</v>
+        <v>37.605949371529</v>
       </c>
       <c r="D8" t="n">
-        <v>203.1523211823718</v>
+        <v>39.94822903473322</v>
       </c>
       <c r="E8" t="n">
-        <v>173.1679884879799</v>
+        <v>34.60109164976974</v>
       </c>
       <c r="F8" t="n">
-        <v>131.2377465091797</v>
+        <v>27.22136910148872</v>
       </c>
       <c r="G8" t="n">
-        <v>190.3649542965382</v>
+        <v>37.59226296989125</v>
       </c>
       <c r="H8" t="n">
-        <v>190.7165041791245</v>
+        <v>37.81572323283032</v>
       </c>
       <c r="I8" t="n">
-        <v>189.5791397850424</v>
+        <v>37.48920895621629</v>
       </c>
       <c r="J8" t="n">
-        <v>190.7978948599503</v>
+        <v>37.88734862506076</v>
       </c>
       <c r="K8" t="n">
-        <v>128.9582724775963</v>
+        <v>26.66935934443499</v>
       </c>
       <c r="L8" t="n">
-        <v>253.4198184207723</v>
+        <v>48.61485626006305</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103.2555756026386</v>
+        <v>22.13981190760015</v>
       </c>
       <c r="C9" t="n">
-        <v>122.1242227325796</v>
+        <v>25.57152932074015</v>
       </c>
       <c r="D9" t="n">
-        <v>122.3612149064148</v>
+        <v>25.72899440721316</v>
       </c>
       <c r="E9" t="n">
-        <v>143.0225092123596</v>
+        <v>29.29548732600954</v>
       </c>
       <c r="F9" t="n">
-        <v>121.2923393092438</v>
+        <v>25.47097744378466</v>
       </c>
       <c r="G9" t="n">
-        <v>122.077860442368</v>
+        <v>25.57373451668094</v>
       </c>
       <c r="H9" t="n">
-        <v>122.4294103247809</v>
+        <v>25.79719477958951</v>
       </c>
       <c r="I9" t="n">
-        <v>121.2920459308721</v>
+        <v>25.47068050300594</v>
       </c>
       <c r="J9" t="n">
-        <v>122.498949927228</v>
+        <v>25.86673438203658</v>
       </c>
       <c r="K9" t="n">
-        <v>111.1828008426923</v>
+        <v>23.46296908577935</v>
       </c>
       <c r="L9" t="n">
-        <v>122.1422134567895</v>
+        <v>25.5099979115982</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.0028069050752</v>
+        <v>18.00280690507511</v>
       </c>
       <c r="C2" t="n">
-        <v>7.756182964698716</v>
+        <v>7.75618296469872</v>
       </c>
       <c r="D2" t="n">
-        <v>18.91747302047921</v>
+        <v>18.91747302047918</v>
       </c>
       <c r="E2" t="n">
-        <v>9.322454911150187</v>
+        <v>9.322454911150013</v>
       </c>
       <c r="F2" t="n">
-        <v>9.322454911150187</v>
+        <v>9.322454911150031</v>
       </c>
       <c r="G2" t="n">
-        <v>19.09700069331497</v>
+        <v>19.0970006933149</v>
       </c>
       <c r="H2" t="n">
-        <v>28.52315829907208</v>
+        <v>28.52315829907204</v>
       </c>
       <c r="I2" t="n">
-        <v>18.58924952600104</v>
+        <v>18.58924952600096</v>
       </c>
       <c r="J2" t="n">
-        <v>17.00820384684177</v>
+        <v>17.00820384684166</v>
       </c>
       <c r="K2" t="n">
-        <v>29.23443469273321</v>
+        <v>29.23443469273317</v>
       </c>
       <c r="L2" t="n">
-        <v>22.25181081168996</v>
+        <v>22.25181081168975</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.71016699538828</v>
+        <v>19.71016699538809</v>
       </c>
       <c r="C3" t="n">
         <v>9.483960249717146</v>
       </c>
       <c r="D3" t="n">
-        <v>20.7622225006179</v>
+        <v>20.76222250061772</v>
       </c>
       <c r="E3" t="n">
-        <v>11.11772886309317</v>
+        <v>11.11772886309319</v>
       </c>
       <c r="F3" t="n">
-        <v>11.11772886309317</v>
+        <v>11.11772886309299</v>
       </c>
       <c r="G3" t="n">
-        <v>20.96871651342441</v>
+        <v>20.96871651342423</v>
       </c>
       <c r="H3" t="n">
-        <v>31.81700201152044</v>
+        <v>31.81700201152042</v>
       </c>
       <c r="I3" t="n">
-        <v>20.38142957900747</v>
+        <v>20.38142957900731</v>
       </c>
       <c r="J3" t="n">
-        <v>18.85373594733374</v>
+        <v>18.8537359473336</v>
       </c>
       <c r="K3" t="n">
         <v>31.01838122025655</v>
       </c>
       <c r="L3" t="n">
-        <v>24.59737751606512</v>
+        <v>24.59737751606495</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.84983593158178</v>
+        <v>11.06314064034084</v>
       </c>
       <c r="C4" t="n">
-        <v>37.9836163505804</v>
+        <v>10.9869036537896</v>
       </c>
       <c r="D4" t="n">
-        <v>39.39356617949854</v>
+        <v>11.60687088825926</v>
       </c>
       <c r="E4" t="n">
-        <v>38.04511945391734</v>
+        <v>11.20820207477771</v>
       </c>
       <c r="F4" t="n">
-        <v>38.04511945391734</v>
+        <v>11.20820207477771</v>
       </c>
       <c r="G4" t="n">
-        <v>39.34404946485959</v>
+        <v>11.68609454030936</v>
       </c>
       <c r="H4" t="n">
-        <v>45.10201094290778</v>
+        <v>17.31531565167111</v>
       </c>
       <c r="I4" t="n">
-        <v>38.20790062532289</v>
+        <v>11.23654046588353</v>
       </c>
       <c r="J4" t="n">
-        <v>39.39666346640892</v>
+        <v>11.60996817516649</v>
       </c>
       <c r="K4" t="n">
-        <v>39.15293329990307</v>
+        <v>11.36623800866454</v>
       </c>
       <c r="L4" t="n">
-        <v>41.37577135311791</v>
+        <v>13.58907606187588</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>122.3351319947635</v>
+        <v>25.75655266784622</v>
       </c>
       <c r="C5" t="n">
-        <v>175.9487598562164</v>
+        <v>35.26876877920774</v>
       </c>
       <c r="D5" t="n">
-        <v>216.253887001115</v>
+        <v>42.73428718419889</v>
       </c>
       <c r="E5" t="n">
-        <v>197.6823680191048</v>
+        <v>39.30435767000918</v>
       </c>
       <c r="F5" t="n">
-        <v>197.6823680191048</v>
+        <v>39.30435767000918</v>
       </c>
       <c r="G5" t="n">
-        <v>230.7261258109943</v>
+        <v>45.36933979471218</v>
       </c>
       <c r="H5" t="n">
-        <v>863.9444862578273</v>
+        <v>161.431590526182</v>
       </c>
       <c r="I5" t="n">
-        <v>197.6819904767434</v>
+        <v>39.3039801276475</v>
       </c>
       <c r="J5" t="n">
-        <v>224.8487857031571</v>
+        <v>44.24954151197193</v>
       </c>
       <c r="K5" t="n">
-        <v>193.4797606872372</v>
+        <v>38.52775948165961</v>
       </c>
       <c r="L5" t="n">
-        <v>462.8613977356505</v>
+        <v>87.7705459032384</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>215.5538501501927</v>
+        <v>29.30063751602294</v>
       </c>
       <c r="C6" t="n">
-        <v>142.1115718358414</v>
+        <v>29.31342371989141</v>
       </c>
       <c r="D6" t="n">
-        <v>142.9506746146223</v>
+        <v>29.8329218740829</v>
       </c>
       <c r="E6" t="n">
-        <v>131.5222295975177</v>
+        <v>27.66017337090459</v>
       </c>
       <c r="F6" t="n">
-        <v>141.8543430038773</v>
+        <v>29.47862532057045</v>
       </c>
       <c r="G6" t="n">
-        <v>216.0480636834699</v>
+        <v>42.78600087427105</v>
       </c>
       <c r="H6" t="n">
-        <v>221.4252420835381</v>
+        <v>48.34820416427043</v>
       </c>
       <c r="I6" t="n">
-        <v>141.8300425259328</v>
+        <v>42.33644679983965</v>
       </c>
       <c r="J6" t="n">
-        <v>214.6343532571524</v>
+        <v>42.45180141122451</v>
       </c>
       <c r="K6" t="n">
-        <v>142.681203439297</v>
+        <v>29.5872134544694</v>
       </c>
       <c r="L6" t="n">
-        <v>145.0876399118833</v>
+        <v>31.8423648293161</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63.47539956148934</v>
+        <v>15.39723981572367</v>
       </c>
       <c r="C7" t="n">
-        <v>63.47023630976292</v>
+        <v>15.47254874229979</v>
       </c>
       <c r="D7" t="n">
-        <v>64.01874351181829</v>
+        <v>15.94090207526945</v>
       </c>
       <c r="E7" t="n">
-        <v>62.91734739988051</v>
+        <v>15.5857141695472</v>
       </c>
       <c r="F7" t="n">
-        <v>62.91734739988051</v>
+        <v>15.5857141695472</v>
       </c>
       <c r="G7" t="n">
-        <v>63.96961309476715</v>
+        <v>16.02019371568953</v>
       </c>
       <c r="H7" t="n">
-        <v>69.72757457281517</v>
+        <v>21.64941482704858</v>
       </c>
       <c r="I7" t="n">
-        <v>62.83346425523037</v>
+        <v>15.57063964126247</v>
       </c>
       <c r="J7" t="n">
-        <v>64.02222709631627</v>
+        <v>15.94406735055201</v>
       </c>
       <c r="K7" t="n">
-        <v>63.77849692981044</v>
+        <v>15.7003371840421</v>
       </c>
       <c r="L7" t="n">
-        <v>66.00133498302561</v>
+        <v>17.92317523726004</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>135.8022240657714</v>
+        <v>28.12676085950498</v>
       </c>
       <c r="C8" t="n">
-        <v>199.7618268285979</v>
+        <v>39.45986854363689</v>
       </c>
       <c r="D8" t="n">
-        <v>213.4621421162205</v>
+        <v>42.24294008711676</v>
       </c>
       <c r="E8" t="n">
-        <v>181.6471416947095</v>
+        <v>36.48215785220758</v>
       </c>
       <c r="F8" t="n">
-        <v>137.2353533674939</v>
+        <v>28.665683148972</v>
       </c>
       <c r="G8" t="n">
-        <v>200.1683651387962</v>
+        <v>39.99117394554909</v>
       </c>
       <c r="H8" t="n">
-        <v>205.9263266168931</v>
+        <v>45.62039505692172</v>
       </c>
       <c r="I8" t="n">
-        <v>199.0322162992595</v>
+        <v>39.54161987112241</v>
       </c>
       <c r="J8" t="n">
-        <v>200.2335318087693</v>
+        <v>39.9172568500374</v>
       </c>
       <c r="K8" t="n">
-        <v>134.9188675876592</v>
+        <v>28.22104235198727</v>
       </c>
       <c r="L8" t="n">
-        <v>268.9196562306279</v>
+        <v>53.63679958331818</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116.1142556993572</v>
+        <v>24.66167844578177</v>
       </c>
       <c r="C9" t="n">
-        <v>138.4647691216393</v>
+        <v>28.67158644566963</v>
       </c>
       <c r="D9" t="n">
-        <v>139.0136620174242</v>
+        <v>29.14000766072442</v>
       </c>
       <c r="E9" t="n">
-        <v>163.6263343151068</v>
+        <v>33.31049577058347</v>
       </c>
       <c r="F9" t="n">
-        <v>137.8283613187465</v>
+        <v>28.77005254782692</v>
       </c>
       <c r="G9" t="n">
-        <v>138.9641459066435</v>
+        <v>29.21923141905683</v>
       </c>
       <c r="H9" t="n">
-        <v>144.7221073846914</v>
+        <v>34.84845253041991</v>
       </c>
       <c r="I9" t="n">
-        <v>137.8279970671066</v>
+        <v>28.76967734463234</v>
       </c>
       <c r="J9" t="n">
-        <v>139.0167599081925</v>
+        <v>29.14310505391926</v>
       </c>
       <c r="K9" t="n">
-        <v>125.2945444118085</v>
+        <v>26.61965268727639</v>
       </c>
       <c r="L9" t="n">
-        <v>140.995867794902</v>
+        <v>31.1222129406273</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.16558358281918</v>
+        <v>18.16558358281909</v>
       </c>
       <c r="C2" t="n">
-        <v>7.659313807099752</v>
+        <v>7.659313807099736</v>
       </c>
       <c r="D2" t="n">
-        <v>18.34444469563954</v>
+        <v>18.34444469563947</v>
       </c>
       <c r="E2" t="n">
-        <v>8.873586732332946</v>
+        <v>8.8735867323329</v>
       </c>
       <c r="F2" t="n">
-        <v>8.873586732332946</v>
+        <v>8.873586732332909</v>
       </c>
       <c r="G2" t="n">
-        <v>18.21329805848423</v>
+        <v>18.21329805848418</v>
       </c>
       <c r="H2" t="n">
-        <v>18.50276174180122</v>
+        <v>18.50276174180118</v>
       </c>
       <c r="I2" t="n">
-        <v>18.50312639703806</v>
+        <v>18.50312639703817</v>
       </c>
       <c r="J2" t="n">
-        <v>16.46698403545917</v>
+        <v>16.46698403545923</v>
       </c>
       <c r="K2" t="n">
-        <v>28.27722698289303</v>
+        <v>28.27722698289299</v>
       </c>
       <c r="L2" t="n">
-        <v>18.01518769221832</v>
+        <v>18.01518769221831</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.8358235978941</v>
+        <v>19.83582359789416</v>
       </c>
       <c r="C3" t="n">
-        <v>9.364114641844409</v>
+        <v>9.364114641844417</v>
       </c>
       <c r="D3" t="n">
-        <v>20.04155092860556</v>
+        <v>20.0415509286055</v>
       </c>
       <c r="E3" t="n">
-        <v>10.59437851080613</v>
+        <v>10.59437851080606</v>
       </c>
       <c r="F3" t="n">
-        <v>10.59437851080613</v>
+        <v>10.59437851080605</v>
       </c>
       <c r="G3" t="n">
-        <v>19.89070512893288</v>
+        <v>19.89070512893285</v>
       </c>
       <c r="H3" t="n">
-        <v>20.22968632942074</v>
+        <v>20.22968632942069</v>
       </c>
       <c r="I3" t="n">
-        <v>20.22197661123472</v>
+        <v>20.22197661123469</v>
       </c>
       <c r="J3" t="n">
-        <v>18.23127568432182</v>
+        <v>18.23127568432174</v>
       </c>
       <c r="K3" t="n">
-        <v>29.936540438995</v>
+        <v>29.9365404389949</v>
       </c>
       <c r="L3" t="n">
-        <v>19.66298487024129</v>
+        <v>19.66298487024127</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.51059683509055</v>
+        <v>10.90347872154449</v>
       </c>
       <c r="C4" t="n">
-        <v>37.72984824815241</v>
+        <v>10.88872085091362</v>
       </c>
       <c r="D4" t="n">
-        <v>38.61692218767402</v>
+        <v>11.00980407412794</v>
       </c>
       <c r="E4" t="n">
-        <v>37.68240850362896</v>
+        <v>10.92256942430414</v>
       </c>
       <c r="F4" t="n">
-        <v>37.68240850362895</v>
+        <v>10.92256942430414</v>
       </c>
       <c r="G4" t="n">
-        <v>38.38416730820359</v>
+        <v>10.90459925373404</v>
       </c>
       <c r="H4" t="n">
-        <v>38.71142138358051</v>
+        <v>11.10430327003445</v>
       </c>
       <c r="I4" t="n">
-        <v>37.73028362692038</v>
+        <v>10.93077379244423</v>
       </c>
       <c r="J4" t="n">
-        <v>38.88281421098206</v>
+        <v>11.27569609743596</v>
       </c>
       <c r="K4" t="n">
-        <v>38.46735404445802</v>
+        <v>10.86023593091207</v>
       </c>
       <c r="L4" t="n">
-        <v>38.42200643083584</v>
+        <v>10.81488831728982</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110.007895754502</v>
+        <v>23.48700326317576</v>
       </c>
       <c r="C5" t="n">
-        <v>166.1109635153001</v>
+        <v>33.48379701549788</v>
       </c>
       <c r="D5" t="n">
-        <v>158.9842555237541</v>
+        <v>32.19445462648666</v>
       </c>
       <c r="E5" t="n">
-        <v>167.7333025282663</v>
+        <v>33.81152664861332</v>
       </c>
       <c r="F5" t="n">
-        <v>167.7333025282663</v>
+        <v>33.81152664861332</v>
       </c>
       <c r="G5" t="n">
-        <v>153.7823315351009</v>
+        <v>31.21467604761579</v>
       </c>
       <c r="H5" t="n">
-        <v>182.2083338572311</v>
+        <v>36.3597597285472</v>
       </c>
       <c r="I5" t="n">
-        <v>167.733033531282</v>
+        <v>33.81125765163108</v>
       </c>
       <c r="J5" t="n">
-        <v>190.0317450743214</v>
+        <v>37.87790778523667</v>
       </c>
       <c r="K5" t="n">
-        <v>145.604595442986</v>
+        <v>29.71639031487883</v>
       </c>
       <c r="L5" t="n">
-        <v>154.1683441505336</v>
+        <v>31.18624364557218</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>205.4894795210524</v>
+        <v>28.16541640120692</v>
       </c>
       <c r="C6" t="n">
-        <v>136.3838199562661</v>
+        <v>28.25181977745783</v>
       </c>
       <c r="D6" t="n">
-        <v>136.6232277114669</v>
+        <v>28.25889998567764</v>
       </c>
       <c r="E6" t="n">
-        <v>126.1137552607906</v>
+        <v>26.48648636922994</v>
       </c>
       <c r="F6" t="n">
-        <v>135.8407169104304</v>
+        <v>28.1984316102901</v>
       </c>
       <c r="G6" t="n">
-        <v>136.4633592013743</v>
+        <v>28.16653693339648</v>
       </c>
       <c r="H6" t="n">
-        <v>205.7704496000606</v>
+        <v>40.50669207681509</v>
       </c>
       <c r="I6" t="n">
-        <v>135.8094755200911</v>
+        <v>40.31905698593</v>
       </c>
       <c r="J6" t="n">
-        <v>142.1182051827688</v>
+        <v>40.42942360206719</v>
       </c>
       <c r="K6" t="n">
-        <v>136.4672460088901</v>
+        <v>28.10821682319207</v>
       </c>
       <c r="L6" t="n">
-        <v>136.5033926944279</v>
+        <v>28.07721220614434</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.30897660289489</v>
+        <v>14.91599353893587</v>
       </c>
       <c r="C7" t="n">
-        <v>61.36237400756763</v>
+        <v>15.04804536203296</v>
       </c>
       <c r="D7" t="n">
-        <v>61.41495833706653</v>
+        <v>15.02225841467917</v>
       </c>
       <c r="E7" t="n">
-        <v>60.63923164253052</v>
+        <v>14.96297027485751</v>
       </c>
       <c r="F7" t="n">
-        <v>60.63923164253052</v>
+        <v>14.96297027485751</v>
       </c>
       <c r="G7" t="n">
-        <v>61.18254707600785</v>
+        <v>14.91711407112542</v>
       </c>
       <c r="H7" t="n">
-        <v>61.50980115138482</v>
+        <v>15.11681808742581</v>
       </c>
       <c r="I7" t="n">
-        <v>60.52866339472486</v>
+        <v>14.94328860983557</v>
       </c>
       <c r="J7" t="n">
-        <v>61.6811939787863</v>
+        <v>15.28821091482735</v>
       </c>
       <c r="K7" t="n">
-        <v>61.2657338122625</v>
+        <v>14.87275074830338</v>
       </c>
       <c r="L7" t="n">
-        <v>61.22038619864017</v>
+        <v>14.82740313468118</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>129.572470489174</v>
+        <v>26.93036839781985</v>
       </c>
       <c r="C8" t="n">
-        <v>189.6914428759156</v>
+        <v>37.633961360478</v>
       </c>
       <c r="D8" t="n">
-        <v>202.0573046708392</v>
+        <v>39.77531123529609</v>
       </c>
       <c r="E8" t="n">
-        <v>172.4502488744034</v>
+        <v>34.64170920103574</v>
       </c>
       <c r="F8" t="n">
-        <v>130.7586865392932</v>
+        <v>27.30399426981655</v>
       </c>
       <c r="G8" t="n">
-        <v>189.3939585539981</v>
+        <v>37.48232236897967</v>
       </c>
       <c r="H8" t="n">
-        <v>189.7212126295358</v>
+        <v>37.68202638530833</v>
       </c>
       <c r="I8" t="n">
-        <v>188.740074872715</v>
+        <v>37.50849690768978</v>
       </c>
       <c r="J8" t="n">
-        <v>189.9043869440996</v>
+        <v>37.85549275443921</v>
       </c>
       <c r="K8" t="n">
-        <v>128.4156643514559</v>
+        <v>26.69113845916222</v>
       </c>
       <c r="L8" t="n">
-        <v>252.0524103688381</v>
+        <v>48.41383920664438</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106.2240508774342</v>
+        <v>22.8210465684203</v>
       </c>
       <c r="C9" t="n">
-        <v>125.9128628119465</v>
+        <v>26.40893133004327</v>
       </c>
       <c r="D9" t="n">
-        <v>125.9657966364968</v>
+        <v>26.38320589381828</v>
       </c>
       <c r="E9" t="n">
-        <v>147.7382733001238</v>
+        <v>30.29240152352966</v>
       </c>
       <c r="F9" t="n">
-        <v>125.0794170058953</v>
+        <v>26.30444283735484</v>
       </c>
       <c r="G9" t="n">
-        <v>125.7330358803867</v>
+        <v>26.2780000391357</v>
       </c>
       <c r="H9" t="n">
-        <v>126.0602899557637</v>
+        <v>26.47770405543633</v>
       </c>
       <c r="I9" t="n">
-        <v>125.0791521991037</v>
+        <v>26.30417457784613</v>
       </c>
       <c r="J9" t="n">
-        <v>126.2316827831653</v>
+        <v>26.64909688283774</v>
       </c>
       <c r="K9" t="n">
-        <v>101.0917292913897</v>
+        <v>24.23131397464775</v>
       </c>
       <c r="L9" t="n">
-        <v>125.7708750030192</v>
+        <v>26.1882891026918</v>
       </c>
     </row>
   </sheetData>
@@ -4484,16 +4484,16 @@
         <v>17.29958522145385</v>
       </c>
       <c r="E2" t="n">
-        <v>8.473548685851105</v>
+        <v>8.473548685851123</v>
       </c>
       <c r="F2" t="n">
-        <v>8.473548685851103</v>
+        <v>8.473548685851123</v>
       </c>
       <c r="G2" t="n">
-        <v>17.09601654566626</v>
+        <v>17.09601654566627</v>
       </c>
       <c r="H2" t="n">
-        <v>17.37479053136388</v>
+        <v>17.37479053136389</v>
       </c>
       <c r="I2" t="n">
         <v>17.17045260904762</v>
@@ -4502,10 +4502,10 @@
         <v>16.22570033219401</v>
       </c>
       <c r="K2" t="n">
-        <v>28.29881452127475</v>
+        <v>28.29881452127473</v>
       </c>
       <c r="L2" t="n">
-        <v>16.93021755950075</v>
+        <v>16.93021755950074</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.5444114523054</v>
+        <v>18.54441145230541</v>
       </c>
       <c r="C3" t="n">
         <v>9.037785842367065</v>
       </c>
       <c r="D3" t="n">
-        <v>19.00159692958121</v>
+        <v>19.00159692958123</v>
       </c>
       <c r="E3" t="n">
-        <v>10.15600940950917</v>
+        <v>10.15600940950918</v>
       </c>
       <c r="F3" t="n">
-        <v>10.15600940950917</v>
+        <v>10.15600940950918</v>
       </c>
       <c r="G3" t="n">
-        <v>18.76745078330136</v>
+        <v>18.76745078330137</v>
       </c>
       <c r="H3" t="n">
-        <v>19.09385509138251</v>
+        <v>19.09385509138252</v>
       </c>
       <c r="I3" t="n">
         <v>18.8509229223089</v>
       </c>
       <c r="J3" t="n">
-        <v>17.97129854479951</v>
+        <v>17.97129854479952</v>
       </c>
       <c r="K3" t="n">
-        <v>29.95328266981367</v>
+        <v>29.95328266981365</v>
       </c>
       <c r="L3" t="n">
-        <v>18.57689029542933</v>
+        <v>18.57689029542932</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.4489676947318</v>
+        <v>10.74912873126092</v>
       </c>
       <c r="C4" t="n">
-        <v>37.65470221490902</v>
+        <v>10.72938109892805</v>
       </c>
       <c r="D4" t="n">
-        <v>38.68525330102107</v>
+        <v>10.98541433755013</v>
       </c>
       <c r="E4" t="n">
-        <v>37.5192978026972</v>
+        <v>10.71644942521092</v>
       </c>
       <c r="F4" t="n">
-        <v>37.51929780269721</v>
+        <v>10.71644942521093</v>
       </c>
       <c r="G4" t="n">
-        <v>38.40832932093768</v>
+        <v>10.83696104490511</v>
       </c>
       <c r="H4" t="n">
-        <v>38.73035185352626</v>
+        <v>11.03051289005536</v>
       </c>
       <c r="I4" t="n">
-        <v>37.62037277066869</v>
+        <v>10.73399251577885</v>
       </c>
       <c r="J4" t="n">
-        <v>38.85775061624885</v>
+        <v>11.15791165277798</v>
       </c>
       <c r="K4" t="n">
-        <v>38.49709560212828</v>
+        <v>10.79725663865734</v>
       </c>
       <c r="L4" t="n">
-        <v>38.46648216633105</v>
+        <v>10.76664320286014</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94.33437260924498</v>
+        <v>20.58495994291876</v>
       </c>
       <c r="C5" t="n">
-        <v>150.2236870301359</v>
+        <v>30.54152231905384</v>
       </c>
       <c r="D5" t="n">
-        <v>155.7513790525024</v>
+        <v>31.5890523581679</v>
       </c>
       <c r="E5" t="n">
-        <v>148.5751476385909</v>
+        <v>30.26227889041667</v>
       </c>
       <c r="F5" t="n">
-        <v>148.5751476385909</v>
+        <v>30.26227889041667</v>
       </c>
       <c r="G5" t="n">
-        <v>146.3747381120774</v>
+        <v>29.83904888918066</v>
       </c>
       <c r="H5" t="n">
-        <v>173.3972275728484</v>
+        <v>34.73188288822777</v>
       </c>
       <c r="I5" t="n">
-        <v>148.5748489690536</v>
+        <v>30.26198022088042</v>
       </c>
       <c r="J5" t="n">
-        <v>177.5893435530076</v>
+        <v>35.57467187734276</v>
       </c>
       <c r="K5" t="n">
-        <v>138.7969109974254</v>
+        <v>28.45002405257628</v>
       </c>
       <c r="L5" t="n">
-        <v>147.8912011170275</v>
+        <v>30.02539363382718</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>205.4996007686618</v>
+        <v>28.01065432415636</v>
       </c>
       <c r="C6" t="n">
-        <v>136.30205200316</v>
+        <v>28.09131456758285</v>
       </c>
       <c r="D6" t="n">
-        <v>136.6974249914742</v>
+        <v>28.23555646159821</v>
       </c>
       <c r="E6" t="n">
-        <v>125.9725067822996</v>
+        <v>26.2842141212654</v>
       </c>
       <c r="F6" t="n">
-        <v>135.7235345379291</v>
+        <v>28.00039499695692</v>
       </c>
       <c r="G6" t="n">
-        <v>205.4589623948677</v>
+        <v>40.23787230660484</v>
       </c>
       <c r="H6" t="n">
-        <v>205.9344349153721</v>
+        <v>40.45843134948197</v>
       </c>
       <c r="I6" t="n">
-        <v>135.6972232617414</v>
+        <v>40.13490377747855</v>
       </c>
       <c r="J6" t="n">
-        <v>204.5839772471995</v>
+        <v>29.32694520894401</v>
       </c>
       <c r="K6" t="n">
-        <v>136.5004876197836</v>
+        <v>28.04585354030138</v>
       </c>
       <c r="L6" t="n">
-        <v>136.5521105110709</v>
+        <v>28.02971369799247</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.07792845629294</v>
+        <v>14.73182580371498</v>
       </c>
       <c r="C7" t="n">
-        <v>61.1273405389832</v>
+        <v>14.86056542157989</v>
       </c>
       <c r="D7" t="n">
-        <v>61.31385796772703</v>
+        <v>14.96804873731004</v>
       </c>
       <c r="E7" t="n">
-        <v>60.35151926559664</v>
+        <v>14.7349203809067</v>
       </c>
       <c r="F7" t="n">
-        <v>60.35151926559664</v>
+        <v>14.7349203809067</v>
       </c>
       <c r="G7" t="n">
-        <v>61.03729008249874</v>
+        <v>14.81965811735918</v>
       </c>
       <c r="H7" t="n">
-        <v>61.35931261508736</v>
+        <v>15.01320996250945</v>
       </c>
       <c r="I7" t="n">
-        <v>60.24933353222971</v>
+        <v>14.71668958823292</v>
       </c>
       <c r="J7" t="n">
-        <v>61.48671137780996</v>
+        <v>15.14060872523205</v>
       </c>
       <c r="K7" t="n">
-        <v>61.12605636368933</v>
+        <v>14.77995371111144</v>
       </c>
       <c r="L7" t="n">
-        <v>61.09544292789216</v>
+        <v>14.74934027531422</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>129.3244854809516</v>
+        <v>26.74321977496995</v>
       </c>
       <c r="C8" t="n">
-        <v>189.3273430969694</v>
+        <v>37.42376574952435</v>
       </c>
       <c r="D8" t="n">
-        <v>201.8135689992178</v>
+        <v>39.69599774486146</v>
       </c>
       <c r="E8" t="n">
-        <v>172.071168947752</v>
+        <v>34.39757861842189</v>
       </c>
       <c r="F8" t="n">
-        <v>130.4541381847944</v>
+        <v>27.07298124383039</v>
       </c>
       <c r="G8" t="n">
-        <v>189.1276439064574</v>
+        <v>37.36356026821944</v>
       </c>
       <c r="H8" t="n">
-        <v>189.4496664392153</v>
+        <v>37.55711211339948</v>
       </c>
       <c r="I8" t="n">
-        <v>188.3396873561883</v>
+        <v>37.26059173909314</v>
       </c>
       <c r="J8" t="n">
-        <v>189.5888262254212</v>
+        <v>37.68658081624391</v>
       </c>
       <c r="K8" t="n">
-        <v>128.2609841384595</v>
+        <v>26.59570093544607</v>
       </c>
       <c r="L8" t="n">
-        <v>251.6976465691992</v>
+        <v>48.29532793441186</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102.8606563395863</v>
+        <v>22.08558587132748</v>
       </c>
       <c r="C9" t="n">
-        <v>121.6385816549485</v>
+        <v>25.51054380028171</v>
       </c>
       <c r="D9" t="n">
-        <v>121.8254610855366</v>
+        <v>25.61809082833612</v>
       </c>
       <c r="E9" t="n">
-        <v>142.3731806779097</v>
+        <v>29.17073271125181</v>
       </c>
       <c r="F9" t="n">
-        <v>120.7608692045192</v>
+        <v>25.36696591254624</v>
       </c>
       <c r="G9" t="n">
-        <v>121.548531198464</v>
+        <v>25.46963649606105</v>
       </c>
       <c r="H9" t="n">
-        <v>121.8705537310524</v>
+        <v>25.66318834121125</v>
       </c>
       <c r="I9" t="n">
-        <v>120.7605746481949</v>
+        <v>25.36666796693475</v>
       </c>
       <c r="J9" t="n">
-        <v>121.9979524937751</v>
+        <v>25.79058710393387</v>
       </c>
       <c r="K9" t="n">
-        <v>110.3456717503298</v>
+        <v>23.44260597222068</v>
       </c>
       <c r="L9" t="n">
-        <v>121.6066840438572</v>
+        <v>25.39931865401605</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.22202273144147</v>
+        <v>21.22202273144149</v>
       </c>
       <c r="C2" t="n">
-        <v>14.88686663001517</v>
+        <v>14.88686663001519</v>
       </c>
       <c r="D2" t="n">
-        <v>38.06552467384175</v>
+        <v>38.06552467384174</v>
       </c>
       <c r="E2" t="n">
         <v>17.16189048414802</v>
       </c>
       <c r="F2" t="n">
-        <v>10.73790757197455</v>
+        <v>10.73790757197453</v>
       </c>
       <c r="G2" t="n">
-        <v>27.72633215458441</v>
+        <v>27.72633215458442</v>
       </c>
       <c r="H2" t="n">
-        <v>49.81562359715351</v>
+        <v>49.8156235971536</v>
       </c>
       <c r="I2" t="n">
-        <v>19.44503036511972</v>
+        <v>19.44503036511973</v>
       </c>
       <c r="J2" t="n">
-        <v>30.91909132611949</v>
+        <v>30.91909132611946</v>
       </c>
       <c r="K2" t="n">
-        <v>29.55007318430358</v>
+        <v>29.55007318430359</v>
       </c>
       <c r="L2" t="n">
-        <v>45.67892364775915</v>
+        <v>45.67892364775917</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.91836253961655</v>
+        <v>23.91836253961656</v>
       </c>
       <c r="C3" t="n">
         <v>17.31178124368953</v>
       </c>
       <c r="D3" t="n">
-        <v>43.29187889429285</v>
+        <v>43.29187889429286</v>
       </c>
       <c r="E3" t="n">
-        <v>19.59090926467539</v>
+        <v>19.59090926467538</v>
       </c>
       <c r="F3" t="n">
-        <v>13.16692635250191</v>
+        <v>13.16692635250189</v>
       </c>
       <c r="G3" t="n">
-        <v>31.39966573986884</v>
+        <v>31.39966573986886</v>
       </c>
       <c r="H3" t="n">
-        <v>56.81279766558153</v>
+        <v>56.81279766558168</v>
       </c>
       <c r="I3" t="n">
-        <v>21.86408049497449</v>
+        <v>21.8640804949745</v>
       </c>
       <c r="J3" t="n">
-        <v>34.07232818677303</v>
+        <v>34.07232818677304</v>
       </c>
       <c r="K3" t="n">
         <v>32.36400863091875</v>
       </c>
       <c r="L3" t="n">
-        <v>52.0481926736116</v>
+        <v>52.04819267361167</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.78585321913611</v>
+        <v>13.90159737009897</v>
       </c>
       <c r="C4" t="n">
-        <v>39.74033726741736</v>
+        <v>12.4938324370371</v>
       </c>
       <c r="D4" t="n">
-        <v>52.79860140417256</v>
+        <v>23.91434555513551</v>
       </c>
       <c r="E4" t="n">
-        <v>39.87815171425964</v>
+        <v>12.51809456357247</v>
       </c>
       <c r="F4" t="n">
-        <v>39.87815171425966</v>
+        <v>12.51809456357247</v>
       </c>
       <c r="G4" t="n">
-        <v>46.47574163072042</v>
+        <v>17.73704367576347</v>
       </c>
       <c r="H4" t="n">
-        <v>59.77890810285261</v>
+        <v>30.89465225381552</v>
       </c>
       <c r="I4" t="n">
-        <v>40.60529283619971</v>
+        <v>12.64488123317106</v>
       </c>
       <c r="J4" t="n">
-        <v>44.59406233871852</v>
+        <v>15.70980648968141</v>
       </c>
       <c r="K4" t="n">
-        <v>43.25124800489155</v>
+        <v>14.36699215585446</v>
       </c>
       <c r="L4" t="n">
-        <v>57.32150445588285</v>
+        <v>28.43724860684572</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>389.0067227983337</v>
+        <v>74.83647008585582</v>
       </c>
       <c r="C5" t="n">
-        <v>292.2264619752957</v>
+        <v>56.93139014483403</v>
       </c>
       <c r="D5" t="n">
-        <v>1363.317362427119</v>
+        <v>254.5656462453659</v>
       </c>
       <c r="E5" t="n">
-        <v>292.2264702083315</v>
+        <v>56.93139837787107</v>
       </c>
       <c r="F5" t="n">
-        <v>292.2264702083314</v>
+        <v>56.93139837787107</v>
       </c>
       <c r="G5" t="n">
-        <v>785.423483666634</v>
+        <v>147.7918455693687</v>
       </c>
       <c r="H5" t="n">
-        <v>2299.796106970055</v>
+        <v>425.1376771181974</v>
       </c>
       <c r="I5" t="n">
-        <v>292.2250258307012</v>
+        <v>56.92995400023992</v>
       </c>
       <c r="J5" t="n">
-        <v>600.1531922318666</v>
+        <v>113.4882128210528</v>
       </c>
       <c r="K5" t="n">
-        <v>439.7082877846651</v>
+        <v>84.14343077900368</v>
       </c>
       <c r="L5" t="n">
-        <v>406.9946096745283</v>
+        <v>89.97971479185293</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>227.005908709139</v>
+        <v>46.32432696065352</v>
       </c>
       <c r="C6" t="n">
-        <v>146.417044693282</v>
+        <v>31.26893284225446</v>
       </c>
       <c r="D6" t="n">
-        <v>161.0197462733517</v>
+        <v>42.96126694890326</v>
       </c>
       <c r="E6" t="n">
-        <v>136.1165851781694</v>
+        <v>29.45605876144053</v>
       </c>
       <c r="F6" t="n">
-        <v>147.2906389262178</v>
+        <v>31.42269221044058</v>
       </c>
       <c r="G6" t="n">
-        <v>153.2040086572927</v>
+        <v>50.15977326631796</v>
       </c>
       <c r="H6" t="n">
-        <v>167.1562331001962</v>
+        <v>63.10156594348453</v>
       </c>
       <c r="I6" t="n">
-        <v>224.8253483262026</v>
+        <v>45.06761082372554</v>
       </c>
       <c r="J6" t="n">
-        <v>226.9689441518524</v>
+        <v>47.80778551486678</v>
       </c>
       <c r="K6" t="n">
-        <v>149.6222650651544</v>
+        <v>33.08829105701739</v>
       </c>
       <c r="L6" t="n">
-        <v>164.6143325182447</v>
+        <v>47.32078624349898</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.75347145348678</v>
+        <v>18.64789815362637</v>
       </c>
       <c r="C7" t="n">
-        <v>67.57434721514446</v>
+        <v>17.39261816129249</v>
       </c>
       <c r="D7" t="n">
-        <v>79.76570050698162</v>
+        <v>28.66055497151207</v>
       </c>
       <c r="E7" t="n">
-        <v>67.55841741408999</v>
+        <v>17.38982130034466</v>
       </c>
       <c r="F7" t="n">
-        <v>67.55841741408999</v>
+        <v>17.38982130034466</v>
       </c>
       <c r="G7" t="n">
-        <v>73.44335986507119</v>
+        <v>22.48334445929085</v>
       </c>
       <c r="H7" t="n">
-        <v>86.74652633720322</v>
+        <v>35.64095303734292</v>
       </c>
       <c r="I7" t="n">
-        <v>67.57291107055042</v>
+        <v>17.39118201669843</v>
       </c>
       <c r="J7" t="n">
-        <v>71.56168057306922</v>
+        <v>20.45610727320881</v>
       </c>
       <c r="K7" t="n">
-        <v>70.21886623924227</v>
+        <v>19.11329293938187</v>
       </c>
       <c r="L7" t="n">
-        <v>84.28912269023347</v>
+        <v>33.18354939037314</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>144.5307378932741</v>
+        <v>31.8086969757158</v>
       </c>
       <c r="C8" t="n">
-        <v>209.5803507754514</v>
+        <v>42.38567465247907</v>
       </c>
       <c r="D8" t="n">
-        <v>235.7142363658857</v>
+        <v>56.10749713395515</v>
       </c>
       <c r="E8" t="n">
-        <v>191.1935729067304</v>
+        <v>39.14960854914172</v>
       </c>
       <c r="F8" t="n">
-        <v>144.4735154625786</v>
+        <v>30.92687848352671</v>
       </c>
       <c r="G8" t="n">
-        <v>215.4507686194878</v>
+        <v>47.47664826463934</v>
       </c>
       <c r="H8" t="n">
-        <v>228.7539350916239</v>
+        <v>60.63425684269217</v>
       </c>
       <c r="I8" t="n">
-        <v>209.5803198249671</v>
+        <v>42.38448582204693</v>
       </c>
       <c r="J8" t="n">
-        <v>213.5823019814549</v>
+        <v>45.45173650564334</v>
       </c>
       <c r="K8" t="n">
-        <v>143.7472982691423</v>
+        <v>32.05429690652213</v>
       </c>
       <c r="L8" t="n">
-        <v>296.5240367896548</v>
+        <v>70.53689406946837</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134.9929824172206</v>
+        <v>30.13005202102627</v>
       </c>
       <c r="C9" t="n">
-        <v>159.4383053279379</v>
+        <v>33.56067470153586</v>
       </c>
       <c r="D9" t="n">
-        <v>171.6301745038415</v>
+        <v>44.82870230735061</v>
       </c>
       <c r="E9" t="n">
-        <v>190.1623173039343</v>
+        <v>38.96810756403309</v>
       </c>
       <c r="F9" t="n">
-        <v>159.438280919404</v>
+        <v>33.56067718965649</v>
       </c>
       <c r="G9" t="n">
-        <v>165.3073179778646</v>
+        <v>38.6514009995342</v>
       </c>
       <c r="H9" t="n">
-        <v>178.6104844499967</v>
+        <v>51.80900957758628</v>
       </c>
       <c r="I9" t="n">
-        <v>159.4368691833438</v>
+        <v>33.55923855694181</v>
       </c>
       <c r="J9" t="n">
-        <v>163.4256386858627</v>
+        <v>36.62416381345217</v>
       </c>
       <c r="K9" t="n">
-        <v>146.6565137457323</v>
+        <v>32.5663188276275</v>
       </c>
       <c r="L9" t="n">
-        <v>176.153080803027</v>
+        <v>49.35160593061653</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.1518337075751</v>
+        <v>21.15183370757511</v>
       </c>
       <c r="C2" t="n">
-        <v>15.74331854512387</v>
+        <v>15.74331854512383</v>
       </c>
       <c r="D2" t="n">
-        <v>36.68984759834063</v>
+        <v>36.68984759834039</v>
       </c>
       <c r="E2" t="n">
-        <v>18.00437206970173</v>
+        <v>18.00437206970175</v>
       </c>
       <c r="F2" t="n">
-        <v>11.61980454946767</v>
+        <v>11.61980454946758</v>
       </c>
       <c r="G2" t="n">
-        <v>27.46882568391502</v>
+        <v>27.46882568391494</v>
       </c>
       <c r="H2" t="n">
-        <v>45.55713009650955</v>
+        <v>45.5571300965095</v>
       </c>
       <c r="I2" t="n">
-        <v>20.30462202478754</v>
+        <v>20.30462202478756</v>
       </c>
       <c r="J2" t="n">
-        <v>28.75728844901694</v>
+        <v>28.75728844901692</v>
       </c>
       <c r="K2" t="n">
-        <v>29.50748524681165</v>
+        <v>29.50748524681164</v>
       </c>
       <c r="L2" t="n">
-        <v>43.63037615323972</v>
+        <v>43.63037615323968</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.82693156450277</v>
+        <v>23.8269315645028</v>
       </c>
       <c r="C3" t="n">
-        <v>18.28673093724518</v>
+        <v>18.286730937245</v>
       </c>
       <c r="D3" t="n">
-        <v>41.6988662287639</v>
+        <v>41.69886622876348</v>
       </c>
       <c r="E3" t="n">
-        <v>20.55183947270309</v>
+        <v>20.55183947270312</v>
       </c>
       <c r="F3" t="n">
-        <v>14.16727195246908</v>
+        <v>14.16727195246895</v>
       </c>
       <c r="G3" t="n">
-        <v>31.09278089823943</v>
+        <v>31.09278089823938</v>
       </c>
       <c r="H3" t="n">
-        <v>51.90361287996944</v>
+        <v>51.90361287996942</v>
       </c>
       <c r="I3" t="n">
-        <v>22.84324546407338</v>
+        <v>22.84324546407341</v>
       </c>
       <c r="J3" t="n">
-        <v>31.58682621935489</v>
+        <v>31.58682621935486</v>
       </c>
       <c r="K3" t="n">
-        <v>32.30622764835471</v>
+        <v>32.3062276483547</v>
       </c>
       <c r="L3" t="n">
-        <v>49.68132472071083</v>
+        <v>49.68132472071093</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.50688947977557</v>
+        <v>13.82184935716274</v>
       </c>
       <c r="C4" t="n">
-        <v>40.11891777531646</v>
+        <v>12.9853502045325</v>
       </c>
       <c r="D4" t="n">
-        <v>51.74358033633644</v>
+        <v>23.0585402137235</v>
       </c>
       <c r="E4" t="n">
-        <v>40.24754470384708</v>
+        <v>13.00799533578115</v>
       </c>
       <c r="F4" t="n">
-        <v>40.24754470384709</v>
+        <v>13.00799533578115</v>
       </c>
       <c r="G4" t="n">
-        <v>46.08773540947995</v>
+        <v>17.54634990332992</v>
       </c>
       <c r="H4" t="n">
-        <v>57.01109830535656</v>
+        <v>28.32605818274373</v>
       </c>
       <c r="I4" t="n">
-        <v>40.89409022833904</v>
+        <v>13.12072286052128</v>
       </c>
       <c r="J4" t="n">
-        <v>43.11809863146776</v>
+        <v>14.43305850885491</v>
       </c>
       <c r="K4" t="n">
-        <v>42.99622332850002</v>
+        <v>14.3111832058872</v>
       </c>
       <c r="L4" t="n">
-        <v>55.86689179903907</v>
+        <v>27.18185167642636</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>365.0153521737342</v>
+        <v>70.58333848373138</v>
       </c>
       <c r="C5" t="n">
-        <v>318.1006538774872</v>
+        <v>61.91013549340975</v>
       </c>
       <c r="D5" t="n">
-        <v>1184.340439039012</v>
+        <v>222.3955862652639</v>
       </c>
       <c r="E5" t="n">
-        <v>318.1006621201408</v>
+        <v>61.91014373606751</v>
       </c>
       <c r="F5" t="n">
-        <v>318.1006621201408</v>
+        <v>61.91014373606751</v>
       </c>
       <c r="G5" t="n">
-        <v>714.8357609962452</v>
+        <v>135.246001768833</v>
       </c>
       <c r="H5" t="n">
-        <v>1892.477053384931</v>
+        <v>351.368064526312</v>
       </c>
       <c r="I5" t="n">
-        <v>318.0993702670439</v>
+        <v>61.90885188296967</v>
       </c>
       <c r="J5" t="n">
-        <v>443.8847799411753</v>
+        <v>84.96799403716248</v>
       </c>
       <c r="K5" t="n">
-        <v>398.1829608288842</v>
+        <v>76.82404866722226</v>
       </c>
       <c r="L5" t="n">
-        <v>1847.151875570191</v>
+        <v>92.33954256526351</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>141.994123901022</v>
+        <v>44.01574148260421</v>
       </c>
       <c r="C6" t="n">
-        <v>139.6363269266719</v>
+        <v>30.50041412026385</v>
       </c>
       <c r="D6" t="n">
-        <v>152.4843442089275</v>
+        <v>40.78891455922489</v>
       </c>
       <c r="E6" t="n">
-        <v>130.0408235013959</v>
+        <v>28.81161231851624</v>
       </c>
       <c r="F6" t="n">
-        <v>140.3697793424388</v>
+        <v>30.62950853668937</v>
       </c>
       <c r="G6" t="n">
-        <v>145.5749698307263</v>
+        <v>47.74024202877133</v>
       </c>
       <c r="H6" t="n">
-        <v>227.3895932938017</v>
+        <v>58.31267313822445</v>
       </c>
       <c r="I6" t="n">
-        <v>140.3813246495856</v>
+        <v>43.31461498596271</v>
       </c>
       <c r="J6" t="n">
-        <v>147.9289990938177</v>
+        <v>44.32374175715402</v>
       </c>
       <c r="K6" t="n">
-        <v>142.155577416365</v>
+        <v>31.76322943078566</v>
       </c>
       <c r="L6" t="n">
-        <v>155.8462188593087</v>
+        <v>44.77821314368615</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.27630549142386</v>
+        <v>18.18126655159092</v>
       </c>
       <c r="C7" t="n">
-        <v>65.66478985042752</v>
+        <v>17.48142366538961</v>
       </c>
       <c r="D7" t="n">
-        <v>76.51251538959812</v>
+        <v>27.41787275947607</v>
       </c>
       <c r="E7" t="n">
-        <v>65.64793174185384</v>
+        <v>17.47846343024666</v>
       </c>
       <c r="F7" t="n">
-        <v>65.64793174185384</v>
+        <v>17.47846343024666</v>
       </c>
       <c r="G7" t="n">
-        <v>70.85715142112829</v>
+        <v>21.90576709775814</v>
       </c>
       <c r="H7" t="n">
-        <v>81.7805143170049</v>
+        <v>32.68547537717189</v>
       </c>
       <c r="I7" t="n">
-        <v>65.66350623998738</v>
+        <v>17.48014005494943</v>
       </c>
       <c r="J7" t="n">
-        <v>67.88751464311611</v>
+        <v>18.79247570328304</v>
       </c>
       <c r="K7" t="n">
-        <v>67.7656393401484</v>
+        <v>18.67060040031536</v>
       </c>
       <c r="L7" t="n">
-        <v>80.63630781068741</v>
+        <v>31.54126887085452</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>136.7496849350895</v>
+        <v>30.40858126742102</v>
       </c>
       <c r="C8" t="n">
-        <v>197.3626183540471</v>
+        <v>40.66024135645766</v>
       </c>
       <c r="D8" t="n">
-        <v>221.1174807733486</v>
+        <v>52.86834652911008</v>
       </c>
       <c r="E8" t="n">
-        <v>180.3441547891406</v>
+        <v>37.66499857718618</v>
       </c>
       <c r="F8" t="n">
-        <v>137.1009271142458</v>
+        <v>30.05419054764469</v>
       </c>
       <c r="G8" t="n">
-        <v>202.5583021035654</v>
+        <v>45.08516949226702</v>
       </c>
       <c r="H8" t="n">
-        <v>213.4816649994502</v>
+        <v>55.86487777168217</v>
       </c>
       <c r="I8" t="n">
-        <v>197.3646569224249</v>
+        <v>40.65954244945839</v>
       </c>
       <c r="J8" t="n">
-        <v>199.600894869942</v>
+        <v>41.97403049759265</v>
       </c>
       <c r="K8" t="n">
-        <v>136.0831059849037</v>
+        <v>30.69447446463963</v>
       </c>
       <c r="L8" t="n">
-        <v>277.3395689576474</v>
+        <v>66.16104264512853</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123.0461180407534</v>
+        <v>27.99675350708663</v>
       </c>
       <c r="C9" t="n">
-        <v>144.7296706435545</v>
+        <v>31.39684260957769</v>
       </c>
       <c r="D9" t="n">
-        <v>155.5778766969033</v>
+        <v>41.33337627415919</v>
       </c>
       <c r="E9" t="n">
-        <v>171.6116600804303</v>
+        <v>36.12807951678116</v>
       </c>
       <c r="F9" t="n">
-        <v>144.7296523083238</v>
+        <v>31.3968461745271</v>
       </c>
       <c r="G9" t="n">
-        <v>149.9220322142551</v>
+        <v>35.82118604194631</v>
       </c>
       <c r="H9" t="n">
-        <v>160.8453951101318</v>
+        <v>46.60089432135997</v>
       </c>
       <c r="I9" t="n">
-        <v>144.7283870331142</v>
+        <v>31.39555899913755</v>
       </c>
       <c r="J9" t="n">
-        <v>146.952395436243</v>
+        <v>32.70789464747118</v>
       </c>
       <c r="K9" t="n">
-        <v>117.4978711745008</v>
+        <v>27.42347315573302</v>
       </c>
       <c r="L9" t="n">
-        <v>159.701188603814</v>
+        <v>45.45668781504268</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.97345120584507</v>
+        <v>20.97345120584451</v>
       </c>
       <c r="C2" t="n">
-        <v>17.18631145425298</v>
+        <v>17.18631145425303</v>
       </c>
       <c r="D2" t="n">
-        <v>34.01477592236554</v>
+        <v>34.01477592236553</v>
       </c>
       <c r="E2" t="n">
-        <v>19.43778992791535</v>
+        <v>19.43778992791539</v>
       </c>
       <c r="F2" t="n">
-        <v>13.08039035965894</v>
+        <v>13.08039035965893</v>
       </c>
       <c r="G2" t="n">
-        <v>26.37413228691486</v>
+        <v>26.37413228691452</v>
       </c>
       <c r="H2" t="n">
-        <v>40.84476137017097</v>
+        <v>40.84476137017104</v>
       </c>
       <c r="I2" t="n">
-        <v>21.70579558849826</v>
+        <v>21.70579558849832</v>
       </c>
       <c r="J2" t="n">
-        <v>28.33710601045942</v>
+        <v>28.337106010459</v>
       </c>
       <c r="K2" t="n">
-        <v>28.74393878880567</v>
+        <v>28.7439387888055</v>
       </c>
       <c r="L2" t="n">
-        <v>41.05571741725953</v>
+        <v>41.05571741725986</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.61110204420081</v>
+        <v>23.61110204419986</v>
       </c>
       <c r="C3" t="n">
-        <v>19.92966790021167</v>
+        <v>19.92966790021173</v>
       </c>
       <c r="D3" t="n">
-        <v>38.61132697047542</v>
+        <v>38.61132697047549</v>
       </c>
       <c r="E3" t="n">
-        <v>22.18514119832912</v>
+        <v>22.18514119832916</v>
       </c>
       <c r="F3" t="n">
-        <v>15.82774163007262</v>
+        <v>15.82774163007261</v>
       </c>
       <c r="G3" t="n">
-        <v>29.82300403514569</v>
+        <v>29.82300403514601</v>
       </c>
       <c r="H3" t="n">
-        <v>46.47252476901649</v>
+        <v>46.47252476901652</v>
       </c>
       <c r="I3" t="n">
-        <v>24.44615512630346</v>
+        <v>24.44615512630363</v>
       </c>
       <c r="J3" t="n">
-        <v>31.09481553694899</v>
+        <v>31.09481553694869</v>
       </c>
       <c r="K3" t="n">
-        <v>31.41932513305444</v>
+        <v>31.41932513305408</v>
       </c>
       <c r="L3" t="n">
-        <v>46.70934209967253</v>
+        <v>46.70934209967233</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.55070759050354</v>
+        <v>13.75234611154259</v>
       </c>
       <c r="C4" t="n">
-        <v>41.23219350923879</v>
+        <v>13.87801957482439</v>
       </c>
       <c r="D4" t="n">
-        <v>50.30322252667092</v>
+        <v>21.50486104770969</v>
       </c>
       <c r="E4" t="n">
-        <v>41.35735587319429</v>
+        <v>13.90005484840225</v>
       </c>
       <c r="F4" t="n">
-        <v>41.35735587319431</v>
+        <v>13.90005484840225</v>
       </c>
       <c r="G4" t="n">
-        <v>45.59204353127226</v>
+        <v>16.9330535077744</v>
       </c>
       <c r="H4" t="n">
-        <v>54.36048587614667</v>
+        <v>25.56212439718553</v>
       </c>
       <c r="I4" t="n">
-        <v>41.9107196767529</v>
+        <v>13.99666326536986</v>
       </c>
       <c r="J4" t="n">
-        <v>43.02585010585157</v>
+        <v>14.22748862689038</v>
       </c>
       <c r="K4" t="n">
-        <v>42.70004907895972</v>
+        <v>13.90168759999829</v>
       </c>
       <c r="L4" t="n">
-        <v>54.48652127206812</v>
+        <v>25.68815979310677</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>352.6110312473066</v>
+        <v>68.32296277944114</v>
       </c>
       <c r="C5" t="n">
-        <v>388.3872607009482</v>
+        <v>74.97731106949297</v>
       </c>
       <c r="D5" t="n">
-        <v>1016.478377712652</v>
+        <v>191.5516874390259</v>
       </c>
       <c r="E5" t="n">
-        <v>388.3872688291535</v>
+        <v>74.9773191976974</v>
       </c>
       <c r="F5" t="n">
-        <v>388.3872688291535</v>
+        <v>74.9773191976974</v>
       </c>
       <c r="G5" t="n">
-        <v>646.4052270524891</v>
+        <v>122.6761732345235</v>
       </c>
       <c r="H5" t="n">
-        <v>1547.768018439758</v>
+        <v>288.4018487041573</v>
       </c>
       <c r="I5" t="n">
-        <v>388.3863178438012</v>
+        <v>74.97636821234485</v>
       </c>
       <c r="J5" t="n">
-        <v>423.1756272195846</v>
+        <v>81.13384903636739</v>
       </c>
       <c r="K5" t="n">
-        <v>352.7528687336338</v>
+        <v>68.47098356353179</v>
       </c>
       <c r="L5" t="n">
-        <v>1663.73249401698</v>
+        <v>308.9154494615178</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>142.0711444147631</v>
+        <v>31.26794289770204</v>
       </c>
       <c r="C6" t="n">
-        <v>140.9258432748105</v>
+        <v>31.42410183848964</v>
       </c>
       <c r="D6" t="n">
-        <v>220.1304657408381</v>
+        <v>51.3944556914432</v>
       </c>
       <c r="E6" t="n">
-        <v>131.3257599596246</v>
+        <v>29.73449388181348</v>
       </c>
       <c r="F6" t="n">
-        <v>141.4755515994606</v>
+        <v>31.52085720074501</v>
       </c>
       <c r="G6" t="n">
-        <v>145.1124803555313</v>
+        <v>34.44865029393387</v>
       </c>
       <c r="H6" t="n">
-        <v>224.4256233340882</v>
+        <v>55.49358842759651</v>
       </c>
       <c r="I6" t="n">
-        <v>213.185740717219</v>
+        <v>44.1410668051513</v>
       </c>
       <c r="J6" t="n">
-        <v>212.5651097422338</v>
+        <v>32.68006982636726</v>
       </c>
       <c r="K6" t="n">
-        <v>141.8771283036951</v>
+        <v>31.35685344896906</v>
       </c>
       <c r="L6" t="n">
-        <v>154.460932639332</v>
+        <v>43.2836560984023</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.05309424699161</v>
+        <v>18.06476613971701</v>
       </c>
       <c r="C7" t="n">
-        <v>66.41404919038698</v>
+        <v>18.3100261506913</v>
       </c>
       <c r="D7" t="n">
-        <v>74.8051253196754</v>
+        <v>25.81719591591164</v>
       </c>
       <c r="E7" t="n">
-        <v>66.39984748367426</v>
+        <v>18.30753334796432</v>
       </c>
       <c r="F7" t="n">
-        <v>66.39984748367426</v>
+        <v>18.30753334796432</v>
       </c>
       <c r="G7" t="n">
-        <v>70.09443018775936</v>
+        <v>21.24547353594873</v>
       </c>
       <c r="H7" t="n">
-        <v>78.86287253263382</v>
+        <v>29.87454442535995</v>
       </c>
       <c r="I7" t="n">
-        <v>66.41310633324004</v>
+        <v>18.30908329354431</v>
       </c>
       <c r="J7" t="n">
-        <v>67.52823676233868</v>
+        <v>18.5399086550648</v>
       </c>
       <c r="K7" t="n">
-        <v>67.20243573544637</v>
+        <v>18.21410762817274</v>
       </c>
       <c r="L7" t="n">
-        <v>78.98890792855519</v>
+        <v>30.00057982128145</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>136.2192470493055</v>
+        <v>30.23800896696231</v>
       </c>
       <c r="C8" t="n">
-        <v>197.3864694508134</v>
+        <v>41.36117199162117</v>
       </c>
       <c r="D8" t="n">
-        <v>218.5950001650118</v>
+        <v>51.12421375156208</v>
       </c>
       <c r="E8" t="n">
-        <v>180.4827852124247</v>
+        <v>38.38613027942652</v>
       </c>
       <c r="F8" t="n">
-        <v>137.5312124194139</v>
+        <v>30.82665350881842</v>
       </c>
       <c r="G8" t="n">
-        <v>201.0677106193533</v>
+        <v>44.29677076700335</v>
       </c>
       <c r="H8" t="n">
-        <v>209.8361529642402</v>
+        <v>52.92584165641679</v>
       </c>
       <c r="I8" t="n">
-        <v>197.3863867648334</v>
+        <v>41.36038052459892</v>
       </c>
       <c r="J8" t="n">
-        <v>198.5136640698477</v>
+        <v>41.59334373626887</v>
       </c>
       <c r="K8" t="n">
-        <v>135.2204894098447</v>
+        <v>30.18528500999962</v>
       </c>
       <c r="L8" t="n">
-        <v>274.5249014009722</v>
+        <v>64.41491448594884</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118.3447635963549</v>
+        <v>27.09209989628926</v>
       </c>
       <c r="C9" t="n">
-        <v>139.6642108528814</v>
+        <v>31.20205453343343</v>
       </c>
       <c r="D9" t="n">
-        <v>148.0557715558763</v>
+        <v>38.70930958362574</v>
       </c>
       <c r="E9" t="n">
-        <v>165.0038261345306</v>
+        <v>35.66183349647892</v>
       </c>
       <c r="F9" t="n">
-        <v>139.6641965629131</v>
+        <v>31.20205871604003</v>
       </c>
       <c r="G9" t="n">
-        <v>143.3445918502538</v>
+        <v>34.137501918691</v>
       </c>
       <c r="H9" t="n">
-        <v>152.1130341951283</v>
+        <v>42.76657280810218</v>
       </c>
       <c r="I9" t="n">
-        <v>139.6632679957347</v>
+        <v>31.20111167628653</v>
       </c>
       <c r="J9" t="n">
-        <v>140.7783984248333</v>
+        <v>31.43193703780698</v>
       </c>
       <c r="K9" t="n">
-        <v>127.7297610127853</v>
+        <v>28.86691681926097</v>
       </c>
       <c r="L9" t="n">
-        <v>152.2390695910498</v>
+        <v>42.89260820402352</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.60945248781434</v>
+        <v>18.60945248781436</v>
       </c>
       <c r="C2" t="n">
-        <v>13.03836108304211</v>
+        <v>13.03836108304212</v>
       </c>
       <c r="D2" t="n">
-        <v>22.03893389758824</v>
+        <v>22.03893389758827</v>
       </c>
       <c r="E2" t="n">
-        <v>15.27399899051238</v>
+        <v>15.27399899051237</v>
       </c>
       <c r="F2" t="n">
-        <v>8.965929679965782</v>
+        <v>8.965929679965754</v>
       </c>
       <c r="G2" t="n">
-        <v>19.81468763591866</v>
+        <v>19.81468763591862</v>
       </c>
       <c r="H2" t="n">
-        <v>26.9672656265794</v>
+        <v>26.96726562657941</v>
       </c>
       <c r="I2" t="n">
-        <v>17.61628571021207</v>
+        <v>17.61628571021205</v>
       </c>
       <c r="J2" t="n">
-        <v>28.47632786959203</v>
+        <v>28.47632786959197</v>
       </c>
       <c r="K2" t="n">
-        <v>26.78310580123571</v>
+        <v>26.78310580123568</v>
       </c>
       <c r="L2" t="n">
-        <v>23.55534242457435</v>
+        <v>23.55534242457436</v>
       </c>
     </row>
     <row r="3">
@@ -6099,16 +6099,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.88956782866556</v>
+        <v>20.88956782866554</v>
       </c>
       <c r="C3" t="n">
-        <v>15.16560049003215</v>
+        <v>15.16560049003214</v>
       </c>
       <c r="D3" t="n">
-        <v>24.83418186483938</v>
+        <v>24.83418186483934</v>
       </c>
       <c r="E3" t="n">
-        <v>17.40469913346122</v>
+        <v>17.4046991334612</v>
       </c>
       <c r="F3" t="n">
         <v>11.0966298229146</v>
@@ -6120,16 +6120,16 @@
         <v>30.5084326127215</v>
       </c>
       <c r="I3" t="n">
-        <v>19.74103088934183</v>
+        <v>19.7410308893418</v>
       </c>
       <c r="J3" t="n">
-        <v>31.26580347645017</v>
+        <v>31.26580347645012</v>
       </c>
       <c r="K3" t="n">
-        <v>29.16775503105006</v>
+        <v>29.16775503105001</v>
       </c>
       <c r="L3" t="n">
-        <v>26.57830014339611</v>
+        <v>26.57830014339612</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.87082897666436</v>
+        <v>12.15294601253686</v>
       </c>
       <c r="C4" t="n">
-        <v>37.61794870490499</v>
+        <v>11.26918206140335</v>
       </c>
       <c r="D4" t="n">
-        <v>41.9095103553205</v>
+        <v>14.19162739119301</v>
       </c>
       <c r="E4" t="n">
-        <v>37.7297929464816</v>
+        <v>11.28887318221209</v>
       </c>
       <c r="F4" t="n">
-        <v>37.7297929464816</v>
+        <v>11.28887318221209</v>
       </c>
       <c r="G4" t="n">
-        <v>40.42363405859582</v>
+        <v>12.84060375684459</v>
       </c>
       <c r="H4" t="n">
-        <v>44.83798282370363</v>
+        <v>17.1200998595761</v>
       </c>
       <c r="I4" t="n">
-        <v>38.24052628384183</v>
+        <v>11.37826019852935</v>
       </c>
       <c r="J4" t="n">
-        <v>41.88666574591154</v>
+        <v>14.16878278178401</v>
       </c>
       <c r="K4" t="n">
-        <v>40.2845307729514</v>
+        <v>12.56664780882383</v>
       </c>
       <c r="L4" t="n">
-        <v>42.81096064377584</v>
+        <v>15.09307767964831</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>269.3421350431003</v>
+        <v>52.53989566138869</v>
       </c>
       <c r="C5" t="n">
-        <v>218.478588906805</v>
+        <v>43.10065456445565</v>
       </c>
       <c r="D5" t="n">
-        <v>448.6682266744292</v>
+        <v>85.78116107544085</v>
       </c>
       <c r="E5" t="n">
-        <v>218.4785968368995</v>
+        <v>43.10066249455014</v>
       </c>
       <c r="F5" t="n">
-        <v>218.4785968368995</v>
+        <v>43.10066249455014</v>
       </c>
       <c r="G5" t="n">
-        <v>341.3780101498384</v>
+        <v>65.80857366189085</v>
       </c>
       <c r="H5" t="n">
-        <v>783.3000288387685</v>
+        <v>147.0894192539752</v>
       </c>
       <c r="I5" t="n">
-        <v>218.4779875522267</v>
+        <v>43.10005320987725</v>
       </c>
       <c r="J5" t="n">
-        <v>491.5931570516361</v>
+        <v>93.31712482271789</v>
       </c>
       <c r="K5" t="n">
-        <v>305.242410499403</v>
+        <v>59.19923438799581</v>
       </c>
       <c r="L5" t="n">
-        <v>205.3917376991953</v>
+        <v>117.6218489812871</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>145.7473660137689</v>
+        <v>30.78721643009549</v>
       </c>
       <c r="C6" t="n">
-        <v>143.6880236598462</v>
+        <v>29.93751515231664</v>
       </c>
       <c r="D6" t="n">
-        <v>148.059291883554</v>
+        <v>45.66995895315024</v>
       </c>
       <c r="E6" t="n">
-        <v>133.4267234400108</v>
+        <v>28.13153285780956</v>
       </c>
       <c r="F6" t="n">
-        <v>144.103169866864</v>
+        <v>30.01058741875382</v>
       </c>
       <c r="G6" t="n">
-        <v>220.9881240218847</v>
+        <v>31.47487417440332</v>
       </c>
       <c r="H6" t="n">
-        <v>223.8358419376677</v>
+        <v>48.62372289292819</v>
       </c>
       <c r="I6" t="n">
-        <v>218.8050162471309</v>
+        <v>30.01253061608807</v>
       </c>
       <c r="J6" t="n">
-        <v>220.5103728265013</v>
+        <v>45.60655505761891</v>
       </c>
       <c r="K6" t="n">
-        <v>146.1283461238009</v>
+        <v>31.19515920963278</v>
       </c>
       <c r="L6" t="n">
-        <v>148.8223855021973</v>
+        <v>33.75108835363018</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64.46314034876181</v>
+        <v>16.48119279057294</v>
       </c>
       <c r="C7" t="n">
-        <v>62.83343901051764</v>
+        <v>15.70710833114383</v>
       </c>
       <c r="D7" t="n">
-        <v>66.50132586360746</v>
+        <v>18.51978689719893</v>
       </c>
       <c r="E7" t="n">
-        <v>62.82011007045551</v>
+        <v>15.70476897210352</v>
       </c>
       <c r="F7" t="n">
-        <v>62.82011007045551</v>
+        <v>15.70476897210352</v>
       </c>
       <c r="G7" t="n">
-        <v>65.01594543069329</v>
+        <v>17.16885053488069</v>
       </c>
       <c r="H7" t="n">
-        <v>69.43029419580104</v>
+        <v>21.44834663761221</v>
       </c>
       <c r="I7" t="n">
-        <v>62.83283765593927</v>
+        <v>15.70650697656543</v>
       </c>
       <c r="J7" t="n">
-        <v>66.47897711800891</v>
+        <v>18.49702955982009</v>
       </c>
       <c r="K7" t="n">
-        <v>64.8768421450488</v>
+        <v>16.89489458685991</v>
       </c>
       <c r="L7" t="n">
-        <v>67.4032720158733</v>
+        <v>19.42132445768442</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>137.2261874185855</v>
+        <v>29.28748900546969</v>
       </c>
       <c r="C8" t="n">
-        <v>199.5671346238569</v>
+        <v>39.77223862866489</v>
       </c>
       <c r="D8" t="n">
-        <v>216.4997471590399</v>
+        <v>44.91950890214545</v>
       </c>
       <c r="E8" t="n">
-        <v>182.0717221004904</v>
+        <v>36.69305257566246</v>
       </c>
       <c r="F8" t="n">
-        <v>137.6165913547411</v>
+        <v>28.86894960680632</v>
       </c>
       <c r="G8" t="n">
-        <v>201.7492261809669</v>
+        <v>41.23390781652988</v>
       </c>
       <c r="H8" t="n">
-        <v>206.1635749460771</v>
+        <v>45.51340391926184</v>
       </c>
       <c r="I8" t="n">
-        <v>199.5661184062129</v>
+        <v>39.77156425821463</v>
       </c>
       <c r="J8" t="n">
-        <v>203.224829857529</v>
+        <v>42.56429951156466</v>
       </c>
       <c r="K8" t="n">
-        <v>136.4516092814277</v>
+        <v>29.4920535346036</v>
       </c>
       <c r="L8" t="n">
-        <v>270.9588109543221</v>
+        <v>55.24709911672579</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120.8878858515497</v>
+        <v>26.41194794525277</v>
       </c>
       <c r="C9" t="n">
-        <v>142.5830136641163</v>
+        <v>29.74303339412205</v>
       </c>
       <c r="D9" t="n">
-        <v>146.2513987565157</v>
+        <v>32.55579965029515</v>
       </c>
       <c r="E9" t="n">
-        <v>169.4993654646535</v>
+        <v>34.48031781974512</v>
       </c>
       <c r="F9" t="n">
-        <v>142.5830083536093</v>
+        <v>29.74303899387072</v>
       </c>
       <c r="G9" t="n">
-        <v>144.7655200842918</v>
+        <v>31.20477559785892</v>
       </c>
       <c r="H9" t="n">
-        <v>149.1798688493998</v>
+        <v>35.48427170059041</v>
       </c>
       <c r="I9" t="n">
-        <v>142.5824123095378</v>
+        <v>29.74243203954367</v>
       </c>
       <c r="J9" t="n">
-        <v>146.2285517716075</v>
+        <v>32.53295462279829</v>
       </c>
       <c r="K9" t="n">
-        <v>115.2562928148338</v>
+        <v>28.55226825857148</v>
       </c>
       <c r="L9" t="n">
-        <v>147.1528466694719</v>
+        <v>33.45724952066263</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.23775997764419</v>
+        <v>19.23775997764428</v>
       </c>
       <c r="C2" t="n">
         <v>13.69559675588555</v>
       </c>
       <c r="D2" t="n">
-        <v>17.76002094479035</v>
+        <v>17.76002094479049</v>
       </c>
       <c r="E2" t="n">
-        <v>15.91280645933028</v>
+        <v>15.91280645933021</v>
       </c>
       <c r="F2" t="n">
-        <v>9.658096944924146</v>
+        <v>9.658096944924125</v>
       </c>
       <c r="G2" t="n">
-        <v>18.26625211444247</v>
+        <v>18.26625211444253</v>
       </c>
       <c r="H2" t="n">
-        <v>17.12601163296267</v>
+        <v>17.12601163296266</v>
       </c>
       <c r="I2" t="n">
-        <v>18.27225255478113</v>
+        <v>18.27225255478122</v>
       </c>
       <c r="J2" t="n">
-        <v>26.77695221996324</v>
+        <v>26.77695221996327</v>
       </c>
       <c r="K2" t="n">
-        <v>26.1447480830667</v>
+        <v>26.14474808306662</v>
       </c>
       <c r="L2" t="n">
         <v>16.88795706047278</v>
@@ -6495,34 +6495,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.60006790485761</v>
+        <v>21.60006790485771</v>
       </c>
       <c r="C3" t="n">
         <v>15.90932127094101</v>
       </c>
       <c r="D3" t="n">
-        <v>19.90036190435722</v>
+        <v>19.90036190435733</v>
       </c>
       <c r="E3" t="n">
-        <v>18.12991675173505</v>
+        <v>18.12991675173516</v>
       </c>
       <c r="F3" t="n">
-        <v>11.87520723732892</v>
+        <v>11.87520723732896</v>
       </c>
       <c r="G3" t="n">
-        <v>20.48263261492804</v>
+        <v>20.48263261492821</v>
       </c>
       <c r="H3" t="n">
         <v>19.17670619935397</v>
       </c>
       <c r="I3" t="n">
-        <v>20.48496170247224</v>
+        <v>20.48496170247226</v>
       </c>
       <c r="J3" t="n">
-        <v>29.31241458192891</v>
+        <v>29.31241458192887</v>
       </c>
       <c r="K3" t="n">
-        <v>28.42517457526276</v>
+        <v>28.42517457526273</v>
       </c>
       <c r="L3" t="n">
         <v>18.89748487215716</v>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.90217588558697</v>
+        <v>12.47867820133447</v>
       </c>
       <c r="C4" t="n">
-        <v>37.83175038564339</v>
+        <v>11.64078010320962</v>
       </c>
       <c r="D4" t="n">
-        <v>39.02372264766978</v>
+        <v>11.60022496341735</v>
       </c>
       <c r="E4" t="n">
-        <v>37.92822674022344</v>
+        <v>11.65776634839708</v>
       </c>
       <c r="F4" t="n">
-        <v>37.92822674022344</v>
+        <v>11.65776634839709</v>
       </c>
       <c r="G4" t="n">
-        <v>39.16566782970355</v>
+        <v>11.87317609073457</v>
       </c>
       <c r="H4" t="n">
-        <v>38.64752941367659</v>
+        <v>11.22403172942412</v>
       </c>
       <c r="I4" t="n">
-        <v>38.31865868866303</v>
+        <v>11.72622894979129</v>
       </c>
       <c r="J4" t="n">
-        <v>40.58744935434058</v>
+        <v>13.16395167008799</v>
       </c>
       <c r="K4" t="n">
-        <v>39.57812311107302</v>
+        <v>12.15462542682059</v>
       </c>
       <c r="L4" t="n">
-        <v>38.50644200297921</v>
+        <v>11.08294431872669</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>291.8872042274558</v>
+        <v>56.82804294919173</v>
       </c>
       <c r="C5" t="n">
-        <v>242.9522393797118</v>
+        <v>47.74198597054756</v>
       </c>
       <c r="D5" t="n">
-        <v>218.7665783398018</v>
+        <v>43.23496739381636</v>
       </c>
       <c r="E5" t="n">
-        <v>242.9522471550438</v>
+        <v>47.74199374587931</v>
       </c>
       <c r="F5" t="n">
-        <v>242.9522471550437</v>
+        <v>47.74199374587931</v>
       </c>
       <c r="G5" t="n">
-        <v>244.3526123070487</v>
+        <v>47.98607812306544</v>
       </c>
       <c r="H5" t="n">
-        <v>205.7645902126967</v>
+        <v>40.6366342706764</v>
       </c>
       <c r="I5" t="n">
-        <v>242.9519396050943</v>
+        <v>47.74168619592965</v>
       </c>
       <c r="J5" t="n">
-        <v>364.9495716021651</v>
+        <v>70.25168487636924</v>
       </c>
       <c r="K5" t="n">
-        <v>259.3852698522605</v>
+        <v>50.84068304364515</v>
       </c>
       <c r="L5" t="n">
-        <v>153.6287637601471</v>
+        <v>31.34447283819898</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138.4928066886614</v>
+        <v>41.98409549664146</v>
       </c>
       <c r="C6" t="n">
-        <v>136.6877468179123</v>
+        <v>29.0394353810126</v>
       </c>
       <c r="D6" t="n">
-        <v>137.4942730714029</v>
+        <v>28.9310319534802</v>
       </c>
       <c r="E6" t="n">
-        <v>127.1320720791586</v>
+        <v>27.35764304297825</v>
       </c>
       <c r="F6" t="n">
-        <v>136.9126651626422</v>
+        <v>29.07902741634389</v>
       </c>
       <c r="G6" t="n">
-        <v>137.7562986327779</v>
+        <v>29.22512701805233</v>
       </c>
       <c r="H6" t="n">
-        <v>204.6667607610073</v>
+        <v>28.57424538711284</v>
       </c>
       <c r="I6" t="n">
-        <v>136.9092894917373</v>
+        <v>29.07817987710905</v>
       </c>
       <c r="J6" t="n">
-        <v>144.3780781553397</v>
+        <v>42.34537141378722</v>
       </c>
       <c r="K6" t="n">
-        <v>138.1557554147148</v>
+        <v>29.50428861825056</v>
       </c>
       <c r="L6" t="n">
-        <v>137.0850765426813</v>
+        <v>28.43278390370241</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.25451207085112</v>
+        <v>16.41268934862413</v>
       </c>
       <c r="C7" t="n">
-        <v>60.67129464854514</v>
+        <v>15.66053987169884</v>
       </c>
       <c r="D7" t="n">
-        <v>61.37559471659713</v>
+        <v>15.53415442623215</v>
       </c>
       <c r="E7" t="n">
-        <v>60.66178051720846</v>
+        <v>15.65887179146604</v>
       </c>
       <c r="F7" t="n">
-        <v>60.66178051720846</v>
+        <v>15.65887179146604</v>
       </c>
       <c r="G7" t="n">
-        <v>61.51800401496771</v>
+        <v>15.80718723802426</v>
       </c>
       <c r="H7" t="n">
-        <v>60.99986559894084</v>
+        <v>15.15804287671378</v>
       </c>
       <c r="I7" t="n">
-        <v>60.67099487392719</v>
+        <v>15.66024009708092</v>
       </c>
       <c r="J7" t="n">
-        <v>62.93978553960464</v>
+        <v>17.09796281737765</v>
       </c>
       <c r="K7" t="n">
-        <v>61.93045929633738</v>
+        <v>16.08863657411024</v>
       </c>
       <c r="L7" t="n">
-        <v>60.85877818824337</v>
+        <v>15.01695546601635</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>129.489980284744</v>
+        <v>28.24613169014849</v>
       </c>
       <c r="C8" t="n">
-        <v>186.6839293590745</v>
+        <v>37.83876346057698</v>
       </c>
       <c r="D8" t="n">
-        <v>199.5728957515129</v>
+        <v>39.85687927658207</v>
       </c>
       <c r="E8" t="n">
-        <v>170.6093263880943</v>
+        <v>35.00963975988774</v>
       </c>
       <c r="F8" t="n">
-        <v>129.7644174401678</v>
+        <v>27.82093582400549</v>
       </c>
       <c r="G8" t="n">
-        <v>187.5276353350338</v>
+        <v>37.98488223018369</v>
       </c>
       <c r="H8" t="n">
-        <v>187.0094969190048</v>
+        <v>37.33573786887288</v>
       </c>
       <c r="I8" t="n">
-        <v>186.6806261939932</v>
+        <v>37.83793508924034</v>
       </c>
       <c r="J8" t="n">
-        <v>188.9609676720775</v>
+        <v>39.27769075250968</v>
       </c>
       <c r="K8" t="n">
-        <v>128.0741672553681</v>
+        <v>27.72992911182009</v>
       </c>
       <c r="L8" t="n">
-        <v>248.2629374932274</v>
+        <v>48.00008732497093</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>109.5487719916407</v>
+        <v>24.73647904957978</v>
       </c>
       <c r="C9" t="n">
-        <v>128.0323686346187</v>
+        <v>27.51608882900723</v>
       </c>
       <c r="D9" t="n">
-        <v>128.7371399326758</v>
+        <v>27.38978632002099</v>
       </c>
       <c r="E9" t="n">
-        <v>151.1890557233276</v>
+        <v>31.59167214140941</v>
       </c>
       <c r="F9" t="n">
-        <v>128.0323723592294</v>
+        <v>27.5160958914121</v>
       </c>
       <c r="G9" t="n">
-        <v>128.8790780010413</v>
+        <v>27.66273619533264</v>
       </c>
       <c r="H9" t="n">
-        <v>128.3609395850145</v>
+        <v>27.01359183402219</v>
       </c>
       <c r="I9" t="n">
-        <v>128.0320688600009</v>
+        <v>27.51578905438933</v>
       </c>
       <c r="J9" t="n">
-        <v>130.3008595256783</v>
+        <v>28.95351177468606</v>
       </c>
       <c r="K9" t="n">
-        <v>117.1930316365332</v>
+        <v>25.81484925328221</v>
       </c>
       <c r="L9" t="n">
-        <v>128.2198521743171</v>
+        <v>26.87250442332476</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.13980371458857</v>
+        <v>19.13980371458858</v>
       </c>
       <c r="C2" t="n">
-        <v>13.57897627739343</v>
+        <v>13.57897627739346</v>
       </c>
       <c r="D2" t="n">
-        <v>17.30944175326366</v>
+        <v>17.30944175326369</v>
       </c>
       <c r="E2" t="n">
-        <v>15.79308616062233</v>
+        <v>15.79308616062234</v>
       </c>
       <c r="F2" t="n">
-        <v>9.548029469751429</v>
+        <v>9.548029469751459</v>
       </c>
       <c r="G2" t="n">
-        <v>17.97381225978612</v>
+        <v>17.97381225978615</v>
       </c>
       <c r="H2" t="n">
-        <v>17.01499747451165</v>
+        <v>17.01499747451169</v>
       </c>
       <c r="I2" t="n">
-        <v>18.16281656484163</v>
+        <v>18.16281656484165</v>
       </c>
       <c r="J2" t="n">
-        <v>26.42862790400013</v>
+        <v>26.42862790400017</v>
       </c>
       <c r="K2" t="n">
-        <v>25.44570684516099</v>
+        <v>25.44570684516101</v>
       </c>
       <c r="L2" t="n">
-        <v>17.05189517333408</v>
+        <v>17.0518951733341</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.48342777676497</v>
+        <v>21.48342777676498</v>
       </c>
       <c r="C3" t="n">
-        <v>15.77216535487709</v>
+        <v>15.77216535487712</v>
       </c>
       <c r="D3" t="n">
-        <v>19.37813236290329</v>
+        <v>19.37813236290332</v>
       </c>
       <c r="E3" t="n">
-        <v>17.98979273925844</v>
+        <v>17.98979273925848</v>
       </c>
       <c r="F3" t="n">
-        <v>11.74473604838755</v>
+        <v>11.74473604838757</v>
       </c>
       <c r="G3" t="n">
-        <v>20.14229606933989</v>
+        <v>20.14229606933996</v>
       </c>
       <c r="H3" t="n">
-        <v>19.0448842970934</v>
+        <v>19.04488429709343</v>
       </c>
       <c r="I3" t="n">
-        <v>20.35539073494416</v>
+        <v>20.3553907349442</v>
       </c>
       <c r="J3" t="n">
-        <v>28.91098729078941</v>
+        <v>28.91098729078945</v>
       </c>
       <c r="K3" t="n">
-        <v>27.62155279129518</v>
+        <v>27.62155279129521</v>
       </c>
       <c r="L3" t="n">
-        <v>19.08205032972949</v>
+        <v>19.0820503297295</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.79254769663983</v>
+        <v>12.41381012577272</v>
       </c>
       <c r="C4" t="n">
-        <v>37.71997975502139</v>
+        <v>11.56992643239265</v>
       </c>
       <c r="D4" t="n">
-        <v>38.70447506964759</v>
+        <v>11.32573749878052</v>
       </c>
       <c r="E4" t="n">
-        <v>37.81672565232114</v>
+        <v>11.58696012922478</v>
       </c>
       <c r="F4" t="n">
-        <v>37.81672565232114</v>
+        <v>11.58696012922478</v>
       </c>
       <c r="G4" t="n">
-        <v>38.94079497150153</v>
+        <v>11.69276045589169</v>
       </c>
       <c r="H4" t="n">
-        <v>38.53009600967658</v>
+        <v>11.15135843880942</v>
       </c>
       <c r="I4" t="n">
-        <v>38.20459490852929</v>
+        <v>11.65499236245237</v>
       </c>
       <c r="J4" t="n">
-        <v>40.34160459646536</v>
+        <v>12.96286702559824</v>
       </c>
       <c r="K4" t="n">
-        <v>39.12855146850018</v>
+        <v>11.74981389763299</v>
       </c>
       <c r="L4" t="n">
-        <v>38.5523821055544</v>
+        <v>11.1736445346873</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>286.6910917014685</v>
+        <v>55.86795363516168</v>
       </c>
       <c r="C5" t="n">
-        <v>238.4291203674062</v>
+        <v>46.89473498876019</v>
       </c>
       <c r="D5" t="n">
-        <v>195.943493838407</v>
+        <v>38.99980465212742</v>
       </c>
       <c r="E5" t="n">
-        <v>238.4291281574544</v>
+        <v>46.89474277880865</v>
       </c>
       <c r="F5" t="n">
-        <v>238.4291281574544</v>
+        <v>46.89474277880865</v>
       </c>
       <c r="G5" t="n">
-        <v>230.9171768405647</v>
+        <v>45.48060348176477</v>
       </c>
       <c r="H5" t="n">
-        <v>196.2655217007348</v>
+        <v>38.91279321000752</v>
       </c>
       <c r="I5" t="n">
-        <v>238.4288456871938</v>
+        <v>46.89446030854842</v>
       </c>
       <c r="J5" t="n">
-        <v>350.7195923156756</v>
+        <v>67.58939256817973</v>
       </c>
       <c r="K5" t="n">
-        <v>226.0742910201032</v>
+        <v>44.6522638804298</v>
       </c>
       <c r="L5" t="n">
-        <v>189.656028653182</v>
+        <v>39.3011006537725</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138.3407053079427</v>
+        <v>29.75828577137914</v>
       </c>
       <c r="C6" t="n">
-        <v>136.5346080836974</v>
+        <v>28.96130092400274</v>
       </c>
       <c r="D6" t="n">
-        <v>204.5792173958025</v>
+        <v>28.64313784678166</v>
       </c>
       <c r="E6" t="n">
-        <v>126.9827582782773</v>
+        <v>27.28018178635765</v>
       </c>
       <c r="F6" t="n">
-        <v>136.7466092315722</v>
+        <v>28.99861954482607</v>
       </c>
       <c r="G6" t="n">
-        <v>137.4889525828044</v>
+        <v>41.18987524485155</v>
       </c>
       <c r="H6" t="n">
-        <v>204.4478662620313</v>
+        <v>40.35288584499239</v>
       </c>
       <c r="I6" t="n">
-        <v>136.7527525198321</v>
+        <v>28.99946800805886</v>
       </c>
       <c r="J6" t="n">
-        <v>144.0713262377188</v>
+        <v>42.12609377219764</v>
       </c>
       <c r="K6" t="n">
-        <v>137.6055250811085</v>
+        <v>29.08176115953705</v>
       </c>
       <c r="L6" t="n">
-        <v>137.0829932474896</v>
+        <v>28.5150320017017</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.03805062745094</v>
+        <v>16.32901862038052</v>
       </c>
       <c r="C7" t="n">
-        <v>60.450372519553</v>
+        <v>15.57047553727288</v>
       </c>
       <c r="D7" t="n">
-        <v>60.94951699869458</v>
+        <v>15.2408648570783</v>
       </c>
       <c r="E7" t="n">
-        <v>60.44010656501887</v>
+        <v>15.5686751482843</v>
       </c>
       <c r="F7" t="n">
-        <v>60.44010656501887</v>
+        <v>15.5686751482843</v>
       </c>
       <c r="G7" t="n">
-        <v>61.18629790231269</v>
+        <v>15.60796895049946</v>
       </c>
       <c r="H7" t="n">
-        <v>60.77559894048775</v>
+        <v>15.06656693341731</v>
       </c>
       <c r="I7" t="n">
-        <v>60.45009783934032</v>
+        <v>15.57020085706016</v>
       </c>
       <c r="J7" t="n">
-        <v>62.58710752727644</v>
+        <v>16.87807552020602</v>
       </c>
       <c r="K7" t="n">
-        <v>61.37405439931096</v>
+        <v>15.66502239224075</v>
       </c>
       <c r="L7" t="n">
-        <v>60.79788503636554</v>
+        <v>15.08885302929502</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>129.1354107186027</v>
+        <v>28.13815393243419</v>
       </c>
       <c r="C8" t="n">
-        <v>186.1526708795475</v>
+        <v>37.69407992877809</v>
       </c>
       <c r="D8" t="n">
-        <v>198.8016787723729</v>
+        <v>39.50284519777955</v>
       </c>
       <c r="E8" t="n">
-        <v>170.1250446065575</v>
+        <v>34.87322413899135</v>
       </c>
       <c r="F8" t="n">
-        <v>129.3995014347196</v>
+        <v>27.7055285795868</v>
       </c>
       <c r="G8" t="n">
-        <v>186.8863489441771</v>
+        <v>37.73117781399081</v>
       </c>
       <c r="H8" t="n">
-        <v>186.4756499823501</v>
+        <v>37.18977579690811</v>
       </c>
       <c r="I8" t="n">
-        <v>186.1501488812051</v>
+        <v>37.69340972055149</v>
       </c>
       <c r="J8" t="n">
-        <v>188.298675682461</v>
+        <v>39.0033113956306</v>
       </c>
       <c r="K8" t="n">
-        <v>127.382839418907</v>
+        <v>27.28256849273877</v>
       </c>
       <c r="L8" t="n">
-        <v>247.7133470586105</v>
+        <v>47.98597416695377</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106.0905915811013</v>
+        <v>24.08226578621139</v>
       </c>
       <c r="C9" t="n">
-        <v>123.6367748398045</v>
+        <v>26.69128228537793</v>
       </c>
       <c r="D9" t="n">
-        <v>124.136386932253</v>
+        <v>26.36175390512495</v>
       </c>
       <c r="E9" t="n">
-        <v>145.7168539811004</v>
+        <v>30.57738261218839</v>
       </c>
       <c r="F9" t="n">
-        <v>123.6367786785464</v>
+        <v>26.6912893799961</v>
       </c>
       <c r="G9" t="n">
-        <v>124.372700222564</v>
+        <v>26.72877569860457</v>
       </c>
       <c r="H9" t="n">
-        <v>123.9620012607389</v>
+        <v>26.1873736815222</v>
       </c>
       <c r="I9" t="n">
-        <v>123.636500159592</v>
+        <v>26.69100760516513</v>
       </c>
       <c r="J9" t="n">
-        <v>125.7735098475277</v>
+        <v>27.99888226831105</v>
       </c>
       <c r="K9" t="n">
-        <v>113.4742250800795</v>
+        <v>24.75549062938159</v>
       </c>
       <c r="L9" t="n">
-        <v>123.9842873566168</v>
+        <v>26.20965977740004</v>
       </c>
     </row>
   </sheetData>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.94187505569491</v>
+        <v>19.94187505569492</v>
       </c>
       <c r="C2" t="n">
-        <v>14.18717817301125</v>
+        <v>14.18717817301126</v>
       </c>
       <c r="D2" t="n">
         <v>36.97566783440629</v>
@@ -7259,25 +7259,25 @@
         <v>16.44456377070398</v>
       </c>
       <c r="F2" t="n">
-        <v>10.07283267840316</v>
+        <v>10.07283267840315</v>
       </c>
       <c r="G2" t="n">
-        <v>26.04807478661642</v>
+        <v>26.04807478661643</v>
       </c>
       <c r="H2" t="n">
-        <v>48.77191246942948</v>
+        <v>48.77191246942945</v>
       </c>
       <c r="I2" t="n">
         <v>18.78700684096369</v>
       </c>
       <c r="J2" t="n">
-        <v>29.61898911893883</v>
+        <v>29.61898911893885</v>
       </c>
       <c r="K2" t="n">
-        <v>29.00601156682438</v>
+        <v>29.00601156682437</v>
       </c>
       <c r="L2" t="n">
-        <v>41.65118031396644</v>
+        <v>41.65118031396645</v>
       </c>
     </row>
     <row r="3">
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.43305075518467</v>
+        <v>22.43305075518466</v>
       </c>
       <c r="C3" t="n">
-        <v>16.50056029353123</v>
+        <v>16.50056029353124</v>
       </c>
       <c r="D3" t="n">
         <v>42.02544099024673</v>
@@ -7302,22 +7302,22 @@
         <v>12.39015967805515</v>
       </c>
       <c r="G3" t="n">
-        <v>29.45644534120802</v>
+        <v>29.45644534120801</v>
       </c>
       <c r="H3" t="n">
-        <v>55.59908976121451</v>
+        <v>55.59908976121446</v>
       </c>
       <c r="I3" t="n">
         <v>21.0952856601185</v>
       </c>
       <c r="J3" t="n">
-        <v>32.58146624554267</v>
+        <v>32.58146624554269</v>
       </c>
       <c r="K3" t="n">
-        <v>31.73097139087668</v>
+        <v>31.73097139087666</v>
       </c>
       <c r="L3" t="n">
-        <v>47.40266034003581</v>
+        <v>47.4026603400358</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.59603465895155</v>
+        <v>13.07624922064204</v>
       </c>
       <c r="C4" t="n">
-        <v>38.97037579188722</v>
+        <v>12.04719712968334</v>
       </c>
       <c r="D4" t="n">
-        <v>51.7219026828683</v>
+        <v>23.20211724455879</v>
       </c>
       <c r="E4" t="n">
-        <v>39.10316891711524</v>
+        <v>12.07057548011427</v>
       </c>
       <c r="F4" t="n">
-        <v>39.10316891711525</v>
+        <v>12.07057548011426</v>
       </c>
       <c r="G4" t="n">
-        <v>45.05128902364629</v>
+        <v>16.67539263567792</v>
       </c>
       <c r="H4" t="n">
-        <v>58.72948625397641</v>
+        <v>30.20970081566691</v>
       </c>
       <c r="I4" t="n">
-        <v>39.79838255514096</v>
+        <v>12.19185849436899</v>
       </c>
       <c r="J4" t="n">
-        <v>43.46125032177321</v>
+        <v>14.94146488346367</v>
       </c>
       <c r="K4" t="n">
-        <v>42.52125530494695</v>
+        <v>14.00146986663746</v>
       </c>
       <c r="L4" t="n">
-        <v>54.49883036944433</v>
+        <v>25.97904493113484</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>323.5501524369445</v>
+        <v>62.70017368067639</v>
       </c>
       <c r="C5" t="n">
-        <v>262.9464860840438</v>
+        <v>51.46699232750258</v>
       </c>
       <c r="D5" t="n">
-        <v>1258.511722697782</v>
+        <v>235.5971244162991</v>
       </c>
       <c r="E5" t="n">
-        <v>262.9464942885553</v>
+        <v>51.46700053201405</v>
       </c>
       <c r="F5" t="n">
-        <v>262.9464942885552</v>
+        <v>51.46700053201405</v>
       </c>
       <c r="G5" t="n">
-        <v>680.0083843800237</v>
+        <v>128.4278408128582</v>
       </c>
       <c r="H5" t="n">
-        <v>2073.67357398797</v>
+        <v>384.8398583352495</v>
       </c>
       <c r="I5" t="n">
-        <v>262.945190180092</v>
+        <v>51.46569642355101</v>
       </c>
       <c r="J5" t="n">
-        <v>534.9586060922497</v>
+        <v>101.4449990303393</v>
       </c>
       <c r="K5" t="n">
-        <v>412.2435084485711</v>
+        <v>79.07258606732078</v>
       </c>
       <c r="L5" t="n">
-        <v>1837.943458420868</v>
+        <v>339.8652977673603</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>148.1496587526753</v>
+        <v>31.82968695951997</v>
       </c>
       <c r="C6" t="n">
-        <v>145.5071410045902</v>
+        <v>30.79766770551767</v>
       </c>
       <c r="D6" t="n">
-        <v>159.7769488326597</v>
+        <v>42.21980526387308</v>
       </c>
       <c r="E6" t="n">
-        <v>135.2197448145158</v>
+        <v>28.98709274639289</v>
       </c>
       <c r="F6" t="n">
-        <v>146.3053167739473</v>
+        <v>30.93815340068077</v>
       </c>
       <c r="G6" t="n">
-        <v>228.4315103391156</v>
+        <v>48.95031141231549</v>
       </c>
       <c r="H6" t="n">
-        <v>240.9151350568</v>
+        <v>62.27437483121808</v>
       </c>
       <c r="I6" t="n">
-        <v>146.3520066488649</v>
+        <v>44.46677727100664</v>
       </c>
       <c r="J6" t="n">
-        <v>225.0173234124584</v>
+        <v>46.89533357427887</v>
       </c>
       <c r="K6" t="n">
-        <v>148.796952753916</v>
+        <v>32.70599251630361</v>
       </c>
       <c r="L6" t="n">
-        <v>161.5371300456047</v>
+        <v>44.81778557205939</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.76012229342699</v>
+        <v>17.68112861935769</v>
       </c>
       <c r="C7" t="n">
-        <v>65.96376609356804</v>
+        <v>16.79803379703625</v>
       </c>
       <c r="D7" t="n">
-        <v>77.88548208601539</v>
+        <v>27.80690719456111</v>
       </c>
       <c r="E7" t="n">
-        <v>65.94742355981826</v>
+        <v>16.79516427162933</v>
       </c>
       <c r="F7" t="n">
-        <v>65.94742355981828</v>
+        <v>16.79516427162933</v>
       </c>
       <c r="G7" t="n">
-        <v>71.21537665812174</v>
+        <v>21.28027203439357</v>
       </c>
       <c r="H7" t="n">
-        <v>84.89357388845183</v>
+        <v>34.81458021438254</v>
       </c>
       <c r="I7" t="n">
-        <v>65.96247018961637</v>
+        <v>16.79673789308466</v>
       </c>
       <c r="J7" t="n">
-        <v>69.62533795624861</v>
+        <v>19.54634428217933</v>
       </c>
       <c r="K7" t="n">
-        <v>68.68534293942241</v>
+        <v>18.60634926535314</v>
       </c>
       <c r="L7" t="n">
-        <v>80.66291800391971</v>
+        <v>30.5839243298505</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.8919702150373</v>
+        <v>30.72833378286348</v>
       </c>
       <c r="C8" t="n">
-        <v>206.2501262782623</v>
+        <v>41.4884330557844</v>
       </c>
       <c r="D8" t="n">
-        <v>231.8923630288266</v>
+        <v>54.91211809362348</v>
       </c>
       <c r="E8" t="n">
-        <v>188.1570376794028</v>
+        <v>38.30405624012803</v>
       </c>
       <c r="F8" t="n">
-        <v>142.1832314333438</v>
+        <v>30.21266638466565</v>
       </c>
       <c r="G8" t="n">
-        <v>211.5037606461215</v>
+        <v>45.9710274824921</v>
       </c>
       <c r="H8" t="n">
-        <v>225.1819578764579</v>
+        <v>59.50533566248217</v>
       </c>
       <c r="I8" t="n">
-        <v>206.2508541776161</v>
+        <v>41.4874933411832</v>
       </c>
       <c r="J8" t="n">
-        <v>209.9267236039381</v>
+        <v>44.23938802237083</v>
       </c>
       <c r="K8" t="n">
-        <v>141.5882992383842</v>
+        <v>31.43726950444471</v>
       </c>
       <c r="L8" t="n">
-        <v>290.0573358372515</v>
+        <v>67.43734166882282</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131.2075808008452</v>
+        <v>28.84788125615507</v>
       </c>
       <c r="C9" t="n">
-        <v>155.2512755007094</v>
+        <v>32.51263536754193</v>
       </c>
       <c r="D9" t="n">
-        <v>167.1734943509669</v>
+        <v>43.52159726804094</v>
       </c>
       <c r="E9" t="n">
-        <v>185.0701099173202</v>
+        <v>37.76075695694544</v>
       </c>
       <c r="F9" t="n">
-        <v>155.251251888358</v>
+        <v>32.51263797228558</v>
       </c>
       <c r="G9" t="n">
-        <v>160.5028860652631</v>
+        <v>36.9948736048993</v>
       </c>
       <c r="H9" t="n">
-        <v>174.1810832955932</v>
+        <v>50.52918178488825</v>
       </c>
       <c r="I9" t="n">
-        <v>155.2499795967578</v>
+        <v>32.51133946359036</v>
       </c>
       <c r="J9" t="n">
-        <v>158.9128473633899</v>
+        <v>35.26094585268504</v>
       </c>
       <c r="K9" t="n">
-        <v>142.3935973072461</v>
+        <v>31.68590890511473</v>
       </c>
       <c r="L9" t="n">
-        <v>169.9504274110611</v>
+        <v>46.29852590035618</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.07727612533935</v>
+        <v>19.07727612533933</v>
       </c>
       <c r="C2" t="n">
-        <v>13.48435282036737</v>
+        <v>13.48435282036736</v>
       </c>
       <c r="D2" t="n">
-        <v>32.42413449545591</v>
+        <v>32.42413449545596</v>
       </c>
       <c r="E2" t="n">
         <v>15.72256861722847</v>
       </c>
       <c r="F2" t="n">
-        <v>9.407034829624649</v>
+        <v>9.407034829624651</v>
       </c>
       <c r="G2" t="n">
-        <v>22.03293286898388</v>
+        <v>22.03293286898389</v>
       </c>
       <c r="H2" t="n">
-        <v>20.3518362643007</v>
+        <v>20.35183626430069</v>
       </c>
       <c r="I2" t="n">
-        <v>18.08193382409074</v>
+        <v>18.08193382409073</v>
       </c>
       <c r="J2" t="n">
         <v>27.57136865193543</v>
       </c>
       <c r="K2" t="n">
-        <v>25.52239157847289</v>
+        <v>25.5223915784729</v>
       </c>
       <c r="L2" t="n">
-        <v>31.4307027876286</v>
+        <v>31.43070278762858</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.42384615498672</v>
+        <v>21.42384615498671</v>
       </c>
       <c r="C3" t="n">
         <v>15.67742332229235</v>
       </c>
       <c r="D3" t="n">
-        <v>36.7754980740029</v>
+        <v>36.77549807400296</v>
       </c>
       <c r="E3" t="n">
-        <v>17.91934391794684</v>
+        <v>17.91934391794683</v>
       </c>
       <c r="F3" t="n">
-        <v>11.60381013034302</v>
+        <v>11.60381013034301</v>
       </c>
       <c r="G3" t="n">
-        <v>24.82346367262789</v>
+        <v>24.82346367262792</v>
       </c>
       <c r="H3" t="n">
-        <v>22.89558153999035</v>
+        <v>22.89558153999033</v>
       </c>
       <c r="I3" t="n">
-        <v>20.27214399187944</v>
+        <v>20.27214399187945</v>
       </c>
       <c r="J3" t="n">
-        <v>30.22364666171153</v>
+        <v>30.22364666171155</v>
       </c>
       <c r="K3" t="n">
         <v>27.72490639765674</v>
       </c>
       <c r="L3" t="n">
-        <v>35.63252865330031</v>
+        <v>35.63252865330028</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.22656900490308</v>
+        <v>12.43329499121022</v>
       </c>
       <c r="C4" t="n">
-        <v>37.92248666401519</v>
+        <v>11.53928174599518</v>
       </c>
       <c r="D4" t="n">
-        <v>48.16071075157355</v>
+        <v>20.36743673788076</v>
       </c>
       <c r="E4" t="n">
-        <v>38.03385682946217</v>
+        <v>11.55888948956252</v>
       </c>
       <c r="F4" t="n">
-        <v>38.03385682946218</v>
+        <v>11.55888948956252</v>
       </c>
       <c r="G4" t="n">
-        <v>41.81621994754241</v>
+        <v>14.16085201572669</v>
       </c>
       <c r="H4" t="n">
-        <v>40.98508355592004</v>
+        <v>13.19180954222725</v>
       </c>
       <c r="I4" t="n">
-        <v>38.57091894540662</v>
+        <v>11.65271215721782</v>
       </c>
       <c r="J4" t="n">
-        <v>41.43643445402164</v>
+        <v>13.64316044032882</v>
       </c>
       <c r="K4" t="n">
-        <v>39.65645820232611</v>
+        <v>11.86318418863332</v>
       </c>
       <c r="L4" t="n">
-        <v>47.56895796141761</v>
+        <v>19.77568394772473</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>272.4276983146984</v>
+        <v>53.30069352828995</v>
       </c>
       <c r="C5" t="n">
-        <v>223.7383422997404</v>
+        <v>44.24287216067499</v>
       </c>
       <c r="D5" t="n">
-        <v>923.9427225892196</v>
+        <v>174.505069986096</v>
       </c>
       <c r="E5" t="n">
-        <v>223.7383503028407</v>
+        <v>44.24288016377557</v>
       </c>
       <c r="F5" t="n">
-        <v>223.7383503028407</v>
+        <v>44.24288016377557</v>
       </c>
       <c r="G5" t="n">
-        <v>428.6997020777139</v>
+        <v>82.25234450167616</v>
       </c>
       <c r="H5" t="n">
-        <v>367.3636147885346</v>
+        <v>70.63443072790838</v>
       </c>
       <c r="I5" t="n">
-        <v>223.7375004676007</v>
+        <v>44.24203032853536</v>
       </c>
       <c r="J5" t="n">
-        <v>402.8392810739334</v>
+        <v>77.2500611007727</v>
       </c>
       <c r="K5" t="n">
-        <v>221.1732401634937</v>
+        <v>43.81013764069088</v>
       </c>
       <c r="L5" t="n">
-        <v>1066.569420677853</v>
+        <v>46.19978984683348</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>139.0597975489285</v>
+        <v>42.20559325478584</v>
       </c>
       <c r="C6" t="n">
-        <v>136.8898193050595</v>
+        <v>28.95753219643643</v>
       </c>
       <c r="D6" t="n">
-        <v>148.2197964414891</v>
+        <v>37.97783572388146</v>
       </c>
       <c r="E6" t="n">
-        <v>127.3246216160077</v>
+        <v>27.27406400684028</v>
       </c>
       <c r="F6" t="n">
-        <v>137.3841456348694</v>
+        <v>29.04454022456638</v>
       </c>
       <c r="G6" t="n">
-        <v>210.9770064526556</v>
+        <v>31.55550014522043</v>
       </c>
       <c r="H6" t="n">
-        <v>208.6242189458888</v>
+        <v>42.69629721098856</v>
       </c>
       <c r="I6" t="n">
-        <v>207.7317054505199</v>
+        <v>41.42501042079346</v>
       </c>
       <c r="J6" t="n">
-        <v>208.8376778372467</v>
+        <v>31.96256200096351</v>
       </c>
       <c r="K6" t="n">
-        <v>138.1830980127011</v>
+        <v>29.20387270129699</v>
       </c>
       <c r="L6" t="n">
-        <v>146.673566998592</v>
+        <v>37.21809504375395</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63.51243710492236</v>
+        <v>16.53160775460651</v>
       </c>
       <c r="C7" t="n">
-        <v>61.85762887756555</v>
+        <v>15.75186675275375</v>
       </c>
       <c r="D7" t="n">
-        <v>71.44611332266109</v>
+        <v>24.46566756818551</v>
       </c>
       <c r="E7" t="n">
-        <v>61.84340477965178</v>
+        <v>15.74936990608938</v>
       </c>
       <c r="F7" t="n">
-        <v>61.84340477965179</v>
+        <v>15.74936990608938</v>
       </c>
       <c r="G7" t="n">
-        <v>65.10208804756179</v>
+        <v>18.25916477912295</v>
       </c>
       <c r="H7" t="n">
-        <v>64.27095165593937</v>
+        <v>17.29012230562352</v>
       </c>
       <c r="I7" t="n">
-        <v>61.85678704542592</v>
+        <v>15.7510249206141</v>
       </c>
       <c r="J7" t="n">
-        <v>64.72230255404101</v>
+        <v>17.74147320372509</v>
       </c>
       <c r="K7" t="n">
-        <v>62.94232630234555</v>
+        <v>15.96149695202959</v>
       </c>
       <c r="L7" t="n">
-        <v>70.85482606143692</v>
+        <v>23.87399671112101</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>131.7027290603413</v>
+        <v>28.5330990737289</v>
       </c>
       <c r="C8" t="n">
-        <v>190.2214216294641</v>
+        <v>38.34389415469673</v>
       </c>
       <c r="D8" t="n">
-        <v>212.289216985628</v>
+        <v>49.25405367854923</v>
       </c>
       <c r="E8" t="n">
-        <v>173.7642268148946</v>
+        <v>35.44743447755607</v>
       </c>
       <c r="F8" t="n">
-        <v>131.9471622699182</v>
+        <v>28.08763115752007</v>
       </c>
       <c r="G8" t="n">
-        <v>193.4671049595954</v>
+        <v>40.85140763322241</v>
       </c>
       <c r="H8" t="n">
-        <v>192.6359685679724</v>
+        <v>39.88236515972292</v>
       </c>
       <c r="I8" t="n">
-        <v>190.2218039574593</v>
+        <v>38.34326777471355</v>
       </c>
       <c r="J8" t="n">
-        <v>193.0991455285882</v>
+        <v>40.33579744481567</v>
       </c>
       <c r="K8" t="n">
-        <v>130.014841847526</v>
+        <v>27.76625962401604</v>
       </c>
       <c r="L8" t="n">
-        <v>262.0773749238543</v>
+        <v>57.5291651285424</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114.2415915090106</v>
+        <v>25.45993888134693</v>
       </c>
       <c r="C9" t="n">
-        <v>133.9490693027814</v>
+        <v>28.43996019883993</v>
       </c>
       <c r="D9" t="n">
-        <v>143.538030116439</v>
+        <v>37.15384485513817</v>
       </c>
       <c r="E9" t="n">
-        <v>158.6007032888334</v>
+        <v>32.77865435143035</v>
       </c>
       <c r="F9" t="n">
-        <v>133.9490701613862</v>
+        <v>28.43996694450926</v>
       </c>
       <c r="G9" t="n">
-        <v>137.1935284727776</v>
+        <v>30.94725822520913</v>
       </c>
       <c r="H9" t="n">
-        <v>136.3623920811551</v>
+        <v>29.97821575170973</v>
       </c>
       <c r="I9" t="n">
-        <v>133.9482274706417</v>
+        <v>28.43911836670032</v>
       </c>
       <c r="J9" t="n">
-        <v>136.8137429792569</v>
+        <v>30.42956664981131</v>
       </c>
       <c r="K9" t="n">
-        <v>122.6563788698635</v>
+        <v>23.91537802840699</v>
       </c>
       <c r="L9" t="n">
-        <v>142.9462664866527</v>
+        <v>36.56209015720722</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.29143996540591</v>
+        <v>21.33991348475567</v>
       </c>
       <c r="C2" t="n">
-        <v>16.17579206403444</v>
+        <v>17.41919829146524</v>
       </c>
       <c r="D2" t="n">
-        <v>38.80103637525619</v>
+        <v>22.26140876694653</v>
       </c>
       <c r="E2" t="n">
-        <v>18.45789882856366</v>
+        <v>19.33046084864236</v>
       </c>
       <c r="F2" t="n">
-        <v>12.01150050606007</v>
+        <v>13.96735192430232</v>
       </c>
       <c r="G2" t="n">
-        <v>27.87386109729492</v>
+        <v>21.68633323518562</v>
       </c>
       <c r="H2" t="n">
-        <v>52.26061188267933</v>
+        <v>22.8421648861414</v>
       </c>
       <c r="I2" t="n">
-        <v>20.67334297961293</v>
+        <v>21.30725334942071</v>
       </c>
       <c r="J2" t="n">
-        <v>32.20919887894134</v>
+        <v>27.17077269095305</v>
       </c>
       <c r="K2" t="n">
-        <v>30.68193860806652</v>
+        <v>27.77094870012874</v>
       </c>
       <c r="L2" t="n">
-        <v>46.57055747694821</v>
+        <v>22.67956394717066</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.00047437121385</v>
+        <v>21.86941746753847</v>
       </c>
       <c r="C3" t="n">
-        <v>18.78775569419621</v>
+        <v>15.31917975180637</v>
       </c>
       <c r="D3" t="n">
-        <v>44.14013734451088</v>
+        <v>28.43153281167445</v>
       </c>
       <c r="E3" t="n">
-        <v>21.07371698946796</v>
+        <v>18.46344189863041</v>
       </c>
       <c r="F3" t="n">
-        <v>14.62731866696431</v>
+        <v>9.608907407295769</v>
       </c>
       <c r="G3" t="n">
-        <v>31.57162221731574</v>
+        <v>24.34283331561892</v>
       </c>
       <c r="H3" t="n">
-        <v>59.62777470433645</v>
+        <v>33.43013135612891</v>
       </c>
       <c r="I3" t="n">
-        <v>23.28011104934949</v>
+        <v>21.63879096026018</v>
       </c>
       <c r="J3" t="n">
-        <v>35.54560423089646</v>
+        <v>32.708048861794</v>
       </c>
       <c r="K3" t="n">
-        <v>33.65783883892499</v>
+        <v>32.99818610143582</v>
       </c>
       <c r="L3" t="n">
-        <v>53.07598446174642</v>
+        <v>31.44465313567576</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.04976533365169</v>
+        <v>14.04976533365194</v>
       </c>
       <c r="C4" t="n">
-        <v>13.33304862022393</v>
+        <v>13.33304862022392</v>
       </c>
       <c r="D4" t="n">
-        <v>24.45847845477068</v>
+        <v>24.45847845477072</v>
       </c>
       <c r="E4" t="n">
         <v>13.35841075584037</v>
       </c>
       <c r="F4" t="n">
-        <v>13.35841075584038</v>
+        <v>13.35841075584037</v>
       </c>
       <c r="G4" t="n">
-        <v>17.93202097655913</v>
+        <v>17.93202097655923</v>
       </c>
       <c r="H4" t="n">
-        <v>32.45446690165758</v>
+        <v>32.45446690165753</v>
       </c>
       <c r="I4" t="n">
-        <v>13.48462719554327</v>
+        <v>13.48462719554326</v>
       </c>
       <c r="J4" t="n">
-        <v>16.53263945164335</v>
+        <v>16.53263945164343</v>
       </c>
       <c r="K4" t="n">
         <v>15.10590963562127</v>
       </c>
       <c r="L4" t="n">
-        <v>29.07402429668762</v>
+        <v>29.07402429668755</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.59701105872118</v>
+        <v>79.59701105872392</v>
       </c>
       <c r="C5" t="n">
-        <v>73.441339285569</v>
+        <v>73.44133928556903</v>
       </c>
       <c r="D5" t="n">
-        <v>280.5033847264604</v>
+        <v>280.5033847264611</v>
       </c>
       <c r="E5" t="n">
-        <v>73.44134743514331</v>
+        <v>73.4413474351433</v>
       </c>
       <c r="F5" t="n">
-        <v>73.44134743514331</v>
+        <v>73.4413474351433</v>
       </c>
       <c r="G5" t="n">
-        <v>158.9599411771654</v>
+        <v>158.9599411771653</v>
       </c>
       <c r="H5" t="n">
-        <v>485.1872853426917</v>
+        <v>485.1872853426911</v>
       </c>
       <c r="I5" t="n">
-        <v>73.44005007081046</v>
+        <v>73.44005007081034</v>
       </c>
       <c r="J5" t="n">
-        <v>134.2108606077579</v>
+        <v>134.2108606077594</v>
       </c>
       <c r="K5" t="n">
-        <v>100.9744064976917</v>
+        <v>100.9744064976925</v>
       </c>
       <c r="L5" t="n">
-        <v>81.02394192100328</v>
+        <v>425.3055222804073</v>
       </c>
     </row>
     <row r="6">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.15619584384044</v>
+        <v>34.15619584384057</v>
       </c>
       <c r="C6" t="n">
-        <v>33.44002181429862</v>
+        <v>33.4400218142985</v>
       </c>
       <c r="D6" t="n">
-        <v>44.85085231063151</v>
+        <v>44.85086315789158</v>
       </c>
       <c r="E6" t="n">
         <v>31.50009286972811</v>
@@ -690,22 +690,22 @@
         <v>33.58928665718595</v>
       </c>
       <c r="G6" t="n">
-        <v>52.63330557155307</v>
+        <v>52.63330557155308</v>
       </c>
       <c r="H6" t="n">
-        <v>66.92466659175624</v>
+        <v>66.92466659175615</v>
       </c>
       <c r="I6" t="n">
-        <v>33.59105770573191</v>
+        <v>48.1859117905372</v>
       </c>
       <c r="J6" t="n">
-        <v>37.72669041780554</v>
+        <v>50.88221659732611</v>
       </c>
       <c r="K6" t="n">
-        <v>35.15971827063555</v>
+        <v>35.15971827063553</v>
       </c>
       <c r="L6" t="n">
-        <v>49.28885621042186</v>
+        <v>49.28885621042182</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.1845999593715</v>
+        <v>19.18459995937147</v>
       </c>
       <c r="C7" t="n">
-        <v>18.62075103602145</v>
+        <v>18.62075103602142</v>
       </c>
       <c r="D7" t="n">
         <v>29.59321388130522</v>
       </c>
       <c r="E7" t="n">
-        <v>18.61828339533193</v>
+        <v>18.6182833953319</v>
       </c>
       <c r="F7" t="n">
-        <v>18.61828339533193</v>
+        <v>18.6182833953319</v>
       </c>
       <c r="G7" t="n">
-        <v>23.06685560227872</v>
+        <v>23.0668556022787</v>
       </c>
       <c r="H7" t="n">
-        <v>37.5893015273771</v>
+        <v>37.58930152737705</v>
       </c>
       <c r="I7" t="n">
-        <v>18.6194618212628</v>
+        <v>18.61946182126279</v>
       </c>
       <c r="J7" t="n">
-        <v>21.66747407736298</v>
+        <v>21.66747407736295</v>
       </c>
       <c r="K7" t="n">
-        <v>20.24074426134078</v>
+        <v>20.24074426134079</v>
       </c>
       <c r="L7" t="n">
-        <v>34.20885892240713</v>
+        <v>34.20885892240707</v>
       </c>
     </row>
     <row r="8">
@@ -758,34 +758,34 @@
         <v>33.2774559076496</v>
       </c>
       <c r="C8" t="n">
-        <v>45.42452083334489</v>
+        <v>45.42452083337679</v>
       </c>
       <c r="D8" t="n">
-        <v>59.0324725044944</v>
+        <v>59.03247250449435</v>
       </c>
       <c r="E8" t="n">
-        <v>41.94823185508292</v>
+        <v>41.94823185508287</v>
       </c>
       <c r="F8" t="n">
-        <v>33.11510581659033</v>
+        <v>33.11510581659032</v>
       </c>
       <c r="G8" t="n">
-        <v>49.87037595887624</v>
+        <v>49.8703759588762</v>
       </c>
       <c r="H8" t="n">
-        <v>64.39282188397533</v>
+        <v>64.39282188397523</v>
       </c>
       <c r="I8" t="n">
-        <v>45.42298217786025</v>
+        <v>45.42298217786029</v>
       </c>
       <c r="J8" t="n">
-        <v>48.47349244460318</v>
+        <v>48.4734924446032</v>
       </c>
       <c r="K8" t="n">
-        <v>34.09749309249641</v>
+        <v>34.09749309249644</v>
       </c>
       <c r="L8" t="n">
-        <v>74.28973110278321</v>
+        <v>74.28973110278305</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.89833123701089</v>
+        <v>32.89833123701077</v>
       </c>
       <c r="C9" t="n">
-        <v>37.76199643219208</v>
+        <v>37.76199643219198</v>
       </c>
       <c r="D9" t="n">
-        <v>48.7345574048925</v>
+        <v>48.73455740489241</v>
       </c>
       <c r="E9" t="n">
-        <v>44.02523169340945</v>
+        <v>44.02523169340934</v>
       </c>
       <c r="F9" t="n">
-        <v>37.76199807744466</v>
+        <v>37.76199807744456</v>
       </c>
       <c r="G9" t="n">
-        <v>42.20810099844925</v>
+        <v>42.20810099844927</v>
       </c>
       <c r="H9" t="n">
-        <v>56.73054692354771</v>
+        <v>56.73054692354761</v>
       </c>
       <c r="I9" t="n">
-        <v>37.76070721743343</v>
+        <v>37.76070721743336</v>
       </c>
       <c r="J9" t="n">
-        <v>40.80871947353363</v>
+        <v>40.80871947353351</v>
       </c>
       <c r="K9" t="n">
-        <v>36.23726621096191</v>
+        <v>32.54778085221869</v>
       </c>
       <c r="L9" t="n">
-        <v>53.35010431857782</v>
+        <v>53.35010431857766</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.58722731413548</v>
+        <v>20.26956749029967</v>
       </c>
       <c r="C2" t="n">
-        <v>13.44610160398867</v>
+        <v>16.30103385784642</v>
       </c>
       <c r="D2" t="n">
-        <v>18.18703022697144</v>
+        <v>20.24850591245767</v>
       </c>
       <c r="E2" t="n">
-        <v>15.6702330551428</v>
+        <v>18.15794706717953</v>
       </c>
       <c r="F2" t="n">
-        <v>9.394969158606408</v>
+        <v>12.9372799257134</v>
       </c>
       <c r="G2" t="n">
-        <v>18.29472252636475</v>
+        <v>20.25417354428065</v>
       </c>
       <c r="H2" t="n">
-        <v>18.00953833950601</v>
+        <v>20.10001209066036</v>
       </c>
       <c r="I2" t="n">
-        <v>18.00977035452516</v>
+        <v>20.23911395815743</v>
       </c>
       <c r="J2" t="n">
-        <v>26.44318031336615</v>
+        <v>25.69634799173861</v>
       </c>
       <c r="K2" t="n">
-        <v>24.55128744449823</v>
+        <v>26.36003245726499</v>
       </c>
       <c r="L2" t="n">
-        <v>17.05257780189185</v>
+        <v>20.18506366345935</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.85282365467644</v>
+        <v>20.33944495077643</v>
       </c>
       <c r="C3" t="n">
-        <v>15.62119794535907</v>
+        <v>13.71639962845308</v>
       </c>
       <c r="D3" t="n">
-        <v>20.39251410386094</v>
+        <v>20.19070695996551</v>
       </c>
       <c r="E3" t="n">
-        <v>17.84891108131562</v>
+        <v>16.7769055554436</v>
       </c>
       <c r="F3" t="n">
-        <v>11.57364718477922</v>
+        <v>8.15750074498775</v>
       </c>
       <c r="G3" t="n">
-        <v>20.51638255655585</v>
+        <v>20.2319777035631</v>
       </c>
       <c r="H3" t="n">
-        <v>20.19375713820114</v>
+        <v>19.99279074238479</v>
       </c>
       <c r="I3" t="n">
-        <v>20.18441920390727</v>
+        <v>20.12453667971762</v>
       </c>
       <c r="J3" t="n">
-        <v>28.92304209766635</v>
+        <v>29.71380391130236</v>
       </c>
       <c r="K3" t="n">
-        <v>26.59994291337842</v>
+        <v>29.97872801456194</v>
       </c>
       <c r="L3" t="n">
-        <v>19.0878303882822</v>
+        <v>19.76944187547963</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.09397264279853</v>
+        <v>12.09397264279856</v>
       </c>
       <c r="C4" t="n">
-        <v>11.4833144445997</v>
+        <v>11.48331444459971</v>
       </c>
       <c r="D4" t="n">
-        <v>11.85607243226859</v>
+        <v>11.8560724322686</v>
       </c>
       <c r="E4" t="n">
-        <v>11.50066907907136</v>
+        <v>11.50066907907142</v>
       </c>
       <c r="F4" t="n">
-        <v>11.50066907907137</v>
+        <v>11.5006690790714</v>
       </c>
       <c r="G4" t="n">
-        <v>11.89202554482187</v>
+        <v>11.89202554482191</v>
       </c>
       <c r="H4" t="n">
-        <v>11.75106218151137</v>
+        <v>11.7510621815114</v>
       </c>
       <c r="I4" t="n">
-        <v>11.57160327155938</v>
+        <v>11.57160327155943</v>
       </c>
       <c r="J4" t="n">
-        <v>12.94194644196215</v>
+        <v>12.94194644196216</v>
       </c>
       <c r="K4" t="n">
         <v>11.23541060914301</v>
       </c>
       <c r="L4" t="n">
-        <v>11.18278299329034</v>
+        <v>11.18278299329037</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.21824640037843</v>
+        <v>50.21824640037836</v>
       </c>
       <c r="C5" t="n">
-        <v>45.22075461701538</v>
+        <v>45.22075461701554</v>
       </c>
       <c r="D5" t="n">
-        <v>46.82914532644302</v>
+        <v>46.82914532644301</v>
       </c>
       <c r="E5" t="n">
-        <v>45.2207624318867</v>
+        <v>45.22076243188565</v>
       </c>
       <c r="F5" t="n">
-        <v>45.2207624318867</v>
+        <v>45.22076243188565</v>
       </c>
       <c r="G5" t="n">
-        <v>48.35859393639851</v>
+        <v>48.35859393639856</v>
       </c>
       <c r="H5" t="n">
-        <v>48.92684167565049</v>
+        <v>48.92684167565056</v>
       </c>
       <c r="I5" t="n">
-        <v>45.22041523977191</v>
+        <v>45.22041523977281</v>
       </c>
       <c r="J5" t="n">
-        <v>67.59535491083224</v>
+        <v>67.59535491083241</v>
       </c>
       <c r="K5" t="n">
-        <v>36.52126098335805</v>
+        <v>36.52126098335812</v>
       </c>
       <c r="L5" t="n">
-        <v>39.06091064793512</v>
+        <v>39.06091064793521</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.58613171343413</v>
+        <v>29.42662357067469</v>
       </c>
       <c r="C6" t="n">
-        <v>28.86733614421266</v>
+        <v>28.8673361442126</v>
       </c>
       <c r="D6" t="n">
-        <v>41.06372966580038</v>
+        <v>41.06372966580032</v>
       </c>
       <c r="E6" t="n">
-        <v>27.18603212328016</v>
+        <v>27.18603212328019</v>
       </c>
       <c r="F6" t="n">
-        <v>28.90905866488243</v>
+        <v>28.90905866488247</v>
       </c>
       <c r="G6" t="n">
-        <v>29.22467647269804</v>
+        <v>41.38418461545749</v>
       </c>
       <c r="H6" t="n">
-        <v>40.97173834651712</v>
+        <v>40.97173834651716</v>
       </c>
       <c r="I6" t="n">
-        <v>28.90425419943554</v>
+        <v>28.90425419943559</v>
       </c>
       <c r="J6" t="n">
-        <v>42.11750741770222</v>
+        <v>31.19360245189786</v>
       </c>
       <c r="K6" t="n">
-        <v>28.54379731239833</v>
+        <v>28.54379731239861</v>
       </c>
       <c r="L6" t="n">
-        <v>28.51905313959865</v>
+        <v>28.51905313959864</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.05969257427956</v>
+        <v>16.05969257427959</v>
       </c>
       <c r="C7" t="n">
-        <v>15.53766258028313</v>
+        <v>15.5376625802831</v>
       </c>
       <c r="D7" t="n">
-        <v>15.82171075333504</v>
+        <v>15.82171075333508</v>
       </c>
       <c r="E7" t="n">
-        <v>15.53582027475663</v>
+        <v>15.53582027475669</v>
       </c>
       <c r="F7" t="n">
-        <v>15.53582027475663</v>
+        <v>15.53582027475669</v>
       </c>
       <c r="G7" t="n">
-        <v>15.8577454763029</v>
+        <v>15.85774547630291</v>
       </c>
       <c r="H7" t="n">
-        <v>15.71678211299239</v>
+        <v>15.71678211299243</v>
       </c>
       <c r="I7" t="n">
-        <v>15.53732320304042</v>
+        <v>15.53732320304045</v>
       </c>
       <c r="J7" t="n">
         <v>16.90766637344316</v>
       </c>
       <c r="K7" t="n">
-        <v>15.20113054062402</v>
+        <v>15.20113054062405</v>
       </c>
       <c r="L7" t="n">
-        <v>15.14850292477136</v>
+        <v>15.14850292477133</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.91723713816788</v>
+        <v>27.91723713816794</v>
       </c>
       <c r="C8" t="n">
-        <v>37.78234465722865</v>
+        <v>37.78234465725423</v>
       </c>
       <c r="D8" t="n">
-        <v>40.2198679396676</v>
+        <v>40.21986793966763</v>
       </c>
       <c r="E8" t="n">
-        <v>34.94161037345661</v>
+        <v>34.94161037345668</v>
       </c>
       <c r="F8" t="n">
-        <v>27.72340443764901</v>
+        <v>27.72340443764907</v>
       </c>
       <c r="G8" t="n">
-        <v>38.10205721496807</v>
+        <v>38.10205721496813</v>
       </c>
       <c r="H8" t="n">
-        <v>37.96109385165772</v>
+        <v>37.96109385165778</v>
       </c>
       <c r="I8" t="n">
-        <v>37.78163494170558</v>
+        <v>37.78163494170563</v>
       </c>
       <c r="J8" t="n">
-        <v>39.15401941040127</v>
+        <v>39.15401941040133</v>
       </c>
       <c r="K8" t="n">
-        <v>26.86573557158445</v>
+        <v>26.86573557158448</v>
       </c>
       <c r="L8" t="n">
-        <v>48.2426615057038</v>
+        <v>48.24266150570379</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.84325019629254</v>
+        <v>23.84325019629256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.71541463645305</v>
+        <v>26.71541463645304</v>
       </c>
       <c r="D9" t="n">
-        <v>26.99954557599548</v>
+        <v>26.99954557599547</v>
       </c>
       <c r="E9" t="n">
-        <v>30.63225082512734</v>
+        <v>30.63225082512735</v>
       </c>
       <c r="F9" t="n">
-        <v>26.71542158753275</v>
+        <v>26.71542158753277</v>
       </c>
       <c r="G9" t="n">
-        <v>27.03549753247285</v>
+        <v>27.03549753247286</v>
       </c>
       <c r="H9" t="n">
-        <v>26.89453416916233</v>
+        <v>26.89453416916226</v>
       </c>
       <c r="I9" t="n">
-        <v>26.71507525921032</v>
+        <v>26.71507525921038</v>
       </c>
       <c r="J9" t="n">
         <v>28.08541842961311</v>
       </c>
       <c r="K9" t="n">
-        <v>24.41227349785573</v>
+        <v>24.41227349785589</v>
       </c>
       <c r="L9" t="n">
-        <v>26.3262549809413</v>
+        <v>26.32625498094123</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.60071749263891</v>
+        <v>20.09320250457098</v>
       </c>
       <c r="C2" t="n">
-        <v>8.336032983377592</v>
+        <v>11.47937714976199</v>
       </c>
       <c r="D2" t="n">
-        <v>29.83938582192935</v>
+        <v>20.68467129694833</v>
       </c>
       <c r="E2" t="n">
-        <v>10.52541051764368</v>
+        <v>12.52308593039655</v>
       </c>
       <c r="F2" t="n">
-        <v>10.52541051764368</v>
+        <v>12.525759824487</v>
       </c>
       <c r="G2" t="n">
-        <v>23.48208940578883</v>
+        <v>20.35009941317463</v>
       </c>
       <c r="H2" t="n">
-        <v>34.51773430698231</v>
+        <v>20.79699147892</v>
       </c>
       <c r="I2" t="n">
-        <v>19.51783561043902</v>
+        <v>20.14137268337615</v>
       </c>
       <c r="J2" t="n">
-        <v>22.87074930675237</v>
+        <v>19.12340805029738</v>
       </c>
       <c r="K2" t="n">
-        <v>32.21533046484323</v>
+        <v>29.49466647623669</v>
       </c>
       <c r="L2" t="n">
-        <v>23.50624009397491</v>
+        <v>20.3478030838472</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.45285747783327</v>
+        <v>21.55138031294576</v>
       </c>
       <c r="C3" t="n">
-        <v>10.1708104956469</v>
+        <v>7.415545075124289</v>
       </c>
       <c r="D3" t="n">
-        <v>33.37965413964835</v>
+        <v>25.77679894386842</v>
       </c>
       <c r="E3" t="n">
-        <v>12.51503441521323</v>
+        <v>9.420363443010025</v>
       </c>
       <c r="F3" t="n">
-        <v>12.51503441521323</v>
+        <v>9.423037337100565</v>
       </c>
       <c r="G3" t="n">
-        <v>26.06744635110174</v>
+        <v>23.39779029616255</v>
       </c>
       <c r="H3" t="n">
-        <v>38.76719099820504</v>
+        <v>27.44037874880471</v>
       </c>
       <c r="I3" t="n">
-        <v>21.50055032396858</v>
+        <v>21.90803887047647</v>
       </c>
       <c r="J3" t="n">
-        <v>25.59438705794508</v>
+        <v>21.6422219260717</v>
       </c>
       <c r="K3" t="n">
-        <v>34.43943813623305</v>
+        <v>37.79661620163262</v>
       </c>
       <c r="L3" t="n">
-        <v>26.09541948601869</v>
+        <v>23.42115929401099</v>
       </c>
     </row>
     <row r="4">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.72587477958608</v>
+        <v>11.72587477958611</v>
       </c>
       <c r="C4" t="n">
         <v>11.47176050868657</v>
@@ -1396,28 +1396,28 @@
         <v>18.40678687857539</v>
       </c>
       <c r="E4" t="n">
-        <v>11.98665482707024</v>
+        <v>11.98665482707028</v>
       </c>
       <c r="F4" t="n">
-        <v>11.98665482707023</v>
+        <v>11.98665482707028</v>
       </c>
       <c r="G4" t="n">
-        <v>14.59879303847948</v>
+        <v>14.59879303847953</v>
       </c>
       <c r="H4" t="n">
-        <v>21.18578702305129</v>
+        <v>21.18578702305131</v>
       </c>
       <c r="I4" t="n">
-        <v>12.08639915951015</v>
+        <v>12.08639915951016</v>
       </c>
       <c r="J4" t="n">
         <v>15.17490164378918</v>
       </c>
       <c r="K4" t="n">
-        <v>13.19796867627477</v>
+        <v>13.19796867627473</v>
       </c>
       <c r="L4" t="n">
-        <v>14.64299701492615</v>
+        <v>14.64299701492616</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.71726375391178</v>
+        <v>32.71726375391233</v>
       </c>
       <c r="C5" t="n">
         <v>39.50784719718195</v>
       </c>
       <c r="D5" t="n">
-        <v>159.3277722255966</v>
+        <v>159.3277722255965</v>
       </c>
       <c r="E5" t="n">
-        <v>49.70335805625165</v>
+        <v>49.70335805625155</v>
       </c>
       <c r="F5" t="n">
-        <v>49.70335805625165</v>
+        <v>49.70335805625155</v>
       </c>
       <c r="G5" t="n">
-        <v>93.78239060881165</v>
+        <v>93.78239060880779</v>
       </c>
       <c r="H5" t="n">
-        <v>233.7014218995842</v>
+        <v>233.7014218995841</v>
       </c>
       <c r="I5" t="n">
-        <v>49.7025052704978</v>
+        <v>49.70250527049754</v>
       </c>
       <c r="J5" t="n">
-        <v>105.9141808011634</v>
+        <v>105.914180801163</v>
       </c>
       <c r="K5" t="n">
-        <v>66.35065006306127</v>
+        <v>66.35065006306124</v>
       </c>
       <c r="L5" t="n">
-        <v>103.5751992413303</v>
+        <v>103.5751992413302</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.05777580995465</v>
+        <v>43.13919577876917</v>
       </c>
       <c r="C6" t="n">
-        <v>29.85884218066518</v>
+        <v>29.85884218066525</v>
       </c>
       <c r="D6" t="n">
-        <v>36.88366696021675</v>
+        <v>36.88368071379606</v>
       </c>
       <c r="E6" t="n">
         <v>28.54277812864488</v>
       </c>
       <c r="F6" t="n">
-        <v>30.41622618368531</v>
+        <v>30.41622618368532</v>
       </c>
       <c r="G6" t="n">
-        <v>46.01211403766266</v>
+        <v>32.93069406884803</v>
       </c>
       <c r="H6" t="n">
         <v>52.56231942528726</v>
       </c>
       <c r="I6" t="n">
-        <v>43.49972015869326</v>
+        <v>30.41830018987871</v>
       </c>
       <c r="J6" t="n">
-        <v>46.34340188335386</v>
+        <v>46.34340188335381</v>
       </c>
       <c r="K6" t="n">
-        <v>31.50320457939222</v>
+        <v>31.50320457939225</v>
       </c>
       <c r="L6" t="n">
-        <v>32.99329783451907</v>
+        <v>32.9932978345191</v>
       </c>
     </row>
     <row r="7">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.30127939577978</v>
+        <v>16.30127939577982</v>
       </c>
       <c r="C7" t="n">
-        <v>16.22598972946975</v>
+        <v>16.22598972946974</v>
       </c>
       <c r="D7" t="n">
-        <v>22.98212135486205</v>
+        <v>22.98212135486207</v>
       </c>
       <c r="E7" t="n">
         <v>16.66298960956792</v>
@@ -1522,22 +1522,22 @@
         <v>16.66298960956792</v>
       </c>
       <c r="G7" t="n">
-        <v>19.17419765467323</v>
+        <v>19.17419765467321</v>
       </c>
       <c r="H7" t="n">
         <v>25.761191639245</v>
       </c>
       <c r="I7" t="n">
-        <v>16.66180377570385</v>
+        <v>16.66180377570386</v>
       </c>
       <c r="J7" t="n">
         <v>19.75030625998289</v>
       </c>
       <c r="K7" t="n">
-        <v>17.77337329246846</v>
+        <v>17.77337329246842</v>
       </c>
       <c r="L7" t="n">
-        <v>19.21840163111984</v>
+        <v>19.21840163111986</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.20736572878957</v>
+        <v>29.2073657287896</v>
       </c>
       <c r="C8" t="n">
-        <v>40.69037905861174</v>
+        <v>40.69037905861177</v>
       </c>
       <c r="D8" t="n">
         <v>49.84003798729351</v>
       </c>
       <c r="E8" t="n">
-        <v>37.96638660447805</v>
+        <v>37.96638660447809</v>
       </c>
       <c r="F8" t="n">
-        <v>29.93527891183326</v>
+        <v>29.93527891183327</v>
       </c>
       <c r="G8" t="n">
-        <v>43.63590984722499</v>
+        <v>43.63590984722539</v>
       </c>
       <c r="H8" t="n">
-        <v>50.22290383180868</v>
+        <v>50.22290383180867</v>
       </c>
       <c r="I8" t="n">
-        <v>41.12351596825602</v>
+        <v>41.12351596825605</v>
       </c>
       <c r="J8" t="n">
-        <v>44.21428946495536</v>
+        <v>44.21428946495534</v>
       </c>
       <c r="K8" t="n">
-        <v>30.46480794238059</v>
+        <v>30.46480794238067</v>
       </c>
       <c r="L8" t="n">
-        <v>55.75093130052847</v>
+        <v>55.75093130052854</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.47053305594626</v>
+        <v>26.4705330559462</v>
       </c>
       <c r="C9" t="n">
         <v>30.66798512037435</v>
       </c>
       <c r="D9" t="n">
-        <v>37.42418744712514</v>
+        <v>37.42418744712518</v>
       </c>
       <c r="E9" t="n">
-        <v>36.03530203397548</v>
+        <v>36.03530203397547</v>
       </c>
       <c r="F9" t="n">
-        <v>31.10464892320664</v>
+        <v>31.10464892320673</v>
       </c>
       <c r="G9" t="n">
         <v>33.61619304557777</v>
       </c>
       <c r="H9" t="n">
-        <v>40.20318703014947</v>
+        <v>40.20318703014958</v>
       </c>
       <c r="I9" t="n">
-        <v>31.10379916660839</v>
+        <v>31.1037991666085</v>
       </c>
       <c r="J9" t="n">
         <v>34.19230165088746</v>
       </c>
       <c r="K9" t="n">
-        <v>29.7397255803776</v>
+        <v>29.73972558037758</v>
       </c>
       <c r="L9" t="n">
-        <v>33.66039702202433</v>
+        <v>33.66039702202445</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.72284784328007</v>
+        <v>19.67467414365947</v>
       </c>
       <c r="C2" t="n">
-        <v>8.324267555784314</v>
+        <v>11.32985763492817</v>
       </c>
       <c r="D2" t="n">
-        <v>25.85481656597785</v>
+        <v>20.10264350614425</v>
       </c>
       <c r="E2" t="n">
-        <v>9.52737691951393</v>
+        <v>12.30621249387135</v>
       </c>
       <c r="F2" t="n">
-        <v>9.52737691951393</v>
+        <v>12.30888515525465</v>
       </c>
       <c r="G2" t="n">
-        <v>20.76660139709417</v>
+        <v>19.83486084781522</v>
       </c>
       <c r="H2" t="n">
-        <v>26.27619415264349</v>
+        <v>19.98840729122223</v>
       </c>
       <c r="I2" t="n">
-        <v>18.25281560243128</v>
+        <v>19.70248383823705</v>
       </c>
       <c r="J2" t="n">
-        <v>20.083173825162</v>
+        <v>18.79979409683693</v>
       </c>
       <c r="K2" t="n">
-        <v>30.15195944438054</v>
+        <v>29.20634360688329</v>
       </c>
       <c r="L2" t="n">
-        <v>18.88100899519133</v>
+        <v>19.73108709485559</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.48186441621316</v>
+        <v>20.87451350253848</v>
       </c>
       <c r="C3" t="n">
-        <v>10.15307303997902</v>
+        <v>7.348925338906149</v>
       </c>
       <c r="D3" t="n">
-        <v>28.8353129795617</v>
+        <v>23.93575091220836</v>
       </c>
       <c r="E3" t="n">
-        <v>11.36576595290528</v>
+        <v>8.965057339553608</v>
       </c>
       <c r="F3" t="n">
-        <v>11.36576595290528</v>
+        <v>8.967730000936903</v>
       </c>
       <c r="G3" t="n">
-        <v>22.98281151474855</v>
+        <v>22.03111986796621</v>
       </c>
       <c r="H3" t="n">
-        <v>29.32619144349348</v>
+        <v>23.98259707356003</v>
       </c>
       <c r="I3" t="n">
-        <v>20.08610491311126</v>
+        <v>21.08626410643711</v>
       </c>
       <c r="J3" t="n">
-        <v>22.3891918507476</v>
+        <v>20.49763687185377</v>
       </c>
       <c r="K3" t="n">
-        <v>32.06777176881042</v>
+        <v>36.92231154831357</v>
       </c>
       <c r="L3" t="n">
-        <v>20.81426316824234</v>
+        <v>21.32698469207796</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.3050510665231</v>
+        <v>11.30505106652315</v>
       </c>
       <c r="C4" t="n">
-        <v>11.40895877774336</v>
+        <v>11.4089587777435</v>
       </c>
       <c r="D4" t="n">
-        <v>16.13916189142221</v>
+        <v>16.13916189142223</v>
       </c>
       <c r="E4" t="n">
-        <v>11.37311050800347</v>
+        <v>11.37311050800348</v>
       </c>
       <c r="F4" t="n">
-        <v>11.37311050800347</v>
+        <v>11.37311050800349</v>
       </c>
       <c r="G4" t="n">
-        <v>13.0861074257915</v>
+        <v>13.08610742579154</v>
       </c>
       <c r="H4" t="n">
-        <v>16.38884808015845</v>
+        <v>16.38884808015848</v>
       </c>
       <c r="I4" t="n">
-        <v>11.4391586420468</v>
+        <v>11.43915864204685</v>
       </c>
       <c r="J4" t="n">
-        <v>13.4698560477452</v>
+        <v>13.46985604774521</v>
       </c>
       <c r="K4" t="n">
-        <v>11.92558364871039</v>
+        <v>11.92558364871042</v>
       </c>
       <c r="L4" t="n">
-        <v>11.99487552243334</v>
+        <v>11.99487552243337</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.32119199888997</v>
+        <v>26.32119199888992</v>
       </c>
       <c r="C5" t="n">
-        <v>38.78588915372676</v>
+        <v>38.78588915372828</v>
       </c>
       <c r="D5" t="n">
         <v>115.343690850935</v>
       </c>
       <c r="E5" t="n">
-        <v>38.5752000622954</v>
+        <v>38.57520006229555</v>
       </c>
       <c r="F5" t="n">
-        <v>38.5752000622954</v>
+        <v>38.57520006229564</v>
       </c>
       <c r="G5" t="n">
-        <v>65.21094165128351</v>
+        <v>65.21094165128484</v>
       </c>
       <c r="H5" t="n">
-        <v>132.9345590789405</v>
+        <v>132.9345590789407</v>
       </c>
       <c r="I5" t="n">
-        <v>38.57454625135011</v>
+        <v>38.57454625135021</v>
       </c>
       <c r="J5" t="n">
-        <v>72.79534829098561</v>
+        <v>72.7953482909856</v>
       </c>
       <c r="K5" t="n">
-        <v>43.84206547802657</v>
+        <v>43.84206547802651</v>
       </c>
       <c r="L5" t="n">
-        <v>49.54077501834423</v>
+        <v>49.54077501834426</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.91744633614647</v>
+        <v>40.91744633614648</v>
       </c>
       <c r="C6" t="n">
-        <v>28.80401060934994</v>
+        <v>28.80401060934991</v>
       </c>
       <c r="D6" t="n">
-        <v>45.57164704939011</v>
+        <v>45.57164704939016</v>
       </c>
       <c r="E6" t="n">
-        <v>26.9964060886446</v>
+        <v>26.99640608864457</v>
       </c>
       <c r="F6" t="n">
-        <v>28.75050920356977</v>
+        <v>28.75050920356975</v>
       </c>
       <c r="G6" t="n">
-        <v>30.39727311266437</v>
+        <v>42.69850269541482</v>
       </c>
       <c r="H6" t="n">
-        <v>46.062454620255</v>
+        <v>46.06245462025505</v>
       </c>
       <c r="I6" t="n">
         <v>28.75032432891961</v>
       </c>
       <c r="J6" t="n">
-        <v>31.70544804543063</v>
+        <v>31.70544804543066</v>
       </c>
       <c r="K6" t="n">
-        <v>29.20662798418511</v>
+        <v>29.20662798418495</v>
       </c>
       <c r="L6" t="n">
-        <v>29.31085610437884</v>
+        <v>29.31085610437889</v>
       </c>
     </row>
     <row r="7">
@@ -1903,34 +1903,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.5558496312712</v>
+        <v>15.55584963127124</v>
       </c>
       <c r="C7" t="n">
-        <v>15.82705193922467</v>
+        <v>15.82705193922481</v>
       </c>
       <c r="D7" t="n">
-        <v>20.38989849700122</v>
+        <v>20.38989849700125</v>
       </c>
       <c r="E7" t="n">
-        <v>15.6980740758682</v>
+        <v>15.69807407586821</v>
       </c>
       <c r="F7" t="n">
-        <v>15.6980740758682</v>
+        <v>15.69807407586821</v>
       </c>
       <c r="G7" t="n">
-        <v>17.33690599053959</v>
+        <v>17.33690599053965</v>
       </c>
       <c r="H7" t="n">
         <v>20.63964664490658</v>
       </c>
       <c r="I7" t="n">
-        <v>15.68995720679491</v>
+        <v>15.68995720679494</v>
       </c>
       <c r="J7" t="n">
-        <v>17.72065461249326</v>
+        <v>17.72065461249333</v>
       </c>
       <c r="K7" t="n">
-        <v>16.1763822134585</v>
+        <v>16.17638221345851</v>
       </c>
       <c r="L7" t="n">
         <v>16.24567408718147</v>
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.75819653568812</v>
+        <v>27.75819653568815</v>
       </c>
       <c r="C8" t="n">
-        <v>38.91016723267639</v>
+        <v>38.91016723262301</v>
       </c>
       <c r="D8" t="n">
-        <v>45.71798340363269</v>
+        <v>45.71798340363275</v>
       </c>
       <c r="E8" t="n">
         <v>35.79948487805284</v>
       </c>
       <c r="F8" t="n">
-        <v>28.24205408964368</v>
+        <v>28.2420540896437</v>
       </c>
       <c r="G8" t="n">
-        <v>40.41066981820276</v>
+        <v>40.41066981820278</v>
       </c>
       <c r="H8" t="n">
-        <v>43.71341047260336</v>
+        <v>43.71341047260343</v>
       </c>
       <c r="I8" t="n">
-        <v>38.76372103445804</v>
+        <v>38.76372103445807</v>
       </c>
       <c r="J8" t="n">
-        <v>40.79655498577239</v>
+        <v>40.7965549857724</v>
       </c>
       <c r="K8" t="n">
-        <v>28.17678696703982</v>
+        <v>28.1767869670399</v>
       </c>
       <c r="L8" t="n">
-        <v>50.67554194505111</v>
+        <v>50.67554194505109</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.99833150567086</v>
+        <v>23.99833150567091</v>
       </c>
       <c r="C9" t="n">
-        <v>27.96154600706733</v>
+        <v>27.96154600706747</v>
       </c>
       <c r="D9" t="n">
-        <v>32.52445545728516</v>
+        <v>32.52445545728521</v>
       </c>
       <c r="E9" t="n">
-        <v>32.08560739683914</v>
+        <v>32.08560739683919</v>
       </c>
       <c r="F9" t="n">
-        <v>27.82510322931427</v>
+        <v>27.82510322931428</v>
       </c>
       <c r="G9" t="n">
-        <v>29.4714000583823</v>
+        <v>29.47140005838237</v>
       </c>
       <c r="H9" t="n">
         <v>32.77414071274933</v>
       </c>
       <c r="I9" t="n">
-        <v>27.82445127463762</v>
+        <v>27.82445127463769</v>
       </c>
       <c r="J9" t="n">
-        <v>29.85514868033597</v>
+        <v>29.85514868033605</v>
       </c>
       <c r="K9" t="n">
-        <v>26.17171030930165</v>
+        <v>26.17171030930169</v>
       </c>
       <c r="L9" t="n">
-        <v>28.38016815502416</v>
+        <v>28.38016815502428</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.98517481409519</v>
+        <v>19.27523523616764</v>
       </c>
       <c r="C2" t="n">
-        <v>8.029713388121269</v>
+        <v>11.19142510902287</v>
       </c>
       <c r="D2" t="n">
-        <v>22.64072405464076</v>
+        <v>19.57287555987199</v>
       </c>
       <c r="E2" t="n">
-        <v>8.579122774852076</v>
+        <v>12.1152811268264</v>
       </c>
       <c r="F2" t="n">
-        <v>8.579122774852076</v>
+        <v>12.11795298347012</v>
       </c>
       <c r="G2" t="n">
-        <v>18.75078992425761</v>
+        <v>19.36815605262135</v>
       </c>
       <c r="H2" t="n">
-        <v>21.54151547180616</v>
+        <v>19.3775051816141</v>
       </c>
       <c r="I2" t="n">
-        <v>17.02280209279177</v>
+        <v>19.27714150004637</v>
       </c>
       <c r="J2" t="n">
-        <v>17.45845906799615</v>
+        <v>18.51137113211296</v>
       </c>
       <c r="K2" t="n">
-        <v>29.06255167525436</v>
+        <v>29.05242363881525</v>
       </c>
       <c r="L2" t="n">
-        <v>17.14216547405779</v>
+        <v>19.27947469485519</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.67922425196308</v>
+        <v>20.22894838047431</v>
       </c>
       <c r="C3" t="n">
-        <v>9.814439536170084</v>
+        <v>7.173452875591495</v>
       </c>
       <c r="D3" t="n">
-        <v>25.18427742208624</v>
+        <v>22.36216203392851</v>
       </c>
       <c r="E3" t="n">
-        <v>10.27861293605892</v>
+        <v>8.521970990437811</v>
       </c>
       <c r="F3" t="n">
-        <v>10.27861293605892</v>
+        <v>8.524642847081509</v>
       </c>
       <c r="G3" t="n">
-        <v>20.71004737471809</v>
+        <v>20.90576875690665</v>
       </c>
       <c r="H3" t="n">
-        <v>23.92598070181288</v>
+        <v>21.82763415927106</v>
       </c>
       <c r="I3" t="n">
-        <v>18.71783435719787</v>
+        <v>20.25624034136905</v>
       </c>
       <c r="J3" t="n">
-        <v>19.375545973423</v>
+        <v>19.41202517199758</v>
       </c>
       <c r="K3" t="n">
-        <v>30.80970180529492</v>
+        <v>36.48334148821181</v>
       </c>
       <c r="L3" t="n">
-        <v>18.86002982555307</v>
+        <v>20.30292680913491</v>
       </c>
     </row>
     <row r="4">
@@ -2182,34 +2182,34 @@
         <v>11.0158989056911</v>
       </c>
       <c r="C4" t="n">
-        <v>11.20917811074971</v>
+        <v>11.2091781107497</v>
       </c>
       <c r="D4" t="n">
-        <v>14.37788328324551</v>
+        <v>14.3778832832455</v>
       </c>
       <c r="E4" t="n">
-        <v>10.80043546854777</v>
+        <v>10.80043546854775</v>
       </c>
       <c r="F4" t="n">
-        <v>10.80043546854776</v>
+        <v>10.80043546854775</v>
       </c>
       <c r="G4" t="n">
-        <v>12.03744317135448</v>
+        <v>12.03744317135445</v>
       </c>
       <c r="H4" t="n">
-        <v>13.72426902765769</v>
+        <v>13.72426902765767</v>
       </c>
       <c r="I4" t="n">
-        <v>10.85936467844287</v>
+        <v>10.85936467844286</v>
       </c>
       <c r="J4" t="n">
-        <v>11.89858873846805</v>
+        <v>11.89858873846801</v>
       </c>
       <c r="K4" t="n">
-        <v>11.2260494315516</v>
+        <v>11.22604943155159</v>
       </c>
       <c r="L4" t="n">
-        <v>11.11043908928693</v>
+        <v>11.11043908928691</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.69308716516695</v>
+        <v>22.69308716516694</v>
       </c>
       <c r="C5" t="n">
-        <v>36.61129685439098</v>
+        <v>36.61129685439093</v>
       </c>
       <c r="D5" t="n">
-        <v>86.78816664258619</v>
+        <v>86.78816664258574</v>
       </c>
       <c r="E5" t="n">
-        <v>29.98926674902826</v>
+        <v>29.98926674902819</v>
       </c>
       <c r="F5" t="n">
-        <v>29.98926674902826</v>
+        <v>29.98926674902819</v>
       </c>
       <c r="G5" t="n">
-        <v>48.29718279359213</v>
+        <v>48.29718279359018</v>
       </c>
       <c r="H5" t="n">
-        <v>83.50097824288615</v>
+        <v>83.50097824288609</v>
       </c>
       <c r="I5" t="n">
-        <v>29.98872094872043</v>
+        <v>29.98872094872039</v>
       </c>
       <c r="J5" t="n">
-        <v>46.20226174670166</v>
+        <v>46.20226174670174</v>
       </c>
       <c r="K5" t="n">
-        <v>33.29228977663358</v>
+        <v>33.29228977663345</v>
       </c>
       <c r="L5" t="n">
-        <v>33.88673205420495</v>
+        <v>33.88673205420491</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.28112348576042</v>
+        <v>28.28112348576041</v>
       </c>
       <c r="C6" t="n">
-        <v>28.57287389895061</v>
+        <v>28.57287389895059</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71591420340515</v>
+        <v>31.7158998609363</v>
       </c>
       <c r="E6" t="n">
-        <v>26.38227878935442</v>
+        <v>26.38227878935433</v>
       </c>
       <c r="F6" t="n">
-        <v>28.12448161982802</v>
+        <v>28.12448161982797</v>
       </c>
       <c r="G6" t="n">
-        <v>41.54812068667779</v>
+        <v>41.54812068667756</v>
       </c>
       <c r="H6" t="n">
-        <v>43.292722967055</v>
+        <v>43.29272296705495</v>
       </c>
       <c r="I6" t="n">
-        <v>40.37004219376604</v>
+        <v>40.37004219376601</v>
       </c>
       <c r="J6" t="n">
-        <v>41.18407780374984</v>
+        <v>41.18407780374974</v>
       </c>
       <c r="K6" t="n">
-        <v>28.46496098809582</v>
+        <v>28.46496098809573</v>
       </c>
       <c r="L6" t="n">
-        <v>28.37705004159637</v>
+        <v>28.37705004159628</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.20102573080296</v>
+        <v>15.20102573080294</v>
       </c>
       <c r="C7" t="n">
-        <v>15.55576292555399</v>
+        <v>15.55576292555397</v>
       </c>
       <c r="D7" t="n">
-        <v>18.56294740493566</v>
+        <v>18.56294740493562</v>
       </c>
       <c r="E7" t="n">
-        <v>15.0539751587182</v>
+        <v>15.05397515871819</v>
       </c>
       <c r="F7" t="n">
-        <v>15.0539751587182</v>
+        <v>15.05397515871819</v>
       </c>
       <c r="G7" t="n">
-        <v>16.22256999646645</v>
+        <v>16.22256999646628</v>
       </c>
       <c r="H7" t="n">
         <v>17.90939585276956</v>
       </c>
       <c r="I7" t="n">
-        <v>15.04449150355475</v>
+        <v>15.04449150355471</v>
       </c>
       <c r="J7" t="n">
-        <v>16.0837155635799</v>
+        <v>16.08371556357988</v>
       </c>
       <c r="K7" t="n">
-        <v>15.41117625666348</v>
+        <v>15.41117625666343</v>
       </c>
       <c r="L7" t="n">
-        <v>15.2955659143988</v>
+        <v>15.29556591439878</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.36852202432418</v>
+        <v>27.36852202432415</v>
       </c>
       <c r="C8" t="n">
-        <v>38.53289987924268</v>
+        <v>38.53289987930486</v>
       </c>
       <c r="D8" t="n">
-        <v>43.76861482480239</v>
+        <v>43.76861482480233</v>
       </c>
       <c r="E8" t="n">
-        <v>35.06761652416746</v>
+        <v>35.06761652416737</v>
       </c>
       <c r="F8" t="n">
-        <v>27.56021095882257</v>
+        <v>27.56021095882255</v>
       </c>
       <c r="G8" t="n">
-        <v>39.18895482657152</v>
+        <v>39.18895482657154</v>
       </c>
       <c r="H8" t="n">
-        <v>40.87578068290894</v>
+        <v>40.8757806829089</v>
       </c>
       <c r="I8" t="n">
         <v>38.01087633366001</v>
       </c>
       <c r="J8" t="n">
-        <v>39.05222268536166</v>
+        <v>39.05222268536157</v>
       </c>
       <c r="K8" t="n">
-        <v>27.37807765135893</v>
+        <v>27.37807765135889</v>
       </c>
       <c r="L8" t="n">
-        <v>49.54229281010795</v>
+        <v>49.54229281010788</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.79021385337964</v>
+        <v>22.79021385337958</v>
       </c>
       <c r="C9" t="n">
-        <v>26.57905030393125</v>
+        <v>26.5790503039312</v>
       </c>
       <c r="D9" t="n">
-        <v>29.58629851372504</v>
+        <v>29.58629851372493</v>
       </c>
       <c r="E9" t="n">
-        <v>30.03120164511976</v>
+        <v>30.03120164511969</v>
       </c>
       <c r="F9" t="n">
-        <v>26.06832332861625</v>
+        <v>26.06832332861615</v>
       </c>
       <c r="G9" t="n">
-        <v>27.24585737484368</v>
+        <v>27.24585737484355</v>
       </c>
       <c r="H9" t="n">
-        <v>28.93268323114685</v>
+        <v>28.93268323114684</v>
       </c>
       <c r="I9" t="n">
-        <v>26.06777888193209</v>
+        <v>26.06777888193196</v>
       </c>
       <c r="J9" t="n">
-        <v>27.10700294195712</v>
+        <v>27.10700294195717</v>
       </c>
       <c r="K9" t="n">
-        <v>22.110319421267</v>
+        <v>24.36400756362009</v>
       </c>
       <c r="L9" t="n">
-        <v>26.31885329277609</v>
+        <v>26.31885329277601</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.97186291997789</v>
+        <v>19.97300098374303</v>
       </c>
       <c r="C2" t="n">
-        <v>7.664720051496458</v>
+        <v>11.24974009249704</v>
       </c>
       <c r="D2" t="n">
-        <v>24.31837226992446</v>
+        <v>20.30700516564785</v>
       </c>
       <c r="E2" t="n">
-        <v>9.509096257822272</v>
+        <v>12.2675915357024</v>
       </c>
       <c r="F2" t="n">
-        <v>9.509096257822272</v>
+        <v>12.27026381194012</v>
       </c>
       <c r="G2" t="n">
-        <v>21.19324064554285</v>
+        <v>20.142535695268</v>
       </c>
       <c r="H2" t="n">
-        <v>30.84583756123577</v>
+        <v>20.51650168745685</v>
       </c>
       <c r="I2" t="n">
-        <v>18.64858893764058</v>
+        <v>20.00853594401612</v>
       </c>
       <c r="J2" t="n">
-        <v>22.3459287895141</v>
+        <v>18.87640991134464</v>
       </c>
       <c r="K2" t="n">
-        <v>30.76102369418658</v>
+        <v>29.17935773487561</v>
       </c>
       <c r="L2" t="n">
-        <v>23.34723166038436</v>
+        <v>20.25435343023631</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.70347665515531</v>
+        <v>21.35578889791584</v>
       </c>
       <c r="C3" t="n">
-        <v>9.393599051010316</v>
+        <v>7.065853530528925</v>
       </c>
       <c r="D3" t="n">
-        <v>27.00327708304508</v>
+        <v>23.74787721015711</v>
       </c>
       <c r="E3" t="n">
-        <v>11.34213135961316</v>
+        <v>8.932483639038487</v>
       </c>
       <c r="F3" t="n">
-        <v>11.34213135961316</v>
+        <v>8.935155915276175</v>
       </c>
       <c r="G3" t="n">
-        <v>23.4087283459405</v>
+        <v>22.57907171845412</v>
       </c>
       <c r="H3" t="n">
-        <v>34.51759348307138</v>
+        <v>26.09554623480579</v>
       </c>
       <c r="I3" t="n">
-        <v>20.47710802319741</v>
+        <v>21.62263591339127</v>
       </c>
       <c r="J3" t="n">
-        <v>24.99014739361275</v>
+        <v>21.31612486785475</v>
       </c>
       <c r="K3" t="n">
-        <v>32.76983266273072</v>
+        <v>37.09752973757349</v>
       </c>
       <c r="L3" t="n">
-        <v>25.88631980209491</v>
+        <v>23.40325953180857</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.17760790678828</v>
+        <v>11.17760790678829</v>
       </c>
       <c r="C4" t="n">
-        <v>10.99349461954628</v>
+        <v>10.99349461954629</v>
       </c>
       <c r="D4" t="n">
-        <v>14.95033879091813</v>
+        <v>14.9503387909181</v>
       </c>
       <c r="E4" t="n">
-        <v>11.35090277010214</v>
+        <v>11.35090277010212</v>
       </c>
       <c r="F4" t="n">
-        <v>11.35090277010214</v>
+        <v>11.35090277010212</v>
       </c>
       <c r="G4" t="n">
-        <v>13.0643254324849</v>
+        <v>13.06432543248489</v>
       </c>
       <c r="H4" t="n">
         <v>18.82887002773</v>
       </c>
       <c r="I4" t="n">
-        <v>11.39936881310691</v>
+        <v>11.3993688131069</v>
       </c>
       <c r="J4" t="n">
         <v>14.78931964274087</v>
       </c>
       <c r="K4" t="n">
-        <v>12.27463172464735</v>
+        <v>12.27463172464736</v>
       </c>
       <c r="L4" t="n">
-        <v>14.37344259961406</v>
+        <v>14.37344259961407</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.6949267327447</v>
+        <v>25.69492673274467</v>
       </c>
       <c r="C5" t="n">
-        <v>33.55175943591739</v>
+        <v>33.55175943591738</v>
       </c>
       <c r="D5" t="n">
-        <v>100.4650936970931</v>
+        <v>100.4650936970929</v>
       </c>
       <c r="E5" t="n">
-        <v>40.22831613952408</v>
+        <v>40.22831613952383</v>
       </c>
       <c r="F5" t="n">
-        <v>40.22831613952408</v>
+        <v>40.22831613952383</v>
       </c>
       <c r="G5" t="n">
-        <v>68.5977765892018</v>
+        <v>68.59777658920183</v>
       </c>
       <c r="H5" t="n">
-        <v>189.5727041554517</v>
+        <v>189.5727041554516</v>
       </c>
       <c r="I5" t="n">
-        <v>40.22765950589324</v>
+        <v>40.22765950589302</v>
       </c>
       <c r="J5" t="n">
         <v>101.7985877951732</v>
       </c>
       <c r="K5" t="n">
-        <v>52.75153276694692</v>
+        <v>52.75153276694698</v>
       </c>
       <c r="L5" t="n">
-        <v>101.473477636688</v>
+        <v>101.4734776366879</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.46692935897445</v>
+        <v>29.46692935897448</v>
       </c>
       <c r="C6" t="n">
-        <v>29.35279640069959</v>
+        <v>29.35279640069952</v>
       </c>
       <c r="D6" t="n">
-        <v>33.30829331268077</v>
+        <v>33.30827948920277</v>
       </c>
       <c r="E6" t="n">
-        <v>27.84076042982094</v>
+        <v>27.84076042982085</v>
       </c>
       <c r="F6" t="n">
-        <v>29.6903281154467</v>
+        <v>29.69032811544666</v>
       </c>
       <c r="G6" t="n">
-        <v>31.35364688467114</v>
+        <v>31.35364688467107</v>
       </c>
       <c r="H6" t="n">
-        <v>50.01873037362041</v>
+        <v>50.01873037362046</v>
       </c>
       <c r="I6" t="n">
-        <v>29.68869026529313</v>
+        <v>42.64569557900479</v>
       </c>
       <c r="J6" t="n">
-        <v>45.78537702103599</v>
+        <v>34.06172808994929</v>
       </c>
       <c r="K6" t="n">
         <v>30.54625407699038</v>
       </c>
       <c r="L6" t="n">
-        <v>32.68255806079313</v>
+        <v>32.6825580607931</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.62761621631744</v>
+        <v>15.62761621631745</v>
       </c>
       <c r="C7" t="n">
-        <v>15.61076398227569</v>
+        <v>15.61076398227571</v>
       </c>
       <c r="D7" t="n">
-        <v>19.40027831086265</v>
+        <v>19.40027831086267</v>
       </c>
       <c r="E7" t="n">
-        <v>15.86240819788552</v>
+        <v>15.86240819788551</v>
       </c>
       <c r="F7" t="n">
-        <v>15.86240819788552</v>
+        <v>15.86240819788551</v>
       </c>
       <c r="G7" t="n">
         <v>17.51433374201406</v>
       </c>
       <c r="H7" t="n">
-        <v>23.27887833725916</v>
+        <v>23.27887833725919</v>
       </c>
       <c r="I7" t="n">
-        <v>15.84937712263607</v>
+        <v>15.84937712263606</v>
       </c>
       <c r="J7" t="n">
         <v>19.23932795227005</v>
       </c>
       <c r="K7" t="n">
-        <v>16.7246400341765</v>
+        <v>16.72464003417652</v>
       </c>
       <c r="L7" t="n">
-        <v>18.82345090914323</v>
+        <v>18.82345090914325</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.44403026382151</v>
+        <v>28.44403026382155</v>
       </c>
       <c r="C8" t="n">
-        <v>39.83398830343178</v>
+        <v>39.8339883034747</v>
       </c>
       <c r="D8" t="n">
-        <v>45.97176313611698</v>
+        <v>45.97176313611708</v>
       </c>
       <c r="E8" t="n">
-        <v>36.95595804366043</v>
+        <v>36.9559580436605</v>
       </c>
       <c r="F8" t="n">
         <v>29.03500051788419</v>
       </c>
       <c r="G8" t="n">
-        <v>41.72340755826698</v>
+        <v>41.72340755826703</v>
       </c>
       <c r="H8" t="n">
-        <v>47.48795215352101</v>
+        <v>47.48795215352106</v>
       </c>
       <c r="I8" t="n">
-        <v>40.058450938889</v>
+        <v>40.05845093888902</v>
       </c>
       <c r="J8" t="n">
-        <v>43.45064075341238</v>
+        <v>43.45064075341242</v>
       </c>
       <c r="K8" t="n">
-        <v>29.32942957738923</v>
+        <v>29.32942957738926</v>
       </c>
       <c r="L8" t="n">
-        <v>54.93311049339032</v>
+        <v>54.93311049339042</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.30907486907538</v>
+        <v>25.30907486907536</v>
       </c>
       <c r="C9" t="n">
-        <v>29.38393017089331</v>
+        <v>29.3839301708933</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17351361475862</v>
+        <v>33.17351361475861</v>
       </c>
       <c r="E9" t="n">
-        <v>34.34494071698674</v>
+        <v>34.34494071698673</v>
       </c>
       <c r="F9" t="n">
-        <v>29.62319733649217</v>
+        <v>29.6231973364921</v>
       </c>
       <c r="G9" t="n">
-        <v>31.28749993063168</v>
+        <v>31.28749993063165</v>
       </c>
       <c r="H9" t="n">
-        <v>37.05204452587679</v>
+        <v>37.05204452587684</v>
       </c>
       <c r="I9" t="n">
-        <v>29.6225433112537</v>
+        <v>29.62254331125367</v>
       </c>
       <c r="J9" t="n">
-        <v>33.01249414088765</v>
+        <v>33.01249414088764</v>
       </c>
       <c r="K9" t="n">
-        <v>25.34561598352429</v>
+        <v>28.12705494412864</v>
       </c>
       <c r="L9" t="n">
-        <v>32.59661709776081</v>
+        <v>32.59661709776088</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.43248609858527</v>
+        <v>19.52807632340071</v>
       </c>
       <c r="C2" t="n">
-        <v>7.559886111600817</v>
+        <v>11.01621779875996</v>
       </c>
       <c r="D2" t="n">
-        <v>17.67912876207943</v>
+        <v>19.54105663690872</v>
       </c>
       <c r="E2" t="n">
-        <v>8.944542262518056</v>
+        <v>11.9969788500949</v>
       </c>
       <c r="F2" t="n">
-        <v>8.944542262518056</v>
+        <v>11.99964955885747</v>
       </c>
       <c r="G2" t="n">
-        <v>17.71101695590133</v>
+        <v>19.54273484921445</v>
       </c>
       <c r="H2" t="n">
-        <v>18.3836709904005</v>
+        <v>19.43979986157747</v>
       </c>
       <c r="I2" t="n">
-        <v>17.85829861722607</v>
+        <v>19.55043220838668</v>
       </c>
       <c r="J2" t="n">
-        <v>17.77106920602612</v>
+        <v>18.33454966772516</v>
       </c>
       <c r="K2" t="n">
-        <v>28.56767056241978</v>
+        <v>28.76486564580422</v>
       </c>
       <c r="L2" t="n">
-        <v>17.90690032277328</v>
+        <v>19.55064524643202</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.10589334895252</v>
+        <v>20.8116795056088</v>
       </c>
       <c r="C3" t="n">
-        <v>9.259858839394523</v>
+        <v>6.924915798989034</v>
       </c>
       <c r="D3" t="n">
-        <v>19.38958350384462</v>
+        <v>20.91746885047202</v>
       </c>
       <c r="E3" t="n">
-        <v>10.68175609630934</v>
+        <v>8.603963430382638</v>
       </c>
       <c r="F3" t="n">
-        <v>10.68175609630934</v>
+        <v>8.606634139145093</v>
       </c>
       <c r="G3" t="n">
-        <v>19.42626153235946</v>
+        <v>20.9302508245319</v>
       </c>
       <c r="H3" t="n">
-        <v>20.20612242676112</v>
+        <v>21.04974177921935</v>
       </c>
       <c r="I3" t="n">
-        <v>19.59301646828468</v>
+        <v>20.98463150388143</v>
       </c>
       <c r="J3" t="n">
-        <v>19.72868419059967</v>
+        <v>19.40316790080638</v>
       </c>
       <c r="K3" t="n">
-        <v>30.24720334433256</v>
+        <v>36.08390737492303</v>
       </c>
       <c r="L3" t="n">
-        <v>19.65169959902234</v>
+        <v>21.00699640222982</v>
       </c>
     </row>
     <row r="4">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.92042500953844</v>
+        <v>10.92042500953845</v>
       </c>
       <c r="C4" t="n">
-        <v>10.87380154404424</v>
+        <v>10.87380154404425</v>
       </c>
       <c r="D4" t="n">
-        <v>11.06704362184949</v>
+        <v>11.06704362184948</v>
       </c>
       <c r="E4" t="n">
         <v>10.97857615579879</v>
@@ -2986,19 +2986,19 @@
         <v>10.97857615579879</v>
       </c>
       <c r="G4" t="n">
-        <v>11.05871419312323</v>
+        <v>11.05871419312322</v>
       </c>
       <c r="H4" t="n">
-        <v>11.48616336013444</v>
+        <v>11.48616336013446</v>
       </c>
       <c r="I4" t="n">
-        <v>10.99990694035014</v>
+        <v>10.99990694035013</v>
       </c>
       <c r="J4" t="n">
-        <v>12.04520139857359</v>
+        <v>12.0452013985736</v>
       </c>
       <c r="K4" t="n">
-        <v>10.94466732395597</v>
+        <v>10.94466732395596</v>
       </c>
       <c r="L4" t="n">
         <v>11.20317599678788</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.18407475905267</v>
+        <v>23.18407475905268</v>
       </c>
       <c r="C5" t="n">
-        <v>32.63085958337757</v>
+        <v>32.63085958337756</v>
       </c>
       <c r="D5" t="n">
         <v>32.59098870418148</v>
       </c>
       <c r="E5" t="n">
-        <v>34.42017834672859</v>
+        <v>34.42017834672865</v>
       </c>
       <c r="F5" t="n">
-        <v>34.42017834672859</v>
+        <v>34.42017834672865</v>
       </c>
       <c r="G5" t="n">
-        <v>33.31588056071493</v>
+        <v>33.31588056071477</v>
       </c>
       <c r="H5" t="n">
-        <v>43.01653736381152</v>
+        <v>43.01653736381142</v>
       </c>
       <c r="I5" t="n">
-        <v>34.41989079488157</v>
+        <v>34.41989079488223</v>
       </c>
       <c r="J5" t="n">
-        <v>51.00780205244429</v>
+        <v>51.0078020524443</v>
       </c>
       <c r="K5" t="n">
-        <v>30.57844004073051</v>
+        <v>30.57844004073045</v>
       </c>
       <c r="L5" t="n">
-        <v>38.09536290029484</v>
+        <v>38.09536290029487</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.18058475885094</v>
+        <v>28.180584758851</v>
       </c>
       <c r="C6" t="n">
         <v>28.23145811065088</v>
       </c>
       <c r="D6" t="n">
-        <v>28.31274727131364</v>
+        <v>40.26432362076403</v>
       </c>
       <c r="E6" t="n">
-        <v>26.54988902156996</v>
+        <v>26.54988902156994</v>
       </c>
       <c r="F6" t="n">
-        <v>28.26513224799422</v>
+        <v>28.26513224799425</v>
       </c>
       <c r="G6" t="n">
-        <v>40.45973893374633</v>
+        <v>28.31887394243562</v>
       </c>
       <c r="H6" t="n">
-        <v>40.90794869882151</v>
+        <v>40.90794869882152</v>
       </c>
       <c r="I6" t="n">
         <v>40.40093168097327</v>
       </c>
       <c r="J6" t="n">
-        <v>30.21780280523482</v>
+        <v>41.21317226111232</v>
       </c>
       <c r="K6" t="n">
-        <v>28.18963538758034</v>
+        <v>28.18963538758036</v>
       </c>
       <c r="L6" t="n">
         <v>28.46578359589996</v>
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.98644432219432</v>
+        <v>14.98644432219431</v>
       </c>
       <c r="C7" t="n">
         <v>15.08685787708934</v>
       </c>
       <c r="D7" t="n">
-        <v>15.13300131014965</v>
+        <v>15.13300131014964</v>
       </c>
       <c r="E7" t="n">
         <v>15.08209893039129</v>
@@ -3106,16 +3106,16 @@
         <v>15.08209893039129</v>
       </c>
       <c r="G7" t="n">
-        <v>15.12473350577909</v>
+        <v>15.12473350577911</v>
       </c>
       <c r="H7" t="n">
-        <v>15.5521826727903</v>
+        <v>15.55218267279029</v>
       </c>
       <c r="I7" t="n">
         <v>15.065926253006</v>
       </c>
       <c r="J7" t="n">
-        <v>16.11122071122946</v>
+        <v>16.11122071122947</v>
       </c>
       <c r="K7" t="n">
         <v>15.01068663661183</v>
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.04788908359488</v>
+        <v>27.04788908359486</v>
       </c>
       <c r="C8" t="n">
-        <v>37.79063917737989</v>
+        <v>37.79063917732651</v>
       </c>
       <c r="D8" t="n">
-        <v>40.02265135474568</v>
+        <v>40.02265135474569</v>
       </c>
       <c r="E8" t="n">
-        <v>34.862305127754</v>
+        <v>34.86230512775392</v>
       </c>
       <c r="F8" t="n">
-        <v>27.47396716316288</v>
+        <v>27.47396716316284</v>
       </c>
       <c r="G8" t="n">
         <v>37.81116227632462</v>
       </c>
       <c r="H8" t="n">
-        <v>38.23861144336499</v>
+        <v>38.23861144336496</v>
       </c>
       <c r="I8" t="n">
-        <v>37.75235502355154</v>
+        <v>37.75235502355157</v>
       </c>
       <c r="J8" t="n">
-        <v>38.79973759625565</v>
+        <v>38.79973759625567</v>
       </c>
       <c r="K8" t="n">
-        <v>26.87476686507641</v>
+        <v>26.87476686507637</v>
       </c>
       <c r="L8" t="n">
-        <v>49.05430832502689</v>
+        <v>49.05430832502686</v>
       </c>
     </row>
     <row r="9">
@@ -3174,34 +3174,34 @@
         <v>22.91409311491329</v>
       </c>
       <c r="C9" t="n">
-        <v>26.49584546387149</v>
+        <v>26.49584546387145</v>
       </c>
       <c r="D9" t="n">
         <v>26.54205155201554</v>
       </c>
       <c r="E9" t="n">
-        <v>30.4925924334142</v>
+        <v>30.49259243341418</v>
       </c>
       <c r="F9" t="n">
-        <v>26.47520055801575</v>
+        <v>26.47520055801578</v>
       </c>
       <c r="G9" t="n">
-        <v>26.53372109256124</v>
+        <v>26.53372109256125</v>
       </c>
       <c r="H9" t="n">
-        <v>26.96117025957248</v>
+        <v>26.96117025957246</v>
       </c>
       <c r="I9" t="n">
-        <v>26.47491383978814</v>
+        <v>26.47491383978817</v>
       </c>
       <c r="J9" t="n">
-        <v>27.52020829801162</v>
+        <v>27.5202082980116</v>
       </c>
       <c r="K9" t="n">
-        <v>22.0360469977512</v>
+        <v>24.40257328736297</v>
       </c>
       <c r="L9" t="n">
-        <v>26.67818289622591</v>
+        <v>26.67818289622589</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.96223545333388</v>
+        <v>19.37675710157454</v>
       </c>
       <c r="C2" t="n">
-        <v>7.265124000711545</v>
+        <v>10.98868055599395</v>
       </c>
       <c r="D2" t="n">
-        <v>17.42482160244249</v>
+        <v>19.40110209183203</v>
       </c>
       <c r="E2" t="n">
-        <v>8.509649667395923</v>
+        <v>11.95688192274636</v>
       </c>
       <c r="F2" t="n">
-        <v>8.509649667395923</v>
+        <v>11.95955350164048</v>
       </c>
       <c r="G2" t="n">
-        <v>17.20966768896324</v>
+        <v>19.38977896869572</v>
       </c>
       <c r="H2" t="n">
-        <v>17.53891035908639</v>
+        <v>19.26865237112307</v>
       </c>
       <c r="I2" t="n">
-        <v>17.28315403267037</v>
+        <v>19.39359253859909</v>
       </c>
       <c r="J2" t="n">
-        <v>16.25857710159265</v>
+        <v>18.24968285431498</v>
       </c>
       <c r="K2" t="n">
-        <v>28.3132728177203</v>
+        <v>28.81566543888131</v>
       </c>
       <c r="L2" t="n">
-        <v>17.05507538134657</v>
+        <v>19.37902805949554</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.59625566185691</v>
+        <v>20.46669277033244</v>
       </c>
       <c r="C3" t="n">
-        <v>8.929915927300719</v>
+        <v>6.792468632126342</v>
       </c>
       <c r="D3" t="n">
-        <v>19.12832555776392</v>
+        <v>20.65359580916553</v>
       </c>
       <c r="E3" t="n">
-        <v>10.19172038779356</v>
+        <v>8.412463753634048</v>
       </c>
       <c r="F3" t="n">
-        <v>10.19172038779356</v>
+        <v>8.415135332528177</v>
       </c>
       <c r="G3" t="n">
-        <v>18.88085398826389</v>
+        <v>20.57360056473631</v>
       </c>
       <c r="H3" t="n">
-        <v>19.2654283329871</v>
+        <v>20.56283566155844</v>
       </c>
       <c r="I3" t="n">
-        <v>18.96278859666499</v>
+        <v>20.60042647528935</v>
       </c>
       <c r="J3" t="n">
-        <v>17.99688536759028</v>
+        <v>18.82168061618171</v>
       </c>
       <c r="K3" t="n">
-        <v>29.94909392185423</v>
+        <v>36.06441376431807</v>
       </c>
       <c r="L3" t="n">
-        <v>18.70318167614126</v>
+        <v>20.51703730684776</v>
       </c>
     </row>
     <row r="4">
@@ -3367,34 +3367,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.76128574145095</v>
+        <v>10.76128574145102</v>
       </c>
       <c r="C4" t="n">
-        <v>10.73140975659138</v>
+        <v>10.73140975659139</v>
       </c>
       <c r="D4" t="n">
-        <v>11.03627360565813</v>
+        <v>11.03627360565819</v>
       </c>
       <c r="E4" t="n">
-        <v>10.74812049821019</v>
+        <v>10.74812049821022</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7481204982102</v>
+        <v>10.74812049821022</v>
       </c>
       <c r="G4" t="n">
-        <v>10.88101477326443</v>
+        <v>10.88101477326482</v>
       </c>
       <c r="H4" t="n">
-        <v>11.1044750361726</v>
+        <v>11.10447503617258</v>
       </c>
       <c r="I4" t="n">
-        <v>10.77796075958916</v>
+        <v>10.77796075958892</v>
       </c>
       <c r="J4" t="n">
-        <v>11.17401463861965</v>
+        <v>11.17401463861972</v>
       </c>
       <c r="K4" t="n">
-        <v>10.76841293968822</v>
+        <v>10.76841293968825</v>
       </c>
       <c r="L4" t="n">
         <v>10.8172781681813</v>
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.11294781537884</v>
+        <v>20.11294781538329</v>
       </c>
       <c r="C5" t="n">
-        <v>29.87333177658044</v>
+        <v>29.87333177658015</v>
       </c>
       <c r="D5" t="n">
-        <v>31.79206103538762</v>
+        <v>31.79206103538765</v>
       </c>
       <c r="E5" t="n">
-        <v>30.33975769530326</v>
+        <v>30.33975769530342</v>
       </c>
       <c r="F5" t="n">
-        <v>30.33975769530326</v>
+        <v>30.33975769530342</v>
       </c>
       <c r="G5" t="n">
-        <v>29.92672249757113</v>
+        <v>29.92672249757117</v>
       </c>
       <c r="H5" t="n">
-        <v>35.39996014407034</v>
+        <v>35.39996014407038</v>
       </c>
       <c r="I5" t="n">
-        <v>30.33945999362205</v>
+        <v>30.33945999362223</v>
       </c>
       <c r="J5" t="n">
-        <v>35.16635757400358</v>
+        <v>35.16635757400347</v>
       </c>
       <c r="K5" t="n">
-        <v>27.29360694193645</v>
+        <v>27.2936069419365</v>
       </c>
       <c r="L5" t="n">
-        <v>30.25084949516999</v>
+        <v>30.25084949517007</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.17730270372422</v>
+        <v>40.17730270372427</v>
       </c>
       <c r="C6" t="n">
-        <v>28.08946135893774</v>
+        <v>28.08946135893775</v>
       </c>
       <c r="D6" t="n">
-        <v>28.28471896284614</v>
+        <v>28.28471896284615</v>
       </c>
       <c r="E6" t="n">
-        <v>26.32309796028757</v>
+        <v>26.3230979602876</v>
       </c>
       <c r="F6" t="n">
-        <v>28.04160879141894</v>
+        <v>28.04160879141897</v>
       </c>
       <c r="G6" t="n">
-        <v>40.29703173553717</v>
+        <v>40.29703173553723</v>
       </c>
       <c r="H6" t="n">
-        <v>40.55694906374291</v>
+        <v>28.3669967614148</v>
       </c>
       <c r="I6" t="n">
-        <v>28.03733428997176</v>
+        <v>40.19397772186233</v>
       </c>
       <c r="J6" t="n">
-        <v>40.35935755197219</v>
+        <v>29.34319799990635</v>
       </c>
       <c r="K6" t="n">
-        <v>28.01297468063352</v>
+        <v>28.01297468063196</v>
       </c>
       <c r="L6" t="n">
-        <v>28.077880595181</v>
+        <v>28.07788059518105</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.79531184970612</v>
+        <v>14.79531184970608</v>
       </c>
       <c r="C7" t="n">
         <v>14.9128356855784</v>
       </c>
       <c r="D7" t="n">
-        <v>15.0702361450914</v>
+        <v>15.07023614509142</v>
       </c>
       <c r="E7" t="n">
-        <v>14.82663509836952</v>
+        <v>14.82663509836955</v>
       </c>
       <c r="F7" t="n">
-        <v>14.82663509836952</v>
+        <v>14.82663509836955</v>
       </c>
       <c r="G7" t="n">
-        <v>14.91504088151918</v>
+        <v>14.91504088151923</v>
       </c>
       <c r="H7" t="n">
-        <v>15.13850114442775</v>
+        <v>15.13850114442776</v>
       </c>
       <c r="I7" t="n">
-        <v>14.8119868678442</v>
+        <v>14.81198686784422</v>
       </c>
       <c r="J7" t="n">
-        <v>15.20804074687481</v>
+        <v>15.20804074687484</v>
       </c>
       <c r="K7" t="n">
-        <v>14.80243904794338</v>
+        <v>14.80243904794337</v>
       </c>
       <c r="L7" t="n">
-        <v>14.85130427643646</v>
+        <v>14.85130427643644</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.85937698546856</v>
+        <v>26.85937698546847</v>
       </c>
       <c r="C8" t="n">
-        <v>37.605949371529</v>
+        <v>37.60594937159414</v>
       </c>
       <c r="D8" t="n">
-        <v>39.94822903473322</v>
+        <v>39.9482290347332</v>
       </c>
       <c r="E8" t="n">
-        <v>34.60109164976974</v>
+        <v>34.60109164976977</v>
       </c>
       <c r="F8" t="n">
-        <v>27.22136910148872</v>
+        <v>27.22136910148874</v>
       </c>
       <c r="G8" t="n">
-        <v>37.59226296989125</v>
+        <v>37.59226296989131</v>
       </c>
       <c r="H8" t="n">
-        <v>37.81572323283032</v>
+        <v>37.81572323283039</v>
       </c>
       <c r="I8" t="n">
-        <v>37.48920895621629</v>
+        <v>37.48920895621627</v>
       </c>
       <c r="J8" t="n">
-        <v>37.88734862506076</v>
+        <v>37.88734862506079</v>
       </c>
       <c r="K8" t="n">
-        <v>26.66935934443499</v>
+        <v>26.669359344435</v>
       </c>
       <c r="L8" t="n">
-        <v>48.61485626006305</v>
+        <v>48.61485626006304</v>
       </c>
     </row>
     <row r="9">
@@ -3570,34 +3570,34 @@
         <v>22.13981190760015</v>
       </c>
       <c r="C9" t="n">
-        <v>25.57152932074015</v>
+        <v>25.5715293207402</v>
       </c>
       <c r="D9" t="n">
-        <v>25.72899440721316</v>
+        <v>25.72899440721315</v>
       </c>
       <c r="E9" t="n">
-        <v>29.29548732600954</v>
+        <v>29.29548732600957</v>
       </c>
       <c r="F9" t="n">
-        <v>25.47097744378466</v>
+        <v>25.4709774437847</v>
       </c>
       <c r="G9" t="n">
-        <v>25.57373451668094</v>
+        <v>25.57373451668099</v>
       </c>
       <c r="H9" t="n">
-        <v>25.79719477958951</v>
+        <v>25.7971947795896</v>
       </c>
       <c r="I9" t="n">
-        <v>25.47068050300594</v>
+        <v>25.47068050300599</v>
       </c>
       <c r="J9" t="n">
-        <v>25.86673438203658</v>
+        <v>25.86673438203659</v>
       </c>
       <c r="K9" t="n">
-        <v>23.46296908577935</v>
+        <v>23.54087635364395</v>
       </c>
       <c r="L9" t="n">
-        <v>25.5099979115982</v>
+        <v>25.50999791159825</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.00280690507511</v>
+        <v>19.90093192478811</v>
       </c>
       <c r="C2" t="n">
-        <v>7.75618296469872</v>
+        <v>11.10977952219823</v>
       </c>
       <c r="D2" t="n">
-        <v>18.91747302047918</v>
+        <v>19.94906898576908</v>
       </c>
       <c r="E2" t="n">
-        <v>9.322454911150013</v>
+        <v>12.08453060828772</v>
       </c>
       <c r="F2" t="n">
-        <v>9.322454911150031</v>
+        <v>12.08720156850737</v>
       </c>
       <c r="G2" t="n">
-        <v>19.0970006933149</v>
+        <v>19.95851717061973</v>
       </c>
       <c r="H2" t="n">
-        <v>28.52315829907204</v>
+        <v>20.32106229559304</v>
       </c>
       <c r="I2" t="n">
-        <v>18.58924952600096</v>
+        <v>19.93173426639352</v>
       </c>
       <c r="J2" t="n">
-        <v>17.00820384684166</v>
+        <v>18.35578894502712</v>
       </c>
       <c r="K2" t="n">
-        <v>29.23443469273317</v>
+        <v>28.85222759050203</v>
       </c>
       <c r="L2" t="n">
-        <v>22.25181081168975</v>
+        <v>20.12415928337437</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.71016699538809</v>
+        <v>21.41504682205348</v>
       </c>
       <c r="C3" t="n">
-        <v>9.483960249717146</v>
+        <v>7.055764333819901</v>
       </c>
       <c r="D3" t="n">
-        <v>20.76222250061772</v>
+        <v>21.77113248901863</v>
       </c>
       <c r="E3" t="n">
-        <v>11.11772886309319</v>
+        <v>8.782572702084408</v>
       </c>
       <c r="F3" t="n">
-        <v>11.11772886309299</v>
+        <v>8.785243662303929</v>
       </c>
       <c r="G3" t="n">
-        <v>20.96871651342423</v>
+        <v>21.83979963268636</v>
       </c>
       <c r="H3" t="n">
-        <v>31.81700201152042</v>
+        <v>25.26734192212595</v>
       </c>
       <c r="I3" t="n">
-        <v>20.38142957900731</v>
+        <v>21.6481257173708</v>
       </c>
       <c r="J3" t="n">
-        <v>18.8537359473336</v>
+        <v>19.14530058546322</v>
       </c>
       <c r="K3" t="n">
-        <v>31.01838122025655</v>
+        <v>36.35104652332012</v>
       </c>
       <c r="L3" t="n">
-        <v>24.59737751606495</v>
+        <v>23.03805963516994</v>
       </c>
     </row>
     <row r="4">
@@ -3763,13 +3763,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.06314064034084</v>
+        <v>11.06314064034811</v>
       </c>
       <c r="C4" t="n">
         <v>10.9869036537896</v>
       </c>
       <c r="D4" t="n">
-        <v>11.60687088825926</v>
+        <v>11.60687088826422</v>
       </c>
       <c r="E4" t="n">
         <v>11.20820207477771</v>
@@ -3778,22 +3778,22 @@
         <v>11.20820207477771</v>
       </c>
       <c r="G4" t="n">
-        <v>11.68609454030936</v>
+        <v>11.6860945403133</v>
       </c>
       <c r="H4" t="n">
-        <v>17.31531565167111</v>
+        <v>17.31531565167621</v>
       </c>
       <c r="I4" t="n">
         <v>11.23654046588353</v>
       </c>
       <c r="J4" t="n">
-        <v>11.60996817516649</v>
+        <v>11.6099681751716</v>
       </c>
       <c r="K4" t="n">
-        <v>11.36623800866454</v>
+        <v>11.36623800866628</v>
       </c>
       <c r="L4" t="n">
-        <v>13.58907606187588</v>
+        <v>13.58907606187763</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.75655266784622</v>
+        <v>25.75655266784671</v>
       </c>
       <c r="C5" t="n">
-        <v>35.26876877920774</v>
+        <v>35.2687687792077</v>
       </c>
       <c r="D5" t="n">
-        <v>42.73428718419889</v>
+        <v>42.73428718420506</v>
       </c>
       <c r="E5" t="n">
-        <v>39.30435767000918</v>
+        <v>39.30435767000875</v>
       </c>
       <c r="F5" t="n">
-        <v>39.30435767000918</v>
+        <v>39.30435767000876</v>
       </c>
       <c r="G5" t="n">
-        <v>45.36933979471218</v>
+        <v>45.3693397947145</v>
       </c>
       <c r="H5" t="n">
-        <v>161.431590526182</v>
+        <v>161.4315905261934</v>
       </c>
       <c r="I5" t="n">
-        <v>39.3039801276475</v>
+        <v>39.30398012764726</v>
       </c>
       <c r="J5" t="n">
-        <v>44.24954151197193</v>
+        <v>44.24954151197711</v>
       </c>
       <c r="K5" t="n">
-        <v>38.52775948165961</v>
+        <v>38.52775948165881</v>
       </c>
       <c r="L5" t="n">
-        <v>87.7705459032384</v>
+        <v>87.77054590324855</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.30063751602294</v>
+        <v>29.30063751603163</v>
       </c>
       <c r="C6" t="n">
-        <v>29.31342371989141</v>
+        <v>29.31342371989138</v>
       </c>
       <c r="D6" t="n">
-        <v>29.8329218740829</v>
+        <v>29.83292187408406</v>
       </c>
       <c r="E6" t="n">
-        <v>27.66017337090459</v>
+        <v>27.66017337090457</v>
       </c>
       <c r="F6" t="n">
-        <v>29.47862532057045</v>
+        <v>29.47862532057047</v>
       </c>
       <c r="G6" t="n">
-        <v>42.78600087427105</v>
+        <v>29.92359141599618</v>
       </c>
       <c r="H6" t="n">
-        <v>48.34820416427043</v>
+        <v>48.34820416426715</v>
       </c>
       <c r="I6" t="n">
-        <v>42.33644679983965</v>
+        <v>29.47403734156907</v>
       </c>
       <c r="J6" t="n">
-        <v>42.45180141122451</v>
+        <v>30.80832591334311</v>
       </c>
       <c r="K6" t="n">
-        <v>29.5872134544694</v>
+        <v>29.58721345446955</v>
       </c>
       <c r="L6" t="n">
-        <v>31.8423648293161</v>
+        <v>31.8423648293157</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.39723981572367</v>
+        <v>15.39723981572454</v>
       </c>
       <c r="C7" t="n">
         <v>15.47254874229979</v>
       </c>
       <c r="D7" t="n">
-        <v>15.94090207526945</v>
+        <v>15.94090207526595</v>
       </c>
       <c r="E7" t="n">
-        <v>15.5857141695472</v>
+        <v>15.58571416954721</v>
       </c>
       <c r="F7" t="n">
-        <v>15.5857141695472</v>
+        <v>15.58571416954721</v>
       </c>
       <c r="G7" t="n">
-        <v>16.02019371568953</v>
+        <v>16.02019371569373</v>
       </c>
       <c r="H7" t="n">
-        <v>21.64941482704858</v>
+        <v>21.64941482705396</v>
       </c>
       <c r="I7" t="n">
-        <v>15.57063964126247</v>
+        <v>15.57063964126246</v>
       </c>
       <c r="J7" t="n">
-        <v>15.94406735055201</v>
+        <v>15.9440673505547</v>
       </c>
       <c r="K7" t="n">
-        <v>15.7003371840421</v>
+        <v>15.70033718404269</v>
       </c>
       <c r="L7" t="n">
-        <v>17.92317523726004</v>
+        <v>17.92317523726074</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.12676085950498</v>
+        <v>28.12676085950223</v>
       </c>
       <c r="C8" t="n">
-        <v>39.45986854363689</v>
+        <v>39.45986854359447</v>
       </c>
       <c r="D8" t="n">
-        <v>42.24294008711676</v>
+        <v>42.24294008712099</v>
       </c>
       <c r="E8" t="n">
-        <v>36.48215785220758</v>
+        <v>36.48215785220756</v>
       </c>
       <c r="F8" t="n">
-        <v>28.665683148972</v>
+        <v>28.66568314897197</v>
       </c>
       <c r="G8" t="n">
-        <v>39.99117394554909</v>
+        <v>39.99117394554985</v>
       </c>
       <c r="H8" t="n">
-        <v>45.62039505692172</v>
+        <v>45.62039505691836</v>
       </c>
       <c r="I8" t="n">
         <v>39.54161987112241</v>
       </c>
       <c r="J8" t="n">
-        <v>39.9172568500374</v>
+        <v>39.91725685005048</v>
       </c>
       <c r="K8" t="n">
-        <v>28.22104235198727</v>
+        <v>28.22104235198262</v>
       </c>
       <c r="L8" t="n">
-        <v>53.63679958331818</v>
+        <v>53.63679958332524</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.66167844578177</v>
+        <v>24.66167844578914</v>
       </c>
       <c r="C9" t="n">
-        <v>28.67158644566963</v>
+        <v>28.67158644566961</v>
       </c>
       <c r="D9" t="n">
-        <v>29.14000766072442</v>
+        <v>29.14000766073294</v>
       </c>
       <c r="E9" t="n">
-        <v>33.31049577058347</v>
+        <v>33.31049577058344</v>
       </c>
       <c r="F9" t="n">
-        <v>28.77005254782692</v>
+        <v>28.77005254782689</v>
       </c>
       <c r="G9" t="n">
-        <v>29.21923141905683</v>
+        <v>29.21923141906276</v>
       </c>
       <c r="H9" t="n">
-        <v>34.84845253041991</v>
+        <v>34.84845253042695</v>
       </c>
       <c r="I9" t="n">
-        <v>28.76967734463234</v>
+        <v>28.76967734463233</v>
       </c>
       <c r="J9" t="n">
-        <v>29.14310505391926</v>
+        <v>29.14310505392371</v>
       </c>
       <c r="K9" t="n">
-        <v>26.61965268727639</v>
+        <v>26.6196526872826</v>
       </c>
       <c r="L9" t="n">
-        <v>31.1222129406273</v>
+        <v>31.12221294063107</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.16558358281909</v>
+        <v>20.11032485115278</v>
       </c>
       <c r="C2" t="n">
-        <v>7.659313807099736</v>
+        <v>11.03000596439337</v>
       </c>
       <c r="D2" t="n">
-        <v>18.34444469563947</v>
+        <v>20.11973795627373</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8735867323329</v>
+        <v>11.97876810862673</v>
       </c>
       <c r="F2" t="n">
-        <v>8.873586732332909</v>
+        <v>11.9814387460544</v>
       </c>
       <c r="G2" t="n">
-        <v>18.21329805848418</v>
+        <v>20.11283596923846</v>
       </c>
       <c r="H2" t="n">
-        <v>18.50276174180118</v>
+        <v>19.98961371602755</v>
       </c>
       <c r="I2" t="n">
-        <v>18.50312639703817</v>
+        <v>20.12803665058977</v>
       </c>
       <c r="J2" t="n">
-        <v>16.46698403545923</v>
+        <v>18.20823030170464</v>
       </c>
       <c r="K2" t="n">
-        <v>28.27722698289299</v>
+        <v>28.58366907336348</v>
       </c>
       <c r="L2" t="n">
-        <v>18.01518769221831</v>
+        <v>20.09974657509543</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.83582359789416</v>
+        <v>21.79245432665959</v>
       </c>
       <c r="C3" t="n">
-        <v>9.364114641844417</v>
+        <v>6.982350694934508</v>
       </c>
       <c r="D3" t="n">
-        <v>20.0415509286055</v>
+        <v>21.87280978011039</v>
       </c>
       <c r="E3" t="n">
-        <v>10.59437851080606</v>
+        <v>8.568120169914854</v>
       </c>
       <c r="F3" t="n">
-        <v>10.59437851080605</v>
+        <v>8.57079080734249</v>
       </c>
       <c r="G3" t="n">
-        <v>19.89070512893285</v>
+        <v>21.82437264049364</v>
       </c>
       <c r="H3" t="n">
-        <v>20.22968632942069</v>
+        <v>21.7988412983038</v>
       </c>
       <c r="I3" t="n">
-        <v>20.22197661123469</v>
+        <v>21.93229204882805</v>
       </c>
       <c r="J3" t="n">
-        <v>18.23127568432174</v>
+        <v>18.84855647149995</v>
       </c>
       <c r="K3" t="n">
-        <v>29.9365404389949</v>
+        <v>35.77175301404463</v>
       </c>
       <c r="L3" t="n">
-        <v>19.66298487024127</v>
+        <v>21.75162359176867</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.90347872154449</v>
+        <v>10.90347872154451</v>
       </c>
       <c r="C4" t="n">
-        <v>10.88872085091362</v>
+        <v>10.88872085091361</v>
       </c>
       <c r="D4" t="n">
-        <v>11.00980407412794</v>
+        <v>11.00980407412796</v>
       </c>
       <c r="E4" t="n">
-        <v>10.92256942430414</v>
+        <v>10.92256942430415</v>
       </c>
       <c r="F4" t="n">
-        <v>10.92256942430414</v>
+        <v>10.92256942430415</v>
       </c>
       <c r="G4" t="n">
-        <v>10.90459925373404</v>
+        <v>10.90459925373396</v>
       </c>
       <c r="H4" t="n">
-        <v>11.10430327003445</v>
+        <v>11.1043032700345</v>
       </c>
       <c r="I4" t="n">
         <v>10.93077379244423</v>
       </c>
       <c r="J4" t="n">
-        <v>11.27569609743596</v>
+        <v>11.27569609743597</v>
       </c>
       <c r="K4" t="n">
-        <v>10.86023593091207</v>
+        <v>10.86023593091204</v>
       </c>
       <c r="L4" t="n">
-        <v>10.81488831728982</v>
+        <v>10.81488831728984</v>
       </c>
     </row>
     <row r="5">
@@ -4205,31 +4205,31 @@
         <v>33.48379701549788</v>
       </c>
       <c r="D5" t="n">
-        <v>32.19445462648666</v>
+        <v>32.19445462648685</v>
       </c>
       <c r="E5" t="n">
-        <v>33.81152664861332</v>
+        <v>33.8115266486134</v>
       </c>
       <c r="F5" t="n">
-        <v>33.81152664861332</v>
+        <v>33.8115266486134</v>
       </c>
       <c r="G5" t="n">
-        <v>31.21467604761579</v>
+        <v>31.21467604761416</v>
       </c>
       <c r="H5" t="n">
-        <v>36.3597597285472</v>
+        <v>36.35975972854758</v>
       </c>
       <c r="I5" t="n">
-        <v>33.81125765163108</v>
+        <v>33.81125765163125</v>
       </c>
       <c r="J5" t="n">
-        <v>37.87790778523667</v>
+        <v>37.87790778523691</v>
       </c>
       <c r="K5" t="n">
-        <v>29.71639031487883</v>
+        <v>29.71639031487891</v>
       </c>
       <c r="L5" t="n">
-        <v>31.18624364557218</v>
+        <v>31.18624364557233</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.16541640120692</v>
+        <v>40.29176191503028</v>
       </c>
       <c r="C6" t="n">
         <v>28.25181977745783</v>
       </c>
       <c r="D6" t="n">
-        <v>28.25889998567764</v>
+        <v>28.25891375284971</v>
       </c>
       <c r="E6" t="n">
-        <v>26.48648636922994</v>
+        <v>26.48648636922995</v>
       </c>
       <c r="F6" t="n">
-        <v>28.1984316102901</v>
+        <v>28.19843161029011</v>
       </c>
       <c r="G6" t="n">
-        <v>28.16653693339648</v>
+        <v>28.16653693339643</v>
       </c>
       <c r="H6" t="n">
-        <v>40.50669207681509</v>
+        <v>40.5066920768151</v>
       </c>
       <c r="I6" t="n">
-        <v>40.31905698593</v>
+        <v>40.31905698593005</v>
       </c>
       <c r="J6" t="n">
-        <v>40.42942360206719</v>
+        <v>29.44512481001751</v>
       </c>
       <c r="K6" t="n">
-        <v>28.10821682319207</v>
+        <v>28.10821682319183</v>
       </c>
       <c r="L6" t="n">
-        <v>28.07721220614434</v>
+        <v>28.07721220614435</v>
       </c>
     </row>
     <row r="7">
@@ -4279,31 +4279,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.91599353893587</v>
+        <v>14.91599353893586</v>
       </c>
       <c r="C7" t="n">
         <v>15.04804536203296</v>
       </c>
       <c r="D7" t="n">
-        <v>15.02225841467917</v>
+        <v>15.02225841467919</v>
       </c>
       <c r="E7" t="n">
-        <v>14.96297027485751</v>
+        <v>14.96297027485748</v>
       </c>
       <c r="F7" t="n">
-        <v>14.96297027485751</v>
+        <v>14.96297027485748</v>
       </c>
       <c r="G7" t="n">
-        <v>14.91711407112542</v>
+        <v>14.91711407112534</v>
       </c>
       <c r="H7" t="n">
-        <v>15.11681808742581</v>
+        <v>15.11681808742584</v>
       </c>
       <c r="I7" t="n">
-        <v>14.94328860983557</v>
+        <v>14.94328860983559</v>
       </c>
       <c r="J7" t="n">
-        <v>15.28821091482735</v>
+        <v>15.28821091482732</v>
       </c>
       <c r="K7" t="n">
         <v>14.87275074830338</v>
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.93036839781985</v>
+        <v>26.9303683978198</v>
       </c>
       <c r="C8" t="n">
-        <v>37.633961360478</v>
+        <v>37.63396136047797</v>
       </c>
       <c r="D8" t="n">
-        <v>39.77531123529609</v>
+        <v>39.77531123529598</v>
       </c>
       <c r="E8" t="n">
-        <v>34.64170920103574</v>
+        <v>34.64170920103568</v>
       </c>
       <c r="F8" t="n">
-        <v>27.30399426981655</v>
+        <v>27.30399426981656</v>
       </c>
       <c r="G8" t="n">
-        <v>37.48232236897967</v>
+        <v>37.48232236897954</v>
       </c>
       <c r="H8" t="n">
-        <v>37.68202638530833</v>
+        <v>37.6820263853083</v>
       </c>
       <c r="I8" t="n">
-        <v>37.50849690768978</v>
+        <v>37.50849690768983</v>
       </c>
       <c r="J8" t="n">
-        <v>37.85549275443921</v>
+        <v>37.85549275443918</v>
       </c>
       <c r="K8" t="n">
-        <v>26.69113845916222</v>
+        <v>26.6911384591622</v>
       </c>
       <c r="L8" t="n">
-        <v>48.41383920664438</v>
+        <v>48.4138392066443</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.8210465684203</v>
+        <v>22.82104656842038</v>
       </c>
       <c r="C9" t="n">
-        <v>26.40893133004327</v>
+        <v>26.40893133004345</v>
       </c>
       <c r="D9" t="n">
-        <v>26.38320589381828</v>
+        <v>26.3832058938184</v>
       </c>
       <c r="E9" t="n">
-        <v>30.29240152352966</v>
+        <v>30.29240152352968</v>
       </c>
       <c r="F9" t="n">
-        <v>26.30444283735484</v>
+        <v>26.30444283735468</v>
       </c>
       <c r="G9" t="n">
-        <v>26.2780000391357</v>
+        <v>26.27800003913577</v>
       </c>
       <c r="H9" t="n">
-        <v>26.47770405543633</v>
+        <v>26.47770405543631</v>
       </c>
       <c r="I9" t="n">
-        <v>26.30417457784613</v>
+        <v>26.30417457784605</v>
       </c>
       <c r="J9" t="n">
-        <v>26.64909688283774</v>
+        <v>26.64909688283777</v>
       </c>
       <c r="K9" t="n">
-        <v>24.23131397464775</v>
+        <v>21.88212591464872</v>
       </c>
       <c r="L9" t="n">
-        <v>26.1882891026918</v>
+        <v>26.18828910269167</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.90210423072633</v>
+        <v>19.34404636412915</v>
       </c>
       <c r="C2" t="n">
-        <v>7.361842444902132</v>
+        <v>11.07215755374452</v>
       </c>
       <c r="D2" t="n">
-        <v>17.29958522145385</v>
+        <v>19.36496499921031</v>
       </c>
       <c r="E2" t="n">
-        <v>8.473548685851123</v>
+        <v>11.98516818007536</v>
       </c>
       <c r="F2" t="n">
-        <v>8.473548685851123</v>
+        <v>11.98783945646363</v>
       </c>
       <c r="G2" t="n">
-        <v>17.09601654566627</v>
+        <v>19.35425158412357</v>
       </c>
       <c r="H2" t="n">
-        <v>17.37479053136389</v>
+        <v>19.23050776837155</v>
       </c>
       <c r="I2" t="n">
-        <v>17.17045260904762</v>
+        <v>19.3581149292535</v>
       </c>
       <c r="J2" t="n">
-        <v>16.22570033219401</v>
+        <v>18.24483377081076</v>
       </c>
       <c r="K2" t="n">
-        <v>28.29881452127473</v>
+        <v>28.76719141453417</v>
       </c>
       <c r="L2" t="n">
-        <v>16.93021755950074</v>
+        <v>19.34289873379101</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.54441145230541</v>
+        <v>20.33935570003002</v>
       </c>
       <c r="C3" t="n">
-        <v>9.037785842367065</v>
+        <v>6.862138065568285</v>
       </c>
       <c r="D3" t="n">
-        <v>19.00159692958123</v>
+        <v>20.50182298848498</v>
       </c>
       <c r="E3" t="n">
-        <v>10.15600940950918</v>
+        <v>8.370640229659921</v>
       </c>
       <c r="F3" t="n">
-        <v>10.15600940950918</v>
+        <v>8.373311506048196</v>
       </c>
       <c r="G3" t="n">
-        <v>18.76745078330137</v>
+        <v>20.42616692964214</v>
       </c>
       <c r="H3" t="n">
-        <v>19.09385509138252</v>
+        <v>20.3963941327429</v>
       </c>
       <c r="I3" t="n">
-        <v>18.8509229223089</v>
+        <v>20.4533494904624</v>
       </c>
       <c r="J3" t="n">
-        <v>17.97129854479952</v>
+        <v>18.73842944739078</v>
       </c>
       <c r="K3" t="n">
-        <v>29.95328266981365</v>
+        <v>35.93089248156518</v>
       </c>
       <c r="L3" t="n">
-        <v>18.57689029542932</v>
+        <v>20.36534315044106</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.74912873126092</v>
+        <v>10.7491287312609</v>
       </c>
       <c r="C4" t="n">
-        <v>10.72938109892805</v>
+        <v>10.72938109892803</v>
       </c>
       <c r="D4" t="n">
-        <v>10.98541433755013</v>
+        <v>10.98541433755011</v>
       </c>
       <c r="E4" t="n">
-        <v>10.71644942521092</v>
+        <v>10.7164494252109</v>
       </c>
       <c r="F4" t="n">
-        <v>10.71644942521093</v>
+        <v>10.7164494252109</v>
       </c>
       <c r="G4" t="n">
-        <v>10.83696104490511</v>
+        <v>10.8369610449051</v>
       </c>
       <c r="H4" t="n">
-        <v>11.03051289005536</v>
+        <v>11.03051289005533</v>
       </c>
       <c r="I4" t="n">
-        <v>10.73399251577885</v>
+        <v>10.73399251577883</v>
       </c>
       <c r="J4" t="n">
-        <v>11.15791165277798</v>
+        <v>11.15791165277797</v>
       </c>
       <c r="K4" t="n">
         <v>10.79725663865734</v>
       </c>
       <c r="L4" t="n">
-        <v>10.76664320286014</v>
+        <v>10.76664320286013</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.58495994291876</v>
+        <v>20.58495994291873</v>
       </c>
       <c r="C5" t="n">
-        <v>30.54152231905384</v>
+        <v>30.54152231905374</v>
       </c>
       <c r="D5" t="n">
-        <v>31.5890523581679</v>
+        <v>31.58905235816781</v>
       </c>
       <c r="E5" t="n">
-        <v>30.26227889041667</v>
+        <v>30.26227889041699</v>
       </c>
       <c r="F5" t="n">
-        <v>30.26227889041667</v>
+        <v>30.26227889041699</v>
       </c>
       <c r="G5" t="n">
         <v>29.83904888918066</v>
       </c>
       <c r="H5" t="n">
-        <v>34.73188288822777</v>
+        <v>34.73188288822769</v>
       </c>
       <c r="I5" t="n">
-        <v>30.26198022088042</v>
+        <v>30.26198022088015</v>
       </c>
       <c r="J5" t="n">
-        <v>35.57467187734276</v>
+        <v>35.57467187734274</v>
       </c>
       <c r="K5" t="n">
         <v>28.45002405257628</v>
       </c>
       <c r="L5" t="n">
-        <v>30.02539363382718</v>
+        <v>30.02539363382716</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.01065432415636</v>
+        <v>40.15003999296067</v>
       </c>
       <c r="C6" t="n">
-        <v>28.09131456758285</v>
+        <v>28.09131456758284</v>
       </c>
       <c r="D6" t="n">
-        <v>28.23555646159821</v>
+        <v>28.23554250436005</v>
       </c>
       <c r="E6" t="n">
-        <v>26.2842141212654</v>
+        <v>26.28421412126537</v>
       </c>
       <c r="F6" t="n">
         <v>28.00039499695692</v>
       </c>
       <c r="G6" t="n">
-        <v>40.23787230660484</v>
+        <v>28.09848663780053</v>
       </c>
       <c r="H6" t="n">
-        <v>40.45843134948197</v>
+        <v>40.45843134948194</v>
       </c>
       <c r="I6" t="n">
-        <v>40.13490377747855</v>
+        <v>27.99551810867425</v>
       </c>
       <c r="J6" t="n">
-        <v>29.32694520894401</v>
+        <v>40.32572738177638</v>
       </c>
       <c r="K6" t="n">
-        <v>28.04585354030138</v>
+        <v>28.04585354030136</v>
       </c>
       <c r="L6" t="n">
-        <v>28.02971369799247</v>
+        <v>28.02971369799253</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.73182580371498</v>
+        <v>14.73182580371499</v>
       </c>
       <c r="C7" t="n">
-        <v>14.86056542157989</v>
+        <v>14.86056542157986</v>
       </c>
       <c r="D7" t="n">
         <v>14.96804873731004</v>
       </c>
       <c r="E7" t="n">
-        <v>14.7349203809067</v>
+        <v>14.73492038090669</v>
       </c>
       <c r="F7" t="n">
-        <v>14.7349203809067</v>
+        <v>14.73492038090669</v>
       </c>
       <c r="G7" t="n">
-        <v>14.81965811735918</v>
+        <v>14.81965811735917</v>
       </c>
       <c r="H7" t="n">
-        <v>15.01320996250945</v>
+        <v>15.01320996250944</v>
       </c>
       <c r="I7" t="n">
-        <v>14.71668958823292</v>
+        <v>14.71668958823291</v>
       </c>
       <c r="J7" t="n">
-        <v>15.14060872523205</v>
+        <v>15.14060872523204</v>
       </c>
       <c r="K7" t="n">
         <v>14.77995371111144</v>
       </c>
       <c r="L7" t="n">
-        <v>14.74934027531422</v>
+        <v>14.74934027531421</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.74321977496995</v>
+        <v>26.74321977496992</v>
       </c>
       <c r="C8" t="n">
-        <v>37.42376574952435</v>
+        <v>37.42376574946056</v>
       </c>
       <c r="D8" t="n">
-        <v>39.69599774486146</v>
+        <v>39.69599774486141</v>
       </c>
       <c r="E8" t="n">
-        <v>34.39757861842189</v>
+        <v>34.39757861842185</v>
       </c>
       <c r="F8" t="n">
-        <v>27.07298124383039</v>
+        <v>27.07298124383041</v>
       </c>
       <c r="G8" t="n">
-        <v>37.36356026821944</v>
+        <v>37.36356026821939</v>
       </c>
       <c r="H8" t="n">
         <v>37.55711211339948</v>
       </c>
       <c r="I8" t="n">
-        <v>37.26059173909314</v>
+        <v>37.2605917390931</v>
       </c>
       <c r="J8" t="n">
-        <v>37.68658081624391</v>
+        <v>37.68658081624395</v>
       </c>
       <c r="K8" t="n">
-        <v>26.59570093544607</v>
+        <v>26.59570093544612</v>
       </c>
       <c r="L8" t="n">
-        <v>48.29532793441186</v>
+        <v>48.29532793441182</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.08558587132748</v>
+        <v>22.08558587132749</v>
       </c>
       <c r="C9" t="n">
-        <v>25.51054380028171</v>
+        <v>25.5105438002817</v>
       </c>
       <c r="D9" t="n">
-        <v>25.61809082833612</v>
+        <v>25.61809082833609</v>
       </c>
       <c r="E9" t="n">
-        <v>29.17073271125181</v>
+        <v>29.17073271125178</v>
       </c>
       <c r="F9" t="n">
-        <v>25.36696591254624</v>
+        <v>25.36696591254617</v>
       </c>
       <c r="G9" t="n">
-        <v>25.46963649606105</v>
+        <v>25.46963649606102</v>
       </c>
       <c r="H9" t="n">
-        <v>25.66318834121125</v>
+        <v>25.66318834121124</v>
       </c>
       <c r="I9" t="n">
-        <v>25.36666796693475</v>
+        <v>25.36666796693472</v>
       </c>
       <c r="J9" t="n">
-        <v>25.79058710393387</v>
+        <v>25.79058710393384</v>
       </c>
       <c r="K9" t="n">
-        <v>23.44260597222068</v>
+        <v>23.44260597222065</v>
       </c>
       <c r="L9" t="n">
-        <v>25.39931865401605</v>
+        <v>25.39931865401602</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.22202273144149</v>
+        <v>21.26846084658009</v>
       </c>
       <c r="C2" t="n">
-        <v>14.88686663001519</v>
+        <v>17.23674337091066</v>
       </c>
       <c r="D2" t="n">
-        <v>38.06552467384174</v>
+        <v>22.15490089991921</v>
       </c>
       <c r="E2" t="n">
-        <v>17.16189048414802</v>
+        <v>19.14182707079213</v>
       </c>
       <c r="F2" t="n">
-        <v>10.73790757197453</v>
+        <v>13.79737629270874</v>
       </c>
       <c r="G2" t="n">
-        <v>27.72633215458442</v>
+        <v>21.61076973292107</v>
       </c>
       <c r="H2" t="n">
-        <v>49.8156235971536</v>
+        <v>22.64442095558955</v>
       </c>
       <c r="I2" t="n">
-        <v>19.44503036511973</v>
+        <v>21.17479969395703</v>
       </c>
       <c r="J2" t="n">
-        <v>30.91909132611946</v>
+        <v>26.9682030028336</v>
       </c>
       <c r="K2" t="n">
-        <v>29.55007318430359</v>
+        <v>27.59002420690042</v>
       </c>
       <c r="L2" t="n">
-        <v>45.67892364775917</v>
+        <v>22.56430859818732</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.91836253961656</v>
+        <v>21.80651848787782</v>
       </c>
       <c r="C3" t="n">
-        <v>17.31178124368953</v>
+        <v>14.74015769332459</v>
       </c>
       <c r="D3" t="n">
-        <v>43.29187889429286</v>
+        <v>28.11584022283081</v>
       </c>
       <c r="E3" t="n">
-        <v>19.59090926467538</v>
+        <v>17.87409803836276</v>
       </c>
       <c r="F3" t="n">
-        <v>13.16692635250189</v>
+        <v>9.050362075061702</v>
       </c>
       <c r="G3" t="n">
-        <v>31.39966573986886</v>
+        <v>24.24937536746134</v>
       </c>
       <c r="H3" t="n">
-        <v>56.81279766558168</v>
+        <v>32.46728661175591</v>
       </c>
       <c r="I3" t="n">
-        <v>21.8640804949745</v>
+        <v>21.14218216517193</v>
       </c>
       <c r="J3" t="n">
-        <v>34.07232818677304</v>
+        <v>32.10128296481924</v>
       </c>
       <c r="K3" t="n">
-        <v>32.36400863091875</v>
+        <v>32.46837721587346</v>
       </c>
       <c r="L3" t="n">
-        <v>52.04819267361167</v>
+        <v>31.07159932849292</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.90159737009897</v>
+        <v>13.90159737009902</v>
       </c>
       <c r="C4" t="n">
-        <v>12.4938324370371</v>
+        <v>12.49383243703709</v>
       </c>
       <c r="D4" t="n">
-        <v>23.91434555513551</v>
+        <v>23.91434555513549</v>
       </c>
       <c r="E4" t="n">
-        <v>12.51809456357247</v>
+        <v>12.51809456357246</v>
       </c>
       <c r="F4" t="n">
-        <v>12.51809456357247</v>
+        <v>12.51809456357246</v>
       </c>
       <c r="G4" t="n">
-        <v>17.73704367576347</v>
+        <v>17.73704367576352</v>
       </c>
       <c r="H4" t="n">
-        <v>30.89465225381552</v>
+        <v>30.8946522538155</v>
       </c>
       <c r="I4" t="n">
-        <v>12.64488123317106</v>
+        <v>12.64488123317105</v>
       </c>
       <c r="J4" t="n">
-        <v>15.70980648968141</v>
+        <v>15.70980648968143</v>
       </c>
       <c r="K4" t="n">
-        <v>14.36699215585446</v>
+        <v>14.36699215585447</v>
       </c>
       <c r="L4" t="n">
-        <v>28.43724860684572</v>
+        <v>28.43724860684571</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.83647008585582</v>
+        <v>74.83647008585677</v>
       </c>
       <c r="C5" t="n">
-        <v>56.93139014483403</v>
+        <v>56.93139014483383</v>
       </c>
       <c r="D5" t="n">
-        <v>254.5656462453659</v>
+        <v>254.5656462453657</v>
       </c>
       <c r="E5" t="n">
-        <v>56.93139837787107</v>
+        <v>56.931398377871</v>
       </c>
       <c r="F5" t="n">
-        <v>56.93139837787107</v>
+        <v>56.931398377871</v>
       </c>
       <c r="G5" t="n">
         <v>147.7918455693687</v>
       </c>
       <c r="H5" t="n">
-        <v>425.1376771181974</v>
+        <v>425.1376771181963</v>
       </c>
       <c r="I5" t="n">
-        <v>56.92995400023992</v>
+        <v>56.92995400023985</v>
       </c>
       <c r="J5" t="n">
         <v>113.4882128210528</v>
       </c>
       <c r="K5" t="n">
-        <v>84.14343077900368</v>
+        <v>84.14343077900409</v>
       </c>
       <c r="L5" t="n">
-        <v>89.97971479185293</v>
+        <v>89.97971479185286</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.32432696065352</v>
+        <v>32.68577226499175</v>
       </c>
       <c r="C6" t="n">
-        <v>31.26893284225446</v>
+        <v>31.26893284225443</v>
       </c>
       <c r="D6" t="n">
-        <v>42.96126694890326</v>
+        <v>42.96127707431575</v>
       </c>
       <c r="E6" t="n">
-        <v>29.45605876144053</v>
+        <v>29.4560587614405</v>
       </c>
       <c r="F6" t="n">
-        <v>31.42269221044058</v>
+        <v>31.42269221044055</v>
       </c>
       <c r="G6" t="n">
-        <v>50.15977326631796</v>
+        <v>36.52121857065616</v>
       </c>
       <c r="H6" t="n">
-        <v>63.10156594348453</v>
+        <v>63.10156594348452</v>
       </c>
       <c r="I6" t="n">
         <v>45.06761082372554</v>
       </c>
       <c r="J6" t="n">
-        <v>47.80778551486678</v>
+        <v>35.50649269171795</v>
       </c>
       <c r="K6" t="n">
-        <v>33.08829105701739</v>
+        <v>33.08829105701733</v>
       </c>
       <c r="L6" t="n">
         <v>47.32078624349898</v>
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.64789815362637</v>
+        <v>18.6478981536264</v>
       </c>
       <c r="C7" t="n">
-        <v>17.39261816129249</v>
+        <v>17.39261816129248</v>
       </c>
       <c r="D7" t="n">
-        <v>28.66055497151207</v>
+        <v>28.66055497151205</v>
       </c>
       <c r="E7" t="n">
-        <v>17.38982130034466</v>
+        <v>17.38982130034464</v>
       </c>
       <c r="F7" t="n">
-        <v>17.38982130034466</v>
+        <v>17.38982130034464</v>
       </c>
       <c r="G7" t="n">
-        <v>22.48334445929085</v>
+        <v>22.4833444592909</v>
       </c>
       <c r="H7" t="n">
-        <v>35.64095303734292</v>
+        <v>35.6409530373429</v>
       </c>
       <c r="I7" t="n">
-        <v>17.39118201669843</v>
+        <v>17.39118201669844</v>
       </c>
       <c r="J7" t="n">
-        <v>20.45610727320881</v>
+        <v>20.45610727320883</v>
       </c>
       <c r="K7" t="n">
         <v>19.11329293938187</v>
       </c>
       <c r="L7" t="n">
-        <v>33.18354939037314</v>
+        <v>33.18354939037307</v>
       </c>
     </row>
     <row r="8">
@@ -5111,28 +5111,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.8086969757158</v>
+        <v>31.80869697571587</v>
       </c>
       <c r="C8" t="n">
-        <v>42.38567465247907</v>
+        <v>42.38567465250941</v>
       </c>
       <c r="D8" t="n">
-        <v>56.10749713395515</v>
+        <v>56.10749713395516</v>
       </c>
       <c r="E8" t="n">
         <v>39.14960854914172</v>
       </c>
       <c r="F8" t="n">
-        <v>30.92687848352671</v>
+        <v>30.92687848352667</v>
       </c>
       <c r="G8" t="n">
-        <v>47.47664826463934</v>
+        <v>47.47664826463939</v>
       </c>
       <c r="H8" t="n">
-        <v>60.63425684269217</v>
+        <v>60.63425684269213</v>
       </c>
       <c r="I8" t="n">
-        <v>42.38448582204693</v>
+        <v>42.38448582204695</v>
       </c>
       <c r="J8" t="n">
         <v>45.45173650564334</v>
@@ -5141,7 +5141,7 @@
         <v>32.05429690652213</v>
       </c>
       <c r="L8" t="n">
-        <v>70.53689406946837</v>
+        <v>70.53689406946825</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.13005202102627</v>
+        <v>30.13005202102629</v>
       </c>
       <c r="C9" t="n">
-        <v>33.56067470153586</v>
+        <v>33.56067470153582</v>
       </c>
       <c r="D9" t="n">
-        <v>44.82870230735061</v>
+        <v>44.8287023073506</v>
       </c>
       <c r="E9" t="n">
         <v>38.96810756403309</v>
       </c>
       <c r="F9" t="n">
-        <v>33.56067718965649</v>
+        <v>33.56067718965645</v>
       </c>
       <c r="G9" t="n">
-        <v>38.6514009995342</v>
+        <v>38.65140099953419</v>
       </c>
       <c r="H9" t="n">
-        <v>51.80900957758628</v>
+        <v>51.80900957758632</v>
       </c>
       <c r="I9" t="n">
-        <v>33.55923855694181</v>
+        <v>33.55923855694178</v>
       </c>
       <c r="J9" t="n">
-        <v>36.62416381345217</v>
+        <v>36.6241638134522</v>
       </c>
       <c r="K9" t="n">
-        <v>32.5663188276275</v>
+        <v>32.56631882762754</v>
       </c>
       <c r="L9" t="n">
-        <v>49.35160593061653</v>
+        <v>49.35160593061647</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.15183370757511</v>
+        <v>21.22973120497483</v>
       </c>
       <c r="C2" t="n">
-        <v>15.74331854512383</v>
+        <v>17.24447916340507</v>
       </c>
       <c r="D2" t="n">
-        <v>36.68984759834039</v>
+        <v>22.04746601506454</v>
       </c>
       <c r="E2" t="n">
-        <v>18.00437206970175</v>
+        <v>19.13762709943478</v>
       </c>
       <c r="F2" t="n">
-        <v>11.61980454946758</v>
+        <v>13.82598426591408</v>
       </c>
       <c r="G2" t="n">
-        <v>27.46882568391494</v>
+        <v>21.56218194613299</v>
       </c>
       <c r="H2" t="n">
-        <v>45.5571300965095</v>
+        <v>22.38306472662305</v>
       </c>
       <c r="I2" t="n">
-        <v>20.30462202478756</v>
+        <v>21.18501337813671</v>
       </c>
       <c r="J2" t="n">
-        <v>28.75728844901692</v>
+        <v>26.75856536255273</v>
       </c>
       <c r="K2" t="n">
-        <v>29.50748524681164</v>
+        <v>27.54286834483264</v>
       </c>
       <c r="L2" t="n">
-        <v>43.63037615323968</v>
+        <v>22.42017611046566</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.8269315645028</v>
+        <v>21.76190860463673</v>
       </c>
       <c r="C3" t="n">
-        <v>18.286730937245</v>
+        <v>15.03700286855412</v>
       </c>
       <c r="D3" t="n">
-        <v>41.69886622876348</v>
+        <v>27.57582760848664</v>
       </c>
       <c r="E3" t="n">
-        <v>20.55183947270312</v>
+        <v>18.15175759423301</v>
       </c>
       <c r="F3" t="n">
-        <v>14.16727195246895</v>
+        <v>9.382177295611424</v>
       </c>
       <c r="G3" t="n">
-        <v>31.09278089823938</v>
+        <v>24.13130076499439</v>
       </c>
       <c r="H3" t="n">
-        <v>51.90361287996942</v>
+        <v>30.84247134535405</v>
       </c>
       <c r="I3" t="n">
-        <v>22.84324546407341</v>
+        <v>21.44363364305852</v>
       </c>
       <c r="J3" t="n">
-        <v>31.58682621935486</v>
+        <v>31.19203200798133</v>
       </c>
       <c r="K3" t="n">
-        <v>32.3062276483547</v>
+        <v>32.41591551551308</v>
       </c>
       <c r="L3" t="n">
-        <v>49.68132472071093</v>
+        <v>30.27975065342601</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.82184935716274</v>
+        <v>13.82184935716277</v>
       </c>
       <c r="C4" t="n">
-        <v>12.9853502045325</v>
+        <v>12.98535020453251</v>
       </c>
       <c r="D4" t="n">
-        <v>23.0585402137235</v>
+        <v>23.05854021372362</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00799533578115</v>
+        <v>13.00799533578116</v>
       </c>
       <c r="F4" t="n">
         <v>13.00799533578115</v>
       </c>
       <c r="G4" t="n">
-        <v>17.54634990332992</v>
+        <v>17.54634990333001</v>
       </c>
       <c r="H4" t="n">
         <v>28.32605818274373</v>
       </c>
       <c r="I4" t="n">
-        <v>13.12072286052128</v>
+        <v>13.12072286052129</v>
       </c>
       <c r="J4" t="n">
-        <v>14.43305850885491</v>
+        <v>14.4330585088549</v>
       </c>
       <c r="K4" t="n">
         <v>14.3111832058872</v>
       </c>
       <c r="L4" t="n">
-        <v>27.18185167642636</v>
+        <v>27.18185167642637</v>
       </c>
     </row>
     <row r="5">
@@ -5387,25 +5387,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.58333848373138</v>
+        <v>70.58333848373144</v>
       </c>
       <c r="C5" t="n">
-        <v>61.91013549340975</v>
+        <v>61.9101354934098</v>
       </c>
       <c r="D5" t="n">
-        <v>222.3955862652639</v>
+        <v>222.3955862652653</v>
       </c>
       <c r="E5" t="n">
-        <v>61.91014373606751</v>
+        <v>61.91014373606745</v>
       </c>
       <c r="F5" t="n">
-        <v>61.91014373606751</v>
+        <v>61.91014373606747</v>
       </c>
       <c r="G5" t="n">
-        <v>135.246001768833</v>
+        <v>135.2460017688338</v>
       </c>
       <c r="H5" t="n">
-        <v>351.368064526312</v>
+        <v>351.3680645263113</v>
       </c>
       <c r="I5" t="n">
         <v>61.90885188296967</v>
@@ -5414,10 +5414,10 @@
         <v>84.96799403716248</v>
       </c>
       <c r="K5" t="n">
-        <v>76.82404866722226</v>
+        <v>76.82404866722241</v>
       </c>
       <c r="L5" t="n">
-        <v>92.33954256526351</v>
+        <v>92.3395425652636</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.01574148260421</v>
+        <v>31.33160252042375</v>
       </c>
       <c r="C6" t="n">
         <v>30.50041412026385</v>
       </c>
       <c r="D6" t="n">
-        <v>40.78891455922489</v>
+        <v>40.78891455922573</v>
       </c>
       <c r="E6" t="n">
-        <v>28.81161231851624</v>
+        <v>28.81161231851625</v>
       </c>
       <c r="F6" t="n">
-        <v>30.62950853668937</v>
+        <v>30.62950853668938</v>
       </c>
       <c r="G6" t="n">
-        <v>47.74024202877133</v>
+        <v>35.05610306659097</v>
       </c>
       <c r="H6" t="n">
         <v>58.31267313822445</v>
       </c>
       <c r="I6" t="n">
-        <v>43.31461498596271</v>
+        <v>43.31461498596269</v>
       </c>
       <c r="J6" t="n">
-        <v>44.32374175715402</v>
+        <v>32.879776890273</v>
       </c>
       <c r="K6" t="n">
-        <v>31.76322943078566</v>
+        <v>31.76322943078568</v>
       </c>
       <c r="L6" t="n">
-        <v>44.77821314368615</v>
+        <v>44.77821314368619</v>
       </c>
     </row>
     <row r="7">
@@ -5470,34 +5470,34 @@
         <v>18.18126655159092</v>
       </c>
       <c r="C7" t="n">
-        <v>17.48142366538961</v>
+        <v>17.48142366538963</v>
       </c>
       <c r="D7" t="n">
-        <v>27.41787275947607</v>
+        <v>27.4178727594762</v>
       </c>
       <c r="E7" t="n">
-        <v>17.47846343024666</v>
+        <v>17.47846343024667</v>
       </c>
       <c r="F7" t="n">
-        <v>17.47846343024666</v>
+        <v>17.47846343024667</v>
       </c>
       <c r="G7" t="n">
-        <v>21.90576709775814</v>
+        <v>21.90576709775818</v>
       </c>
       <c r="H7" t="n">
-        <v>32.68547537717189</v>
+        <v>32.68547537717188</v>
       </c>
       <c r="I7" t="n">
-        <v>17.48014005494943</v>
+        <v>17.48014005494944</v>
       </c>
       <c r="J7" t="n">
-        <v>18.79247570328304</v>
+        <v>18.79247570328307</v>
       </c>
       <c r="K7" t="n">
-        <v>18.67060040031536</v>
+        <v>18.67060040031538</v>
       </c>
       <c r="L7" t="n">
-        <v>31.54126887085452</v>
+        <v>31.54126887085453</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.40858126742102</v>
+        <v>30.40858126742105</v>
       </c>
       <c r="C8" t="n">
-        <v>40.66024135645766</v>
+        <v>40.66024135645776</v>
       </c>
       <c r="D8" t="n">
-        <v>52.86834652911008</v>
+        <v>52.8683465291102</v>
       </c>
       <c r="E8" t="n">
-        <v>37.66499857718618</v>
+        <v>37.66499857718623</v>
       </c>
       <c r="F8" t="n">
-        <v>30.05419054764469</v>
+        <v>30.05419054764472</v>
       </c>
       <c r="G8" t="n">
-        <v>45.08516949226702</v>
+        <v>45.08516949226711</v>
       </c>
       <c r="H8" t="n">
-        <v>55.86487777168217</v>
+        <v>55.8648777716822</v>
       </c>
       <c r="I8" t="n">
-        <v>40.65954244945839</v>
+        <v>40.6595424494584</v>
       </c>
       <c r="J8" t="n">
-        <v>41.97403049759265</v>
+        <v>41.97403049759274</v>
       </c>
       <c r="K8" t="n">
-        <v>30.69447446463963</v>
+        <v>30.69447446463964</v>
       </c>
       <c r="L8" t="n">
-        <v>66.16104264512853</v>
+        <v>66.1610426451286</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.99675350708663</v>
+        <v>27.99675350708672</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39684260957769</v>
+        <v>31.39684260957781</v>
       </c>
       <c r="D9" t="n">
         <v>41.33337627415919</v>
       </c>
       <c r="E9" t="n">
-        <v>36.12807951678116</v>
+        <v>36.12807951678127</v>
       </c>
       <c r="F9" t="n">
-        <v>31.3968461745271</v>
+        <v>31.39684617452713</v>
       </c>
       <c r="G9" t="n">
         <v>35.82118604194631</v>
       </c>
       <c r="H9" t="n">
-        <v>46.60089432135997</v>
+        <v>46.60089432136002</v>
       </c>
       <c r="I9" t="n">
-        <v>31.39555899913755</v>
+        <v>31.39555899913759</v>
       </c>
       <c r="J9" t="n">
-        <v>32.70789464747118</v>
+        <v>32.7078946474712</v>
       </c>
       <c r="K9" t="n">
-        <v>27.42347315573302</v>
+        <v>30.21050261569885</v>
       </c>
       <c r="L9" t="n">
-        <v>45.45668781504268</v>
+        <v>45.45668781504264</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.97345120584451</v>
+        <v>21.14617731975062</v>
       </c>
       <c r="C2" t="n">
-        <v>17.18631145425303</v>
+        <v>17.27914059440026</v>
       </c>
       <c r="D2" t="n">
-        <v>34.01477592236553</v>
+        <v>21.83251633742393</v>
       </c>
       <c r="E2" t="n">
-        <v>19.43778992791539</v>
+        <v>19.16367670255703</v>
       </c>
       <c r="F2" t="n">
-        <v>13.08039035965893</v>
+        <v>13.87464665542704</v>
       </c>
       <c r="G2" t="n">
-        <v>26.37413228691452</v>
+        <v>21.43040443843071</v>
       </c>
       <c r="H2" t="n">
-        <v>40.84476137017104</v>
+        <v>22.05913282498583</v>
       </c>
       <c r="I2" t="n">
-        <v>21.70579558849832</v>
+        <v>21.18461301259619</v>
       </c>
       <c r="J2" t="n">
-        <v>28.337106010459</v>
+        <v>26.65222122762073</v>
       </c>
       <c r="K2" t="n">
-        <v>28.7439387888055</v>
+        <v>27.41820490064688</v>
       </c>
       <c r="L2" t="n">
-        <v>41.05571741725986</v>
+        <v>22.20961948627914</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.61110204419986</v>
+        <v>21.65747216201309</v>
       </c>
       <c r="C3" t="n">
-        <v>19.92966790021173</v>
+        <v>15.58029201294636</v>
       </c>
       <c r="D3" t="n">
-        <v>38.61132697047549</v>
+        <v>26.52911012068123</v>
       </c>
       <c r="E3" t="n">
-        <v>22.18514119832916</v>
+        <v>18.68196190078454</v>
       </c>
       <c r="F3" t="n">
-        <v>15.82774163007261</v>
+        <v>9.94970878834587</v>
       </c>
       <c r="G3" t="n">
-        <v>29.82300403514601</v>
+        <v>23.68138487712032</v>
       </c>
       <c r="H3" t="n">
-        <v>46.47252476901652</v>
+        <v>29.00853588316655</v>
       </c>
       <c r="I3" t="n">
-        <v>24.44615512630363</v>
+        <v>21.93017757311727</v>
       </c>
       <c r="J3" t="n">
-        <v>31.09481553694869</v>
+        <v>30.98549358388583</v>
       </c>
       <c r="K3" t="n">
-        <v>31.41932513305408</v>
+        <v>32.07832791395654</v>
       </c>
       <c r="L3" t="n">
-        <v>46.70934209967233</v>
+        <v>29.26278297701622</v>
       </c>
     </row>
     <row r="4">
@@ -5746,34 +5746,34 @@
         <v>13.75234611154259</v>
       </c>
       <c r="C4" t="n">
-        <v>13.87801957482439</v>
+        <v>13.87801957482444</v>
       </c>
       <c r="D4" t="n">
-        <v>21.50486104770969</v>
+        <v>21.5048610477097</v>
       </c>
       <c r="E4" t="n">
-        <v>13.90005484840225</v>
+        <v>13.90005484840228</v>
       </c>
       <c r="F4" t="n">
-        <v>13.90005484840225</v>
+        <v>13.90005484840228</v>
       </c>
       <c r="G4" t="n">
-        <v>16.9330535077744</v>
+        <v>16.93305350777432</v>
       </c>
       <c r="H4" t="n">
-        <v>25.56212439718553</v>
+        <v>25.56212439718555</v>
       </c>
       <c r="I4" t="n">
-        <v>13.99666326536986</v>
+        <v>13.99666326536987</v>
       </c>
       <c r="J4" t="n">
         <v>14.22748862689038</v>
       </c>
       <c r="K4" t="n">
-        <v>13.90168759999829</v>
+        <v>13.90168759999831</v>
       </c>
       <c r="L4" t="n">
-        <v>25.68815979310677</v>
+        <v>25.68815979310693</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.32296277944114</v>
+        <v>68.32296277944124</v>
       </c>
       <c r="C5" t="n">
-        <v>74.97731106949297</v>
+        <v>74.97731106949242</v>
       </c>
       <c r="D5" t="n">
-        <v>191.5516874390259</v>
+        <v>191.5516874390261</v>
       </c>
       <c r="E5" t="n">
-        <v>74.9773191976974</v>
+        <v>74.97731919769754</v>
       </c>
       <c r="F5" t="n">
-        <v>74.9773191976974</v>
+        <v>74.97731919769754</v>
       </c>
       <c r="G5" t="n">
-        <v>122.6761732345235</v>
+        <v>122.6761732345237</v>
       </c>
       <c r="H5" t="n">
-        <v>288.4018487041573</v>
+        <v>288.4018487041574</v>
       </c>
       <c r="I5" t="n">
-        <v>74.97636821234485</v>
+        <v>74.97636821234552</v>
       </c>
       <c r="J5" t="n">
-        <v>81.13384903636739</v>
+        <v>81.13384903636734</v>
       </c>
       <c r="K5" t="n">
-        <v>68.47098356353179</v>
+        <v>68.47098356353177</v>
       </c>
       <c r="L5" t="n">
-        <v>308.9154494615178</v>
+        <v>78.25346386448811</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.26794289770204</v>
+        <v>31.26794289770206</v>
       </c>
       <c r="C6" t="n">
-        <v>31.42410183848964</v>
+        <v>31.42410183848974</v>
       </c>
       <c r="D6" t="n">
-        <v>51.3944556914432</v>
+        <v>39.20195139464984</v>
       </c>
       <c r="E6" t="n">
-        <v>29.73449388181348</v>
+        <v>29.73449388181343</v>
       </c>
       <c r="F6" t="n">
-        <v>31.52085720074501</v>
+        <v>31.52085720074499</v>
       </c>
       <c r="G6" t="n">
-        <v>34.44865029393387</v>
+        <v>47.07745704755571</v>
       </c>
       <c r="H6" t="n">
-        <v>55.49358842759651</v>
+        <v>55.49358842759653</v>
       </c>
       <c r="I6" t="n">
-        <v>44.1410668051513</v>
+        <v>31.51226005152935</v>
       </c>
       <c r="J6" t="n">
-        <v>32.68006982636726</v>
+        <v>44.06639816120848</v>
       </c>
       <c r="K6" t="n">
-        <v>31.35685344896906</v>
+        <v>31.35685344896905</v>
       </c>
       <c r="L6" t="n">
-        <v>43.2836560984023</v>
+        <v>43.28365609840238</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.06476613971701</v>
+        <v>18.06476613971702</v>
       </c>
       <c r="C7" t="n">
-        <v>18.3100261506913</v>
+        <v>18.31002615069124</v>
       </c>
       <c r="D7" t="n">
-        <v>25.81719591591164</v>
+        <v>25.81719591591162</v>
       </c>
       <c r="E7" t="n">
-        <v>18.30753334796432</v>
+        <v>18.30753334796436</v>
       </c>
       <c r="F7" t="n">
-        <v>18.30753334796432</v>
+        <v>18.30753334796435</v>
       </c>
       <c r="G7" t="n">
-        <v>21.24547353594873</v>
+        <v>21.24547353594867</v>
       </c>
       <c r="H7" t="n">
-        <v>29.87454442535995</v>
+        <v>29.87454442535998</v>
       </c>
       <c r="I7" t="n">
-        <v>18.30908329354431</v>
+        <v>18.3090832935443</v>
       </c>
       <c r="J7" t="n">
         <v>18.5399086550648</v>
       </c>
       <c r="K7" t="n">
-        <v>18.21410762817274</v>
+        <v>18.21410762817275</v>
       </c>
       <c r="L7" t="n">
-        <v>30.00057982128145</v>
+        <v>30.00057982128136</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.23800896696231</v>
+        <v>30.23800896696239</v>
       </c>
       <c r="C8" t="n">
-        <v>41.36117199162117</v>
+        <v>41.36117199162121</v>
       </c>
       <c r="D8" t="n">
-        <v>51.12421375156208</v>
+        <v>51.12421375156217</v>
       </c>
       <c r="E8" t="n">
-        <v>38.38613027942652</v>
+        <v>38.38613027942649</v>
       </c>
       <c r="F8" t="n">
-        <v>30.82665350881842</v>
+        <v>30.82665350881839</v>
       </c>
       <c r="G8" t="n">
-        <v>44.29677076700335</v>
+        <v>44.29677076700341</v>
       </c>
       <c r="H8" t="n">
-        <v>52.92584165641679</v>
+        <v>52.92584165641687</v>
       </c>
       <c r="I8" t="n">
-        <v>41.36038052459892</v>
+        <v>41.36038052459891</v>
       </c>
       <c r="J8" t="n">
-        <v>41.59334373626887</v>
+        <v>41.59334373626891</v>
       </c>
       <c r="K8" t="n">
-        <v>30.18528500999962</v>
+        <v>30.18528500999967</v>
       </c>
       <c r="L8" t="n">
-        <v>64.41491448594884</v>
+        <v>64.41491448594907</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.09209989628926</v>
+        <v>27.09209989628925</v>
       </c>
       <c r="C9" t="n">
-        <v>31.20205453343343</v>
+        <v>31.20205453343344</v>
       </c>
       <c r="D9" t="n">
-        <v>38.70930958362574</v>
+        <v>38.70930958362577</v>
       </c>
       <c r="E9" t="n">
-        <v>35.66183349647892</v>
+        <v>35.66183349647889</v>
       </c>
       <c r="F9" t="n">
         <v>31.20205871604003</v>
       </c>
       <c r="G9" t="n">
-        <v>34.137501918691</v>
+        <v>34.13750191869093</v>
       </c>
       <c r="H9" t="n">
         <v>42.76657280810218</v>
       </c>
       <c r="I9" t="n">
-        <v>31.20111167628653</v>
+        <v>31.20111167628654</v>
       </c>
       <c r="J9" t="n">
-        <v>31.43193703780698</v>
+        <v>31.43193703780701</v>
       </c>
       <c r="K9" t="n">
-        <v>28.86691681926097</v>
+        <v>28.86691681926098</v>
       </c>
       <c r="L9" t="n">
-        <v>42.89260820402352</v>
+        <v>42.89260820402357</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.60945248781436</v>
+        <v>20.40572871450113</v>
       </c>
       <c r="C2" t="n">
-        <v>13.03836108304212</v>
+        <v>16.40275629697887</v>
       </c>
       <c r="D2" t="n">
-        <v>22.03893389758827</v>
+        <v>20.58621550959882</v>
       </c>
       <c r="E2" t="n">
-        <v>15.27399899051237</v>
+        <v>18.27022435759667</v>
       </c>
       <c r="F2" t="n">
-        <v>8.965929679965754</v>
+        <v>13.02225200549186</v>
       </c>
       <c r="G2" t="n">
-        <v>19.81468763591862</v>
+        <v>20.46915784655605</v>
       </c>
       <c r="H2" t="n">
-        <v>26.96726562657941</v>
+        <v>20.71030462770958</v>
       </c>
       <c r="I2" t="n">
-        <v>17.61628571021205</v>
+        <v>20.35337817635575</v>
       </c>
       <c r="J2" t="n">
-        <v>28.47632786959197</v>
+        <v>25.97447067574617</v>
       </c>
       <c r="K2" t="n">
-        <v>26.78310580123568</v>
+        <v>26.6665815549138</v>
       </c>
       <c r="L2" t="n">
-        <v>23.55534242457436</v>
+        <v>20.66569261916641</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.88956782866554</v>
+        <v>20.42027300322491</v>
       </c>
       <c r="C3" t="n">
-        <v>15.16560049003214</v>
+        <v>13.62244751686342</v>
       </c>
       <c r="D3" t="n">
-        <v>24.83418186483934</v>
+        <v>21.6988758350345</v>
       </c>
       <c r="E3" t="n">
-        <v>17.4046991334612</v>
+        <v>16.69919307673124</v>
       </c>
       <c r="F3" t="n">
-        <v>11.0966298229146</v>
+        <v>8.034715357228864</v>
       </c>
       <c r="G3" t="n">
-        <v>22.27583791269422</v>
+        <v>20.87252162410664</v>
       </c>
       <c r="H3" t="n">
-        <v>30.5084326127215</v>
+        <v>23.42473784660208</v>
       </c>
       <c r="I3" t="n">
-        <v>19.7410308893418</v>
+        <v>20.05010445835556</v>
       </c>
       <c r="J3" t="n">
-        <v>31.26580347645012</v>
+        <v>30.59640830615567</v>
       </c>
       <c r="K3" t="n">
-        <v>29.16775503105001</v>
+        <v>30.95380671517343</v>
       </c>
       <c r="L3" t="n">
-        <v>26.57830014339612</v>
+        <v>22.29473345505256</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.15294601253686</v>
+        <v>12.15294601253689</v>
       </c>
       <c r="C4" t="n">
         <v>11.26918206140335</v>
       </c>
       <c r="D4" t="n">
-        <v>14.19162739119301</v>
+        <v>14.191627391193</v>
       </c>
       <c r="E4" t="n">
-        <v>11.28887318221209</v>
+        <v>11.28887318221208</v>
       </c>
       <c r="F4" t="n">
-        <v>11.28887318221209</v>
+        <v>11.28887318221208</v>
       </c>
       <c r="G4" t="n">
         <v>12.84060375684459</v>
       </c>
       <c r="H4" t="n">
-        <v>17.1200998595761</v>
+        <v>17.12009985957611</v>
       </c>
       <c r="I4" t="n">
         <v>11.37826019852935</v>
       </c>
       <c r="J4" t="n">
-        <v>14.16878278178401</v>
+        <v>14.168782781784</v>
       </c>
       <c r="K4" t="n">
-        <v>12.56664780882383</v>
+        <v>12.56664780882385</v>
       </c>
       <c r="L4" t="n">
-        <v>15.09307767964831</v>
+        <v>15.09307767964833</v>
       </c>
     </row>
     <row r="5">
@@ -6179,19 +6179,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.53989566138869</v>
+        <v>52.53989566138932</v>
       </c>
       <c r="C5" t="n">
-        <v>43.10065456445565</v>
+        <v>43.10065456445566</v>
       </c>
       <c r="D5" t="n">
-        <v>85.78116107544085</v>
+        <v>85.78116107544092</v>
       </c>
       <c r="E5" t="n">
-        <v>43.10066249455014</v>
+        <v>43.10066249455018</v>
       </c>
       <c r="F5" t="n">
-        <v>43.10066249455014</v>
+        <v>43.10066249455019</v>
       </c>
       <c r="G5" t="n">
         <v>65.80857366189085</v>
@@ -6200,16 +6200,16 @@
         <v>147.0894192539752</v>
       </c>
       <c r="I5" t="n">
-        <v>43.10005320987725</v>
+        <v>43.10005320987726</v>
       </c>
       <c r="J5" t="n">
-        <v>93.31712482271789</v>
+        <v>93.31712482271817</v>
       </c>
       <c r="K5" t="n">
-        <v>59.19923438799581</v>
+        <v>59.19923438799611</v>
       </c>
       <c r="L5" t="n">
-        <v>117.6218489812871</v>
+        <v>117.6218489812872</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.78721643009549</v>
+        <v>43.93229607387607</v>
       </c>
       <c r="C6" t="n">
         <v>29.93751515231664</v>
       </c>
       <c r="D6" t="n">
-        <v>45.66995895315024</v>
+        <v>45.66995895315021</v>
       </c>
       <c r="E6" t="n">
         <v>28.13153285780956</v>
       </c>
       <c r="F6" t="n">
-        <v>30.01058741875382</v>
+        <v>30.01058741875383</v>
       </c>
       <c r="G6" t="n">
-        <v>31.47487417440332</v>
+        <v>44.61995381818373</v>
       </c>
       <c r="H6" t="n">
-        <v>48.62372289292819</v>
+        <v>35.79009108381887</v>
       </c>
       <c r="I6" t="n">
-        <v>30.01253061608807</v>
+        <v>43.15761025986846</v>
       </c>
       <c r="J6" t="n">
-        <v>45.60655505761891</v>
+        <v>45.60655505761889</v>
       </c>
       <c r="K6" t="n">
-        <v>31.19515920963278</v>
+        <v>31.19515920963279</v>
       </c>
       <c r="L6" t="n">
-        <v>33.75108835363018</v>
+        <v>33.75108835363016</v>
       </c>
     </row>
     <row r="7">
@@ -6259,34 +6259,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.48119279057294</v>
+        <v>16.48119279057295</v>
       </c>
       <c r="C7" t="n">
-        <v>15.70710833114383</v>
+        <v>15.70710833114382</v>
       </c>
       <c r="D7" t="n">
-        <v>18.51978689719893</v>
+        <v>18.51978689719892</v>
       </c>
       <c r="E7" t="n">
-        <v>15.70476897210352</v>
+        <v>15.70476897210351</v>
       </c>
       <c r="F7" t="n">
-        <v>15.70476897210352</v>
+        <v>15.70476897210351</v>
       </c>
       <c r="G7" t="n">
-        <v>17.16885053488069</v>
+        <v>17.1688505348807</v>
       </c>
       <c r="H7" t="n">
-        <v>21.44834663761221</v>
+        <v>21.4483466376122</v>
       </c>
       <c r="I7" t="n">
-        <v>15.70650697656543</v>
+        <v>15.70650697656542</v>
       </c>
       <c r="J7" t="n">
-        <v>18.49702955982009</v>
+        <v>18.49702955982008</v>
       </c>
       <c r="K7" t="n">
-        <v>16.89489458685991</v>
+        <v>16.8948945868599</v>
       </c>
       <c r="L7" t="n">
         <v>19.42132445768442</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.28748900546969</v>
+        <v>29.28748900546973</v>
       </c>
       <c r="C8" t="n">
-        <v>39.77223862866489</v>
+        <v>39.77223862866488</v>
       </c>
       <c r="D8" t="n">
         <v>44.91950890214545</v>
       </c>
       <c r="E8" t="n">
-        <v>36.69305257566246</v>
+        <v>36.69305257566247</v>
       </c>
       <c r="F8" t="n">
-        <v>28.86894960680632</v>
+        <v>28.8689496068063</v>
       </c>
       <c r="G8" t="n">
-        <v>41.23390781652988</v>
+        <v>41.23390781652992</v>
       </c>
       <c r="H8" t="n">
-        <v>45.51340391926184</v>
+        <v>45.51340391926182</v>
       </c>
       <c r="I8" t="n">
-        <v>39.77156425821463</v>
+        <v>39.77156425821464</v>
       </c>
       <c r="J8" t="n">
-        <v>42.56429951156466</v>
+        <v>42.56429951156458</v>
       </c>
       <c r="K8" t="n">
-        <v>29.4920535346036</v>
+        <v>29.49205353460365</v>
       </c>
       <c r="L8" t="n">
-        <v>55.24709911672579</v>
+        <v>55.24709911672574</v>
       </c>
     </row>
     <row r="9">
@@ -6339,16 +6339,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.41194794525277</v>
+        <v>26.41194794525276</v>
       </c>
       <c r="C9" t="n">
         <v>29.74303339412205</v>
       </c>
       <c r="D9" t="n">
-        <v>32.55579965029515</v>
+        <v>32.55579965029517</v>
       </c>
       <c r="E9" t="n">
-        <v>34.48031781974512</v>
+        <v>34.48031781974515</v>
       </c>
       <c r="F9" t="n">
         <v>29.74303899387072</v>
@@ -6357,19 +6357,19 @@
         <v>31.20477559785892</v>
       </c>
       <c r="H9" t="n">
-        <v>35.48427170059041</v>
+        <v>35.48427170059043</v>
       </c>
       <c r="I9" t="n">
-        <v>29.74243203954367</v>
+        <v>29.74243203954366</v>
       </c>
       <c r="J9" t="n">
-        <v>32.53295462279829</v>
+        <v>32.53295462279836</v>
       </c>
       <c r="K9" t="n">
-        <v>28.55226825857148</v>
+        <v>28.55226825857147</v>
       </c>
       <c r="L9" t="n">
-        <v>33.45724952066263</v>
+        <v>33.45724952066266</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.23775997764428</v>
+        <v>20.2994528318961</v>
       </c>
       <c r="C2" t="n">
-        <v>13.69559675588555</v>
+        <v>16.29972330705813</v>
       </c>
       <c r="D2" t="n">
-        <v>17.76002094479049</v>
+        <v>20.22168236162312</v>
       </c>
       <c r="E2" t="n">
-        <v>15.91280645933021</v>
+        <v>18.15079344029017</v>
       </c>
       <c r="F2" t="n">
-        <v>9.658096944924125</v>
+        <v>12.94723517740753</v>
       </c>
       <c r="G2" t="n">
-        <v>18.26625211444253</v>
+        <v>20.24832430262583</v>
       </c>
       <c r="H2" t="n">
-        <v>17.12601163296266</v>
+        <v>20.04868999306133</v>
       </c>
       <c r="I2" t="n">
-        <v>18.27225255478122</v>
+        <v>20.24857999950432</v>
       </c>
       <c r="J2" t="n">
-        <v>26.77695221996327</v>
+        <v>25.67598301611816</v>
       </c>
       <c r="K2" t="n">
-        <v>26.14474808306662</v>
+        <v>26.47367420646552</v>
       </c>
       <c r="L2" t="n">
-        <v>16.88795706047278</v>
+        <v>20.17194805461328</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.60006790485771</v>
+        <v>20.57519220332065</v>
       </c>
       <c r="C3" t="n">
-        <v>15.90932127094101</v>
+        <v>13.78846921769805</v>
       </c>
       <c r="D3" t="n">
-        <v>19.90036190435733</v>
+        <v>20.02389140037926</v>
       </c>
       <c r="E3" t="n">
-        <v>18.12991675173516</v>
+        <v>16.83946686020859</v>
       </c>
       <c r="F3" t="n">
-        <v>11.87520723732896</v>
+        <v>8.248303361005322</v>
       </c>
       <c r="G3" t="n">
-        <v>20.48263261492821</v>
+        <v>20.21298767431444</v>
       </c>
       <c r="H3" t="n">
-        <v>19.17670619935397</v>
+        <v>19.65433100959093</v>
       </c>
       <c r="I3" t="n">
-        <v>20.48496170247226</v>
+        <v>20.21453156039934</v>
       </c>
       <c r="J3" t="n">
-        <v>29.31241458192887</v>
+        <v>29.78550191811717</v>
       </c>
       <c r="K3" t="n">
-        <v>28.42517457526273</v>
+        <v>30.60898391964908</v>
       </c>
       <c r="L3" t="n">
-        <v>18.89748487215716</v>
+        <v>19.69923221913195</v>
       </c>
     </row>
     <row r="4">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.47867820133447</v>
+        <v>12.47867820133449</v>
       </c>
       <c r="C4" t="n">
-        <v>11.64078010320962</v>
+        <v>11.64078010320961</v>
       </c>
       <c r="D4" t="n">
-        <v>11.60022496341735</v>
+        <v>11.60022496341736</v>
       </c>
       <c r="E4" t="n">
         <v>11.65776634839708</v>
@@ -6550,13 +6550,13 @@
         <v>11.65776634839709</v>
       </c>
       <c r="G4" t="n">
-        <v>11.87317609073457</v>
+        <v>11.87317609073461</v>
       </c>
       <c r="H4" t="n">
-        <v>11.22403172942412</v>
+        <v>11.22403172942413</v>
       </c>
       <c r="I4" t="n">
-        <v>11.72622894979129</v>
+        <v>11.72622894979128</v>
       </c>
       <c r="J4" t="n">
         <v>13.16395167008799</v>
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.82804294919173</v>
+        <v>56.8280429491917</v>
       </c>
       <c r="C5" t="n">
-        <v>47.74198597054756</v>
+        <v>47.74198597054757</v>
       </c>
       <c r="D5" t="n">
-        <v>43.23496739381636</v>
+        <v>43.23496739381638</v>
       </c>
       <c r="E5" t="n">
-        <v>47.74199374587931</v>
+        <v>47.74199374587933</v>
       </c>
       <c r="F5" t="n">
-        <v>47.74199374587931</v>
+        <v>47.74199374587933</v>
       </c>
       <c r="G5" t="n">
-        <v>47.98607812306544</v>
+        <v>47.98607812306594</v>
       </c>
       <c r="H5" t="n">
-        <v>40.6366342706764</v>
+        <v>40.63663427067642</v>
       </c>
       <c r="I5" t="n">
-        <v>47.74168619592965</v>
+        <v>47.74168619592962</v>
       </c>
       <c r="J5" t="n">
-        <v>70.25168487636924</v>
+        <v>70.2516848763692</v>
       </c>
       <c r="K5" t="n">
-        <v>50.84068304364515</v>
+        <v>50.8406830436451</v>
       </c>
       <c r="L5" t="n">
-        <v>31.34447283819898</v>
+        <v>31.344472838199</v>
       </c>
     </row>
     <row r="6">
@@ -6615,34 +6615,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.98409549664146</v>
+        <v>41.98409549664148</v>
       </c>
       <c r="C6" t="n">
-        <v>29.0394353810126</v>
+        <v>29.03943538101258</v>
       </c>
       <c r="D6" t="n">
-        <v>28.9310319534802</v>
+        <v>28.93104174408554</v>
       </c>
       <c r="E6" t="n">
-        <v>27.35764304297825</v>
+        <v>27.35764304297824</v>
       </c>
       <c r="F6" t="n">
-        <v>29.07902741634389</v>
+        <v>29.07902741634388</v>
       </c>
       <c r="G6" t="n">
-        <v>29.22512701805233</v>
+        <v>41.37859338604157</v>
       </c>
       <c r="H6" t="n">
-        <v>28.57424538711284</v>
+        <v>40.443416288226</v>
       </c>
       <c r="I6" t="n">
-        <v>29.07817987710905</v>
+        <v>41.23164624509822</v>
       </c>
       <c r="J6" t="n">
-        <v>42.34537141378722</v>
+        <v>31.43110224008147</v>
       </c>
       <c r="K6" t="n">
-        <v>29.50428861825056</v>
+        <v>29.50428861825055</v>
       </c>
       <c r="L6" t="n">
         <v>28.43278390370241</v>
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.41268934862413</v>
+        <v>16.41268934862414</v>
       </c>
       <c r="C7" t="n">
-        <v>15.66053987169884</v>
+        <v>15.66053987169883</v>
       </c>
       <c r="D7" t="n">
-        <v>15.53415442623215</v>
+        <v>15.53415442623216</v>
       </c>
       <c r="E7" t="n">
         <v>15.65887179146604</v>
@@ -6670,22 +6670,22 @@
         <v>15.65887179146604</v>
       </c>
       <c r="G7" t="n">
-        <v>15.80718723802426</v>
+        <v>15.80718723802428</v>
       </c>
       <c r="H7" t="n">
-        <v>15.15804287671378</v>
+        <v>15.15804287671379</v>
       </c>
       <c r="I7" t="n">
         <v>15.66024009708092</v>
       </c>
       <c r="J7" t="n">
-        <v>17.09796281737765</v>
+        <v>17.09796281737766</v>
       </c>
       <c r="K7" t="n">
-        <v>16.08863657411024</v>
+        <v>16.08863657411023</v>
       </c>
       <c r="L7" t="n">
-        <v>15.01695546601635</v>
+        <v>15.01695546601636</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.24613169014849</v>
+        <v>28.24613169014851</v>
       </c>
       <c r="C8" t="n">
-        <v>37.83876346057698</v>
+        <v>37.83876346057693</v>
       </c>
       <c r="D8" t="n">
-        <v>39.85687927658207</v>
+        <v>39.85687927658208</v>
       </c>
       <c r="E8" t="n">
-        <v>35.00963975988774</v>
+        <v>35.00963975988777</v>
       </c>
       <c r="F8" t="n">
-        <v>27.82093582400549</v>
+        <v>27.82093582400546</v>
       </c>
       <c r="G8" t="n">
-        <v>37.98488223018369</v>
+        <v>37.98488223018368</v>
       </c>
       <c r="H8" t="n">
-        <v>37.33573786887288</v>
+        <v>37.33573786887285</v>
       </c>
       <c r="I8" t="n">
         <v>37.83793508924034</v>
       </c>
       <c r="J8" t="n">
-        <v>39.27769075250968</v>
+        <v>39.27769075250969</v>
       </c>
       <c r="K8" t="n">
         <v>27.72992911182009</v>
       </c>
       <c r="L8" t="n">
-        <v>48.00008732497093</v>
+        <v>48.00008732497095</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.73647904957978</v>
+        <v>24.73647904957979</v>
       </c>
       <c r="C9" t="n">
-        <v>27.51608882900723</v>
+        <v>27.51608882900727</v>
       </c>
       <c r="D9" t="n">
-        <v>27.38978632002099</v>
+        <v>27.38978632002103</v>
       </c>
       <c r="E9" t="n">
-        <v>31.59167214140941</v>
+        <v>31.59167214140945</v>
       </c>
       <c r="F9" t="n">
-        <v>27.5160958914121</v>
+        <v>27.51609589141212</v>
       </c>
       <c r="G9" t="n">
-        <v>27.66273619533264</v>
+        <v>27.66273619533268</v>
       </c>
       <c r="H9" t="n">
-        <v>27.01359183402219</v>
+        <v>27.01359183402222</v>
       </c>
       <c r="I9" t="n">
-        <v>27.51578905438933</v>
+        <v>27.51578905438934</v>
       </c>
       <c r="J9" t="n">
-        <v>28.95351177468606</v>
+        <v>28.95351177468609</v>
       </c>
       <c r="K9" t="n">
-        <v>25.81484925328221</v>
+        <v>25.8978708745891</v>
       </c>
       <c r="L9" t="n">
-        <v>26.87250442332476</v>
+        <v>26.87250442332481</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.13980371458858</v>
+        <v>20.26227492372217</v>
       </c>
       <c r="C2" t="n">
-        <v>13.57897627739346</v>
+        <v>16.25628510844684</v>
       </c>
       <c r="D2" t="n">
-        <v>17.30944175326369</v>
+        <v>20.1659466090893</v>
       </c>
       <c r="E2" t="n">
-        <v>15.79308616062234</v>
+        <v>18.10442725390757</v>
       </c>
       <c r="F2" t="n">
-        <v>9.548029469751459</v>
+        <v>12.90890355864397</v>
       </c>
       <c r="G2" t="n">
-        <v>17.97381225978615</v>
+        <v>20.20091110930147</v>
       </c>
       <c r="H2" t="n">
-        <v>17.01499747451169</v>
+        <v>20.01105033836649</v>
       </c>
       <c r="I2" t="n">
-        <v>18.16281656484165</v>
+        <v>20.21079950867553</v>
       </c>
       <c r="J2" t="n">
-        <v>26.42862790400017</v>
+        <v>25.60907968437535</v>
       </c>
       <c r="K2" t="n">
-        <v>25.44570684516101</v>
+        <v>26.38207041936698</v>
       </c>
       <c r="L2" t="n">
-        <v>17.0518951733341</v>
+        <v>20.14893226178934</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.48342777676498</v>
+        <v>20.52124555702142</v>
       </c>
       <c r="C3" t="n">
-        <v>15.77216535487712</v>
+        <v>13.72105724672059</v>
       </c>
       <c r="D3" t="n">
-        <v>19.37813236290332</v>
+        <v>19.83833086420756</v>
       </c>
       <c r="E3" t="n">
-        <v>17.98979273925848</v>
+        <v>16.76749684373199</v>
       </c>
       <c r="F3" t="n">
-        <v>11.74473604838757</v>
+        <v>8.189595965581407</v>
       </c>
       <c r="G3" t="n">
-        <v>20.14229606933996</v>
+        <v>20.08695485324107</v>
       </c>
       <c r="H3" t="n">
-        <v>19.04488429709343</v>
+        <v>19.59447448858984</v>
       </c>
       <c r="I3" t="n">
-        <v>20.3553907349442</v>
+        <v>20.15673349455747</v>
       </c>
       <c r="J3" t="n">
-        <v>28.91098729078945</v>
+        <v>29.6176899749517</v>
       </c>
       <c r="K3" t="n">
-        <v>27.62155279129521</v>
+        <v>30.30159510033943</v>
       </c>
       <c r="L3" t="n">
-        <v>19.0820503297295</v>
+        <v>19.74445358885102</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.41381012577272</v>
+        <v>12.41381012577266</v>
       </c>
       <c r="C4" t="n">
-        <v>11.56992643239265</v>
+        <v>11.56992643239264</v>
       </c>
       <c r="D4" t="n">
-        <v>11.32573749878052</v>
+        <v>11.32573749878044</v>
       </c>
       <c r="E4" t="n">
-        <v>11.58696012922478</v>
+        <v>11.58696012922477</v>
       </c>
       <c r="F4" t="n">
-        <v>11.58696012922478</v>
+        <v>11.58696012922477</v>
       </c>
       <c r="G4" t="n">
-        <v>11.69276045589169</v>
+        <v>11.69276045589162</v>
       </c>
       <c r="H4" t="n">
-        <v>11.15135843880942</v>
+        <v>11.15135843880937</v>
       </c>
       <c r="I4" t="n">
-        <v>11.65499236245237</v>
+        <v>11.65499236245235</v>
       </c>
       <c r="J4" t="n">
-        <v>12.96286702559824</v>
+        <v>12.96286702559816</v>
       </c>
       <c r="K4" t="n">
-        <v>11.74981389763299</v>
+        <v>11.74981389763293</v>
       </c>
       <c r="L4" t="n">
-        <v>11.1736445346873</v>
+        <v>11.17364453468722</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.86795363516168</v>
+        <v>55.86795363516165</v>
       </c>
       <c r="C5" t="n">
-        <v>46.89473498876019</v>
+        <v>46.89473498876124</v>
       </c>
       <c r="D5" t="n">
-        <v>38.99980465212742</v>
+        <v>38.99980465212734</v>
       </c>
       <c r="E5" t="n">
-        <v>46.89474277880865</v>
+        <v>46.89474277880933</v>
       </c>
       <c r="F5" t="n">
-        <v>46.89474277880865</v>
+        <v>46.89474277880933</v>
       </c>
       <c r="G5" t="n">
-        <v>45.48060348176477</v>
+        <v>45.48060348176431</v>
       </c>
       <c r="H5" t="n">
-        <v>38.91279321000752</v>
+        <v>38.91279321000743</v>
       </c>
       <c r="I5" t="n">
-        <v>46.89446030854842</v>
+        <v>46.89446030854858</v>
       </c>
       <c r="J5" t="n">
-        <v>67.58939256817973</v>
+        <v>67.58939256817965</v>
       </c>
       <c r="K5" t="n">
-        <v>44.6522638804298</v>
+        <v>44.65226388042969</v>
       </c>
       <c r="L5" t="n">
-        <v>39.3011006537725</v>
+        <v>37.76788618296603</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.75828577137914</v>
+        <v>29.75828577137909</v>
       </c>
       <c r="C6" t="n">
-        <v>28.96130092400274</v>
+        <v>28.96130092400264</v>
       </c>
       <c r="D6" t="n">
-        <v>28.64313784678166</v>
+        <v>28.64313784678163</v>
       </c>
       <c r="E6" t="n">
-        <v>27.28018178635765</v>
+        <v>27.28018178635767</v>
       </c>
       <c r="F6" t="n">
-        <v>28.99861954482607</v>
+        <v>28.99861954482606</v>
       </c>
       <c r="G6" t="n">
-        <v>41.18987524485155</v>
+        <v>29.03723610149803</v>
       </c>
       <c r="H6" t="n">
-        <v>40.35288584499239</v>
+        <v>40.3528858449923</v>
       </c>
       <c r="I6" t="n">
-        <v>28.99946800805886</v>
+        <v>28.99946800805881</v>
       </c>
       <c r="J6" t="n">
-        <v>42.12609377219764</v>
+        <v>31.21929793553432</v>
       </c>
       <c r="K6" t="n">
-        <v>29.08176115953705</v>
+        <v>29.081761159537</v>
       </c>
       <c r="L6" t="n">
-        <v>28.5150320017017</v>
+        <v>28.51503200170168</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.32901862038052</v>
+        <v>16.32901862038044</v>
       </c>
       <c r="C7" t="n">
-        <v>15.57047553727288</v>
+        <v>15.57047553727282</v>
       </c>
       <c r="D7" t="n">
-        <v>15.2408648570783</v>
+        <v>15.2408648570782</v>
       </c>
       <c r="E7" t="n">
-        <v>15.5686751482843</v>
+        <v>15.56867514828424</v>
       </c>
       <c r="F7" t="n">
-        <v>15.5686751482843</v>
+        <v>15.56867514828424</v>
       </c>
       <c r="G7" t="n">
-        <v>15.60796895049946</v>
+        <v>15.60796895049941</v>
       </c>
       <c r="H7" t="n">
-        <v>15.06656693341731</v>
+        <v>15.06656693341716</v>
       </c>
       <c r="I7" t="n">
-        <v>15.57020085706016</v>
+        <v>15.57020085706013</v>
       </c>
       <c r="J7" t="n">
-        <v>16.87807552020602</v>
+        <v>16.87807552020596</v>
       </c>
       <c r="K7" t="n">
-        <v>15.66502239224075</v>
+        <v>15.6650223922407</v>
       </c>
       <c r="L7" t="n">
-        <v>15.08885302929502</v>
+        <v>15.088853029295</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.13815393243419</v>
+        <v>28.13815393243412</v>
       </c>
       <c r="C8" t="n">
-        <v>37.69407992877809</v>
+        <v>37.69407992877803</v>
       </c>
       <c r="D8" t="n">
-        <v>39.50284519777955</v>
+        <v>39.50284519777957</v>
       </c>
       <c r="E8" t="n">
         <v>34.87322413899135</v>
       </c>
       <c r="F8" t="n">
-        <v>27.7055285795868</v>
+        <v>27.70552857958677</v>
       </c>
       <c r="G8" t="n">
-        <v>37.73117781399081</v>
+        <v>37.7311778139907</v>
       </c>
       <c r="H8" t="n">
-        <v>37.18977579690811</v>
+        <v>37.18977579690809</v>
       </c>
       <c r="I8" t="n">
-        <v>37.69340972055149</v>
+        <v>37.69340972055144</v>
       </c>
       <c r="J8" t="n">
-        <v>39.0033113956306</v>
+        <v>39.00331139563053</v>
       </c>
       <c r="K8" t="n">
-        <v>27.28256849273877</v>
+        <v>27.28256849273874</v>
       </c>
       <c r="L8" t="n">
-        <v>47.98597416695377</v>
+        <v>47.98597416695374</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.08226578621139</v>
+        <v>24.0822657862112</v>
       </c>
       <c r="C9" t="n">
-        <v>26.69128228537793</v>
+        <v>26.69128228537785</v>
       </c>
       <c r="D9" t="n">
-        <v>26.36175390512495</v>
+        <v>26.3617539051248</v>
       </c>
       <c r="E9" t="n">
-        <v>30.57738261218839</v>
+        <v>30.57738261218832</v>
       </c>
       <c r="F9" t="n">
-        <v>26.6912893799961</v>
+        <v>26.69128937999604</v>
       </c>
       <c r="G9" t="n">
-        <v>26.72877569860457</v>
+        <v>26.72877569860444</v>
       </c>
       <c r="H9" t="n">
-        <v>26.1873736815222</v>
+        <v>26.18737368152219</v>
       </c>
       <c r="I9" t="n">
-        <v>26.69100760516513</v>
+        <v>26.69100760516519</v>
       </c>
       <c r="J9" t="n">
-        <v>27.99888226831105</v>
+        <v>27.99888226831098</v>
       </c>
       <c r="K9" t="n">
-        <v>24.75549062938159</v>
+        <v>24.75549062938157</v>
       </c>
       <c r="L9" t="n">
-        <v>26.20965977740004</v>
+        <v>26.20965977740003</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.94187505569492</v>
+        <v>21.01534054552804</v>
       </c>
       <c r="C2" t="n">
-        <v>14.18717817301126</v>
+        <v>16.98280430519173</v>
       </c>
       <c r="D2" t="n">
-        <v>36.97566783440629</v>
+        <v>21.91179522763416</v>
       </c>
       <c r="E2" t="n">
-        <v>16.44456377070398</v>
+        <v>18.8719539390988</v>
       </c>
       <c r="F2" t="n">
-        <v>10.07283267840315</v>
+        <v>13.57099509984816</v>
       </c>
       <c r="G2" t="n">
-        <v>26.04807478661643</v>
+        <v>21.33669770947692</v>
       </c>
       <c r="H2" t="n">
-        <v>48.77191246942945</v>
+        <v>22.40465088981018</v>
       </c>
       <c r="I2" t="n">
-        <v>18.78700684096369</v>
+        <v>20.95442925189692</v>
       </c>
       <c r="J2" t="n">
-        <v>29.61898911893885</v>
+        <v>26.62369850190575</v>
       </c>
       <c r="K2" t="n">
-        <v>29.00601156682437</v>
+        <v>27.34645254895853</v>
       </c>
       <c r="L2" t="n">
-        <v>41.65118031396645</v>
+        <v>22.16514564605766</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.43305075518466</v>
+        <v>21.22428931435005</v>
       </c>
       <c r="C3" t="n">
-        <v>16.50056029353124</v>
+        <v>14.33455823923412</v>
       </c>
       <c r="D3" t="n">
-        <v>42.02544099024673</v>
+        <v>27.58895532705067</v>
       </c>
       <c r="E3" t="n">
-        <v>18.76189077035598</v>
+        <v>17.44331076098839</v>
       </c>
       <c r="F3" t="n">
-        <v>12.39015967805515</v>
+        <v>8.691366777984847</v>
       </c>
       <c r="G3" t="n">
-        <v>29.45644534120801</v>
+        <v>23.51266202543999</v>
       </c>
       <c r="H3" t="n">
-        <v>55.59908976121446</v>
+        <v>31.91927849985432</v>
       </c>
       <c r="I3" t="n">
-        <v>21.0952856601185</v>
+        <v>20.79310624154808</v>
       </c>
       <c r="J3" t="n">
-        <v>32.58146624554269</v>
+        <v>31.39412561142979</v>
       </c>
       <c r="K3" t="n">
-        <v>31.73097139087666</v>
+        <v>32.12232497546029</v>
       </c>
       <c r="L3" t="n">
-        <v>47.4026603400358</v>
+        <v>29.44413837936202</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.07624922064204</v>
+        <v>13.07624922064202</v>
       </c>
       <c r="C4" t="n">
-        <v>12.04719712968334</v>
+        <v>12.0471971296833</v>
       </c>
       <c r="D4" t="n">
-        <v>23.20211724455879</v>
+        <v>23.20211724455876</v>
       </c>
       <c r="E4" t="n">
-        <v>12.07057548011427</v>
+        <v>12.07057548011424</v>
       </c>
       <c r="F4" t="n">
-        <v>12.07057548011426</v>
+        <v>12.07057548011423</v>
       </c>
       <c r="G4" t="n">
-        <v>16.67539263567792</v>
+        <v>16.67539263567785</v>
       </c>
       <c r="H4" t="n">
-        <v>30.20970081566691</v>
+        <v>30.20970081566676</v>
       </c>
       <c r="I4" t="n">
-        <v>12.19185849436899</v>
+        <v>12.19185849436897</v>
       </c>
       <c r="J4" t="n">
-        <v>14.94146488346367</v>
+        <v>14.94146488346365</v>
       </c>
       <c r="K4" t="n">
-        <v>14.00146986663746</v>
+        <v>14.00146986663744</v>
       </c>
       <c r="L4" t="n">
-        <v>25.97904493113484</v>
+        <v>25.9790449311348</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.70017368067639</v>
+        <v>62.70017368067629</v>
       </c>
       <c r="C5" t="n">
-        <v>51.46699232750258</v>
+        <v>51.46699232750235</v>
       </c>
       <c r="D5" t="n">
-        <v>235.5971244162991</v>
+        <v>235.5971244162988</v>
       </c>
       <c r="E5" t="n">
-        <v>51.46700053201405</v>
+        <v>51.46700053201396</v>
       </c>
       <c r="F5" t="n">
-        <v>51.46700053201405</v>
+        <v>51.46700053201396</v>
       </c>
       <c r="G5" t="n">
-        <v>128.4278408128582</v>
+        <v>128.4278408128568</v>
       </c>
       <c r="H5" t="n">
-        <v>384.8398583352495</v>
+        <v>384.8398583352489</v>
       </c>
       <c r="I5" t="n">
-        <v>51.46569642355101</v>
+        <v>51.46569642355087</v>
       </c>
       <c r="J5" t="n">
-        <v>101.4449990303393</v>
+        <v>101.4449990303391</v>
       </c>
       <c r="K5" t="n">
-        <v>79.07258606732078</v>
+        <v>79.07258606732066</v>
       </c>
       <c r="L5" t="n">
-        <v>339.8652977673603</v>
+        <v>68.38723654318474</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.82968695951997</v>
+        <v>31.82968695951995</v>
       </c>
       <c r="C6" t="n">
         <v>30.79766770551767</v>
       </c>
       <c r="D6" t="n">
-        <v>42.21980526387308</v>
+        <v>42.21980526387307</v>
       </c>
       <c r="E6" t="n">
-        <v>28.98709274639289</v>
+        <v>28.98709274639281</v>
       </c>
       <c r="F6" t="n">
-        <v>30.93815340068077</v>
+        <v>30.93815340068076</v>
       </c>
       <c r="G6" t="n">
-        <v>48.95031141231549</v>
+        <v>48.95031141231541</v>
       </c>
       <c r="H6" t="n">
-        <v>62.27437483121808</v>
+        <v>62.27437483121797</v>
       </c>
       <c r="I6" t="n">
-        <v>44.46677727100664</v>
+        <v>44.46677727100655</v>
       </c>
       <c r="J6" t="n">
-        <v>46.89533357427887</v>
+        <v>46.89533357427886</v>
       </c>
       <c r="K6" t="n">
-        <v>32.70599251630361</v>
+        <v>32.7059925163035</v>
       </c>
       <c r="L6" t="n">
-        <v>44.81778557205939</v>
+        <v>44.81778557205929</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.68112861935769</v>
+        <v>17.68112861935764</v>
       </c>
       <c r="C7" t="n">
-        <v>16.79803379703625</v>
+        <v>16.79803379703621</v>
       </c>
       <c r="D7" t="n">
-        <v>27.80690719456111</v>
+        <v>27.80690719456105</v>
       </c>
       <c r="E7" t="n">
-        <v>16.79516427162933</v>
+        <v>16.79516427162927</v>
       </c>
       <c r="F7" t="n">
-        <v>16.79516427162933</v>
+        <v>16.79516427162927</v>
       </c>
       <c r="G7" t="n">
-        <v>21.28027203439357</v>
+        <v>21.28027203439352</v>
       </c>
       <c r="H7" t="n">
-        <v>34.81458021438254</v>
+        <v>34.81458021438243</v>
       </c>
       <c r="I7" t="n">
-        <v>16.79673789308466</v>
+        <v>16.79673789308461</v>
       </c>
       <c r="J7" t="n">
-        <v>19.54634428217933</v>
+        <v>19.54634428217926</v>
       </c>
       <c r="K7" t="n">
-        <v>18.60634926535314</v>
+        <v>18.60634926535309</v>
       </c>
       <c r="L7" t="n">
-        <v>30.5839243298505</v>
+        <v>30.5839243298504</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.72833378286348</v>
+        <v>30.72833378286339</v>
       </c>
       <c r="C8" t="n">
-        <v>41.4884330557844</v>
+        <v>41.48843305575486</v>
       </c>
       <c r="D8" t="n">
-        <v>54.91211809362348</v>
+        <v>54.91211809362338</v>
       </c>
       <c r="E8" t="n">
-        <v>38.30405624012803</v>
+        <v>38.30405624012791</v>
       </c>
       <c r="F8" t="n">
-        <v>30.21266638466565</v>
+        <v>30.21266638466561</v>
       </c>
       <c r="G8" t="n">
-        <v>45.9710274824921</v>
+        <v>45.97102748249196</v>
       </c>
       <c r="H8" t="n">
-        <v>59.50533566248217</v>
+        <v>59.50533566248193</v>
       </c>
       <c r="I8" t="n">
-        <v>41.4874933411832</v>
+        <v>41.48749334118307</v>
       </c>
       <c r="J8" t="n">
-        <v>44.23938802237083</v>
+        <v>44.23938802237072</v>
       </c>
       <c r="K8" t="n">
-        <v>31.43726950444471</v>
+        <v>31.43726950444461</v>
       </c>
       <c r="L8" t="n">
-        <v>67.43734166882282</v>
+        <v>67.43734166882267</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.84788125615507</v>
+        <v>28.84788125615498</v>
       </c>
       <c r="C9" t="n">
-        <v>32.51263536754193</v>
+        <v>32.51263536754176</v>
       </c>
       <c r="D9" t="n">
-        <v>43.52159726804094</v>
+        <v>43.52159726804078</v>
       </c>
       <c r="E9" t="n">
-        <v>37.76075695694544</v>
+        <v>37.7607569569453</v>
       </c>
       <c r="F9" t="n">
-        <v>32.51263797228558</v>
+        <v>32.51263797228547</v>
       </c>
       <c r="G9" t="n">
-        <v>36.9948736048993</v>
+        <v>36.99487360489915</v>
       </c>
       <c r="H9" t="n">
-        <v>50.52918178488825</v>
+        <v>50.52918178488818</v>
       </c>
       <c r="I9" t="n">
-        <v>32.51133946359036</v>
+        <v>32.51133946359028</v>
       </c>
       <c r="J9" t="n">
-        <v>35.26094585268504</v>
+        <v>35.26094585268491</v>
       </c>
       <c r="K9" t="n">
-        <v>31.68590890511473</v>
+        <v>31.68590890511465</v>
       </c>
       <c r="L9" t="n">
-        <v>46.29852590035618</v>
+        <v>46.29852590035607</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.07727612533933</v>
+        <v>20.5998165768747</v>
       </c>
       <c r="C2" t="n">
-        <v>13.48435282036736</v>
+        <v>16.57948797539546</v>
       </c>
       <c r="D2" t="n">
-        <v>32.42413449545596</v>
+        <v>21.30223522389803</v>
       </c>
       <c r="E2" t="n">
-        <v>15.72256861722847</v>
+        <v>18.45025796663667</v>
       </c>
       <c r="F2" t="n">
-        <v>9.407034829624651</v>
+        <v>13.19607365975642</v>
       </c>
       <c r="G2" t="n">
-        <v>22.03293286898389</v>
+        <v>20.75536692088559</v>
       </c>
       <c r="H2" t="n">
-        <v>20.35183626430069</v>
+        <v>20.52587321614725</v>
       </c>
       <c r="I2" t="n">
-        <v>18.08193382409073</v>
+        <v>20.54733306260797</v>
       </c>
       <c r="J2" t="n">
-        <v>27.57136865193543</v>
+        <v>26.08307690433346</v>
       </c>
       <c r="K2" t="n">
-        <v>25.5223915784729</v>
+        <v>26.71234000711039</v>
       </c>
       <c r="L2" t="n">
-        <v>31.43070278762858</v>
+        <v>21.25338360568872</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.42384615498671</v>
+        <v>20.69827692679628</v>
       </c>
       <c r="C3" t="n">
-        <v>15.67742332229235</v>
+        <v>13.87197768723887</v>
       </c>
       <c r="D3" t="n">
-        <v>36.77549807400296</v>
+        <v>25.67457089042729</v>
       </c>
       <c r="E3" t="n">
-        <v>17.91934391794683</v>
+        <v>16.95292200863025</v>
       </c>
       <c r="F3" t="n">
-        <v>11.60381013034301</v>
+        <v>8.278189508461443</v>
       </c>
       <c r="G3" t="n">
-        <v>24.82346367262792</v>
+        <v>21.80440568336622</v>
       </c>
       <c r="H3" t="n">
-        <v>22.89558153999033</v>
+        <v>21.04401045411336</v>
       </c>
       <c r="I3" t="n">
-        <v>20.27214399187945</v>
+        <v>20.32681431546153</v>
       </c>
       <c r="J3" t="n">
-        <v>30.22364666171155</v>
+        <v>30.3419732858064</v>
       </c>
       <c r="K3" t="n">
-        <v>27.72490639765674</v>
+        <v>30.51234877698178</v>
       </c>
       <c r="L3" t="n">
-        <v>35.63252865330028</v>
+        <v>25.37190234644115</v>
       </c>
     </row>
     <row r="4">
@@ -7729,31 +7729,31 @@
         <v>11.53928174599518</v>
       </c>
       <c r="D4" t="n">
-        <v>20.36743673788076</v>
+        <v>20.36743673788075</v>
       </c>
       <c r="E4" t="n">
-        <v>11.55888948956252</v>
+        <v>11.55888948956255</v>
       </c>
       <c r="F4" t="n">
-        <v>11.55888948956252</v>
+        <v>11.55888948956255</v>
       </c>
       <c r="G4" t="n">
         <v>14.16085201572669</v>
       </c>
       <c r="H4" t="n">
-        <v>13.19180954222725</v>
+        <v>13.19180954222724</v>
       </c>
       <c r="I4" t="n">
         <v>11.65271215721782</v>
       </c>
       <c r="J4" t="n">
-        <v>13.64316044032882</v>
+        <v>13.64316044032881</v>
       </c>
       <c r="K4" t="n">
-        <v>11.86318418863332</v>
+        <v>11.8631841886333</v>
       </c>
       <c r="L4" t="n">
-        <v>19.77568394772473</v>
+        <v>19.7756839477247</v>
       </c>
     </row>
     <row r="5">
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.30069352828995</v>
+        <v>53.30069352828991</v>
       </c>
       <c r="C5" t="n">
         <v>44.24287216067499</v>
       </c>
       <c r="D5" t="n">
-        <v>174.505069986096</v>
+        <v>174.5050699860957</v>
       </c>
       <c r="E5" t="n">
         <v>44.24288016377557</v>
@@ -7778,22 +7778,22 @@
         <v>44.24288016377557</v>
       </c>
       <c r="G5" t="n">
-        <v>82.25234450167616</v>
+        <v>82.25234450167642</v>
       </c>
       <c r="H5" t="n">
-        <v>70.63443072790838</v>
+        <v>70.63443072790849</v>
       </c>
       <c r="I5" t="n">
-        <v>44.24203032853536</v>
+        <v>44.24203032853533</v>
       </c>
       <c r="J5" t="n">
-        <v>77.2500611007727</v>
+        <v>77.25006110077267</v>
       </c>
       <c r="K5" t="n">
-        <v>43.81013764069088</v>
+        <v>43.8101376406909</v>
       </c>
       <c r="L5" t="n">
-        <v>46.19978984683348</v>
+        <v>199.1197644140229</v>
       </c>
     </row>
     <row r="6">
@@ -7806,31 +7806,31 @@
         <v>42.20559325478584</v>
       </c>
       <c r="C6" t="n">
-        <v>28.95753219643643</v>
+        <v>28.9575321964364</v>
       </c>
       <c r="D6" t="n">
-        <v>37.97783572388146</v>
+        <v>37.97784700187407</v>
       </c>
       <c r="E6" t="n">
-        <v>27.27406400684028</v>
+        <v>27.27406400684027</v>
       </c>
       <c r="F6" t="n">
-        <v>29.04454022456638</v>
+        <v>29.04454022456637</v>
       </c>
       <c r="G6" t="n">
-        <v>31.55550014522043</v>
+        <v>43.93315027930235</v>
       </c>
       <c r="H6" t="n">
         <v>42.69629721098856</v>
       </c>
       <c r="I6" t="n">
-        <v>41.42501042079346</v>
+        <v>41.42501042079347</v>
       </c>
       <c r="J6" t="n">
-        <v>31.96256200096351</v>
+        <v>31.96256200096348</v>
       </c>
       <c r="K6" t="n">
-        <v>29.20387270129699</v>
+        <v>29.20387270129698</v>
       </c>
       <c r="L6" t="n">
         <v>37.21809504375395</v>
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.53160775460651</v>
+        <v>16.53160775460648</v>
       </c>
       <c r="C7" t="n">
         <v>15.75186675275375</v>
       </c>
       <c r="D7" t="n">
-        <v>24.46566756818551</v>
+        <v>24.46566756818546</v>
       </c>
       <c r="E7" t="n">
-        <v>15.74936990608938</v>
+        <v>15.74936990608937</v>
       </c>
       <c r="F7" t="n">
-        <v>15.74936990608938</v>
+        <v>15.74936990608937</v>
       </c>
       <c r="G7" t="n">
-        <v>18.25916477912295</v>
+        <v>18.25916477912297</v>
       </c>
       <c r="H7" t="n">
-        <v>17.29012230562352</v>
+        <v>17.29012230562349</v>
       </c>
       <c r="I7" t="n">
-        <v>15.7510249206141</v>
+        <v>15.75102492061409</v>
       </c>
       <c r="J7" t="n">
-        <v>17.74147320372509</v>
+        <v>17.74147320372507</v>
       </c>
       <c r="K7" t="n">
-        <v>15.96149695202959</v>
+        <v>15.96149695202957</v>
       </c>
       <c r="L7" t="n">
-        <v>23.87399671112101</v>
+        <v>23.87399671112097</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.5330990737289</v>
+        <v>28.53309907372887</v>
       </c>
       <c r="C8" t="n">
-        <v>38.34389415469673</v>
+        <v>38.34389415469671</v>
       </c>
       <c r="D8" t="n">
-        <v>49.25405367854923</v>
+        <v>49.25405367854916</v>
       </c>
       <c r="E8" t="n">
-        <v>35.44743447755607</v>
+        <v>35.44743447755601</v>
       </c>
       <c r="F8" t="n">
         <v>28.08763115752007</v>
       </c>
       <c r="G8" t="n">
-        <v>40.85140763322241</v>
+        <v>40.85140763322239</v>
       </c>
       <c r="H8" t="n">
-        <v>39.88236515972292</v>
+        <v>39.88236515972287</v>
       </c>
       <c r="I8" t="n">
-        <v>38.34326777471355</v>
+        <v>38.34326777471352</v>
       </c>
       <c r="J8" t="n">
-        <v>40.33579744481567</v>
+        <v>40.33579744481564</v>
       </c>
       <c r="K8" t="n">
-        <v>27.76625962401604</v>
+        <v>27.766259624016</v>
       </c>
       <c r="L8" t="n">
-        <v>57.5291651285424</v>
+        <v>57.52916512854227</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.45993888134693</v>
+        <v>25.4599388813469</v>
       </c>
       <c r="C9" t="n">
-        <v>28.43996019883993</v>
+        <v>28.43996019883996</v>
       </c>
       <c r="D9" t="n">
-        <v>37.15384485513817</v>
+        <v>37.15384485513816</v>
       </c>
       <c r="E9" t="n">
         <v>32.77865435143035</v>
       </c>
       <c r="F9" t="n">
-        <v>28.43996694450926</v>
+        <v>28.43996694450928</v>
       </c>
       <c r="G9" t="n">
-        <v>30.94725822520913</v>
+        <v>30.94725822520918</v>
       </c>
       <c r="H9" t="n">
-        <v>29.97821575170973</v>
+        <v>29.97821575170972</v>
       </c>
       <c r="I9" t="n">
         <v>28.43911836670032</v>
       </c>
       <c r="J9" t="n">
-        <v>30.42956664981131</v>
+        <v>30.42956664981128</v>
       </c>
       <c r="K9" t="n">
-        <v>23.91537802840699</v>
+        <v>26.471170146965</v>
       </c>
       <c r="L9" t="n">
-        <v>36.56209015720722</v>
+        <v>36.56209015720719</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.33991348475567</v>
+        <v>21.33991348475571</v>
       </c>
       <c r="C2" t="n">
-        <v>17.41919829146524</v>
+        <v>17.41919829146521</v>
       </c>
       <c r="D2" t="n">
-        <v>22.26140876694653</v>
+        <v>22.26140876694656</v>
       </c>
       <c r="E2" t="n">
-        <v>19.33046084864236</v>
+        <v>19.33046084864235</v>
       </c>
       <c r="F2" t="n">
-        <v>13.96735192430232</v>
+        <v>13.96735192430233</v>
       </c>
       <c r="G2" t="n">
-        <v>21.68633323518562</v>
+        <v>21.68633323518564</v>
       </c>
       <c r="H2" t="n">
-        <v>22.8421648861414</v>
+        <v>22.84216488614142</v>
       </c>
       <c r="I2" t="n">
-        <v>21.30725334942071</v>
+        <v>21.30725334942072</v>
       </c>
       <c r="J2" t="n">
         <v>27.17077269095305</v>
       </c>
       <c r="K2" t="n">
-        <v>27.77094870012874</v>
+        <v>27.77094870012876</v>
       </c>
       <c r="L2" t="n">
-        <v>22.67956394717066</v>
+        <v>22.67956394717067</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.86941746753847</v>
+        <v>21.86941746753849</v>
       </c>
       <c r="C3" t="n">
-        <v>15.31917975180637</v>
+        <v>15.31917975180635</v>
       </c>
       <c r="D3" t="n">
-        <v>28.43153281167445</v>
+        <v>28.43153281167447</v>
       </c>
       <c r="E3" t="n">
         <v>18.46344189863041</v>
       </c>
       <c r="F3" t="n">
-        <v>9.608907407295769</v>
+        <v>9.608907407295771</v>
       </c>
       <c r="G3" t="n">
-        <v>24.34283331561892</v>
+        <v>24.34283331561895</v>
       </c>
       <c r="H3" t="n">
-        <v>33.43013135612891</v>
+        <v>33.43013135612892</v>
       </c>
       <c r="I3" t="n">
-        <v>21.63879096026018</v>
+        <v>21.6387909602602</v>
       </c>
       <c r="J3" t="n">
-        <v>32.708048861794</v>
+        <v>32.70804886179398</v>
       </c>
       <c r="K3" t="n">
         <v>32.99818610143582</v>
       </c>
       <c r="L3" t="n">
-        <v>31.44465313567576</v>
+        <v>31.44465313567578</v>
       </c>
     </row>
     <row r="4">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.04976533365194</v>
+        <v>14.04976533365193</v>
       </c>
       <c r="C4" t="n">
-        <v>13.33304862022392</v>
+        <v>13.33304862022391</v>
       </c>
       <c r="D4" t="n">
-        <v>24.45847845477072</v>
+        <v>24.45847845477071</v>
       </c>
       <c r="E4" t="n">
         <v>13.35841075584037</v>
@@ -610,7 +610,7 @@
         <v>13.35841075584037</v>
       </c>
       <c r="G4" t="n">
-        <v>17.93202097655923</v>
+        <v>17.93202097655919</v>
       </c>
       <c r="H4" t="n">
         <v>32.45446690165753</v>
@@ -619,13 +619,13 @@
         <v>13.48462719554326</v>
       </c>
       <c r="J4" t="n">
-        <v>16.53263945164343</v>
+        <v>16.53263945164342</v>
       </c>
       <c r="K4" t="n">
-        <v>15.10590963562127</v>
+        <v>15.10590963562126</v>
       </c>
       <c r="L4" t="n">
-        <v>29.07402429668755</v>
+        <v>29.07402429668753</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.59701105872392</v>
+        <v>79.59701105872398</v>
       </c>
       <c r="C5" t="n">
-        <v>73.44133928556903</v>
+        <v>73.44133928556923</v>
       </c>
       <c r="D5" t="n">
         <v>280.5033847264611</v>
       </c>
       <c r="E5" t="n">
-        <v>73.4413474351433</v>
+        <v>73.44134743514334</v>
       </c>
       <c r="F5" t="n">
-        <v>73.4413474351433</v>
+        <v>73.44134743514334</v>
       </c>
       <c r="G5" t="n">
-        <v>158.9599411771653</v>
+        <v>158.9599411771644</v>
       </c>
       <c r="H5" t="n">
-        <v>485.1872853426911</v>
+        <v>485.1872853426908</v>
       </c>
       <c r="I5" t="n">
-        <v>73.44005007081034</v>
+        <v>73.44005007081059</v>
       </c>
       <c r="J5" t="n">
         <v>134.2108606077594</v>
       </c>
       <c r="K5" t="n">
-        <v>100.9744064976925</v>
+        <v>100.9744064976927</v>
       </c>
       <c r="L5" t="n">
-        <v>425.3055222804073</v>
+        <v>425.3055222804078</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.15619584384057</v>
+        <v>34.15619584384056</v>
       </c>
       <c r="C6" t="n">
-        <v>33.4400218142985</v>
+        <v>33.44002181429855</v>
       </c>
       <c r="D6" t="n">
-        <v>44.85086315789158</v>
+        <v>44.85086315789164</v>
       </c>
       <c r="E6" t="n">
-        <v>31.50009286972811</v>
+        <v>31.50009286972808</v>
       </c>
       <c r="F6" t="n">
-        <v>33.58928665718595</v>
+        <v>33.58928665718599</v>
       </c>
       <c r="G6" t="n">
-        <v>52.63330557155308</v>
+        <v>52.63330557155306</v>
       </c>
       <c r="H6" t="n">
-        <v>66.92466659175615</v>
+        <v>66.92466659175616</v>
       </c>
       <c r="I6" t="n">
-        <v>48.1859117905372</v>
+        <v>48.18591179053721</v>
       </c>
       <c r="J6" t="n">
-        <v>50.88221659732611</v>
+        <v>50.88221659732609</v>
       </c>
       <c r="K6" t="n">
-        <v>35.15971827063553</v>
+        <v>35.15971827063557</v>
       </c>
       <c r="L6" t="n">
-        <v>49.28885621042182</v>
+        <v>49.28885621042178</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.18459995937147</v>
+        <v>19.1845999593715</v>
       </c>
       <c r="C7" t="n">
-        <v>18.62075103602142</v>
+        <v>18.6207510360214</v>
       </c>
       <c r="D7" t="n">
-        <v>29.59321388130522</v>
+        <v>29.59321388130521</v>
       </c>
       <c r="E7" t="n">
-        <v>18.6182833953319</v>
+        <v>18.61828339533189</v>
       </c>
       <c r="F7" t="n">
-        <v>18.6182833953319</v>
+        <v>18.61828339533189</v>
       </c>
       <c r="G7" t="n">
         <v>23.0668556022787</v>
       </c>
       <c r="H7" t="n">
-        <v>37.58930152737705</v>
+        <v>37.58930152737704</v>
       </c>
       <c r="I7" t="n">
         <v>18.61946182126279</v>
       </c>
       <c r="J7" t="n">
-        <v>21.66747407736295</v>
+        <v>21.66747407736298</v>
       </c>
       <c r="K7" t="n">
-        <v>20.24074426134079</v>
+        <v>20.24074426134077</v>
       </c>
       <c r="L7" t="n">
-        <v>34.20885892240707</v>
+        <v>34.20885892240703</v>
       </c>
     </row>
     <row r="8">
@@ -758,10 +758,10 @@
         <v>33.2774559076496</v>
       </c>
       <c r="C8" t="n">
-        <v>45.42452083337679</v>
+        <v>45.42452083337682</v>
       </c>
       <c r="D8" t="n">
-        <v>59.03247250449435</v>
+        <v>59.03247250449438</v>
       </c>
       <c r="E8" t="n">
         <v>41.94823185508287</v>
@@ -770,22 +770,22 @@
         <v>33.11510581659032</v>
       </c>
       <c r="G8" t="n">
-        <v>49.8703759588762</v>
+        <v>49.87037595887627</v>
       </c>
       <c r="H8" t="n">
-        <v>64.39282188397523</v>
+        <v>64.39282188397529</v>
       </c>
       <c r="I8" t="n">
-        <v>45.42298217786029</v>
+        <v>45.42298217786032</v>
       </c>
       <c r="J8" t="n">
-        <v>48.4734924446032</v>
+        <v>48.47349244460318</v>
       </c>
       <c r="K8" t="n">
-        <v>34.09749309249644</v>
+        <v>34.09749309249643</v>
       </c>
       <c r="L8" t="n">
-        <v>74.28973110278305</v>
+        <v>74.28973110278312</v>
       </c>
     </row>
     <row r="9">
@@ -798,16 +798,16 @@
         <v>32.89833123701077</v>
       </c>
       <c r="C9" t="n">
-        <v>37.76199643219198</v>
+        <v>37.76199643219199</v>
       </c>
       <c r="D9" t="n">
         <v>48.73455740489241</v>
       </c>
       <c r="E9" t="n">
-        <v>44.02523169340934</v>
+        <v>44.02523169340939</v>
       </c>
       <c r="F9" t="n">
-        <v>37.76199807744456</v>
+        <v>37.76199807744457</v>
       </c>
       <c r="G9" t="n">
         <v>42.20810099844927</v>
@@ -816,16 +816,16 @@
         <v>56.73054692354761</v>
       </c>
       <c r="I9" t="n">
-        <v>37.76070721743336</v>
+        <v>37.76070721743337</v>
       </c>
       <c r="J9" t="n">
         <v>40.80871947353351</v>
       </c>
       <c r="K9" t="n">
-        <v>32.54778085221869</v>
+        <v>32.54778085221868</v>
       </c>
       <c r="L9" t="n">
-        <v>53.35010431857766</v>
+        <v>53.35010431857764</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.26956749029967</v>
+        <v>20.26956749029962</v>
       </c>
       <c r="C2" t="n">
-        <v>16.30103385784642</v>
+        <v>16.30103385784644</v>
       </c>
       <c r="D2" t="n">
-        <v>20.24850591245767</v>
+        <v>20.24850591245758</v>
       </c>
       <c r="E2" t="n">
-        <v>18.15794706717953</v>
+        <v>18.15794706717949</v>
       </c>
       <c r="F2" t="n">
-        <v>12.9372799257134</v>
+        <v>12.93727992571334</v>
       </c>
       <c r="G2" t="n">
-        <v>20.25417354428065</v>
+        <v>20.25417354428069</v>
       </c>
       <c r="H2" t="n">
-        <v>20.10001209066036</v>
+        <v>20.10001209066037</v>
       </c>
       <c r="I2" t="n">
-        <v>20.23911395815743</v>
+        <v>20.23911395815735</v>
       </c>
       <c r="J2" t="n">
         <v>25.69634799173861</v>
       </c>
       <c r="K2" t="n">
-        <v>26.36003245726499</v>
+        <v>26.36003245726492</v>
       </c>
       <c r="L2" t="n">
-        <v>20.18506366345935</v>
+        <v>20.185063663459</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.33944495077643</v>
+        <v>20.33944495077644</v>
       </c>
       <c r="C3" t="n">
-        <v>13.71639962845308</v>
+        <v>13.7163996284531</v>
       </c>
       <c r="D3" t="n">
-        <v>20.19070695996551</v>
+        <v>20.19070695996549</v>
       </c>
       <c r="E3" t="n">
-        <v>16.7769055554436</v>
+        <v>16.77690555544359</v>
       </c>
       <c r="F3" t="n">
-        <v>8.15750074498775</v>
+        <v>8.157500744987729</v>
       </c>
       <c r="G3" t="n">
-        <v>20.2319777035631</v>
+        <v>20.23197770356305</v>
       </c>
       <c r="H3" t="n">
-        <v>19.99279074238479</v>
+        <v>19.99279074238481</v>
       </c>
       <c r="I3" t="n">
-        <v>20.12453667971762</v>
+        <v>20.12453667971766</v>
       </c>
       <c r="J3" t="n">
-        <v>29.71380391130236</v>
+        <v>29.71380391130239</v>
       </c>
       <c r="K3" t="n">
-        <v>29.97872801456194</v>
+        <v>29.97872801456196</v>
       </c>
       <c r="L3" t="n">
-        <v>19.76944187547963</v>
+        <v>19.76944187547948</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.09397264279856</v>
+        <v>12.09397264279853</v>
       </c>
       <c r="C4" t="n">
-        <v>11.48331444459971</v>
+        <v>11.48331444459972</v>
       </c>
       <c r="D4" t="n">
         <v>11.8560724322686</v>
       </c>
       <c r="E4" t="n">
-        <v>11.50066907907142</v>
+        <v>11.50066907907138</v>
       </c>
       <c r="F4" t="n">
-        <v>11.5006690790714</v>
+        <v>11.50066907907138</v>
       </c>
       <c r="G4" t="n">
-        <v>11.89202554482191</v>
+        <v>11.89202554482188</v>
       </c>
       <c r="H4" t="n">
-        <v>11.7510621815114</v>
+        <v>11.75106218151138</v>
       </c>
       <c r="I4" t="n">
-        <v>11.57160327155943</v>
+        <v>11.57160327155941</v>
       </c>
       <c r="J4" t="n">
-        <v>12.94194644196216</v>
+        <v>12.94194644196214</v>
       </c>
       <c r="K4" t="n">
-        <v>11.23541060914301</v>
+        <v>11.235410609143</v>
       </c>
       <c r="L4" t="n">
-        <v>11.18278299329037</v>
+        <v>11.18278299329036</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.21824640037836</v>
+        <v>50.2182464003784</v>
       </c>
       <c r="C5" t="n">
-        <v>45.22075461701554</v>
+        <v>45.22075461701552</v>
       </c>
       <c r="D5" t="n">
-        <v>46.82914532644301</v>
+        <v>46.82914532644308</v>
       </c>
       <c r="E5" t="n">
-        <v>45.22076243188565</v>
+        <v>45.2207624318856</v>
       </c>
       <c r="F5" t="n">
-        <v>45.22076243188565</v>
+        <v>45.2207624318856</v>
       </c>
       <c r="G5" t="n">
-        <v>48.35859393639856</v>
+        <v>48.35859393640012</v>
       </c>
       <c r="H5" t="n">
-        <v>48.92684167565056</v>
+        <v>48.92684167565061</v>
       </c>
       <c r="I5" t="n">
-        <v>45.22041523977281</v>
+        <v>45.22041523977287</v>
       </c>
       <c r="J5" t="n">
-        <v>67.59535491083241</v>
+        <v>67.59535491083207</v>
       </c>
       <c r="K5" t="n">
-        <v>36.52126098335812</v>
+        <v>36.52126098335808</v>
       </c>
       <c r="L5" t="n">
-        <v>39.06091064793521</v>
+        <v>39.06091064793513</v>
       </c>
     </row>
     <row r="6">
@@ -1074,31 +1074,31 @@
         <v>29.42662357067469</v>
       </c>
       <c r="C6" t="n">
-        <v>28.8673361442126</v>
+        <v>28.86733614421262</v>
       </c>
       <c r="D6" t="n">
-        <v>41.06372966580032</v>
+        <v>41.06372966580038</v>
       </c>
       <c r="E6" t="n">
-        <v>27.18603212328019</v>
+        <v>27.18603212328016</v>
       </c>
       <c r="F6" t="n">
-        <v>28.90905866488247</v>
+        <v>28.90905866488244</v>
       </c>
       <c r="G6" t="n">
         <v>41.38418461545749</v>
       </c>
       <c r="H6" t="n">
-        <v>40.97173834651716</v>
+        <v>40.97173834651717</v>
       </c>
       <c r="I6" t="n">
-        <v>28.90425419943559</v>
+        <v>28.90425419943557</v>
       </c>
       <c r="J6" t="n">
-        <v>31.19360245189786</v>
+        <v>31.19360245189783</v>
       </c>
       <c r="K6" t="n">
-        <v>28.54379731239861</v>
+        <v>28.54379731239857</v>
       </c>
       <c r="L6" t="n">
         <v>28.51905313959864</v>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.05969257427959</v>
+        <v>16.05969257427958</v>
       </c>
       <c r="C7" t="n">
-        <v>15.5376625802831</v>
+        <v>15.53766258028315</v>
       </c>
       <c r="D7" t="n">
-        <v>15.82171075333508</v>
+        <v>15.82171075333504</v>
       </c>
       <c r="E7" t="n">
-        <v>15.53582027475669</v>
+        <v>15.53582027475663</v>
       </c>
       <c r="F7" t="n">
-        <v>15.53582027475669</v>
+        <v>15.53582027475663</v>
       </c>
       <c r="G7" t="n">
-        <v>15.85774547630291</v>
+        <v>15.85774547630292</v>
       </c>
       <c r="H7" t="n">
-        <v>15.71678211299243</v>
+        <v>15.7167821129924</v>
       </c>
       <c r="I7" t="n">
-        <v>15.53732320304045</v>
+        <v>15.5373232030404</v>
       </c>
       <c r="J7" t="n">
-        <v>16.90766637344316</v>
+        <v>16.90766637344318</v>
       </c>
       <c r="K7" t="n">
-        <v>15.20113054062405</v>
+        <v>15.20113054062402</v>
       </c>
       <c r="L7" t="n">
-        <v>15.14850292477133</v>
+        <v>15.14850292477136</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.91723713816794</v>
+        <v>27.91723713816792</v>
       </c>
       <c r="C8" t="n">
-        <v>37.78234465725423</v>
+        <v>37.78234465725424</v>
       </c>
       <c r="D8" t="n">
-        <v>40.21986793966763</v>
+        <v>40.21986793966769</v>
       </c>
       <c r="E8" t="n">
-        <v>34.94161037345668</v>
+        <v>34.94161037345667</v>
       </c>
       <c r="F8" t="n">
-        <v>27.72340443764907</v>
+        <v>27.72340443764903</v>
       </c>
       <c r="G8" t="n">
-        <v>38.10205721496813</v>
+        <v>38.10205721496812</v>
       </c>
       <c r="H8" t="n">
-        <v>37.96109385165778</v>
+        <v>37.96109385165782</v>
       </c>
       <c r="I8" t="n">
         <v>37.78163494170563</v>
       </c>
       <c r="J8" t="n">
-        <v>39.15401941040133</v>
+        <v>39.1540194104013</v>
       </c>
       <c r="K8" t="n">
-        <v>26.86573557158448</v>
+        <v>26.86573557158451</v>
       </c>
       <c r="L8" t="n">
-        <v>48.24266150570379</v>
+        <v>48.24266150570389</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.84325019629256</v>
+        <v>23.84325019629253</v>
       </c>
       <c r="C9" t="n">
-        <v>26.71541463645304</v>
+        <v>26.71541463645307</v>
       </c>
       <c r="D9" t="n">
-        <v>26.99954557599547</v>
+        <v>26.9995455759955</v>
       </c>
       <c r="E9" t="n">
-        <v>30.63225082512735</v>
+        <v>30.63225082512741</v>
       </c>
       <c r="F9" t="n">
-        <v>26.71542158753277</v>
+        <v>26.7154215875328</v>
       </c>
       <c r="G9" t="n">
-        <v>27.03549753247286</v>
+        <v>27.03549753247287</v>
       </c>
       <c r="H9" t="n">
-        <v>26.89453416916226</v>
+        <v>26.89453416916233</v>
       </c>
       <c r="I9" t="n">
-        <v>26.71507525921038</v>
+        <v>26.71507525921034</v>
       </c>
       <c r="J9" t="n">
-        <v>28.08541842961311</v>
+        <v>28.08541842961314</v>
       </c>
       <c r="K9" t="n">
-        <v>24.41227349785589</v>
+        <v>24.41227349785576</v>
       </c>
       <c r="L9" t="n">
-        <v>26.32625498094123</v>
+        <v>26.32625498094129</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.09320250457098</v>
+        <v>20.09320250457101</v>
       </c>
       <c r="C2" t="n">
-        <v>11.47937714976199</v>
+        <v>11.47937714976198</v>
       </c>
       <c r="D2" t="n">
-        <v>20.68467129694833</v>
+        <v>20.68467129694837</v>
       </c>
       <c r="E2" t="n">
         <v>12.52308593039655</v>
       </c>
       <c r="F2" t="n">
-        <v>12.525759824487</v>
+        <v>12.52575982448703</v>
       </c>
       <c r="G2" t="n">
-        <v>20.35009941317463</v>
+        <v>20.3500994131746</v>
       </c>
       <c r="H2" t="n">
-        <v>20.79699147892</v>
+        <v>20.79699147892001</v>
       </c>
       <c r="I2" t="n">
-        <v>20.14137268337615</v>
+        <v>20.14137268337616</v>
       </c>
       <c r="J2" t="n">
-        <v>19.12340805029738</v>
+        <v>19.12340805029744</v>
       </c>
       <c r="K2" t="n">
-        <v>29.49466647623669</v>
+        <v>29.49466647623668</v>
       </c>
       <c r="L2" t="n">
-        <v>20.3478030838472</v>
+        <v>20.34780308384721</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.55138031294576</v>
+        <v>21.5513803129458</v>
       </c>
       <c r="C3" t="n">
-        <v>7.415545075124289</v>
+        <v>7.415545075124271</v>
       </c>
       <c r="D3" t="n">
-        <v>25.77679894386842</v>
+        <v>25.77679894386846</v>
       </c>
       <c r="E3" t="n">
-        <v>9.420363443010025</v>
+        <v>9.420363443010022</v>
       </c>
       <c r="F3" t="n">
-        <v>9.423037337100565</v>
+        <v>9.423037337100501</v>
       </c>
       <c r="G3" t="n">
         <v>23.39779029616255</v>
       </c>
       <c r="H3" t="n">
-        <v>27.44037874880471</v>
+        <v>27.44037874880473</v>
       </c>
       <c r="I3" t="n">
-        <v>21.90803887047647</v>
+        <v>21.9080388704765</v>
       </c>
       <c r="J3" t="n">
         <v>21.6422219260717</v>
       </c>
       <c r="K3" t="n">
-        <v>37.79661620163262</v>
+        <v>37.79661620163259</v>
       </c>
       <c r="L3" t="n">
-        <v>23.42115929401099</v>
+        <v>23.42115929401098</v>
       </c>
     </row>
     <row r="4">
@@ -1387,25 +1387,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.72587477958611</v>
+        <v>11.7258747795861</v>
       </c>
       <c r="C4" t="n">
-        <v>11.47176050868657</v>
+        <v>11.47176050868658</v>
       </c>
       <c r="D4" t="n">
         <v>18.40678687857539</v>
       </c>
       <c r="E4" t="n">
-        <v>11.98665482707028</v>
+        <v>11.98665482707029</v>
       </c>
       <c r="F4" t="n">
         <v>11.98665482707028</v>
       </c>
       <c r="G4" t="n">
-        <v>14.59879303847953</v>
+        <v>14.59879303847952</v>
       </c>
       <c r="H4" t="n">
-        <v>21.18578702305131</v>
+        <v>21.1857870230513</v>
       </c>
       <c r="I4" t="n">
         <v>12.08639915951016</v>
@@ -1414,10 +1414,10 @@
         <v>15.17490164378918</v>
       </c>
       <c r="K4" t="n">
-        <v>13.19796867627473</v>
+        <v>13.19796867627472</v>
       </c>
       <c r="L4" t="n">
-        <v>14.64299701492616</v>
+        <v>14.64299701492615</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.71726375391233</v>
+        <v>32.71726375391231</v>
       </c>
       <c r="C5" t="n">
-        <v>39.50784719718195</v>
+        <v>39.50784719718211</v>
       </c>
       <c r="D5" t="n">
         <v>159.3277722255965</v>
       </c>
       <c r="E5" t="n">
-        <v>49.70335805625155</v>
+        <v>49.70335805625169</v>
       </c>
       <c r="F5" t="n">
-        <v>49.70335805625155</v>
+        <v>49.70335805625172</v>
       </c>
       <c r="G5" t="n">
-        <v>93.78239060880779</v>
+        <v>93.78239060880759</v>
       </c>
       <c r="H5" t="n">
-        <v>233.7014218995841</v>
+        <v>233.7014218995847</v>
       </c>
       <c r="I5" t="n">
-        <v>49.70250527049754</v>
+        <v>49.70250527049785</v>
       </c>
       <c r="J5" t="n">
-        <v>105.914180801163</v>
+        <v>105.9141808011629</v>
       </c>
       <c r="K5" t="n">
-        <v>66.35065006306124</v>
+        <v>66.35065006306128</v>
       </c>
       <c r="L5" t="n">
-        <v>103.5751992413302</v>
+        <v>103.5751992413301</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.13919577876917</v>
+        <v>43.13919577876919</v>
       </c>
       <c r="C6" t="n">
-        <v>29.85884218066525</v>
+        <v>29.85884218066523</v>
       </c>
       <c r="D6" t="n">
-        <v>36.88368071379606</v>
+        <v>36.88368071379607</v>
       </c>
       <c r="E6" t="n">
-        <v>28.54277812864488</v>
+        <v>28.54277812864487</v>
       </c>
       <c r="F6" t="n">
-        <v>30.41622618368532</v>
+        <v>30.41622618368535</v>
       </c>
       <c r="G6" t="n">
-        <v>32.93069406884803</v>
+        <v>32.93069406884807</v>
       </c>
       <c r="H6" t="n">
-        <v>52.56231942528726</v>
+        <v>52.56231942528728</v>
       </c>
       <c r="I6" t="n">
-        <v>30.41830018987871</v>
+        <v>30.41830018987874</v>
       </c>
       <c r="J6" t="n">
-        <v>46.34340188335381</v>
+        <v>46.34340188335384</v>
       </c>
       <c r="K6" t="n">
         <v>31.50320457939225</v>
       </c>
       <c r="L6" t="n">
-        <v>32.9932978345191</v>
+        <v>32.99329783451911</v>
       </c>
     </row>
     <row r="7">
@@ -1516,28 +1516,28 @@
         <v>22.98212135486207</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66298960956792</v>
+        <v>16.66298960956794</v>
       </c>
       <c r="F7" t="n">
-        <v>16.66298960956792</v>
+        <v>16.66298960956795</v>
       </c>
       <c r="G7" t="n">
-        <v>19.17419765467321</v>
+        <v>19.17419765467322</v>
       </c>
       <c r="H7" t="n">
-        <v>25.761191639245</v>
+        <v>25.76119163924504</v>
       </c>
       <c r="I7" t="n">
-        <v>16.66180377570386</v>
+        <v>16.66180377570388</v>
       </c>
       <c r="J7" t="n">
-        <v>19.75030625998289</v>
+        <v>19.7503062599829</v>
       </c>
       <c r="K7" t="n">
-        <v>17.77337329246842</v>
+        <v>17.77337329246843</v>
       </c>
       <c r="L7" t="n">
-        <v>19.21840163111986</v>
+        <v>19.21840163111985</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.2073657287896</v>
+        <v>29.20736572878955</v>
       </c>
       <c r="C8" t="n">
         <v>40.69037905861177</v>
       </c>
       <c r="D8" t="n">
-        <v>49.84003798729351</v>
+        <v>49.84003798729356</v>
       </c>
       <c r="E8" t="n">
-        <v>37.96638660447809</v>
+        <v>37.96638660447806</v>
       </c>
       <c r="F8" t="n">
-        <v>29.93527891183327</v>
+        <v>29.9352789118333</v>
       </c>
       <c r="G8" t="n">
-        <v>43.63590984722539</v>
+        <v>43.63590984722535</v>
       </c>
       <c r="H8" t="n">
-        <v>50.22290383180867</v>
+        <v>50.22290383180872</v>
       </c>
       <c r="I8" t="n">
-        <v>41.12351596825605</v>
+        <v>41.123515968256</v>
       </c>
       <c r="J8" t="n">
-        <v>44.21428946495534</v>
+        <v>44.21428946495539</v>
       </c>
       <c r="K8" t="n">
-        <v>30.46480794238067</v>
+        <v>30.46480794238062</v>
       </c>
       <c r="L8" t="n">
-        <v>55.75093130052854</v>
+        <v>55.75093130052846</v>
       </c>
     </row>
     <row r="9">
@@ -1587,34 +1587,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.4705330559462</v>
+        <v>26.47053305594618</v>
       </c>
       <c r="C9" t="n">
-        <v>30.66798512037435</v>
+        <v>30.66798512037437</v>
       </c>
       <c r="D9" t="n">
-        <v>37.42418744712518</v>
+        <v>37.42418744712525</v>
       </c>
       <c r="E9" t="n">
-        <v>36.03530203397547</v>
+        <v>36.03530203397545</v>
       </c>
       <c r="F9" t="n">
-        <v>31.10464892320673</v>
+        <v>31.10464892320675</v>
       </c>
       <c r="G9" t="n">
-        <v>33.61619304557777</v>
+        <v>33.61619304557785</v>
       </c>
       <c r="H9" t="n">
-        <v>40.20318703014958</v>
+        <v>40.20318703014965</v>
       </c>
       <c r="I9" t="n">
-        <v>31.1037991666085</v>
+        <v>31.10379916660847</v>
       </c>
       <c r="J9" t="n">
-        <v>34.19230165088746</v>
+        <v>34.19230165088749</v>
       </c>
       <c r="K9" t="n">
-        <v>29.73972558037758</v>
+        <v>29.73972558037761</v>
       </c>
       <c r="L9" t="n">
         <v>33.66039702202445</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.67467414365947</v>
+        <v>19.67467414365952</v>
       </c>
       <c r="C2" t="n">
-        <v>11.32985763492817</v>
+        <v>11.32985763492814</v>
       </c>
       <c r="D2" t="n">
-        <v>20.10264350614425</v>
+        <v>20.10264350614428</v>
       </c>
       <c r="E2" t="n">
-        <v>12.30621249387135</v>
+        <v>12.30621249387137</v>
       </c>
       <c r="F2" t="n">
-        <v>12.30888515525465</v>
+        <v>12.30888515525467</v>
       </c>
       <c r="G2" t="n">
-        <v>19.83486084781522</v>
+        <v>19.83486084781528</v>
       </c>
       <c r="H2" t="n">
-        <v>19.98840729122223</v>
+        <v>19.98840729122221</v>
       </c>
       <c r="I2" t="n">
-        <v>19.70248383823705</v>
+        <v>19.70248383823708</v>
       </c>
       <c r="J2" t="n">
-        <v>18.79979409683693</v>
+        <v>18.79979409683694</v>
       </c>
       <c r="K2" t="n">
-        <v>29.20634360688329</v>
+        <v>29.20634360688324</v>
       </c>
       <c r="L2" t="n">
-        <v>19.73108709485559</v>
+        <v>19.73108709485558</v>
       </c>
     </row>
     <row r="3">
@@ -1743,19 +1743,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.87451350253848</v>
+        <v>20.87451350253851</v>
       </c>
       <c r="C3" t="n">
-        <v>7.348925338906149</v>
+        <v>7.348925338906154</v>
       </c>
       <c r="D3" t="n">
-        <v>23.93575091220836</v>
+        <v>23.93575091220839</v>
       </c>
       <c r="E3" t="n">
-        <v>8.965057339553608</v>
+        <v>8.965057339553629</v>
       </c>
       <c r="F3" t="n">
-        <v>8.967730000936903</v>
+        <v>8.967730000936925</v>
       </c>
       <c r="G3" t="n">
         <v>22.03111986796621</v>
@@ -1764,16 +1764,16 @@
         <v>23.98259707356003</v>
       </c>
       <c r="I3" t="n">
-        <v>21.08626410643711</v>
+        <v>21.08626410643712</v>
       </c>
       <c r="J3" t="n">
         <v>20.49763687185377</v>
       </c>
       <c r="K3" t="n">
-        <v>36.92231154831357</v>
+        <v>36.92231154831351</v>
       </c>
       <c r="L3" t="n">
-        <v>21.32698469207796</v>
+        <v>21.32698469207795</v>
       </c>
     </row>
     <row r="4">
@@ -1786,34 +1786,34 @@
         <v>11.30505106652315</v>
       </c>
       <c r="C4" t="n">
-        <v>11.4089587777435</v>
+        <v>11.40895877774344</v>
       </c>
       <c r="D4" t="n">
-        <v>16.13916189142223</v>
+        <v>16.13916189142221</v>
       </c>
       <c r="E4" t="n">
+        <v>11.37311050800349</v>
+      </c>
+      <c r="F4" t="n">
         <v>11.37311050800348</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11.37311050800349</v>
       </c>
       <c r="G4" t="n">
         <v>13.08610742579154</v>
       </c>
       <c r="H4" t="n">
-        <v>16.38884808015848</v>
+        <v>16.38884808015847</v>
       </c>
       <c r="I4" t="n">
-        <v>11.43915864204685</v>
+        <v>11.43915864204684</v>
       </c>
       <c r="J4" t="n">
-        <v>13.46985604774521</v>
+        <v>13.46985604774523</v>
       </c>
       <c r="K4" t="n">
-        <v>11.92558364871042</v>
+        <v>11.92558364871044</v>
       </c>
       <c r="L4" t="n">
-        <v>11.99487552243337</v>
+        <v>11.99487552243334</v>
       </c>
     </row>
     <row r="5">
@@ -1823,34 +1823,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.32119199888992</v>
+        <v>26.32119199888999</v>
       </c>
       <c r="C5" t="n">
-        <v>38.78588915372828</v>
+        <v>38.78588915372794</v>
       </c>
       <c r="D5" t="n">
-        <v>115.343690850935</v>
+        <v>115.3436908509352</v>
       </c>
       <c r="E5" t="n">
-        <v>38.57520006229555</v>
+        <v>38.57520006229542</v>
       </c>
       <c r="F5" t="n">
-        <v>38.57520006229564</v>
+        <v>38.57520006229542</v>
       </c>
       <c r="G5" t="n">
-        <v>65.21094165128484</v>
+        <v>65.21094165128517</v>
       </c>
       <c r="H5" t="n">
-        <v>132.9345590789407</v>
+        <v>132.9345590789405</v>
       </c>
       <c r="I5" t="n">
-        <v>38.57454625135021</v>
+        <v>38.57454625135018</v>
       </c>
       <c r="J5" t="n">
-        <v>72.7953482909856</v>
+        <v>72.79534829098559</v>
       </c>
       <c r="K5" t="n">
-        <v>43.84206547802651</v>
+        <v>43.84206547802655</v>
       </c>
       <c r="L5" t="n">
         <v>49.54077501834426</v>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.91744633614648</v>
+        <v>40.91744633614645</v>
       </c>
       <c r="C6" t="n">
-        <v>28.80401060934991</v>
+        <v>28.80401060934999</v>
       </c>
       <c r="D6" t="n">
-        <v>45.57164704939016</v>
+        <v>45.57164704939013</v>
       </c>
       <c r="E6" t="n">
-        <v>26.99640608864457</v>
+        <v>26.99640608864463</v>
       </c>
       <c r="F6" t="n">
-        <v>28.75050920356975</v>
+        <v>28.75050920356976</v>
       </c>
       <c r="G6" t="n">
         <v>42.69850269541482</v>
       </c>
       <c r="H6" t="n">
-        <v>46.06245462025505</v>
+        <v>46.06245462025501</v>
       </c>
       <c r="I6" t="n">
-        <v>28.75032432891961</v>
+        <v>28.75032432891959</v>
       </c>
       <c r="J6" t="n">
-        <v>31.70544804543066</v>
+        <v>31.70544804543067</v>
       </c>
       <c r="K6" t="n">
-        <v>29.20662798418495</v>
+        <v>29.20662798418509</v>
       </c>
       <c r="L6" t="n">
-        <v>29.31085610437889</v>
+        <v>29.3108561043789</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.55584963127124</v>
+        <v>15.55584963127123</v>
       </c>
       <c r="C7" t="n">
-        <v>15.82705193922481</v>
+        <v>15.82705193922472</v>
       </c>
       <c r="D7" t="n">
         <v>20.38989849700125</v>
       </c>
       <c r="E7" t="n">
-        <v>15.69807407586821</v>
+        <v>15.69807407586823</v>
       </c>
       <c r="F7" t="n">
-        <v>15.69807407586821</v>
+        <v>15.69807407586823</v>
       </c>
       <c r="G7" t="n">
-        <v>17.33690599053965</v>
+        <v>17.33690599053966</v>
       </c>
       <c r="H7" t="n">
-        <v>20.63964664490658</v>
+        <v>20.63964664490656</v>
       </c>
       <c r="I7" t="n">
-        <v>15.68995720679494</v>
+        <v>15.68995720679492</v>
       </c>
       <c r="J7" t="n">
         <v>17.72065461249333</v>
       </c>
       <c r="K7" t="n">
-        <v>16.17638221345851</v>
+        <v>16.17638221345852</v>
       </c>
       <c r="L7" t="n">
-        <v>16.24567408718147</v>
+        <v>16.24567408718148</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.75819653568815</v>
+        <v>27.75819653568816</v>
       </c>
       <c r="C8" t="n">
-        <v>38.91016723262301</v>
+        <v>38.91016723262297</v>
       </c>
       <c r="D8" t="n">
-        <v>45.71798340363275</v>
+        <v>45.71798340363269</v>
       </c>
       <c r="E8" t="n">
-        <v>35.79948487805284</v>
+        <v>35.79948487805285</v>
       </c>
       <c r="F8" t="n">
-        <v>28.2420540896437</v>
+        <v>28.24205408964367</v>
       </c>
       <c r="G8" t="n">
-        <v>40.41066981820278</v>
+        <v>40.41066981820276</v>
       </c>
       <c r="H8" t="n">
-        <v>43.71341047260343</v>
+        <v>43.71341047260341</v>
       </c>
       <c r="I8" t="n">
-        <v>38.76372103445807</v>
+        <v>38.76372103445809</v>
       </c>
       <c r="J8" t="n">
-        <v>40.7965549857724</v>
+        <v>40.79655498577237</v>
       </c>
       <c r="K8" t="n">
-        <v>28.1767869670399</v>
+        <v>28.17678696703988</v>
       </c>
       <c r="L8" t="n">
-        <v>50.67554194505109</v>
+        <v>50.6755419450511</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.99833150567091</v>
+        <v>23.99833150567085</v>
       </c>
       <c r="C9" t="n">
-        <v>27.96154600706747</v>
+        <v>27.9615460070675</v>
       </c>
       <c r="D9" t="n">
         <v>32.52445545728521</v>
       </c>
       <c r="E9" t="n">
-        <v>32.08560739683919</v>
+        <v>32.08560739683922</v>
       </c>
       <c r="F9" t="n">
-        <v>27.82510322931428</v>
+        <v>27.8251032293143</v>
       </c>
       <c r="G9" t="n">
-        <v>29.47140005838237</v>
+        <v>29.47140005838238</v>
       </c>
       <c r="H9" t="n">
-        <v>32.77414071274933</v>
+        <v>32.77414071274932</v>
       </c>
       <c r="I9" t="n">
-        <v>27.82445127463769</v>
+        <v>27.82445127463763</v>
       </c>
       <c r="J9" t="n">
-        <v>29.85514868033605</v>
+        <v>29.85514868033608</v>
       </c>
       <c r="K9" t="n">
         <v>26.17171030930169</v>
       </c>
       <c r="L9" t="n">
-        <v>28.38016815502428</v>
+        <v>28.38016815502423</v>
       </c>
     </row>
   </sheetData>
@@ -2099,25 +2099,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.27523523616764</v>
+        <v>19.27523523616773</v>
       </c>
       <c r="C2" t="n">
         <v>11.19142510902287</v>
       </c>
       <c r="D2" t="n">
-        <v>19.57287555987199</v>
+        <v>19.57287555987205</v>
       </c>
       <c r="E2" t="n">
-        <v>12.1152811268264</v>
+        <v>12.11528112682652</v>
       </c>
       <c r="F2" t="n">
-        <v>12.11795298347012</v>
+        <v>12.11795298347014</v>
       </c>
       <c r="G2" t="n">
-        <v>19.36815605262135</v>
+        <v>19.36815605262144</v>
       </c>
       <c r="H2" t="n">
-        <v>19.3775051816141</v>
+        <v>19.37750518161412</v>
       </c>
       <c r="I2" t="n">
         <v>19.27714150004637</v>
@@ -2126,10 +2126,10 @@
         <v>18.51137113211296</v>
       </c>
       <c r="K2" t="n">
-        <v>29.05242363881525</v>
+        <v>29.05242363881528</v>
       </c>
       <c r="L2" t="n">
-        <v>19.27947469485519</v>
+        <v>19.27947469485518</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.22894838047431</v>
+        <v>20.22894838047436</v>
       </c>
       <c r="C3" t="n">
-        <v>7.173452875591495</v>
+        <v>7.173452875591511</v>
       </c>
       <c r="D3" t="n">
-        <v>22.36216203392851</v>
+        <v>22.36216203392857</v>
       </c>
       <c r="E3" t="n">
-        <v>8.521970990437811</v>
+        <v>8.521970990437847</v>
       </c>
       <c r="F3" t="n">
-        <v>8.524642847081509</v>
+        <v>8.524642847081555</v>
       </c>
       <c r="G3" t="n">
-        <v>20.90576875690665</v>
+        <v>20.90576875690671</v>
       </c>
       <c r="H3" t="n">
-        <v>21.82763415927106</v>
+        <v>21.82763415927111</v>
       </c>
       <c r="I3" t="n">
-        <v>20.25624034136905</v>
+        <v>20.25624034136903</v>
       </c>
       <c r="J3" t="n">
-        <v>19.41202517199758</v>
+        <v>19.41202517199774</v>
       </c>
       <c r="K3" t="n">
-        <v>36.48334148821181</v>
+        <v>36.48334148821197</v>
       </c>
       <c r="L3" t="n">
-        <v>20.30292680913491</v>
+        <v>20.30292680913494</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.0158989056911</v>
+        <v>11.01589890569113</v>
       </c>
       <c r="C4" t="n">
-        <v>11.2091781107497</v>
+        <v>11.20917811074972</v>
       </c>
       <c r="D4" t="n">
         <v>14.3778832832455</v>
       </c>
       <c r="E4" t="n">
-        <v>10.80043546854775</v>
+        <v>10.80043546854777</v>
       </c>
       <c r="F4" t="n">
-        <v>10.80043546854775</v>
+        <v>10.80043546854777</v>
       </c>
       <c r="G4" t="n">
-        <v>12.03744317135445</v>
+        <v>12.03744317135435</v>
       </c>
       <c r="H4" t="n">
-        <v>13.72426902765767</v>
+        <v>13.72426902765772</v>
       </c>
       <c r="I4" t="n">
-        <v>10.85936467844286</v>
+        <v>10.85936467844288</v>
       </c>
       <c r="J4" t="n">
-        <v>11.89858873846801</v>
+        <v>11.89858873846805</v>
       </c>
       <c r="K4" t="n">
-        <v>11.22604943155159</v>
+        <v>11.2260494315516</v>
       </c>
       <c r="L4" t="n">
-        <v>11.11043908928691</v>
+        <v>11.11043908928695</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.69308716516694</v>
+        <v>22.69308716516698</v>
       </c>
       <c r="C5" t="n">
-        <v>36.61129685439093</v>
+        <v>36.61129685439124</v>
       </c>
       <c r="D5" t="n">
-        <v>86.78816664258574</v>
+        <v>86.78816664258548</v>
       </c>
       <c r="E5" t="n">
-        <v>29.98926674902819</v>
+        <v>29.98926674902823</v>
       </c>
       <c r="F5" t="n">
-        <v>29.98926674902819</v>
+        <v>29.98926674902823</v>
       </c>
       <c r="G5" t="n">
-        <v>48.29718279359018</v>
+        <v>48.29718279359136</v>
       </c>
       <c r="H5" t="n">
-        <v>83.50097824288609</v>
+        <v>83.50097824288639</v>
       </c>
       <c r="I5" t="n">
-        <v>29.98872094872039</v>
+        <v>29.98872094872042</v>
       </c>
       <c r="J5" t="n">
-        <v>46.20226174670174</v>
+        <v>46.2022617467018</v>
       </c>
       <c r="K5" t="n">
-        <v>33.29228977663345</v>
+        <v>33.29228977663354</v>
       </c>
       <c r="L5" t="n">
-        <v>33.88673205420491</v>
+        <v>33.88673205420496</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.28112348576041</v>
+        <v>28.28112348576045</v>
       </c>
       <c r="C6" t="n">
-        <v>28.57287389895059</v>
+        <v>28.5728738989506</v>
       </c>
       <c r="D6" t="n">
-        <v>31.7158998609363</v>
+        <v>31.71589986093605</v>
       </c>
       <c r="E6" t="n">
-        <v>26.38227878935433</v>
+        <v>26.38227878935438</v>
       </c>
       <c r="F6" t="n">
         <v>28.12448161982797</v>
       </c>
       <c r="G6" t="n">
-        <v>41.54812068667756</v>
+        <v>41.54812068667759</v>
       </c>
       <c r="H6" t="n">
-        <v>43.29272296705495</v>
+        <v>43.29272296705499</v>
       </c>
       <c r="I6" t="n">
-        <v>40.37004219376601</v>
+        <v>40.37004219376602</v>
       </c>
       <c r="J6" t="n">
-        <v>41.18407780374974</v>
+        <v>41.18407780374977</v>
       </c>
       <c r="K6" t="n">
-        <v>28.46496098809573</v>
+        <v>28.4649609880956</v>
       </c>
       <c r="L6" t="n">
-        <v>28.37705004159628</v>
+        <v>28.37705004159636</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.20102573080294</v>
+        <v>15.20102573080299</v>
       </c>
       <c r="C7" t="n">
-        <v>15.55576292555397</v>
+        <v>15.55576292555398</v>
       </c>
       <c r="D7" t="n">
-        <v>18.56294740493562</v>
+        <v>18.56294740493561</v>
       </c>
       <c r="E7" t="n">
-        <v>15.05397515871819</v>
+        <v>15.05397515871821</v>
       </c>
       <c r="F7" t="n">
-        <v>15.05397515871819</v>
+        <v>15.05397515871821</v>
       </c>
       <c r="G7" t="n">
-        <v>16.22256999646628</v>
+        <v>16.22256999646627</v>
       </c>
       <c r="H7" t="n">
-        <v>17.90939585276956</v>
+        <v>17.90939585276959</v>
       </c>
       <c r="I7" t="n">
-        <v>15.04449150355471</v>
+        <v>15.04449150355475</v>
       </c>
       <c r="J7" t="n">
-        <v>16.08371556357988</v>
+        <v>16.08371556357991</v>
       </c>
       <c r="K7" t="n">
-        <v>15.41117625666343</v>
+        <v>15.41117625666346</v>
       </c>
       <c r="L7" t="n">
-        <v>15.29556591439878</v>
+        <v>15.29556591439879</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.36852202432415</v>
+        <v>27.36852202432416</v>
       </c>
       <c r="C8" t="n">
-        <v>38.53289987930486</v>
+        <v>38.53289987930499</v>
       </c>
       <c r="D8" t="n">
-        <v>43.76861482480233</v>
+        <v>43.76861482480228</v>
       </c>
       <c r="E8" t="n">
-        <v>35.06761652416737</v>
+        <v>35.06761652416747</v>
       </c>
       <c r="F8" t="n">
-        <v>27.56021095882255</v>
+        <v>27.56021095882259</v>
       </c>
       <c r="G8" t="n">
-        <v>39.18895482657154</v>
+        <v>39.18895482657162</v>
       </c>
       <c r="H8" t="n">
-        <v>40.8757806829089</v>
+        <v>40.875780682909</v>
       </c>
       <c r="I8" t="n">
         <v>38.01087633366001</v>
       </c>
       <c r="J8" t="n">
-        <v>39.05222268536157</v>
+        <v>39.05222268536161</v>
       </c>
       <c r="K8" t="n">
-        <v>27.37807765135889</v>
+        <v>27.37807765135893</v>
       </c>
       <c r="L8" t="n">
-        <v>49.54229281010788</v>
+        <v>49.54229281010794</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.79021385337958</v>
+        <v>22.7902138533796</v>
       </c>
       <c r="C9" t="n">
-        <v>26.5790503039312</v>
+        <v>26.57905030393141</v>
       </c>
       <c r="D9" t="n">
-        <v>29.58629851372493</v>
+        <v>29.58629851372508</v>
       </c>
       <c r="E9" t="n">
-        <v>30.03120164511969</v>
+        <v>30.03120164511981</v>
       </c>
       <c r="F9" t="n">
-        <v>26.06832332861615</v>
+        <v>26.06832332861611</v>
       </c>
       <c r="G9" t="n">
-        <v>27.24585737484355</v>
+        <v>27.24585737484351</v>
       </c>
       <c r="H9" t="n">
-        <v>28.93268323114684</v>
+        <v>28.93268323114695</v>
       </c>
       <c r="I9" t="n">
-        <v>26.06777888193196</v>
+        <v>26.06777888193207</v>
       </c>
       <c r="J9" t="n">
-        <v>27.10700294195717</v>
+        <v>27.10700294195718</v>
       </c>
       <c r="K9" t="n">
-        <v>24.36400756362009</v>
+        <v>24.36400756362016</v>
       </c>
       <c r="L9" t="n">
-        <v>26.31885329277601</v>
+        <v>26.31885329277616</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.97300098374303</v>
+        <v>19.97300098374301</v>
       </c>
       <c r="C2" t="n">
         <v>11.24974009249704</v>
       </c>
       <c r="D2" t="n">
-        <v>20.30700516564785</v>
+        <v>20.30700516564784</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2675915357024</v>
+        <v>12.26759153570244</v>
       </c>
       <c r="F2" t="n">
-        <v>12.27026381194012</v>
+        <v>12.27026381194014</v>
       </c>
       <c r="G2" t="n">
-        <v>20.142535695268</v>
+        <v>20.14253569526798</v>
       </c>
       <c r="H2" t="n">
-        <v>20.51650168745685</v>
+        <v>20.51650168745688</v>
       </c>
       <c r="I2" t="n">
-        <v>20.00853594401612</v>
+        <v>20.00853594401617</v>
       </c>
       <c r="J2" t="n">
-        <v>18.87640991134464</v>
+        <v>18.87640991134463</v>
       </c>
       <c r="K2" t="n">
-        <v>29.17935773487561</v>
+        <v>29.17935773487563</v>
       </c>
       <c r="L2" t="n">
-        <v>20.25435343023631</v>
+        <v>20.25435343023632</v>
       </c>
     </row>
     <row r="3">
@@ -2538,34 +2538,34 @@
         <v>21.35578889791584</v>
       </c>
       <c r="C3" t="n">
-        <v>7.065853530528925</v>
+        <v>7.065853530528919</v>
       </c>
       <c r="D3" t="n">
-        <v>23.74787721015711</v>
+        <v>23.7478772101571</v>
       </c>
       <c r="E3" t="n">
-        <v>8.932483639038487</v>
+        <v>8.932483639038455</v>
       </c>
       <c r="F3" t="n">
-        <v>8.935155915276175</v>
+        <v>8.935155915276155</v>
       </c>
       <c r="G3" t="n">
         <v>22.57907171845412</v>
       </c>
       <c r="H3" t="n">
-        <v>26.09554623480579</v>
+        <v>26.09554623480584</v>
       </c>
       <c r="I3" t="n">
-        <v>21.62263591339127</v>
+        <v>21.6226359133913</v>
       </c>
       <c r="J3" t="n">
         <v>21.31612486785475</v>
       </c>
       <c r="K3" t="n">
-        <v>37.09752973757349</v>
+        <v>37.09752973757355</v>
       </c>
       <c r="L3" t="n">
-        <v>23.40325953180857</v>
+        <v>23.40325953180858</v>
       </c>
     </row>
     <row r="4">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.17760790678829</v>
+        <v>11.17760790678828</v>
       </c>
       <c r="C4" t="n">
         <v>10.99349461954629</v>
@@ -2584,28 +2584,28 @@
         <v>14.9503387909181</v>
       </c>
       <c r="E4" t="n">
-        <v>11.35090277010212</v>
+        <v>11.35090277010213</v>
       </c>
       <c r="F4" t="n">
-        <v>11.35090277010212</v>
+        <v>11.35090277010213</v>
       </c>
       <c r="G4" t="n">
         <v>13.06432543248489</v>
       </c>
       <c r="H4" t="n">
-        <v>18.82887002773</v>
+        <v>18.82887002773002</v>
       </c>
       <c r="I4" t="n">
-        <v>11.3993688131069</v>
+        <v>11.39936881310691</v>
       </c>
       <c r="J4" t="n">
-        <v>14.78931964274087</v>
+        <v>14.78931964274086</v>
       </c>
       <c r="K4" t="n">
-        <v>12.27463172464736</v>
+        <v>12.27463172464735</v>
       </c>
       <c r="L4" t="n">
-        <v>14.37344259961407</v>
+        <v>14.37344259961405</v>
       </c>
     </row>
     <row r="5">
@@ -2615,31 +2615,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.69492673274467</v>
+        <v>25.6949267327447</v>
       </c>
       <c r="C5" t="n">
-        <v>33.55175943591738</v>
+        <v>33.55175943591757</v>
       </c>
       <c r="D5" t="n">
-        <v>100.4650936970929</v>
+        <v>100.4650936970928</v>
       </c>
       <c r="E5" t="n">
-        <v>40.22831613952383</v>
+        <v>40.22831613952489</v>
       </c>
       <c r="F5" t="n">
-        <v>40.22831613952383</v>
+        <v>40.22831613952489</v>
       </c>
       <c r="G5" t="n">
-        <v>68.59777658920183</v>
+        <v>68.59777658920208</v>
       </c>
       <c r="H5" t="n">
-        <v>189.5727041554516</v>
+        <v>189.5727041554519</v>
       </c>
       <c r="I5" t="n">
-        <v>40.22765950589302</v>
+        <v>40.22765950589435</v>
       </c>
       <c r="J5" t="n">
-        <v>101.7985877951732</v>
+        <v>101.7985877951734</v>
       </c>
       <c r="K5" t="n">
         <v>52.75153276694698</v>
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.46692935897448</v>
+        <v>29.46692935897455</v>
       </c>
       <c r="C6" t="n">
-        <v>29.35279640069952</v>
+        <v>29.35279640069777</v>
       </c>
       <c r="D6" t="n">
         <v>33.30827948920277</v>
       </c>
       <c r="E6" t="n">
-        <v>27.84076042982085</v>
+        <v>27.84076042982094</v>
       </c>
       <c r="F6" t="n">
-        <v>29.69032811544666</v>
+        <v>29.69032811544671</v>
       </c>
       <c r="G6" t="n">
-        <v>31.35364688467107</v>
+        <v>31.35364688467113</v>
       </c>
       <c r="H6" t="n">
-        <v>50.01873037362046</v>
+        <v>50.01873037362053</v>
       </c>
       <c r="I6" t="n">
-        <v>42.64569557900479</v>
+        <v>42.64569557900485</v>
       </c>
       <c r="J6" t="n">
-        <v>34.06172808994929</v>
+        <v>34.06172808994931</v>
       </c>
       <c r="K6" t="n">
-        <v>30.54625407699038</v>
+        <v>30.54625407699043</v>
       </c>
       <c r="L6" t="n">
-        <v>32.6825580607931</v>
+        <v>32.68255806079312</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.62761621631745</v>
+        <v>15.62761621631746</v>
       </c>
       <c r="C7" t="n">
-        <v>15.61076398227571</v>
+        <v>15.61076398227573</v>
       </c>
       <c r="D7" t="n">
-        <v>19.40027831086267</v>
+        <v>19.40027831086266</v>
       </c>
       <c r="E7" t="n">
-        <v>15.86240819788551</v>
+        <v>15.86240819788555</v>
       </c>
       <c r="F7" t="n">
-        <v>15.86240819788551</v>
+        <v>15.86240819788555</v>
       </c>
       <c r="G7" t="n">
-        <v>17.51433374201406</v>
+        <v>17.5143337420141</v>
       </c>
       <c r="H7" t="n">
-        <v>23.27887833725919</v>
+        <v>23.27887833725926</v>
       </c>
       <c r="I7" t="n">
-        <v>15.84937712263606</v>
+        <v>15.84937712263609</v>
       </c>
       <c r="J7" t="n">
-        <v>19.23932795227005</v>
+        <v>19.23932795227008</v>
       </c>
       <c r="K7" t="n">
         <v>16.72464003417652</v>
       </c>
       <c r="L7" t="n">
-        <v>18.82345090914325</v>
+        <v>18.82345090914327</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.44403026382155</v>
+        <v>28.44403026382154</v>
       </c>
       <c r="C8" t="n">
-        <v>39.8339883034747</v>
+        <v>39.83398830347473</v>
       </c>
       <c r="D8" t="n">
-        <v>45.97176313611708</v>
+        <v>45.97176313611705</v>
       </c>
       <c r="E8" t="n">
         <v>36.9559580436605</v>
       </c>
       <c r="F8" t="n">
-        <v>29.03500051788419</v>
+        <v>29.03500051788423</v>
       </c>
       <c r="G8" t="n">
         <v>41.72340755826703</v>
       </c>
       <c r="H8" t="n">
-        <v>47.48795215352106</v>
+        <v>47.48795215352102</v>
       </c>
       <c r="I8" t="n">
         <v>40.05845093888902</v>
       </c>
       <c r="J8" t="n">
-        <v>43.45064075341242</v>
+        <v>43.45064075341246</v>
       </c>
       <c r="K8" t="n">
-        <v>29.32942957738926</v>
+        <v>29.32942957738928</v>
       </c>
       <c r="L8" t="n">
-        <v>54.93311049339042</v>
+        <v>54.93311049339039</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.30907486907536</v>
+        <v>25.30907486907543</v>
       </c>
       <c r="C9" t="n">
-        <v>29.3839301708933</v>
+        <v>29.38393017089339</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17351361475861</v>
+        <v>33.1735136147587</v>
       </c>
       <c r="E9" t="n">
-        <v>34.34494071698673</v>
+        <v>34.34494071698681</v>
       </c>
       <c r="F9" t="n">
-        <v>29.6231973364921</v>
+        <v>29.6231973364922</v>
       </c>
       <c r="G9" t="n">
-        <v>31.28749993063165</v>
+        <v>31.28749993063172</v>
       </c>
       <c r="H9" t="n">
-        <v>37.05204452587684</v>
+        <v>37.05204452587688</v>
       </c>
       <c r="I9" t="n">
-        <v>29.62254331125367</v>
+        <v>29.62254331125375</v>
       </c>
       <c r="J9" t="n">
-        <v>33.01249414088764</v>
+        <v>33.01249414088773</v>
       </c>
       <c r="K9" t="n">
-        <v>28.12705494412864</v>
+        <v>28.1270549441287</v>
       </c>
       <c r="L9" t="n">
-        <v>32.59661709776088</v>
+        <v>32.59661709776094</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.52807632340071</v>
+        <v>19.52807632340077</v>
       </c>
       <c r="C2" t="n">
-        <v>11.01621779875996</v>
+        <v>11.01621779875995</v>
       </c>
       <c r="D2" t="n">
-        <v>19.54105663690872</v>
+        <v>19.54105663690866</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9969788500949</v>
+        <v>11.99697885009495</v>
       </c>
       <c r="F2" t="n">
-        <v>11.99964955885747</v>
+        <v>11.9996495588575</v>
       </c>
       <c r="G2" t="n">
-        <v>19.54273484921445</v>
+        <v>19.54273484921447</v>
       </c>
       <c r="H2" t="n">
-        <v>19.43979986157747</v>
+        <v>19.43979986157748</v>
       </c>
       <c r="I2" t="n">
-        <v>19.55043220838668</v>
+        <v>19.55043220838673</v>
       </c>
       <c r="J2" t="n">
         <v>18.33454966772516</v>
       </c>
       <c r="K2" t="n">
-        <v>28.76486564580422</v>
+        <v>28.76486564580429</v>
       </c>
       <c r="L2" t="n">
-        <v>19.55064524643202</v>
+        <v>19.55064524643204</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.8116795056088</v>
+        <v>20.81167950560877</v>
       </c>
       <c r="C3" t="n">
-        <v>6.924915798989034</v>
+        <v>6.924915798989046</v>
       </c>
       <c r="D3" t="n">
-        <v>20.91746885047202</v>
+        <v>20.91746885047205</v>
       </c>
       <c r="E3" t="n">
-        <v>8.603963430382638</v>
+        <v>8.603963430382546</v>
       </c>
       <c r="F3" t="n">
-        <v>8.606634139145093</v>
+        <v>8.606634139145047</v>
       </c>
       <c r="G3" t="n">
-        <v>20.9302508245319</v>
+        <v>20.93025082453191</v>
       </c>
       <c r="H3" t="n">
-        <v>21.04974177921935</v>
+        <v>21.04974177921936</v>
       </c>
       <c r="I3" t="n">
-        <v>20.98463150388143</v>
+        <v>20.98463150388141</v>
       </c>
       <c r="J3" t="n">
-        <v>19.40316790080638</v>
+        <v>19.40316790080639</v>
       </c>
       <c r="K3" t="n">
-        <v>36.08390737492303</v>
+        <v>36.08390737492306</v>
       </c>
       <c r="L3" t="n">
-        <v>21.00699640222982</v>
+        <v>21.00699640222984</v>
       </c>
     </row>
     <row r="4">
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.92042500953845</v>
+        <v>10.92042500953844</v>
       </c>
       <c r="C4" t="n">
-        <v>10.87380154404425</v>
+        <v>10.87380154404424</v>
       </c>
       <c r="D4" t="n">
         <v>11.06704362184948</v>
@@ -2986,10 +2986,10 @@
         <v>10.97857615579879</v>
       </c>
       <c r="G4" t="n">
-        <v>11.05871419312322</v>
+        <v>11.05871419312321</v>
       </c>
       <c r="H4" t="n">
-        <v>11.48616336013446</v>
+        <v>11.48616336013444</v>
       </c>
       <c r="I4" t="n">
         <v>10.99990694035013</v>
@@ -2998,7 +2998,7 @@
         <v>12.0452013985736</v>
       </c>
       <c r="K4" t="n">
-        <v>10.94466732395596</v>
+        <v>10.94466732395595</v>
       </c>
       <c r="L4" t="n">
         <v>11.20317599678788</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.18407475905268</v>
+        <v>23.18407475905267</v>
       </c>
       <c r="C5" t="n">
         <v>32.63085958337756</v>
       </c>
       <c r="D5" t="n">
-        <v>32.59098870418148</v>
+        <v>32.59098870418145</v>
       </c>
       <c r="E5" t="n">
-        <v>34.42017834672865</v>
+        <v>34.42017834672868</v>
       </c>
       <c r="F5" t="n">
-        <v>34.42017834672865</v>
+        <v>34.42017834672868</v>
       </c>
       <c r="G5" t="n">
-        <v>33.31588056071477</v>
+        <v>33.31588056071497</v>
       </c>
       <c r="H5" t="n">
-        <v>43.01653736381142</v>
+        <v>43.01653736381147</v>
       </c>
       <c r="I5" t="n">
-        <v>34.41989079488223</v>
+        <v>34.41989079488221</v>
       </c>
       <c r="J5" t="n">
-        <v>51.0078020524443</v>
+        <v>51.00780205244433</v>
       </c>
       <c r="K5" t="n">
-        <v>30.57844004073045</v>
+        <v>30.5784400407304</v>
       </c>
       <c r="L5" t="n">
-        <v>38.09536290029487</v>
+        <v>38.09536290029485</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.180584758851</v>
+        <v>28.18058475885095</v>
       </c>
       <c r="C6" t="n">
-        <v>28.23145811065088</v>
+        <v>28.23145811065085</v>
       </c>
       <c r="D6" t="n">
-        <v>40.26432362076403</v>
+        <v>40.26432362076404</v>
       </c>
       <c r="E6" t="n">
-        <v>26.54988902156994</v>
+        <v>26.54988902156997</v>
       </c>
       <c r="F6" t="n">
-        <v>28.26513224799425</v>
+        <v>28.26513224799424</v>
       </c>
       <c r="G6" t="n">
         <v>28.31887394243562</v>
       </c>
       <c r="H6" t="n">
-        <v>40.90794869882152</v>
+        <v>40.90794869882151</v>
       </c>
       <c r="I6" t="n">
-        <v>40.40093168097327</v>
+        <v>40.40093168097328</v>
       </c>
       <c r="J6" t="n">
-        <v>41.21317226111232</v>
+        <v>41.21317226111228</v>
       </c>
       <c r="K6" t="n">
-        <v>28.18963538758036</v>
+        <v>28.18963538757867</v>
       </c>
       <c r="L6" t="n">
         <v>28.46578359589996</v>
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.98644432219431</v>
+        <v>14.98644432219429</v>
       </c>
       <c r="C7" t="n">
-        <v>15.08685787708934</v>
+        <v>15.08685787708932</v>
       </c>
       <c r="D7" t="n">
-        <v>15.13300131014964</v>
+        <v>15.13300131014963</v>
       </c>
       <c r="E7" t="n">
-        <v>15.08209893039129</v>
+        <v>15.08209893039128</v>
       </c>
       <c r="F7" t="n">
-        <v>15.08209893039129</v>
+        <v>15.08209893039128</v>
       </c>
       <c r="G7" t="n">
-        <v>15.12473350577911</v>
+        <v>15.12473350577908</v>
       </c>
       <c r="H7" t="n">
-        <v>15.55218267279029</v>
+        <v>15.55218267279027</v>
       </c>
       <c r="I7" t="n">
-        <v>15.065926253006</v>
+        <v>15.06592625300599</v>
       </c>
       <c r="J7" t="n">
-        <v>16.11122071122947</v>
+        <v>16.11122071122943</v>
       </c>
       <c r="K7" t="n">
-        <v>15.01068663661183</v>
+        <v>15.0106866366118</v>
       </c>
       <c r="L7" t="n">
-        <v>15.26919530944375</v>
+        <v>15.26919530944376</v>
       </c>
     </row>
     <row r="8">
@@ -3134,34 +3134,34 @@
         <v>27.04788908359486</v>
       </c>
       <c r="C8" t="n">
-        <v>37.79063917732651</v>
+        <v>37.79063917732653</v>
       </c>
       <c r="D8" t="n">
-        <v>40.02265135474569</v>
+        <v>40.02265135474568</v>
       </c>
       <c r="E8" t="n">
-        <v>34.86230512775392</v>
+        <v>34.86230512775398</v>
       </c>
       <c r="F8" t="n">
-        <v>27.47396716316284</v>
+        <v>27.47396716316287</v>
       </c>
       <c r="G8" t="n">
-        <v>37.81116227632462</v>
+        <v>37.81116227632458</v>
       </c>
       <c r="H8" t="n">
-        <v>38.23861144336496</v>
+        <v>38.23861144336495</v>
       </c>
       <c r="I8" t="n">
-        <v>37.75235502355157</v>
+        <v>37.75235502355153</v>
       </c>
       <c r="J8" t="n">
-        <v>38.79973759625567</v>
+        <v>38.79973759625562</v>
       </c>
       <c r="K8" t="n">
-        <v>26.87476686507637</v>
+        <v>26.87476686507635</v>
       </c>
       <c r="L8" t="n">
-        <v>49.05430832502686</v>
+        <v>49.05430832502683</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.91409311491329</v>
+        <v>22.91409311491331</v>
       </c>
       <c r="C9" t="n">
-        <v>26.49584546387145</v>
+        <v>26.49584546387148</v>
       </c>
       <c r="D9" t="n">
-        <v>26.54205155201554</v>
+        <v>26.54205155201553</v>
       </c>
       <c r="E9" t="n">
-        <v>30.49259243341418</v>
+        <v>30.49259243341421</v>
       </c>
       <c r="F9" t="n">
-        <v>26.47520055801578</v>
+        <v>26.47520055801575</v>
       </c>
       <c r="G9" t="n">
-        <v>26.53372109256125</v>
+        <v>26.53372109256121</v>
       </c>
       <c r="H9" t="n">
-        <v>26.96117025957246</v>
+        <v>26.9611702595725</v>
       </c>
       <c r="I9" t="n">
-        <v>26.47491383978817</v>
+        <v>26.47491383978815</v>
       </c>
       <c r="J9" t="n">
-        <v>27.5202082980116</v>
+        <v>27.52020829801163</v>
       </c>
       <c r="K9" t="n">
-        <v>24.40257328736297</v>
+        <v>24.40257328736296</v>
       </c>
       <c r="L9" t="n">
-        <v>26.67818289622589</v>
+        <v>26.67818289622591</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.37675710157454</v>
+        <v>19.37675710157444</v>
       </c>
       <c r="C2" t="n">
-        <v>10.98868055599395</v>
+        <v>10.98868055599392</v>
       </c>
       <c r="D2" t="n">
-        <v>19.40110209183203</v>
+        <v>19.40110209183197</v>
       </c>
       <c r="E2" t="n">
-        <v>11.95688192274636</v>
+        <v>11.95688192274643</v>
       </c>
       <c r="F2" t="n">
-        <v>11.95955350164048</v>
+        <v>11.95955350164044</v>
       </c>
       <c r="G2" t="n">
-        <v>19.38977896869572</v>
+        <v>19.38977896869568</v>
       </c>
       <c r="H2" t="n">
-        <v>19.26865237112307</v>
+        <v>19.26865237112305</v>
       </c>
       <c r="I2" t="n">
-        <v>19.39359253859909</v>
+        <v>19.39359253859902</v>
       </c>
       <c r="J2" t="n">
-        <v>18.24968285431498</v>
+        <v>18.24968285431491</v>
       </c>
       <c r="K2" t="n">
-        <v>28.81566543888131</v>
+        <v>28.81566543888125</v>
       </c>
       <c r="L2" t="n">
-        <v>19.37902805949554</v>
+        <v>19.37902805949553</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.46669277033244</v>
+        <v>20.46669277033234</v>
       </c>
       <c r="C3" t="n">
-        <v>6.792468632126342</v>
+        <v>6.792468632126328</v>
       </c>
       <c r="D3" t="n">
-        <v>20.65359580916553</v>
+        <v>20.65359580916539</v>
       </c>
       <c r="E3" t="n">
-        <v>8.412463753634048</v>
+        <v>8.412463753633993</v>
       </c>
       <c r="F3" t="n">
-        <v>8.415135332528177</v>
+        <v>8.415135332528287</v>
       </c>
       <c r="G3" t="n">
         <v>20.57360056473631</v>
       </c>
       <c r="H3" t="n">
-        <v>20.56283566155844</v>
+        <v>20.56283566155842</v>
       </c>
       <c r="I3" t="n">
-        <v>20.60042647528935</v>
+        <v>20.60042647528932</v>
       </c>
       <c r="J3" t="n">
-        <v>18.82168061618171</v>
+        <v>18.82168061618162</v>
       </c>
       <c r="K3" t="n">
-        <v>36.06441376431807</v>
+        <v>36.0644137643182</v>
       </c>
       <c r="L3" t="n">
-        <v>20.51703730684776</v>
+        <v>20.51703730684775</v>
       </c>
     </row>
     <row r="4">
@@ -3367,34 +3367,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.76128574145102</v>
+        <v>10.76128574145095</v>
       </c>
       <c r="C4" t="n">
-        <v>10.73140975659139</v>
+        <v>10.73140975659134</v>
       </c>
       <c r="D4" t="n">
-        <v>11.03627360565819</v>
+        <v>11.03627360565813</v>
       </c>
       <c r="E4" t="n">
-        <v>10.74812049821022</v>
+        <v>10.7481204982102</v>
       </c>
       <c r="F4" t="n">
-        <v>10.74812049821022</v>
+        <v>10.7481204982102</v>
       </c>
       <c r="G4" t="n">
-        <v>10.88101477326482</v>
+        <v>10.88101477326408</v>
       </c>
       <c r="H4" t="n">
-        <v>11.10447503617258</v>
+        <v>11.1044750361726</v>
       </c>
       <c r="I4" t="n">
-        <v>10.77796075958892</v>
+        <v>10.77796075958904</v>
       </c>
       <c r="J4" t="n">
-        <v>11.17401463861972</v>
+        <v>11.17401463861966</v>
       </c>
       <c r="K4" t="n">
-        <v>10.76841293968825</v>
+        <v>10.76841293968822</v>
       </c>
       <c r="L4" t="n">
         <v>10.8172781681813</v>
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.11294781538329</v>
+        <v>20.11294781537883</v>
       </c>
       <c r="C5" t="n">
-        <v>29.87333177658015</v>
+        <v>29.87333177658111</v>
       </c>
       <c r="D5" t="n">
-        <v>31.79206103538765</v>
+        <v>31.79206103538759</v>
       </c>
       <c r="E5" t="n">
-        <v>30.33975769530342</v>
+        <v>30.33975769530328</v>
       </c>
       <c r="F5" t="n">
-        <v>30.33975769530342</v>
+        <v>30.33975769530327</v>
       </c>
       <c r="G5" t="n">
-        <v>29.92672249757117</v>
+        <v>29.92672249757065</v>
       </c>
       <c r="H5" t="n">
-        <v>35.39996014407038</v>
+        <v>35.39996014407035</v>
       </c>
       <c r="I5" t="n">
-        <v>30.33945999362223</v>
+        <v>30.33945999362208</v>
       </c>
       <c r="J5" t="n">
-        <v>35.16635757400347</v>
+        <v>35.16635757400351</v>
       </c>
       <c r="K5" t="n">
-        <v>27.2936069419365</v>
+        <v>27.29360694193649</v>
       </c>
       <c r="L5" t="n">
-        <v>30.25084949517007</v>
+        <v>30.25084949517</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.17730270372427</v>
+        <v>40.17730270372421</v>
       </c>
       <c r="C6" t="n">
-        <v>28.08946135893775</v>
+        <v>28.08946135893774</v>
       </c>
       <c r="D6" t="n">
-        <v>28.28471896284615</v>
+        <v>28.28471896284616</v>
       </c>
       <c r="E6" t="n">
-        <v>26.3230979602876</v>
+        <v>26.32309796028762</v>
       </c>
       <c r="F6" t="n">
-        <v>28.04160879141897</v>
+        <v>28.04160879141895</v>
       </c>
       <c r="G6" t="n">
-        <v>40.29703173553723</v>
+        <v>40.29703173553731</v>
       </c>
       <c r="H6" t="n">
-        <v>28.3669967614148</v>
+        <v>28.36699676141476</v>
       </c>
       <c r="I6" t="n">
-        <v>40.19397772186233</v>
+        <v>40.19397772186232</v>
       </c>
       <c r="J6" t="n">
-        <v>29.34319799990635</v>
+        <v>29.34319799990634</v>
       </c>
       <c r="K6" t="n">
         <v>28.01297468063196</v>
       </c>
       <c r="L6" t="n">
-        <v>28.07788059518105</v>
+        <v>28.07788059518104</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.79531184970608</v>
+        <v>14.79531184970612</v>
       </c>
       <c r="C7" t="n">
-        <v>14.9128356855784</v>
+        <v>14.91283568557837</v>
       </c>
       <c r="D7" t="n">
-        <v>15.07023614509142</v>
+        <v>15.07023614509141</v>
       </c>
       <c r="E7" t="n">
-        <v>14.82663509836955</v>
+        <v>14.82663509836952</v>
       </c>
       <c r="F7" t="n">
-        <v>14.82663509836955</v>
+        <v>14.82663509836953</v>
       </c>
       <c r="G7" t="n">
-        <v>14.91504088151923</v>
+        <v>14.91504088151916</v>
       </c>
       <c r="H7" t="n">
-        <v>15.13850114442776</v>
+        <v>15.13850114442775</v>
       </c>
       <c r="I7" t="n">
-        <v>14.81198686784422</v>
+        <v>14.8119868678442</v>
       </c>
       <c r="J7" t="n">
-        <v>15.20804074687484</v>
+        <v>15.20804074687481</v>
       </c>
       <c r="K7" t="n">
-        <v>14.80243904794337</v>
+        <v>14.80243904794338</v>
       </c>
       <c r="L7" t="n">
-        <v>14.85130427643644</v>
+        <v>14.85130427643646</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.85937698546847</v>
+        <v>26.85937698546855</v>
       </c>
       <c r="C8" t="n">
-        <v>37.60594937159414</v>
+        <v>37.60594937159407</v>
       </c>
       <c r="D8" t="n">
         <v>39.9482290347332</v>
       </c>
       <c r="E8" t="n">
-        <v>34.60109164976977</v>
+        <v>34.60109164976969</v>
       </c>
       <c r="F8" t="n">
-        <v>27.22136910148874</v>
+        <v>27.22136910148871</v>
       </c>
       <c r="G8" t="n">
         <v>37.59226296989131</v>
       </c>
       <c r="H8" t="n">
-        <v>37.81572323283039</v>
+        <v>37.81572323283033</v>
       </c>
       <c r="I8" t="n">
-        <v>37.48920895621627</v>
+        <v>37.48920895621624</v>
       </c>
       <c r="J8" t="n">
-        <v>37.88734862506079</v>
+        <v>37.88734862506075</v>
       </c>
       <c r="K8" t="n">
-        <v>26.669359344435</v>
+        <v>26.66935934443499</v>
       </c>
       <c r="L8" t="n">
-        <v>48.61485626006304</v>
+        <v>48.61485626006301</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.13981190760015</v>
+        <v>22.13981190760018</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5715293207402</v>
+        <v>25.57152932074018</v>
       </c>
       <c r="D9" t="n">
-        <v>25.72899440721315</v>
+        <v>25.72899440721318</v>
       </c>
       <c r="E9" t="n">
         <v>29.29548732600957</v>
       </c>
       <c r="F9" t="n">
-        <v>25.4709774437847</v>
+        <v>25.47097744378471</v>
       </c>
       <c r="G9" t="n">
-        <v>25.57373451668099</v>
+        <v>25.57373451668101</v>
       </c>
       <c r="H9" t="n">
-        <v>25.7971947795896</v>
+        <v>25.79719477958955</v>
       </c>
       <c r="I9" t="n">
-        <v>25.47068050300599</v>
+        <v>25.47068050300596</v>
       </c>
       <c r="J9" t="n">
         <v>25.86673438203659</v>
       </c>
       <c r="K9" t="n">
-        <v>23.54087635364395</v>
+        <v>23.54087635364391</v>
       </c>
       <c r="L9" t="n">
-        <v>25.50999791159825</v>
+        <v>25.50999791159824</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.90093192478811</v>
+        <v>19.9009319247885</v>
       </c>
       <c r="C2" t="n">
-        <v>11.10977952219823</v>
+        <v>11.10977952219866</v>
       </c>
       <c r="D2" t="n">
-        <v>19.94906898576908</v>
+        <v>19.94906898576895</v>
       </c>
       <c r="E2" t="n">
-        <v>12.08453060828772</v>
+        <v>12.08453060828826</v>
       </c>
       <c r="F2" t="n">
-        <v>12.08720156850737</v>
+        <v>12.08720156850773</v>
       </c>
       <c r="G2" t="n">
-        <v>19.95851717061973</v>
+        <v>19.95851717061968</v>
       </c>
       <c r="H2" t="n">
-        <v>20.32106229559304</v>
+        <v>20.32106229559334</v>
       </c>
       <c r="I2" t="n">
-        <v>19.93173426639352</v>
+        <v>19.93173426639341</v>
       </c>
       <c r="J2" t="n">
-        <v>18.35578894502712</v>
+        <v>18.35578894502725</v>
       </c>
       <c r="K2" t="n">
-        <v>28.85222759050203</v>
+        <v>28.85222759050237</v>
       </c>
       <c r="L2" t="n">
-        <v>20.12415928337437</v>
+        <v>20.12415928337448</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.41504682205348</v>
+        <v>21.41504682205352</v>
       </c>
       <c r="C3" t="n">
-        <v>7.055764333819901</v>
+        <v>7.055764333819897</v>
       </c>
       <c r="D3" t="n">
-        <v>21.77113248901863</v>
+        <v>21.77113248901845</v>
       </c>
       <c r="E3" t="n">
-        <v>8.782572702084408</v>
+        <v>8.782572702084288</v>
       </c>
       <c r="F3" t="n">
-        <v>8.785243662303929</v>
+        <v>8.785243662303838</v>
       </c>
       <c r="G3" t="n">
-        <v>21.83979963268636</v>
+        <v>21.83979963268637</v>
       </c>
       <c r="H3" t="n">
-        <v>25.26734192212595</v>
+        <v>25.26734192212594</v>
       </c>
       <c r="I3" t="n">
-        <v>21.6481257173708</v>
+        <v>21.64812571737088</v>
       </c>
       <c r="J3" t="n">
-        <v>19.14530058546322</v>
+        <v>19.14530058546317</v>
       </c>
       <c r="K3" t="n">
-        <v>36.35104652332012</v>
+        <v>36.35104652332018</v>
       </c>
       <c r="L3" t="n">
-        <v>23.03805963516994</v>
+        <v>23.03805963516995</v>
       </c>
     </row>
     <row r="4">
@@ -3763,13 +3763,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.06314064034811</v>
+        <v>11.06314064034606</v>
       </c>
       <c r="C4" t="n">
-        <v>10.9869036537896</v>
+        <v>10.98690365378959</v>
       </c>
       <c r="D4" t="n">
-        <v>11.60687088826422</v>
+        <v>11.60687088826272</v>
       </c>
       <c r="E4" t="n">
         <v>11.20820207477771</v>
@@ -3778,22 +3778,22 @@
         <v>11.20820207477771</v>
       </c>
       <c r="G4" t="n">
-        <v>11.6860945403133</v>
+        <v>11.68609454031215</v>
       </c>
       <c r="H4" t="n">
-        <v>17.31531565167621</v>
+        <v>17.31531565167191</v>
       </c>
       <c r="I4" t="n">
         <v>11.23654046588353</v>
       </c>
       <c r="J4" t="n">
-        <v>11.6099681751716</v>
+        <v>11.60996817517302</v>
       </c>
       <c r="K4" t="n">
-        <v>11.36623800866628</v>
+        <v>11.36623800866715</v>
       </c>
       <c r="L4" t="n">
-        <v>13.58907606187763</v>
+        <v>13.58907606188238</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.75655266784671</v>
+        <v>25.75655266784824</v>
       </c>
       <c r="C5" t="n">
-        <v>35.2687687792077</v>
+        <v>35.26876877920772</v>
       </c>
       <c r="D5" t="n">
-        <v>42.73428718420506</v>
+        <v>42.73428718419981</v>
       </c>
       <c r="E5" t="n">
-        <v>39.30435767000875</v>
+        <v>39.30435767000857</v>
       </c>
       <c r="F5" t="n">
-        <v>39.30435767000876</v>
+        <v>39.30435767000857</v>
       </c>
       <c r="G5" t="n">
-        <v>45.3693397947145</v>
+        <v>45.3693397947157</v>
       </c>
       <c r="H5" t="n">
-        <v>161.4315905261934</v>
+        <v>161.4315905261888</v>
       </c>
       <c r="I5" t="n">
-        <v>39.30398012764726</v>
+        <v>39.30398012764729</v>
       </c>
       <c r="J5" t="n">
-        <v>44.24954151197711</v>
+        <v>44.24954151197984</v>
       </c>
       <c r="K5" t="n">
-        <v>38.52775948165881</v>
+        <v>38.52775948166035</v>
       </c>
       <c r="L5" t="n">
-        <v>87.77054590324855</v>
+        <v>87.77054590324792</v>
       </c>
     </row>
     <row r="6">
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.30063751603163</v>
+        <v>29.30063751603164</v>
       </c>
       <c r="C6" t="n">
-        <v>29.31342371989138</v>
+        <v>29.31342371989139</v>
       </c>
       <c r="D6" t="n">
-        <v>29.83292187408406</v>
+        <v>29.83292187408356</v>
       </c>
       <c r="E6" t="n">
         <v>27.66017337090457</v>
@@ -3858,22 +3858,22 @@
         <v>29.47862532057047</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92359141599618</v>
+        <v>29.92359141599776</v>
       </c>
       <c r="H6" t="n">
-        <v>48.34820416426715</v>
+        <v>48.34820416426787</v>
       </c>
       <c r="I6" t="n">
-        <v>29.47403734156907</v>
+        <v>29.47403734156905</v>
       </c>
       <c r="J6" t="n">
-        <v>30.80832591334311</v>
+        <v>30.80832591334172</v>
       </c>
       <c r="K6" t="n">
-        <v>29.58721345446955</v>
+        <v>29.58721345446934</v>
       </c>
       <c r="L6" t="n">
-        <v>31.8423648293157</v>
+        <v>31.84236482931775</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.39723981572454</v>
+        <v>15.39723981572501</v>
       </c>
       <c r="C7" t="n">
-        <v>15.47254874229979</v>
+        <v>15.47254874229981</v>
       </c>
       <c r="D7" t="n">
-        <v>15.94090207526595</v>
+        <v>15.94090207526661</v>
       </c>
       <c r="E7" t="n">
-        <v>15.58571416954721</v>
+        <v>15.58571416954723</v>
       </c>
       <c r="F7" t="n">
-        <v>15.58571416954721</v>
+        <v>15.58571416954723</v>
       </c>
       <c r="G7" t="n">
-        <v>16.02019371569373</v>
+        <v>16.02019371569111</v>
       </c>
       <c r="H7" t="n">
-        <v>21.64941482705396</v>
+        <v>21.64941482705085</v>
       </c>
       <c r="I7" t="n">
-        <v>15.57063964126246</v>
+        <v>15.57063964126248</v>
       </c>
       <c r="J7" t="n">
-        <v>15.9440673505547</v>
+        <v>15.94406735055197</v>
       </c>
       <c r="K7" t="n">
-        <v>15.70033718404269</v>
+        <v>15.7003371840461</v>
       </c>
       <c r="L7" t="n">
-        <v>17.92317523726074</v>
+        <v>17.92317523726134</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.12676085950223</v>
+        <v>28.12676085950239</v>
       </c>
       <c r="C8" t="n">
-        <v>39.45986854359447</v>
+        <v>39.4598685435945</v>
       </c>
       <c r="D8" t="n">
-        <v>42.24294008712099</v>
+        <v>42.24294008712109</v>
       </c>
       <c r="E8" t="n">
-        <v>36.48215785220756</v>
+        <v>36.48215785220759</v>
       </c>
       <c r="F8" t="n">
-        <v>28.66568314897197</v>
+        <v>28.66568314897203</v>
       </c>
       <c r="G8" t="n">
-        <v>39.99117394554985</v>
+        <v>39.99117394555107</v>
       </c>
       <c r="H8" t="n">
-        <v>45.62039505691836</v>
+        <v>45.62039505691931</v>
       </c>
       <c r="I8" t="n">
-        <v>39.54161987112241</v>
+        <v>39.54161987112246</v>
       </c>
       <c r="J8" t="n">
-        <v>39.91725685005048</v>
+        <v>39.9172568500425</v>
       </c>
       <c r="K8" t="n">
-        <v>28.22104235198262</v>
+        <v>28.22104235198278</v>
       </c>
       <c r="L8" t="n">
-        <v>53.63679958332524</v>
+        <v>53.63679958332143</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.66167844578914</v>
+        <v>24.66167844578943</v>
       </c>
       <c r="C9" t="n">
-        <v>28.67158644566961</v>
+        <v>28.67158644566965</v>
       </c>
       <c r="D9" t="n">
-        <v>29.14000766073294</v>
+        <v>29.14000766073251</v>
       </c>
       <c r="E9" t="n">
-        <v>33.31049577058344</v>
+        <v>33.31049577058347</v>
       </c>
       <c r="F9" t="n">
-        <v>28.77005254782689</v>
+        <v>28.77005254782691</v>
       </c>
       <c r="G9" t="n">
-        <v>29.21923141906276</v>
+        <v>29.21923141906095</v>
       </c>
       <c r="H9" t="n">
-        <v>34.84845253042695</v>
+        <v>34.84845253042067</v>
       </c>
       <c r="I9" t="n">
-        <v>28.76967734463233</v>
+        <v>28.76967734463235</v>
       </c>
       <c r="J9" t="n">
-        <v>29.14310505392371</v>
+        <v>29.14310505392181</v>
       </c>
       <c r="K9" t="n">
-        <v>26.6196526872826</v>
+        <v>26.61965268728089</v>
       </c>
       <c r="L9" t="n">
-        <v>31.12221294063107</v>
+        <v>31.12221294063117</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.11032485115278</v>
+        <v>20.11032485115233</v>
       </c>
       <c r="C2" t="n">
-        <v>11.03000596439337</v>
+        <v>11.03000596439329</v>
       </c>
       <c r="D2" t="n">
-        <v>20.11973795627373</v>
+        <v>20.11973795627324</v>
       </c>
       <c r="E2" t="n">
-        <v>11.97876810862673</v>
+        <v>11.97876810862657</v>
       </c>
       <c r="F2" t="n">
-        <v>11.9814387460544</v>
+        <v>11.98143874605432</v>
       </c>
       <c r="G2" t="n">
-        <v>20.11283596923846</v>
+        <v>20.11283596923802</v>
       </c>
       <c r="H2" t="n">
-        <v>19.98961371602755</v>
+        <v>19.98961371602756</v>
       </c>
       <c r="I2" t="n">
-        <v>20.12803665058977</v>
+        <v>20.12803665058933</v>
       </c>
       <c r="J2" t="n">
-        <v>18.20823030170464</v>
+        <v>18.2082303017045</v>
       </c>
       <c r="K2" t="n">
-        <v>28.58366907336348</v>
+        <v>28.58366907336333</v>
       </c>
       <c r="L2" t="n">
-        <v>20.09974657509543</v>
+        <v>20.09974657509544</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.79245432665959</v>
+        <v>21.79245432665949</v>
       </c>
       <c r="C3" t="n">
-        <v>6.982350694934508</v>
+        <v>6.982350694934528</v>
       </c>
       <c r="D3" t="n">
-        <v>21.87280978011039</v>
+        <v>21.87280978011032</v>
       </c>
       <c r="E3" t="n">
-        <v>8.568120169914854</v>
+        <v>8.568120169914947</v>
       </c>
       <c r="F3" t="n">
-        <v>8.57079080734249</v>
+        <v>8.570790807342645</v>
       </c>
       <c r="G3" t="n">
-        <v>21.82437264049364</v>
+        <v>21.82437264049357</v>
       </c>
       <c r="H3" t="n">
-        <v>21.7988412983038</v>
+        <v>21.79884129830379</v>
       </c>
       <c r="I3" t="n">
-        <v>21.93229204882805</v>
+        <v>21.93229204882796</v>
       </c>
       <c r="J3" t="n">
-        <v>18.84855647149995</v>
+        <v>18.84855647149993</v>
       </c>
       <c r="K3" t="n">
-        <v>35.77175301404463</v>
+        <v>35.77175301404466</v>
       </c>
       <c r="L3" t="n">
-        <v>21.75162359176867</v>
+        <v>21.75162359176866</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.90347872154451</v>
+        <v>10.90347872154503</v>
       </c>
       <c r="C4" t="n">
-        <v>10.88872085091361</v>
+        <v>10.88872085091362</v>
       </c>
       <c r="D4" t="n">
-        <v>11.00980407412796</v>
+        <v>11.00980407413089</v>
       </c>
       <c r="E4" t="n">
-        <v>10.92256942430415</v>
+        <v>10.92256942430416</v>
       </c>
       <c r="F4" t="n">
-        <v>10.92256942430415</v>
+        <v>10.92256942430416</v>
       </c>
       <c r="G4" t="n">
-        <v>10.90459925373396</v>
+        <v>10.90459925373654</v>
       </c>
       <c r="H4" t="n">
-        <v>11.1043032700345</v>
+        <v>11.10430327003512</v>
       </c>
       <c r="I4" t="n">
-        <v>10.93077379244423</v>
+        <v>10.93077379244427</v>
       </c>
       <c r="J4" t="n">
-        <v>11.27569609743597</v>
+        <v>11.27569609743718</v>
       </c>
       <c r="K4" t="n">
-        <v>10.86023593091204</v>
+        <v>10.86023593090472</v>
       </c>
       <c r="L4" t="n">
-        <v>10.81488831728984</v>
+        <v>10.81488831728887</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.48700326317576</v>
+        <v>23.48700326317555</v>
       </c>
       <c r="C5" t="n">
-        <v>33.48379701549788</v>
+        <v>33.48379701549779</v>
       </c>
       <c r="D5" t="n">
-        <v>32.19445462648685</v>
+        <v>32.19445462648525</v>
       </c>
       <c r="E5" t="n">
-        <v>33.8115266486134</v>
+        <v>33.81152664861337</v>
       </c>
       <c r="F5" t="n">
-        <v>33.8115266486134</v>
+        <v>33.81152664861337</v>
       </c>
       <c r="G5" t="n">
-        <v>31.21467604761416</v>
+        <v>31.2146760476177</v>
       </c>
       <c r="H5" t="n">
-        <v>36.35975972854758</v>
+        <v>36.35975972854447</v>
       </c>
       <c r="I5" t="n">
-        <v>33.81125765163125</v>
+        <v>33.81125765163119</v>
       </c>
       <c r="J5" t="n">
-        <v>37.87790778523691</v>
+        <v>37.87790778523094</v>
       </c>
       <c r="K5" t="n">
-        <v>29.71639031487891</v>
+        <v>29.71639031488258</v>
       </c>
       <c r="L5" t="n">
-        <v>31.18624364557233</v>
+        <v>31.18624364557061</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.29176191503028</v>
+        <v>40.29176191503206</v>
       </c>
       <c r="C6" t="n">
-        <v>28.25181977745783</v>
+        <v>28.25181977745768</v>
       </c>
       <c r="D6" t="n">
-        <v>28.25891375284971</v>
+        <v>28.25891375284773</v>
       </c>
       <c r="E6" t="n">
-        <v>26.48648636922995</v>
+        <v>26.48648636922997</v>
       </c>
       <c r="F6" t="n">
-        <v>28.19843161029011</v>
+        <v>28.19843161029014</v>
       </c>
       <c r="G6" t="n">
-        <v>28.16653693339643</v>
+        <v>28.16653693339605</v>
       </c>
       <c r="H6" t="n">
-        <v>40.5066920768151</v>
+        <v>40.5066920768174</v>
       </c>
       <c r="I6" t="n">
-        <v>40.31905698593005</v>
+        <v>40.31905698593106</v>
       </c>
       <c r="J6" t="n">
-        <v>29.44512481001751</v>
+        <v>29.4451248100173</v>
       </c>
       <c r="K6" t="n">
-        <v>28.10821682319183</v>
+        <v>28.10821682318797</v>
       </c>
       <c r="L6" t="n">
-        <v>28.07721220614435</v>
+        <v>28.07721220614232</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.91599353893586</v>
+        <v>14.91599353893201</v>
       </c>
       <c r="C7" t="n">
         <v>15.04804536203296</v>
       </c>
       <c r="D7" t="n">
-        <v>15.02225841467919</v>
+        <v>15.02225841467817</v>
       </c>
       <c r="E7" t="n">
-        <v>14.96297027485748</v>
+        <v>14.96297027485749</v>
       </c>
       <c r="F7" t="n">
-        <v>14.96297027485748</v>
+        <v>14.96297027485749</v>
       </c>
       <c r="G7" t="n">
-        <v>14.91711407112534</v>
+        <v>14.91711407112354</v>
       </c>
       <c r="H7" t="n">
-        <v>15.11681808742584</v>
+        <v>15.11681808742074</v>
       </c>
       <c r="I7" t="n">
-        <v>14.94328860983559</v>
+        <v>14.94328860983562</v>
       </c>
       <c r="J7" t="n">
-        <v>15.28821091482732</v>
+        <v>15.28821091482952</v>
       </c>
       <c r="K7" t="n">
-        <v>14.87275074830338</v>
+        <v>14.87275074830106</v>
       </c>
       <c r="L7" t="n">
-        <v>14.82740313468118</v>
+        <v>14.82740313468252</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.9303683978198</v>
+        <v>26.93036839782472</v>
       </c>
       <c r="C8" t="n">
-        <v>37.63396136047797</v>
+        <v>37.63396136047794</v>
       </c>
       <c r="D8" t="n">
-        <v>39.77531123529598</v>
+        <v>39.77531123529771</v>
       </c>
       <c r="E8" t="n">
         <v>34.64170920103568</v>
       </c>
       <c r="F8" t="n">
-        <v>27.30399426981656</v>
+        <v>27.30399426981655</v>
       </c>
       <c r="G8" t="n">
-        <v>37.48232236897954</v>
+        <v>37.48232236897514</v>
       </c>
       <c r="H8" t="n">
-        <v>37.6820263853083</v>
+        <v>37.68202638530202</v>
       </c>
       <c r="I8" t="n">
-        <v>37.50849690768983</v>
+        <v>37.50849690768982</v>
       </c>
       <c r="J8" t="n">
-        <v>37.85549275443918</v>
+        <v>37.85549275443665</v>
       </c>
       <c r="K8" t="n">
-        <v>26.6911384591622</v>
+        <v>26.69113845916005</v>
       </c>
       <c r="L8" t="n">
-        <v>48.4138392066443</v>
+        <v>48.41383920664508</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.82104656842038</v>
+        <v>22.82104656842141</v>
       </c>
       <c r="C9" t="n">
-        <v>26.40893133004345</v>
+        <v>26.40893133004343</v>
       </c>
       <c r="D9" t="n">
-        <v>26.3832058938184</v>
+        <v>26.38320589381485</v>
       </c>
       <c r="E9" t="n">
-        <v>30.29240152352968</v>
+        <v>30.2924015235297</v>
       </c>
       <c r="F9" t="n">
-        <v>26.30444283735468</v>
+        <v>26.30444283735473</v>
       </c>
       <c r="G9" t="n">
-        <v>26.27800003913577</v>
+        <v>26.27800003913729</v>
       </c>
       <c r="H9" t="n">
-        <v>26.47770405543631</v>
+        <v>26.47770405543455</v>
       </c>
       <c r="I9" t="n">
-        <v>26.30417457784605</v>
+        <v>26.30417457784608</v>
       </c>
       <c r="J9" t="n">
-        <v>26.64909688283777</v>
+        <v>26.6490968828393</v>
       </c>
       <c r="K9" t="n">
-        <v>21.88212591464872</v>
+        <v>21.88212591464227</v>
       </c>
       <c r="L9" t="n">
-        <v>26.18828910269167</v>
+        <v>26.18828910269503</v>
       </c>
     </row>
   </sheetData>
@@ -4478,10 +4478,10 @@
         <v>19.34404636412915</v>
       </c>
       <c r="C2" t="n">
-        <v>11.07215755374452</v>
+        <v>11.07215755374453</v>
       </c>
       <c r="D2" t="n">
-        <v>19.36496499921031</v>
+        <v>19.3649649992103</v>
       </c>
       <c r="E2" t="n">
         <v>11.98516818007536</v>
@@ -4490,19 +4490,19 @@
         <v>11.98783945646363</v>
       </c>
       <c r="G2" t="n">
-        <v>19.35425158412357</v>
+        <v>19.35425158412358</v>
       </c>
       <c r="H2" t="n">
-        <v>19.23050776837155</v>
+        <v>19.23050776837156</v>
       </c>
       <c r="I2" t="n">
-        <v>19.3581149292535</v>
+        <v>19.35811492925349</v>
       </c>
       <c r="J2" t="n">
-        <v>18.24483377081076</v>
+        <v>18.24483377081075</v>
       </c>
       <c r="K2" t="n">
-        <v>28.76719141453417</v>
+        <v>28.76719141453419</v>
       </c>
       <c r="L2" t="n">
         <v>19.34289873379101</v>
@@ -4515,34 +4515,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.33935570003002</v>
+        <v>20.33935570003004</v>
       </c>
       <c r="C3" t="n">
-        <v>6.862138065568285</v>
+        <v>6.862138065568281</v>
       </c>
       <c r="D3" t="n">
         <v>20.50182298848498</v>
       </c>
       <c r="E3" t="n">
-        <v>8.370640229659921</v>
+        <v>8.370640229659928</v>
       </c>
       <c r="F3" t="n">
-        <v>8.373311506048196</v>
+        <v>8.373311506048205</v>
       </c>
       <c r="G3" t="n">
-        <v>20.42616692964214</v>
+        <v>20.42616692964212</v>
       </c>
       <c r="H3" t="n">
-        <v>20.3963941327429</v>
+        <v>20.39639413274291</v>
       </c>
       <c r="I3" t="n">
         <v>20.4533494904624</v>
       </c>
       <c r="J3" t="n">
-        <v>18.73842944739078</v>
+        <v>18.73842944739073</v>
       </c>
       <c r="K3" t="n">
-        <v>35.93089248156518</v>
+        <v>35.9308924815652</v>
       </c>
       <c r="L3" t="n">
         <v>20.36534315044106</v>
@@ -4561,31 +4561,31 @@
         <v>10.72938109892803</v>
       </c>
       <c r="D4" t="n">
-        <v>10.98541433755011</v>
+        <v>10.98541433755012</v>
       </c>
       <c r="E4" t="n">
-        <v>10.7164494252109</v>
+        <v>10.71644942521092</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7164494252109</v>
+        <v>10.71644942521092</v>
       </c>
       <c r="G4" t="n">
-        <v>10.8369610449051</v>
+        <v>10.83696104490511</v>
       </c>
       <c r="H4" t="n">
-        <v>11.03051289005533</v>
+        <v>11.03051289005535</v>
       </c>
       <c r="I4" t="n">
-        <v>10.73399251577883</v>
+        <v>10.73399251577885</v>
       </c>
       <c r="J4" t="n">
-        <v>11.15791165277797</v>
+        <v>11.15791165277795</v>
       </c>
       <c r="K4" t="n">
         <v>10.79725663865734</v>
       </c>
       <c r="L4" t="n">
-        <v>10.76664320286013</v>
+        <v>10.76664320286014</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.58495994291873</v>
+        <v>20.58495994291876</v>
       </c>
       <c r="C5" t="n">
-        <v>30.54152231905374</v>
+        <v>30.54152231905371</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58905235816781</v>
+        <v>31.58905235816788</v>
       </c>
       <c r="E5" t="n">
-        <v>30.26227889041699</v>
+        <v>30.26227889041701</v>
       </c>
       <c r="F5" t="n">
-        <v>30.26227889041699</v>
+        <v>30.26227889041701</v>
       </c>
       <c r="G5" t="n">
-        <v>29.83904888918066</v>
+        <v>29.83904888918115</v>
       </c>
       <c r="H5" t="n">
         <v>34.73188288822769</v>
       </c>
       <c r="I5" t="n">
-        <v>30.26198022088015</v>
+        <v>30.26198022088014</v>
       </c>
       <c r="J5" t="n">
-        <v>35.57467187734274</v>
+        <v>35.57467187734281</v>
       </c>
       <c r="K5" t="n">
-        <v>28.45002405257628</v>
+        <v>28.4500240525763</v>
       </c>
       <c r="L5" t="n">
-        <v>30.02539363382716</v>
+        <v>30.02539363382712</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.15003999296067</v>
+        <v>40.15003999296064</v>
       </c>
       <c r="C6" t="n">
-        <v>28.09131456758284</v>
+        <v>28.09131456758281</v>
       </c>
       <c r="D6" t="n">
-        <v>28.23554250436005</v>
+        <v>28.23554250436006</v>
       </c>
       <c r="E6" t="n">
-        <v>26.28421412126537</v>
+        <v>26.28421412126538</v>
       </c>
       <c r="F6" t="n">
-        <v>28.00039499695692</v>
+        <v>28.00039499695693</v>
       </c>
       <c r="G6" t="n">
-        <v>28.09848663780053</v>
+        <v>28.09848663780052</v>
       </c>
       <c r="H6" t="n">
-        <v>40.45843134948194</v>
+        <v>40.45843134948196</v>
       </c>
       <c r="I6" t="n">
-        <v>27.99551810867425</v>
+        <v>27.99551810867428</v>
       </c>
       <c r="J6" t="n">
-        <v>40.32572738177638</v>
+        <v>40.32572738177635</v>
       </c>
       <c r="K6" t="n">
         <v>28.04585354030136</v>
       </c>
       <c r="L6" t="n">
-        <v>28.02971369799253</v>
+        <v>28.02971369799257</v>
       </c>
     </row>
     <row r="7">
@@ -4675,19 +4675,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.73182580371499</v>
+        <v>14.73182580371498</v>
       </c>
       <c r="C7" t="n">
-        <v>14.86056542157986</v>
+        <v>14.8605654215799</v>
       </c>
       <c r="D7" t="n">
         <v>14.96804873731004</v>
       </c>
       <c r="E7" t="n">
-        <v>14.73492038090669</v>
+        <v>14.73492038090671</v>
       </c>
       <c r="F7" t="n">
-        <v>14.73492038090669</v>
+        <v>14.73492038090671</v>
       </c>
       <c r="G7" t="n">
         <v>14.81965811735917</v>
@@ -4696,16 +4696,16 @@
         <v>15.01320996250944</v>
       </c>
       <c r="I7" t="n">
-        <v>14.71668958823291</v>
+        <v>14.71668958823293</v>
       </c>
       <c r="J7" t="n">
-        <v>15.14060872523204</v>
+        <v>15.14060872523205</v>
       </c>
       <c r="K7" t="n">
-        <v>14.77995371111144</v>
+        <v>14.77995371111143</v>
       </c>
       <c r="L7" t="n">
-        <v>14.74934027531421</v>
+        <v>14.7493402753142</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.74321977496992</v>
+        <v>26.74321977496993</v>
       </c>
       <c r="C8" t="n">
-        <v>37.42376574946056</v>
+        <v>37.42376574946061</v>
       </c>
       <c r="D8" t="n">
-        <v>39.69599774486141</v>
+        <v>39.69599774486147</v>
       </c>
       <c r="E8" t="n">
-        <v>34.39757861842185</v>
+        <v>34.3975786184219</v>
       </c>
       <c r="F8" t="n">
-        <v>27.07298124383041</v>
+        <v>27.07298124383042</v>
       </c>
       <c r="G8" t="n">
-        <v>37.36356026821939</v>
+        <v>37.36356026821942</v>
       </c>
       <c r="H8" t="n">
-        <v>37.55711211339948</v>
+        <v>37.55711211339947</v>
       </c>
       <c r="I8" t="n">
-        <v>37.2605917390931</v>
+        <v>37.26059173909312</v>
       </c>
       <c r="J8" t="n">
-        <v>37.68658081624395</v>
+        <v>37.68658081624397</v>
       </c>
       <c r="K8" t="n">
-        <v>26.59570093544612</v>
+        <v>26.59570093544609</v>
       </c>
       <c r="L8" t="n">
-        <v>48.29532793441182</v>
+        <v>48.29532793441189</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.08558587132749</v>
+        <v>22.08558587132753</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5105438002817</v>
+        <v>25.51054380028174</v>
       </c>
       <c r="D9" t="n">
-        <v>25.61809082833609</v>
+        <v>25.61809082833615</v>
       </c>
       <c r="E9" t="n">
-        <v>29.17073271125178</v>
+        <v>29.17073271125189</v>
       </c>
       <c r="F9" t="n">
-        <v>25.36696591254617</v>
+        <v>25.36696591254626</v>
       </c>
       <c r="G9" t="n">
-        <v>25.46963649606102</v>
+        <v>25.46963649606103</v>
       </c>
       <c r="H9" t="n">
-        <v>25.66318834121124</v>
+        <v>25.6631883412113</v>
       </c>
       <c r="I9" t="n">
-        <v>25.36666796693472</v>
+        <v>25.36666796693479</v>
       </c>
       <c r="J9" t="n">
-        <v>25.79058710393384</v>
+        <v>25.79058710393391</v>
       </c>
       <c r="K9" t="n">
-        <v>23.44260597222065</v>
+        <v>23.4426059722207</v>
       </c>
       <c r="L9" t="n">
-        <v>25.39931865401602</v>
+        <v>25.3993186540161</v>
       </c>
     </row>
   </sheetData>
@@ -4871,16 +4871,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.26846084658009</v>
+        <v>21.26846084658006</v>
       </c>
       <c r="C2" t="n">
-        <v>17.23674337091066</v>
+        <v>17.23674337091064</v>
       </c>
       <c r="D2" t="n">
-        <v>22.15490089991921</v>
+        <v>22.15490089991923</v>
       </c>
       <c r="E2" t="n">
-        <v>19.14182707079213</v>
+        <v>19.14182707079214</v>
       </c>
       <c r="F2" t="n">
         <v>13.79737629270874</v>
@@ -4889,16 +4889,16 @@
         <v>21.61076973292107</v>
       </c>
       <c r="H2" t="n">
-        <v>22.64442095558955</v>
+        <v>22.64442095558957</v>
       </c>
       <c r="I2" t="n">
-        <v>21.17479969395703</v>
+        <v>21.17479969395702</v>
       </c>
       <c r="J2" t="n">
         <v>26.9682030028336</v>
       </c>
       <c r="K2" t="n">
-        <v>27.59002420690042</v>
+        <v>27.59002420690039</v>
       </c>
       <c r="L2" t="n">
         <v>22.56430859818732</v>
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.80651848787782</v>
+        <v>21.80651848787777</v>
       </c>
       <c r="C3" t="n">
         <v>14.74015769332459</v>
       </c>
       <c r="D3" t="n">
-        <v>28.11584022283081</v>
+        <v>28.11584022283082</v>
       </c>
       <c r="E3" t="n">
-        <v>17.87409803836276</v>
+        <v>17.87409803836275</v>
       </c>
       <c r="F3" t="n">
-        <v>9.050362075061702</v>
+        <v>9.050362075061695</v>
       </c>
       <c r="G3" t="n">
-        <v>24.24937536746134</v>
+        <v>24.24937536746131</v>
       </c>
       <c r="H3" t="n">
-        <v>32.46728661175591</v>
+        <v>32.4672866117559</v>
       </c>
       <c r="I3" t="n">
-        <v>21.14218216517193</v>
+        <v>21.14218216517194</v>
       </c>
       <c r="J3" t="n">
-        <v>32.10128296481924</v>
+        <v>32.10128296481922</v>
       </c>
       <c r="K3" t="n">
-        <v>32.46837721587346</v>
+        <v>32.46837721587343</v>
       </c>
       <c r="L3" t="n">
-        <v>31.07159932849292</v>
+        <v>31.0715993284929</v>
       </c>
     </row>
     <row r="4">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.90159737009902</v>
+        <v>13.90159737009898</v>
       </c>
       <c r="C4" t="n">
-        <v>12.49383243703709</v>
+        <v>12.4938324370371</v>
       </c>
       <c r="D4" t="n">
         <v>23.91434555513549</v>
@@ -4966,22 +4966,22 @@
         <v>12.51809456357246</v>
       </c>
       <c r="G4" t="n">
-        <v>17.73704367576352</v>
+        <v>17.73704367576347</v>
       </c>
       <c r="H4" t="n">
-        <v>30.8946522538155</v>
+        <v>30.89465225381552</v>
       </c>
       <c r="I4" t="n">
-        <v>12.64488123317105</v>
+        <v>12.64488123317107</v>
       </c>
       <c r="J4" t="n">
-        <v>15.70980648968143</v>
+        <v>15.70980648968145</v>
       </c>
       <c r="K4" t="n">
-        <v>14.36699215585447</v>
+        <v>14.36699215585448</v>
       </c>
       <c r="L4" t="n">
-        <v>28.43724860684571</v>
+        <v>28.43724860684572</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.83647008585677</v>
+        <v>74.83647008585592</v>
       </c>
       <c r="C5" t="n">
-        <v>56.93139014483383</v>
+        <v>56.93139014483389</v>
       </c>
       <c r="D5" t="n">
-        <v>254.5656462453657</v>
+        <v>254.5656462453658</v>
       </c>
       <c r="E5" t="n">
-        <v>56.931398377871</v>
+        <v>56.93139837787098</v>
       </c>
       <c r="F5" t="n">
         <v>56.931398377871</v>
       </c>
       <c r="G5" t="n">
-        <v>147.7918455693687</v>
+        <v>147.7918455693702</v>
       </c>
       <c r="H5" t="n">
-        <v>425.1376771181963</v>
+        <v>425.1376771181964</v>
       </c>
       <c r="I5" t="n">
-        <v>56.92995400023985</v>
+        <v>56.92995400023979</v>
       </c>
       <c r="J5" t="n">
-        <v>113.4882128210528</v>
+        <v>113.4882128210527</v>
       </c>
       <c r="K5" t="n">
-        <v>84.14343077900409</v>
+        <v>84.14343077900395</v>
       </c>
       <c r="L5" t="n">
-        <v>89.97971479185286</v>
+        <v>89.97971479185277</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.68577226499175</v>
+        <v>32.68577226499165</v>
       </c>
       <c r="C6" t="n">
-        <v>31.26893284225443</v>
+        <v>31.26893284225448</v>
       </c>
       <c r="D6" t="n">
-        <v>42.96127707431575</v>
+        <v>42.96127707431576</v>
       </c>
       <c r="E6" t="n">
         <v>29.4560587614405</v>
       </c>
       <c r="F6" t="n">
-        <v>31.42269221044055</v>
+        <v>31.42269221044054</v>
       </c>
       <c r="G6" t="n">
-        <v>36.52121857065616</v>
+        <v>36.5212185706562</v>
       </c>
       <c r="H6" t="n">
-        <v>63.10156594348452</v>
+        <v>63.1015659434845</v>
       </c>
       <c r="I6" t="n">
-        <v>45.06761082372554</v>
+        <v>45.06761082372553</v>
       </c>
       <c r="J6" t="n">
         <v>35.50649269171795</v>
       </c>
       <c r="K6" t="n">
-        <v>33.08829105701733</v>
+        <v>33.08829105701739</v>
       </c>
       <c r="L6" t="n">
-        <v>47.32078624349898</v>
+        <v>47.32078624349897</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.6478981536264</v>
+        <v>18.64789815362635</v>
       </c>
       <c r="C7" t="n">
-        <v>17.39261816129248</v>
+        <v>17.39261816129247</v>
       </c>
       <c r="D7" t="n">
-        <v>28.66055497151205</v>
+        <v>28.66055497151201</v>
       </c>
       <c r="E7" t="n">
-        <v>17.38982130034464</v>
+        <v>17.38982130034466</v>
       </c>
       <c r="F7" t="n">
-        <v>17.38982130034464</v>
+        <v>17.38982130034466</v>
       </c>
       <c r="G7" t="n">
-        <v>22.4833444592909</v>
+        <v>22.48334445929085</v>
       </c>
       <c r="H7" t="n">
-        <v>35.6409530373429</v>
+        <v>35.64095303734295</v>
       </c>
       <c r="I7" t="n">
-        <v>17.39118201669844</v>
+        <v>17.39118201669843</v>
       </c>
       <c r="J7" t="n">
-        <v>20.45610727320883</v>
+        <v>20.45610727320882</v>
       </c>
       <c r="K7" t="n">
-        <v>19.11329293938187</v>
+        <v>19.11329293938186</v>
       </c>
       <c r="L7" t="n">
-        <v>33.18354939037307</v>
+        <v>33.18354939037309</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.80869697571587</v>
+        <v>31.80869697571573</v>
       </c>
       <c r="C8" t="n">
-        <v>42.38567465250941</v>
+        <v>42.38567465250938</v>
       </c>
       <c r="D8" t="n">
-        <v>56.10749713395516</v>
+        <v>56.10749713395508</v>
       </c>
       <c r="E8" t="n">
-        <v>39.14960854914172</v>
+        <v>39.1496085491417</v>
       </c>
       <c r="F8" t="n">
-        <v>30.92687848352667</v>
+        <v>30.92687848352663</v>
       </c>
       <c r="G8" t="n">
-        <v>47.47664826463939</v>
+        <v>47.47664826463927</v>
       </c>
       <c r="H8" t="n">
-        <v>60.63425684269213</v>
+        <v>60.63425684269211</v>
       </c>
       <c r="I8" t="n">
-        <v>42.38448582204695</v>
+        <v>42.38448582204687</v>
       </c>
       <c r="J8" t="n">
-        <v>45.45173650564334</v>
+        <v>45.45173650564331</v>
       </c>
       <c r="K8" t="n">
-        <v>32.05429690652213</v>
+        <v>32.05429690652204</v>
       </c>
       <c r="L8" t="n">
-        <v>70.53689406946825</v>
+        <v>70.53689406946836</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.13005202102629</v>
+        <v>30.13005202102627</v>
       </c>
       <c r="C9" t="n">
         <v>33.56067470153582</v>
       </c>
       <c r="D9" t="n">
-        <v>44.8287023073506</v>
+        <v>44.82870230735055</v>
       </c>
       <c r="E9" t="n">
-        <v>38.96810756403309</v>
+        <v>38.96810756403302</v>
       </c>
       <c r="F9" t="n">
         <v>33.56067718965645</v>
       </c>
       <c r="G9" t="n">
-        <v>38.65140099953419</v>
+        <v>38.65140099953418</v>
       </c>
       <c r="H9" t="n">
-        <v>51.80900957758632</v>
+        <v>51.80900957758615</v>
       </c>
       <c r="I9" t="n">
-        <v>33.55923855694178</v>
+        <v>33.55923855694175</v>
       </c>
       <c r="J9" t="n">
-        <v>36.6241638134522</v>
+        <v>36.62416381345211</v>
       </c>
       <c r="K9" t="n">
-        <v>32.56631882762754</v>
+        <v>32.56631882762741</v>
       </c>
       <c r="L9" t="n">
-        <v>49.35160593061647</v>
+        <v>49.35160593061643</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.22973120497483</v>
+        <v>21.22973120497487</v>
       </c>
       <c r="C2" t="n">
-        <v>17.24447916340507</v>
+        <v>17.24447916340509</v>
       </c>
       <c r="D2" t="n">
-        <v>22.04746601506454</v>
+        <v>22.04746601506457</v>
       </c>
       <c r="E2" t="n">
-        <v>19.13762709943478</v>
+        <v>19.13762709943481</v>
       </c>
       <c r="F2" t="n">
-        <v>13.82598426591408</v>
+        <v>13.82598426591411</v>
       </c>
       <c r="G2" t="n">
-        <v>21.56218194613299</v>
+        <v>21.56218194613302</v>
       </c>
       <c r="H2" t="n">
-        <v>22.38306472662305</v>
+        <v>22.38306472662309</v>
       </c>
       <c r="I2" t="n">
-        <v>21.18501337813671</v>
+        <v>21.18501337813675</v>
       </c>
       <c r="J2" t="n">
-        <v>26.75856536255273</v>
+        <v>26.75856536255277</v>
       </c>
       <c r="K2" t="n">
-        <v>27.54286834483264</v>
+        <v>27.54286834483266</v>
       </c>
       <c r="L2" t="n">
-        <v>22.42017611046566</v>
+        <v>22.4201761104658</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.76190860463673</v>
+        <v>21.76190860463678</v>
       </c>
       <c r="C3" t="n">
-        <v>15.03700286855412</v>
+        <v>15.03700286855415</v>
       </c>
       <c r="D3" t="n">
-        <v>27.57582760848664</v>
+        <v>27.57582760848668</v>
       </c>
       <c r="E3" t="n">
-        <v>18.15175759423301</v>
+        <v>18.15175759423305</v>
       </c>
       <c r="F3" t="n">
-        <v>9.382177295611424</v>
+        <v>9.382177295611433</v>
       </c>
       <c r="G3" t="n">
-        <v>24.13130076499439</v>
+        <v>24.13130076499443</v>
       </c>
       <c r="H3" t="n">
-        <v>30.84247134535405</v>
+        <v>30.84247134535413</v>
       </c>
       <c r="I3" t="n">
-        <v>21.44363364305852</v>
+        <v>21.44363364305854</v>
       </c>
       <c r="J3" t="n">
-        <v>31.19203200798133</v>
+        <v>31.19203200798136</v>
       </c>
       <c r="K3" t="n">
-        <v>32.41591551551308</v>
+        <v>32.41591551551311</v>
       </c>
       <c r="L3" t="n">
-        <v>30.27975065342601</v>
+        <v>30.27975065342612</v>
       </c>
     </row>
     <row r="4">
@@ -5350,10 +5350,10 @@
         <v>13.82184935716277</v>
       </c>
       <c r="C4" t="n">
-        <v>12.98535020453251</v>
+        <v>12.98535020453252</v>
       </c>
       <c r="D4" t="n">
-        <v>23.05854021372362</v>
+        <v>23.05854021372366</v>
       </c>
       <c r="E4" t="n">
         <v>13.00799533578116</v>
@@ -5362,22 +5362,22 @@
         <v>13.00799533578115</v>
       </c>
       <c r="G4" t="n">
-        <v>17.54634990333001</v>
+        <v>17.54634990333002</v>
       </c>
       <c r="H4" t="n">
-        <v>28.32605818274373</v>
+        <v>28.32605818274374</v>
       </c>
       <c r="I4" t="n">
         <v>13.12072286052129</v>
       </c>
       <c r="J4" t="n">
-        <v>14.4330585088549</v>
+        <v>14.43305850885492</v>
       </c>
       <c r="K4" t="n">
-        <v>14.3111832058872</v>
+        <v>14.31118320588721</v>
       </c>
       <c r="L4" t="n">
-        <v>27.18185167642637</v>
+        <v>27.18185167642633</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.58333848373144</v>
+        <v>70.58333848373155</v>
       </c>
       <c r="C5" t="n">
-        <v>61.9101354934098</v>
+        <v>61.91013549341181</v>
       </c>
       <c r="D5" t="n">
-        <v>222.3955862652653</v>
+        <v>222.3955862652662</v>
       </c>
       <c r="E5" t="n">
-        <v>61.91014373606745</v>
+        <v>61.91014373606815</v>
       </c>
       <c r="F5" t="n">
-        <v>61.91014373606747</v>
+        <v>61.91014373606815</v>
       </c>
       <c r="G5" t="n">
-        <v>135.2460017688338</v>
+        <v>135.2460017688339</v>
       </c>
       <c r="H5" t="n">
-        <v>351.3680645263113</v>
+        <v>351.3680645263125</v>
       </c>
       <c r="I5" t="n">
-        <v>61.90885188296967</v>
+        <v>61.90885188297112</v>
       </c>
       <c r="J5" t="n">
-        <v>84.96799403716248</v>
+        <v>84.96799403716255</v>
       </c>
       <c r="K5" t="n">
-        <v>76.82404866722241</v>
+        <v>76.82404866722216</v>
       </c>
       <c r="L5" t="n">
-        <v>92.3395425652636</v>
+        <v>92.33954256526332</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.33160252042375</v>
+        <v>31.33160252042377</v>
       </c>
       <c r="C6" t="n">
-        <v>30.50041412026385</v>
+        <v>30.50041412026387</v>
       </c>
       <c r="D6" t="n">
-        <v>40.78891455922573</v>
+        <v>40.78891455922576</v>
       </c>
       <c r="E6" t="n">
-        <v>28.81161231851625</v>
+        <v>28.81161231851627</v>
       </c>
       <c r="F6" t="n">
-        <v>30.62950853668938</v>
+        <v>30.62950853668939</v>
       </c>
       <c r="G6" t="n">
-        <v>35.05610306659097</v>
+        <v>35.05610306659096</v>
       </c>
       <c r="H6" t="n">
-        <v>58.31267313822445</v>
+        <v>58.31267313822453</v>
       </c>
       <c r="I6" t="n">
-        <v>43.31461498596269</v>
+        <v>43.31461498596273</v>
       </c>
       <c r="J6" t="n">
-        <v>32.879776890273</v>
+        <v>32.87977689027303</v>
       </c>
       <c r="K6" t="n">
-        <v>31.76322943078568</v>
+        <v>31.76322943078569</v>
       </c>
       <c r="L6" t="n">
-        <v>44.77821314368619</v>
+        <v>44.77821314368612</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.18126655159092</v>
+        <v>18.18126655159094</v>
       </c>
       <c r="C7" t="n">
         <v>17.48142366538963</v>
       </c>
       <c r="D7" t="n">
-        <v>27.4178727594762</v>
+        <v>27.41787275947625</v>
       </c>
       <c r="E7" t="n">
-        <v>17.47846343024667</v>
+        <v>17.47846343024668</v>
       </c>
       <c r="F7" t="n">
-        <v>17.47846343024667</v>
+        <v>17.47846343024668</v>
       </c>
       <c r="G7" t="n">
-        <v>21.90576709775818</v>
+        <v>21.90576709775823</v>
       </c>
       <c r="H7" t="n">
-        <v>32.68547537717188</v>
+        <v>32.6854753771719</v>
       </c>
       <c r="I7" t="n">
-        <v>17.48014005494944</v>
+        <v>17.48014005494947</v>
       </c>
       <c r="J7" t="n">
-        <v>18.79247570328307</v>
+        <v>18.79247570328308</v>
       </c>
       <c r="K7" t="n">
-        <v>18.67060040031538</v>
+        <v>18.67060040031539</v>
       </c>
       <c r="L7" t="n">
-        <v>31.54126887085453</v>
+        <v>31.54126887085451</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.40858126742105</v>
+        <v>30.4085812674211</v>
       </c>
       <c r="C8" t="n">
         <v>40.66024135645776</v>
       </c>
       <c r="D8" t="n">
-        <v>52.8683465291102</v>
+        <v>52.86834652911028</v>
       </c>
       <c r="E8" t="n">
-        <v>37.66499857718623</v>
+        <v>37.66499857718625</v>
       </c>
       <c r="F8" t="n">
-        <v>30.05419054764472</v>
+        <v>30.05419054764473</v>
       </c>
       <c r="G8" t="n">
-        <v>45.08516949226711</v>
+        <v>45.08516949226717</v>
       </c>
       <c r="H8" t="n">
-        <v>55.8648777716822</v>
+        <v>55.86487777168229</v>
       </c>
       <c r="I8" t="n">
-        <v>40.6595424494584</v>
+        <v>40.65954244945844</v>
       </c>
       <c r="J8" t="n">
-        <v>41.97403049759274</v>
+        <v>41.97403049759276</v>
       </c>
       <c r="K8" t="n">
-        <v>30.69447446463964</v>
+        <v>30.6944744646397</v>
       </c>
       <c r="L8" t="n">
-        <v>66.1610426451286</v>
+        <v>66.16104264512862</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.99675350708672</v>
+        <v>27.99675350708675</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39684260957781</v>
+        <v>31.39684260957777</v>
       </c>
       <c r="D9" t="n">
-        <v>41.33337627415919</v>
+        <v>41.33337627415936</v>
       </c>
       <c r="E9" t="n">
-        <v>36.12807951678127</v>
+        <v>36.12807951678128</v>
       </c>
       <c r="F9" t="n">
-        <v>31.39684617452713</v>
+        <v>31.39684617452718</v>
       </c>
       <c r="G9" t="n">
-        <v>35.82118604194631</v>
+        <v>35.8211860419464</v>
       </c>
       <c r="H9" t="n">
-        <v>46.60089432136002</v>
+        <v>46.60089432136011</v>
       </c>
       <c r="I9" t="n">
-        <v>31.39555899913759</v>
+        <v>31.39555899913765</v>
       </c>
       <c r="J9" t="n">
-        <v>32.7078946474712</v>
+        <v>32.70789464747128</v>
       </c>
       <c r="K9" t="n">
-        <v>30.21050261569885</v>
+        <v>30.21050261569891</v>
       </c>
       <c r="L9" t="n">
-        <v>45.45668781504264</v>
+        <v>45.45668781504273</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.14617731975062</v>
+        <v>21.1461773197507</v>
       </c>
       <c r="C2" t="n">
         <v>17.27914059440026</v>
       </c>
       <c r="D2" t="n">
-        <v>21.83251633742393</v>
+        <v>21.83251633742403</v>
       </c>
       <c r="E2" t="n">
-        <v>19.16367670255703</v>
+        <v>19.16367670255711</v>
       </c>
       <c r="F2" t="n">
         <v>13.87464665542704</v>
       </c>
       <c r="G2" t="n">
-        <v>21.43040443843071</v>
+        <v>21.43040443843083</v>
       </c>
       <c r="H2" t="n">
-        <v>22.05913282498583</v>
+        <v>22.05913282498584</v>
       </c>
       <c r="I2" t="n">
-        <v>21.18461301259619</v>
+        <v>21.18461301259629</v>
       </c>
       <c r="J2" t="n">
-        <v>26.65222122762073</v>
+        <v>26.65222122762075</v>
       </c>
       <c r="K2" t="n">
-        <v>27.41820490064688</v>
+        <v>27.41820490064687</v>
       </c>
       <c r="L2" t="n">
-        <v>22.20961948627914</v>
+        <v>22.20961948627915</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.65747216201309</v>
+        <v>21.65747216201311</v>
       </c>
       <c r="C3" t="n">
-        <v>15.58029201294636</v>
+        <v>15.58029201294637</v>
       </c>
       <c r="D3" t="n">
-        <v>26.52911012068123</v>
+        <v>26.5291101206813</v>
       </c>
       <c r="E3" t="n">
-        <v>18.68196190078454</v>
+        <v>18.68196190078455</v>
       </c>
       <c r="F3" t="n">
-        <v>9.94970878834587</v>
+        <v>9.949708788345877</v>
       </c>
       <c r="G3" t="n">
-        <v>23.68138487712032</v>
+        <v>23.68138487712037</v>
       </c>
       <c r="H3" t="n">
         <v>29.00853588316655</v>
       </c>
       <c r="I3" t="n">
-        <v>21.93017757311727</v>
+        <v>21.93017757311719</v>
       </c>
       <c r="J3" t="n">
-        <v>30.98549358388583</v>
+        <v>30.98549358388575</v>
       </c>
       <c r="K3" t="n">
-        <v>32.07832791395654</v>
+        <v>32.07832791395657</v>
       </c>
       <c r="L3" t="n">
-        <v>29.26278297701622</v>
+        <v>29.26278297701624</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.75234611154259</v>
+        <v>13.75234611154264</v>
       </c>
       <c r="C4" t="n">
         <v>13.87801957482444</v>
       </c>
       <c r="D4" t="n">
-        <v>21.5048610477097</v>
+        <v>21.50486104770975</v>
       </c>
       <c r="E4" t="n">
-        <v>13.90005484840228</v>
+        <v>13.90005484840227</v>
       </c>
       <c r="F4" t="n">
-        <v>13.90005484840228</v>
+        <v>13.90005484840227</v>
       </c>
       <c r="G4" t="n">
-        <v>16.93305350777432</v>
+        <v>16.93305350777437</v>
       </c>
       <c r="H4" t="n">
-        <v>25.56212439718555</v>
+        <v>25.5621243971856</v>
       </c>
       <c r="I4" t="n">
         <v>13.99666326536987</v>
       </c>
       <c r="J4" t="n">
-        <v>14.22748862689038</v>
+        <v>14.22748862689043</v>
       </c>
       <c r="K4" t="n">
-        <v>13.90168759999831</v>
+        <v>13.90168759999836</v>
       </c>
       <c r="L4" t="n">
-        <v>25.68815979310693</v>
+        <v>25.68815979310697</v>
       </c>
     </row>
     <row r="5">
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.32296277944124</v>
+        <v>68.3229627794413</v>
       </c>
       <c r="C5" t="n">
         <v>74.97731106949242</v>
@@ -5792,28 +5792,28 @@
         <v>191.5516874390261</v>
       </c>
       <c r="E5" t="n">
-        <v>74.97731919769754</v>
+        <v>74.97731919769755</v>
       </c>
       <c r="F5" t="n">
-        <v>74.97731919769754</v>
+        <v>74.97731919769755</v>
       </c>
       <c r="G5" t="n">
-        <v>122.6761732345237</v>
+        <v>122.6761732345243</v>
       </c>
       <c r="H5" t="n">
         <v>288.4018487041574</v>
       </c>
       <c r="I5" t="n">
-        <v>74.97636821234552</v>
+        <v>74.97636821234551</v>
       </c>
       <c r="J5" t="n">
-        <v>81.13384903636734</v>
+        <v>81.13384903636737</v>
       </c>
       <c r="K5" t="n">
-        <v>68.47098356353177</v>
+        <v>68.47098356353186</v>
       </c>
       <c r="L5" t="n">
-        <v>78.25346386448811</v>
+        <v>78.25346386448838</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.26794289770206</v>
+        <v>31.26794289770207</v>
       </c>
       <c r="C6" t="n">
-        <v>31.42410183848974</v>
+        <v>31.42410183848973</v>
       </c>
       <c r="D6" t="n">
-        <v>39.20195139464984</v>
+        <v>39.20195139464987</v>
       </c>
       <c r="E6" t="n">
-        <v>29.73449388181343</v>
+        <v>29.73449388181341</v>
       </c>
       <c r="F6" t="n">
-        <v>31.52085720074499</v>
+        <v>31.52085720074501</v>
       </c>
       <c r="G6" t="n">
-        <v>47.07745704755571</v>
+        <v>47.07745704755588</v>
       </c>
       <c r="H6" t="n">
-        <v>55.49358842759653</v>
+        <v>55.49358842759655</v>
       </c>
       <c r="I6" t="n">
-        <v>31.51226005152935</v>
+        <v>31.51226005152932</v>
       </c>
       <c r="J6" t="n">
-        <v>44.06639816120848</v>
+        <v>44.0663981612085</v>
       </c>
       <c r="K6" t="n">
-        <v>31.35685344896905</v>
+        <v>31.3568534489691</v>
       </c>
       <c r="L6" t="n">
-        <v>43.28365609840238</v>
+        <v>43.28365609840243</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.06476613971702</v>
+        <v>18.06476613971703</v>
       </c>
       <c r="C7" t="n">
-        <v>18.31002615069124</v>
+        <v>18.31002615069125</v>
       </c>
       <c r="D7" t="n">
-        <v>25.81719591591162</v>
+        <v>25.8171959159117</v>
       </c>
       <c r="E7" t="n">
         <v>18.30753334796436</v>
       </c>
       <c r="F7" t="n">
-        <v>18.30753334796435</v>
+        <v>18.30753334796436</v>
       </c>
       <c r="G7" t="n">
-        <v>21.24547353594867</v>
+        <v>21.24547353594881</v>
       </c>
       <c r="H7" t="n">
-        <v>29.87454442535998</v>
+        <v>29.87454442535999</v>
       </c>
       <c r="I7" t="n">
-        <v>18.3090832935443</v>
+        <v>18.30908329354431</v>
       </c>
       <c r="J7" t="n">
-        <v>18.5399086550648</v>
+        <v>18.53990865506483</v>
       </c>
       <c r="K7" t="n">
-        <v>18.21410762817275</v>
+        <v>18.21410762817277</v>
       </c>
       <c r="L7" t="n">
-        <v>30.00057982128136</v>
+        <v>30.00057982128139</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.23800896696239</v>
+        <v>30.23800896696242</v>
       </c>
       <c r="C8" t="n">
-        <v>41.36117199162121</v>
+        <v>41.36117199162127</v>
       </c>
       <c r="D8" t="n">
-        <v>51.12421375156217</v>
+        <v>51.12421375156223</v>
       </c>
       <c r="E8" t="n">
-        <v>38.38613027942649</v>
+        <v>38.38613027942652</v>
       </c>
       <c r="F8" t="n">
-        <v>30.82665350881839</v>
+        <v>30.82665350881838</v>
       </c>
       <c r="G8" t="n">
-        <v>44.29677076700341</v>
+        <v>44.29677076700344</v>
       </c>
       <c r="H8" t="n">
-        <v>52.92584165641687</v>
+        <v>52.92584165641694</v>
       </c>
       <c r="I8" t="n">
-        <v>41.36038052459891</v>
+        <v>41.36038052459893</v>
       </c>
       <c r="J8" t="n">
-        <v>41.59334373626891</v>
+        <v>41.59334373626902</v>
       </c>
       <c r="K8" t="n">
-        <v>30.18528500999967</v>
+        <v>30.18528500999971</v>
       </c>
       <c r="L8" t="n">
-        <v>64.41491448594907</v>
+        <v>64.41491448594915</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.09209989628925</v>
+        <v>27.09209989628932</v>
       </c>
       <c r="C9" t="n">
-        <v>31.20205453343344</v>
+        <v>31.20205453343346</v>
       </c>
       <c r="D9" t="n">
-        <v>38.70930958362577</v>
+        <v>38.70930958362578</v>
       </c>
       <c r="E9" t="n">
-        <v>35.66183349647889</v>
+        <v>35.66183349647892</v>
       </c>
       <c r="F9" t="n">
-        <v>31.20205871604003</v>
+        <v>31.20205871604002</v>
       </c>
       <c r="G9" t="n">
-        <v>34.13750191869093</v>
+        <v>34.13750191869103</v>
       </c>
       <c r="H9" t="n">
-        <v>42.76657280810218</v>
+        <v>42.76657280810227</v>
       </c>
       <c r="I9" t="n">
         <v>31.20111167628654</v>
       </c>
       <c r="J9" t="n">
-        <v>31.43193703780701</v>
+        <v>31.43193703780705</v>
       </c>
       <c r="K9" t="n">
-        <v>28.86691681926098</v>
+        <v>28.86691681926104</v>
       </c>
       <c r="L9" t="n">
-        <v>42.89260820402357</v>
+        <v>42.89260820402364</v>
       </c>
     </row>
   </sheetData>
@@ -6074,7 +6074,7 @@
         <v>13.02225200549186</v>
       </c>
       <c r="G2" t="n">
-        <v>20.46915784655605</v>
+        <v>20.46915784655603</v>
       </c>
       <c r="H2" t="n">
         <v>20.71030462770958</v>
@@ -6083,13 +6083,13 @@
         <v>20.35337817635575</v>
       </c>
       <c r="J2" t="n">
-        <v>25.97447067574617</v>
+        <v>25.97447067574623</v>
       </c>
       <c r="K2" t="n">
-        <v>26.6665815549138</v>
+        <v>26.66658155491382</v>
       </c>
       <c r="L2" t="n">
-        <v>20.66569261916641</v>
+        <v>20.6656926191664</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.42027300322491</v>
+        <v>20.42027300322488</v>
       </c>
       <c r="C3" t="n">
-        <v>13.62244751686342</v>
+        <v>13.62244751686343</v>
       </c>
       <c r="D3" t="n">
-        <v>21.6988758350345</v>
+        <v>21.69887583503452</v>
       </c>
       <c r="E3" t="n">
-        <v>16.69919307673124</v>
+        <v>16.69919307673128</v>
       </c>
       <c r="F3" t="n">
-        <v>8.034715357228864</v>
+        <v>8.034715357228835</v>
       </c>
       <c r="G3" t="n">
-        <v>20.87252162410664</v>
+        <v>20.87252162410661</v>
       </c>
       <c r="H3" t="n">
         <v>23.42473784660208</v>
       </c>
       <c r="I3" t="n">
-        <v>20.05010445835556</v>
+        <v>20.05010445835554</v>
       </c>
       <c r="J3" t="n">
-        <v>30.59640830615567</v>
+        <v>30.59640830615579</v>
       </c>
       <c r="K3" t="n">
         <v>30.95380671517343</v>
       </c>
       <c r="L3" t="n">
-        <v>22.29473345505256</v>
+        <v>22.29473345505257</v>
       </c>
     </row>
     <row r="4">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.15294601253689</v>
+        <v>12.15294601253686</v>
       </c>
       <c r="C4" t="n">
         <v>11.26918206140335</v>
       </c>
       <c r="D4" t="n">
-        <v>14.191627391193</v>
+        <v>14.19162739119301</v>
       </c>
       <c r="E4" t="n">
         <v>11.28887318221208</v>
@@ -6157,16 +6157,16 @@
         <v>12.84060375684459</v>
       </c>
       <c r="H4" t="n">
-        <v>17.12009985957611</v>
+        <v>17.1200998595761</v>
       </c>
       <c r="I4" t="n">
-        <v>11.37826019852935</v>
+        <v>11.37826019852934</v>
       </c>
       <c r="J4" t="n">
-        <v>14.168782781784</v>
+        <v>14.16878278178401</v>
       </c>
       <c r="K4" t="n">
-        <v>12.56664780882385</v>
+        <v>12.56664780882383</v>
       </c>
       <c r="L4" t="n">
         <v>15.09307767964833</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.53989566138932</v>
+        <v>52.5398956613887</v>
       </c>
       <c r="C5" t="n">
-        <v>43.10065456445566</v>
+        <v>43.10065456445562</v>
       </c>
       <c r="D5" t="n">
-        <v>85.78116107544092</v>
+        <v>85.78116107544083</v>
       </c>
       <c r="E5" t="n">
-        <v>43.10066249455018</v>
+        <v>43.10066249455012</v>
       </c>
       <c r="F5" t="n">
-        <v>43.10066249455019</v>
+        <v>43.10066249455012</v>
       </c>
       <c r="G5" t="n">
-        <v>65.80857366189085</v>
+        <v>65.80857366189076</v>
       </c>
       <c r="H5" t="n">
-        <v>147.0894192539752</v>
+        <v>147.0894192539749</v>
       </c>
       <c r="I5" t="n">
-        <v>43.10005320987726</v>
+        <v>43.10005320987725</v>
       </c>
       <c r="J5" t="n">
-        <v>93.31712482271817</v>
+        <v>93.31712482271813</v>
       </c>
       <c r="K5" t="n">
-        <v>59.19923438799611</v>
+        <v>59.19923438799587</v>
       </c>
       <c r="L5" t="n">
-        <v>117.6218489812872</v>
+        <v>117.621848981287</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.93229607387607</v>
+        <v>43.93229607387605</v>
       </c>
       <c r="C6" t="n">
-        <v>29.93751515231664</v>
+        <v>29.93751515231669</v>
       </c>
       <c r="D6" t="n">
-        <v>45.66995895315021</v>
+        <v>45.66995895315018</v>
       </c>
       <c r="E6" t="n">
-        <v>28.13153285780956</v>
+        <v>28.13153285780958</v>
       </c>
       <c r="F6" t="n">
-        <v>30.01058741875383</v>
+        <v>30.01058741875384</v>
       </c>
       <c r="G6" t="n">
-        <v>44.61995381818373</v>
+        <v>44.6199538181837</v>
       </c>
       <c r="H6" t="n">
         <v>35.79009108381887</v>
       </c>
       <c r="I6" t="n">
-        <v>43.15761025986846</v>
+        <v>43.15761025986843</v>
       </c>
       <c r="J6" t="n">
-        <v>45.60655505761889</v>
+        <v>45.60655505761891</v>
       </c>
       <c r="K6" t="n">
         <v>31.19515920963279</v>
       </c>
       <c r="L6" t="n">
-        <v>33.75108835363016</v>
+        <v>33.75108835363017</v>
       </c>
     </row>
     <row r="7">
@@ -6259,13 +6259,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.48119279057295</v>
+        <v>16.48119279057294</v>
       </c>
       <c r="C7" t="n">
         <v>15.70710833114382</v>
       </c>
       <c r="D7" t="n">
-        <v>18.51978689719892</v>
+        <v>18.51978689719893</v>
       </c>
       <c r="E7" t="n">
         <v>15.70476897210351</v>
@@ -6274,19 +6274,19 @@
         <v>15.70476897210351</v>
       </c>
       <c r="G7" t="n">
-        <v>17.1688505348807</v>
+        <v>17.16885053488069</v>
       </c>
       <c r="H7" t="n">
         <v>21.4483466376122</v>
       </c>
       <c r="I7" t="n">
-        <v>15.70650697656542</v>
+        <v>15.70650697656541</v>
       </c>
       <c r="J7" t="n">
-        <v>18.49702955982008</v>
+        <v>18.49702955982011</v>
       </c>
       <c r="K7" t="n">
-        <v>16.8948945868599</v>
+        <v>16.89489458685992</v>
       </c>
       <c r="L7" t="n">
         <v>19.42132445768442</v>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.28748900546973</v>
+        <v>29.28748900546972</v>
       </c>
       <c r="C8" t="n">
         <v>39.77223862866488</v>
@@ -6308,28 +6308,28 @@
         <v>44.91950890214545</v>
       </c>
       <c r="E8" t="n">
-        <v>36.69305257566247</v>
+        <v>36.69305257566246</v>
       </c>
       <c r="F8" t="n">
         <v>28.8689496068063</v>
       </c>
       <c r="G8" t="n">
-        <v>41.23390781652992</v>
+        <v>41.23390781652986</v>
       </c>
       <c r="H8" t="n">
-        <v>45.51340391926182</v>
+        <v>45.51340391926185</v>
       </c>
       <c r="I8" t="n">
-        <v>39.77156425821464</v>
+        <v>39.77156425821457</v>
       </c>
       <c r="J8" t="n">
-        <v>42.56429951156458</v>
+        <v>42.56429951156461</v>
       </c>
       <c r="K8" t="n">
-        <v>29.49205353460365</v>
+        <v>29.4920535346036</v>
       </c>
       <c r="L8" t="n">
-        <v>55.24709911672574</v>
+        <v>55.2470991167258</v>
       </c>
     </row>
     <row r="9">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.41194794525276</v>
+        <v>26.41194794525278</v>
       </c>
       <c r="C9" t="n">
         <v>29.74303339412205</v>
@@ -6348,28 +6348,28 @@
         <v>32.55579965029517</v>
       </c>
       <c r="E9" t="n">
-        <v>34.48031781974515</v>
+        <v>34.48031781974512</v>
       </c>
       <c r="F9" t="n">
-        <v>29.74303899387072</v>
+        <v>29.74303899387073</v>
       </c>
       <c r="G9" t="n">
         <v>31.20477559785892</v>
       </c>
       <c r="H9" t="n">
-        <v>35.48427170059043</v>
+        <v>35.48427170059041</v>
       </c>
       <c r="I9" t="n">
-        <v>29.74243203954366</v>
+        <v>29.74243203954364</v>
       </c>
       <c r="J9" t="n">
-        <v>32.53295462279836</v>
+        <v>32.53295462279831</v>
       </c>
       <c r="K9" t="n">
         <v>28.55226825857147</v>
       </c>
       <c r="L9" t="n">
-        <v>33.45724952066266</v>
+        <v>33.45724952066264</v>
       </c>
     </row>
   </sheetData>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.2994528318961</v>
+        <v>20.29945283189608</v>
       </c>
       <c r="C2" t="n">
-        <v>16.29972330705813</v>
+        <v>16.29972330705812</v>
       </c>
       <c r="D2" t="n">
         <v>20.22168236162312</v>
@@ -6467,25 +6467,25 @@
         <v>18.15079344029017</v>
       </c>
       <c r="F2" t="n">
-        <v>12.94723517740753</v>
+        <v>12.94723517740751</v>
       </c>
       <c r="G2" t="n">
-        <v>20.24832430262583</v>
+        <v>20.24832430262582</v>
       </c>
       <c r="H2" t="n">
-        <v>20.04868999306133</v>
+        <v>20.04868999306132</v>
       </c>
       <c r="I2" t="n">
-        <v>20.24857999950432</v>
+        <v>20.24857999950431</v>
       </c>
       <c r="J2" t="n">
-        <v>25.67598301611816</v>
+        <v>25.67598301611815</v>
       </c>
       <c r="K2" t="n">
         <v>26.47367420646552</v>
       </c>
       <c r="L2" t="n">
-        <v>20.17194805461328</v>
+        <v>20.17194805461326</v>
       </c>
     </row>
     <row r="3">
@@ -6498,34 +6498,34 @@
         <v>20.57519220332065</v>
       </c>
       <c r="C3" t="n">
-        <v>13.78846921769805</v>
+        <v>13.78846921769803</v>
       </c>
       <c r="D3" t="n">
-        <v>20.02389140037926</v>
+        <v>20.02389140037925</v>
       </c>
       <c r="E3" t="n">
-        <v>16.83946686020859</v>
+        <v>16.8394668602086</v>
       </c>
       <c r="F3" t="n">
-        <v>8.248303361005322</v>
+        <v>8.248303361005318</v>
       </c>
       <c r="G3" t="n">
-        <v>20.21298767431444</v>
+        <v>20.21298767431445</v>
       </c>
       <c r="H3" t="n">
         <v>19.65433100959093</v>
       </c>
       <c r="I3" t="n">
-        <v>20.21453156039934</v>
+        <v>20.21453156039932</v>
       </c>
       <c r="J3" t="n">
-        <v>29.78550191811717</v>
+        <v>29.78550191811712</v>
       </c>
       <c r="K3" t="n">
-        <v>30.60898391964908</v>
+        <v>30.60898391964907</v>
       </c>
       <c r="L3" t="n">
-        <v>19.69923221913195</v>
+        <v>19.69923221913197</v>
       </c>
     </row>
     <row r="4">
@@ -6547,25 +6547,25 @@
         <v>11.65776634839708</v>
       </c>
       <c r="F4" t="n">
-        <v>11.65776634839709</v>
+        <v>11.65776634839708</v>
       </c>
       <c r="G4" t="n">
-        <v>11.87317609073461</v>
+        <v>11.8731760907346</v>
       </c>
       <c r="H4" t="n">
         <v>11.22403172942413</v>
       </c>
       <c r="I4" t="n">
-        <v>11.72622894979128</v>
+        <v>11.72622894979127</v>
       </c>
       <c r="J4" t="n">
         <v>13.16395167008799</v>
       </c>
       <c r="K4" t="n">
-        <v>12.15462542682059</v>
+        <v>12.1546254268206</v>
       </c>
       <c r="L4" t="n">
-        <v>11.08294431872669</v>
+        <v>11.0829443187267</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.8280429491917</v>
+        <v>56.82804294919177</v>
       </c>
       <c r="C5" t="n">
-        <v>47.74198597054757</v>
+        <v>47.74198597054753</v>
       </c>
       <c r="D5" t="n">
-        <v>43.23496739381638</v>
+        <v>43.23496739381635</v>
       </c>
       <c r="E5" t="n">
-        <v>47.74199374587933</v>
+        <v>47.74199374587925</v>
       </c>
       <c r="F5" t="n">
-        <v>47.74199374587933</v>
+        <v>47.74199374587925</v>
       </c>
       <c r="G5" t="n">
-        <v>47.98607812306594</v>
+        <v>47.98607812306575</v>
       </c>
       <c r="H5" t="n">
-        <v>40.63663427067642</v>
+        <v>40.63663427067644</v>
       </c>
       <c r="I5" t="n">
         <v>47.74168619592962</v>
       </c>
       <c r="J5" t="n">
-        <v>70.2516848763692</v>
+        <v>70.25168487636915</v>
       </c>
       <c r="K5" t="n">
-        <v>50.8406830436451</v>
+        <v>50.84068304364513</v>
       </c>
       <c r="L5" t="n">
-        <v>31.344472838199</v>
+        <v>31.34447283819903</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.98409549664148</v>
+        <v>41.98409549664145</v>
       </c>
       <c r="C6" t="n">
-        <v>29.03943538101258</v>
+        <v>29.03943538101251</v>
       </c>
       <c r="D6" t="n">
-        <v>28.93104174408554</v>
+        <v>28.93104174408555</v>
       </c>
       <c r="E6" t="n">
         <v>27.35764304297824</v>
       </c>
       <c r="F6" t="n">
-        <v>29.07902741634388</v>
+        <v>29.07902741634386</v>
       </c>
       <c r="G6" t="n">
-        <v>41.37859338604157</v>
+        <v>41.37859338604155</v>
       </c>
       <c r="H6" t="n">
         <v>40.443416288226</v>
       </c>
       <c r="I6" t="n">
-        <v>41.23164624509822</v>
+        <v>41.23164624509823</v>
       </c>
       <c r="J6" t="n">
-        <v>31.43110224008147</v>
+        <v>31.43110224008146</v>
       </c>
       <c r="K6" t="n">
-        <v>29.50428861825055</v>
+        <v>29.50428861825056</v>
       </c>
       <c r="L6" t="n">
-        <v>28.43278390370241</v>
+        <v>28.4327839037024</v>
       </c>
     </row>
     <row r="7">
@@ -6655,34 +6655,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.41268934862414</v>
+        <v>16.41268934862413</v>
       </c>
       <c r="C7" t="n">
         <v>15.66053987169883</v>
       </c>
       <c r="D7" t="n">
-        <v>15.53415442623216</v>
+        <v>15.53415442623215</v>
       </c>
       <c r="E7" t="n">
-        <v>15.65887179146604</v>
+        <v>15.65887179146602</v>
       </c>
       <c r="F7" t="n">
-        <v>15.65887179146604</v>
+        <v>15.65887179146602</v>
       </c>
       <c r="G7" t="n">
-        <v>15.80718723802428</v>
+        <v>15.80718723802425</v>
       </c>
       <c r="H7" t="n">
-        <v>15.15804287671379</v>
+        <v>15.15804287671378</v>
       </c>
       <c r="I7" t="n">
-        <v>15.66024009708092</v>
+        <v>15.66024009708091</v>
       </c>
       <c r="J7" t="n">
         <v>17.09796281737766</v>
       </c>
       <c r="K7" t="n">
-        <v>16.08863657411023</v>
+        <v>16.08863657411024</v>
       </c>
       <c r="L7" t="n">
         <v>15.01695546601636</v>
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.24613169014851</v>
+        <v>28.24613169014849</v>
       </c>
       <c r="C8" t="n">
-        <v>37.83876346057693</v>
+        <v>37.83876346057698</v>
       </c>
       <c r="D8" t="n">
-        <v>39.85687927658208</v>
+        <v>39.85687927658211</v>
       </c>
       <c r="E8" t="n">
-        <v>35.00963975988777</v>
+        <v>35.00963975988775</v>
       </c>
       <c r="F8" t="n">
-        <v>27.82093582400546</v>
+        <v>27.82093582400548</v>
       </c>
       <c r="G8" t="n">
-        <v>37.98488223018368</v>
+        <v>37.98488223018367</v>
       </c>
       <c r="H8" t="n">
-        <v>37.33573786887285</v>
+        <v>37.33573786887287</v>
       </c>
       <c r="I8" t="n">
         <v>37.83793508924034</v>
       </c>
       <c r="J8" t="n">
-        <v>39.27769075250969</v>
+        <v>39.2776907525097</v>
       </c>
       <c r="K8" t="n">
-        <v>27.72992911182009</v>
+        <v>27.72992911182011</v>
       </c>
       <c r="L8" t="n">
-        <v>48.00008732497095</v>
+        <v>48.00008732497097</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.73647904957979</v>
+        <v>24.73647904957977</v>
       </c>
       <c r="C9" t="n">
-        <v>27.51608882900727</v>
+        <v>27.51608882900722</v>
       </c>
       <c r="D9" t="n">
-        <v>27.38978632002103</v>
+        <v>27.38978632002097</v>
       </c>
       <c r="E9" t="n">
-        <v>31.59167214140945</v>
+        <v>31.59167214140941</v>
       </c>
       <c r="F9" t="n">
-        <v>27.51609589141212</v>
+        <v>27.51609589141208</v>
       </c>
       <c r="G9" t="n">
-        <v>27.66273619533268</v>
+        <v>27.66273619533262</v>
       </c>
       <c r="H9" t="n">
-        <v>27.01359183402222</v>
+        <v>27.01359183402217</v>
       </c>
       <c r="I9" t="n">
-        <v>27.51578905438934</v>
+        <v>27.51578905438931</v>
       </c>
       <c r="J9" t="n">
-        <v>28.95351177468609</v>
+        <v>28.95351177468603</v>
       </c>
       <c r="K9" t="n">
-        <v>25.8978708745891</v>
+        <v>25.89787087458905</v>
       </c>
       <c r="L9" t="n">
-        <v>26.87250442332481</v>
+        <v>26.87250442332477</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.26227492372217</v>
+        <v>20.2622749237222</v>
       </c>
       <c r="C2" t="n">
         <v>16.25628510844684</v>
       </c>
       <c r="D2" t="n">
-        <v>20.1659466090893</v>
+        <v>20.16594660908934</v>
       </c>
       <c r="E2" t="n">
         <v>18.10442725390757</v>
       </c>
       <c r="F2" t="n">
-        <v>12.90890355864397</v>
+        <v>12.90890355864396</v>
       </c>
       <c r="G2" t="n">
-        <v>20.20091110930147</v>
+        <v>20.20091110930148</v>
       </c>
       <c r="H2" t="n">
-        <v>20.01105033836649</v>
+        <v>20.01105033836648</v>
       </c>
       <c r="I2" t="n">
-        <v>20.21079950867553</v>
+        <v>20.21079950867554</v>
       </c>
       <c r="J2" t="n">
-        <v>25.60907968437535</v>
+        <v>25.60907968437536</v>
       </c>
       <c r="K2" t="n">
         <v>26.38207041936698</v>
       </c>
       <c r="L2" t="n">
-        <v>20.14893226178934</v>
+        <v>20.14893226178935</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.52124555702142</v>
+        <v>20.52124555702143</v>
       </c>
       <c r="C3" t="n">
-        <v>13.72105724672059</v>
+        <v>13.72105724672061</v>
       </c>
       <c r="D3" t="n">
         <v>19.83833086420756</v>
       </c>
       <c r="E3" t="n">
-        <v>16.76749684373199</v>
+        <v>16.76749684373198</v>
       </c>
       <c r="F3" t="n">
-        <v>8.189595965581407</v>
+        <v>8.189595965581439</v>
       </c>
       <c r="G3" t="n">
-        <v>20.08695485324107</v>
+        <v>20.08695485324105</v>
       </c>
       <c r="H3" t="n">
-        <v>19.59447448858984</v>
+        <v>19.59447448858987</v>
       </c>
       <c r="I3" t="n">
-        <v>20.15673349455747</v>
+        <v>20.15673349455749</v>
       </c>
       <c r="J3" t="n">
-        <v>29.6176899749517</v>
+        <v>29.61768997495172</v>
       </c>
       <c r="K3" t="n">
-        <v>30.30159510033943</v>
+        <v>30.30159510033944</v>
       </c>
       <c r="L3" t="n">
-        <v>19.74445358885102</v>
+        <v>19.74445358885101</v>
       </c>
     </row>
     <row r="4">
@@ -6937,7 +6937,7 @@
         <v>11.56992643239264</v>
       </c>
       <c r="D4" t="n">
-        <v>11.32573749878044</v>
+        <v>11.32573749878045</v>
       </c>
       <c r="E4" t="n">
         <v>11.58696012922477</v>
@@ -6961,7 +6961,7 @@
         <v>11.74981389763293</v>
       </c>
       <c r="L4" t="n">
-        <v>11.17364453468722</v>
+        <v>11.17364453468721</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.86795363516165</v>
+        <v>55.86795363516154</v>
       </c>
       <c r="C5" t="n">
-        <v>46.89473498876124</v>
+        <v>46.89473498876129</v>
       </c>
       <c r="D5" t="n">
-        <v>38.99980465212734</v>
+        <v>38.99980465212725</v>
       </c>
       <c r="E5" t="n">
-        <v>46.89474277880933</v>
+        <v>46.89474277880934</v>
       </c>
       <c r="F5" t="n">
-        <v>46.89474277880933</v>
+        <v>46.89474277880934</v>
       </c>
       <c r="G5" t="n">
-        <v>45.48060348176431</v>
+        <v>45.48060348176488</v>
       </c>
       <c r="H5" t="n">
-        <v>38.91279321000743</v>
+        <v>38.91279321000744</v>
       </c>
       <c r="I5" t="n">
-        <v>46.89446030854858</v>
+        <v>46.89446030854866</v>
       </c>
       <c r="J5" t="n">
-        <v>67.58939256817965</v>
+        <v>67.58939256817982</v>
       </c>
       <c r="K5" t="n">
-        <v>44.65226388042969</v>
+        <v>44.65226388042974</v>
       </c>
       <c r="L5" t="n">
-        <v>37.76788618296603</v>
+        <v>37.76788618296601</v>
       </c>
     </row>
     <row r="6">
@@ -7014,34 +7014,34 @@
         <v>29.75828577137909</v>
       </c>
       <c r="C6" t="n">
-        <v>28.96130092400264</v>
+        <v>28.96130092400265</v>
       </c>
       <c r="D6" t="n">
-        <v>28.64313784678163</v>
+        <v>28.64313784678162</v>
       </c>
       <c r="E6" t="n">
-        <v>27.28018178635767</v>
+        <v>27.28018178635769</v>
       </c>
       <c r="F6" t="n">
         <v>28.99861954482606</v>
       </c>
       <c r="G6" t="n">
-        <v>29.03723610149803</v>
+        <v>29.03723610149802</v>
       </c>
       <c r="H6" t="n">
-        <v>40.3528858449923</v>
+        <v>40.35288584499231</v>
       </c>
       <c r="I6" t="n">
-        <v>28.99946800805881</v>
+        <v>28.99946800805883</v>
       </c>
       <c r="J6" t="n">
-        <v>31.21929793553432</v>
+        <v>31.21929793553431</v>
       </c>
       <c r="K6" t="n">
-        <v>29.081761159537</v>
+        <v>29.08176115953696</v>
       </c>
       <c r="L6" t="n">
-        <v>28.51503200170168</v>
+        <v>28.51503200170169</v>
       </c>
     </row>
     <row r="7">
@@ -7054,19 +7054,19 @@
         <v>16.32901862038044</v>
       </c>
       <c r="C7" t="n">
-        <v>15.57047553727282</v>
+        <v>15.57047553727283</v>
       </c>
       <c r="D7" t="n">
-        <v>15.2408648570782</v>
+        <v>15.24086485707821</v>
       </c>
       <c r="E7" t="n">
-        <v>15.56867514828424</v>
+        <v>15.56867514828425</v>
       </c>
       <c r="F7" t="n">
-        <v>15.56867514828424</v>
+        <v>15.56867514828425</v>
       </c>
       <c r="G7" t="n">
-        <v>15.60796895049941</v>
+        <v>15.60796895049943</v>
       </c>
       <c r="H7" t="n">
         <v>15.06656693341716</v>
@@ -7075,13 +7075,13 @@
         <v>15.57020085706013</v>
       </c>
       <c r="J7" t="n">
-        <v>16.87807552020596</v>
+        <v>16.87807552020597</v>
       </c>
       <c r="K7" t="n">
-        <v>15.6650223922407</v>
+        <v>15.66502239224073</v>
       </c>
       <c r="L7" t="n">
-        <v>15.088853029295</v>
+        <v>15.08885302929501</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.13815393243412</v>
+        <v>28.13815393243413</v>
       </c>
       <c r="C8" t="n">
-        <v>37.69407992877803</v>
+        <v>37.69407992877802</v>
       </c>
       <c r="D8" t="n">
-        <v>39.50284519777957</v>
+        <v>39.50284519777953</v>
       </c>
       <c r="E8" t="n">
-        <v>34.87322413899135</v>
+        <v>34.8732241389914</v>
       </c>
       <c r="F8" t="n">
         <v>27.70552857958677</v>
       </c>
       <c r="G8" t="n">
-        <v>37.7311778139907</v>
+        <v>37.73117781399067</v>
       </c>
       <c r="H8" t="n">
-        <v>37.18977579690809</v>
+        <v>37.18977579690808</v>
       </c>
       <c r="I8" t="n">
-        <v>37.69340972055144</v>
+        <v>37.69340972055137</v>
       </c>
       <c r="J8" t="n">
-        <v>39.00331139563053</v>
+        <v>39.00331139563055</v>
       </c>
       <c r="K8" t="n">
-        <v>27.28256849273874</v>
+        <v>27.28256849273875</v>
       </c>
       <c r="L8" t="n">
-        <v>47.98597416695374</v>
+        <v>47.98597416695375</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.0822657862112</v>
+        <v>24.08226578621122</v>
       </c>
       <c r="C9" t="n">
         <v>26.69128228537785</v>
       </c>
       <c r="D9" t="n">
-        <v>26.3617539051248</v>
+        <v>26.36175390512482</v>
       </c>
       <c r="E9" t="n">
-        <v>30.57738261218832</v>
+        <v>30.57738261218833</v>
       </c>
       <c r="F9" t="n">
-        <v>26.69128937999604</v>
+        <v>26.69128937999603</v>
       </c>
       <c r="G9" t="n">
-        <v>26.72877569860444</v>
+        <v>26.72877569860448</v>
       </c>
       <c r="H9" t="n">
-        <v>26.18737368152219</v>
+        <v>26.1873736815222</v>
       </c>
       <c r="I9" t="n">
-        <v>26.69100760516519</v>
+        <v>26.6910076051652</v>
       </c>
       <c r="J9" t="n">
-        <v>27.99888226831098</v>
+        <v>27.99888226831101</v>
       </c>
       <c r="K9" t="n">
-        <v>24.75549062938157</v>
+        <v>24.75549062938159</v>
       </c>
       <c r="L9" t="n">
-        <v>26.20965977740003</v>
+        <v>26.20965977740008</v>
       </c>
     </row>
   </sheetData>
@@ -7250,16 +7250,16 @@
         <v>21.01534054552804</v>
       </c>
       <c r="C2" t="n">
-        <v>16.98280430519173</v>
+        <v>16.98280430519175</v>
       </c>
       <c r="D2" t="n">
         <v>21.91179522763416</v>
       </c>
       <c r="E2" t="n">
-        <v>18.8719539390988</v>
+        <v>18.87195393909874</v>
       </c>
       <c r="F2" t="n">
-        <v>13.57099509984816</v>
+        <v>13.57099509984812</v>
       </c>
       <c r="G2" t="n">
         <v>21.33669770947692</v>
@@ -7268,16 +7268,16 @@
         <v>22.40465088981018</v>
       </c>
       <c r="I2" t="n">
-        <v>20.95442925189692</v>
+        <v>20.95442925189691</v>
       </c>
       <c r="J2" t="n">
-        <v>26.62369850190575</v>
+        <v>26.62369850190566</v>
       </c>
       <c r="K2" t="n">
-        <v>27.34645254895853</v>
+        <v>27.34645254895856</v>
       </c>
       <c r="L2" t="n">
-        <v>22.16514564605766</v>
+        <v>22.16514564605765</v>
       </c>
     </row>
     <row r="3">
@@ -7290,34 +7290,34 @@
         <v>21.22428931435005</v>
       </c>
       <c r="C3" t="n">
-        <v>14.33455823923412</v>
+        <v>14.33455823923415</v>
       </c>
       <c r="D3" t="n">
-        <v>27.58895532705067</v>
+        <v>27.58895532705071</v>
       </c>
       <c r="E3" t="n">
-        <v>17.44331076098839</v>
+        <v>17.4433107609884</v>
       </c>
       <c r="F3" t="n">
-        <v>8.691366777984847</v>
+        <v>8.691366777984911</v>
       </c>
       <c r="G3" t="n">
-        <v>23.51266202543999</v>
+        <v>23.51266202544005</v>
       </c>
       <c r="H3" t="n">
-        <v>31.91927849985432</v>
+        <v>31.91927849985433</v>
       </c>
       <c r="I3" t="n">
-        <v>20.79310624154808</v>
+        <v>20.79310624154805</v>
       </c>
       <c r="J3" t="n">
-        <v>31.39412561142979</v>
+        <v>31.39412561142966</v>
       </c>
       <c r="K3" t="n">
-        <v>32.12232497546029</v>
+        <v>32.12232497546019</v>
       </c>
       <c r="L3" t="n">
-        <v>29.44413837936202</v>
+        <v>29.44413837936207</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.07624922064202</v>
+        <v>13.07624922064201</v>
       </c>
       <c r="C4" t="n">
-        <v>12.0471971296833</v>
+        <v>12.04719712968332</v>
       </c>
       <c r="D4" t="n">
-        <v>23.20211724455876</v>
+        <v>23.20211724455875</v>
       </c>
       <c r="E4" t="n">
         <v>12.07057548011424</v>
       </c>
       <c r="F4" t="n">
-        <v>12.07057548011423</v>
+        <v>12.07057548011424</v>
       </c>
       <c r="G4" t="n">
-        <v>16.67539263567785</v>
+        <v>16.67539263567789</v>
       </c>
       <c r="H4" t="n">
-        <v>30.20970081566676</v>
+        <v>30.20970081566684</v>
       </c>
       <c r="I4" t="n">
-        <v>12.19185849436897</v>
+        <v>12.19185849436895</v>
       </c>
       <c r="J4" t="n">
-        <v>14.94146488346365</v>
+        <v>14.94146488346364</v>
       </c>
       <c r="K4" t="n">
-        <v>14.00146986663744</v>
+        <v>14.00146986663743</v>
       </c>
       <c r="L4" t="n">
-        <v>25.9790449311348</v>
+        <v>25.97904493113479</v>
       </c>
     </row>
     <row r="5">
@@ -7370,34 +7370,34 @@
         <v>62.70017368067629</v>
       </c>
       <c r="C5" t="n">
-        <v>51.46699232750235</v>
+        <v>51.46699232750171</v>
       </c>
       <c r="D5" t="n">
-        <v>235.5971244162988</v>
+        <v>235.5971244162993</v>
       </c>
       <c r="E5" t="n">
-        <v>51.46700053201396</v>
+        <v>51.46700053201367</v>
       </c>
       <c r="F5" t="n">
-        <v>51.46700053201396</v>
+        <v>51.46700053201366</v>
       </c>
       <c r="G5" t="n">
-        <v>128.4278408128568</v>
+        <v>128.4278408128577</v>
       </c>
       <c r="H5" t="n">
-        <v>384.8398583352489</v>
+        <v>384.8398583352498</v>
       </c>
       <c r="I5" t="n">
-        <v>51.46569642355087</v>
+        <v>51.46569642355064</v>
       </c>
       <c r="J5" t="n">
-        <v>101.4449990303391</v>
+        <v>101.4449990303389</v>
       </c>
       <c r="K5" t="n">
-        <v>79.07258606732066</v>
+        <v>79.07258606732069</v>
       </c>
       <c r="L5" t="n">
-        <v>68.38723654318474</v>
+        <v>68.3872365431864</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.82968695951995</v>
+        <v>31.82968695951997</v>
       </c>
       <c r="C6" t="n">
-        <v>30.79766770551767</v>
+        <v>30.79766770551765</v>
       </c>
       <c r="D6" t="n">
-        <v>42.21980526387307</v>
+        <v>42.21980526387316</v>
       </c>
       <c r="E6" t="n">
-        <v>28.98709274639281</v>
+        <v>28.98709274639286</v>
       </c>
       <c r="F6" t="n">
         <v>30.93815340068076</v>
       </c>
       <c r="G6" t="n">
-        <v>48.95031141231541</v>
+        <v>48.95031141231546</v>
       </c>
       <c r="H6" t="n">
-        <v>62.27437483121797</v>
+        <v>62.27437483121801</v>
       </c>
       <c r="I6" t="n">
-        <v>44.46677727100655</v>
+        <v>44.4667772710066</v>
       </c>
       <c r="J6" t="n">
-        <v>46.89533357427886</v>
+        <v>46.89533357427882</v>
       </c>
       <c r="K6" t="n">
-        <v>32.7059925163035</v>
+        <v>32.7059925163036</v>
       </c>
       <c r="L6" t="n">
-        <v>44.81778557205929</v>
+        <v>44.81778557205935</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.68112861935764</v>
+        <v>17.68112861935766</v>
       </c>
       <c r="C7" t="n">
-        <v>16.79803379703621</v>
+        <v>16.79803379703623</v>
       </c>
       <c r="D7" t="n">
-        <v>27.80690719456105</v>
+        <v>27.80690719456111</v>
       </c>
       <c r="E7" t="n">
-        <v>16.79516427162927</v>
+        <v>16.7951642716293</v>
       </c>
       <c r="F7" t="n">
-        <v>16.79516427162927</v>
+        <v>16.7951642716293</v>
       </c>
       <c r="G7" t="n">
-        <v>21.28027203439352</v>
+        <v>21.28027203439355</v>
       </c>
       <c r="H7" t="n">
-        <v>34.81458021438243</v>
+        <v>34.81458021438252</v>
       </c>
       <c r="I7" t="n">
-        <v>16.79673789308461</v>
+        <v>16.79673789308463</v>
       </c>
       <c r="J7" t="n">
-        <v>19.54634428217926</v>
+        <v>19.5463442821793</v>
       </c>
       <c r="K7" t="n">
-        <v>18.60634926535309</v>
+        <v>18.60634926535312</v>
       </c>
       <c r="L7" t="n">
-        <v>30.5839243298504</v>
+        <v>30.58392432985048</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.72833378286339</v>
+        <v>30.72833378286344</v>
       </c>
       <c r="C8" t="n">
-        <v>41.48843305575486</v>
+        <v>41.4884330557548</v>
       </c>
       <c r="D8" t="n">
-        <v>54.91211809362338</v>
+        <v>54.91211809362336</v>
       </c>
       <c r="E8" t="n">
-        <v>38.30405624012791</v>
+        <v>38.30405624012798</v>
       </c>
       <c r="F8" t="n">
-        <v>30.21266638466561</v>
+        <v>30.21266638466562</v>
       </c>
       <c r="G8" t="n">
-        <v>45.97102748249196</v>
+        <v>45.971027482492</v>
       </c>
       <c r="H8" t="n">
-        <v>59.50533566248193</v>
+        <v>59.50533566248204</v>
       </c>
       <c r="I8" t="n">
-        <v>41.48749334118307</v>
+        <v>41.48749334118311</v>
       </c>
       <c r="J8" t="n">
-        <v>44.23938802237072</v>
+        <v>44.23938802237076</v>
       </c>
       <c r="K8" t="n">
-        <v>31.43726950444461</v>
+        <v>31.43726950444467</v>
       </c>
       <c r="L8" t="n">
-        <v>67.43734166882267</v>
+        <v>67.4373416688227</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.84788125615498</v>
+        <v>28.84788125615502</v>
       </c>
       <c r="C9" t="n">
-        <v>32.51263536754176</v>
+        <v>32.51263536754189</v>
       </c>
       <c r="D9" t="n">
-        <v>43.52159726804078</v>
+        <v>43.52159726804089</v>
       </c>
       <c r="E9" t="n">
-        <v>37.7607569569453</v>
+        <v>37.76075695694539</v>
       </c>
       <c r="F9" t="n">
-        <v>32.51263797228547</v>
+        <v>32.51263797228551</v>
       </c>
       <c r="G9" t="n">
-        <v>36.99487360489915</v>
+        <v>36.99487360489925</v>
       </c>
       <c r="H9" t="n">
-        <v>50.52918178488818</v>
+        <v>50.52918178488817</v>
       </c>
       <c r="I9" t="n">
-        <v>32.51133946359028</v>
+        <v>32.51133946359031</v>
       </c>
       <c r="J9" t="n">
-        <v>35.26094585268491</v>
+        <v>35.26094585268496</v>
       </c>
       <c r="K9" t="n">
-        <v>31.68590890511465</v>
+        <v>31.68590890511467</v>
       </c>
       <c r="L9" t="n">
-        <v>46.29852590035607</v>
+        <v>46.29852590035613</v>
       </c>
     </row>
   </sheetData>
@@ -7649,13 +7649,13 @@
         <v>16.57948797539546</v>
       </c>
       <c r="D2" t="n">
-        <v>21.30223522389803</v>
+        <v>21.30223522389804</v>
       </c>
       <c r="E2" t="n">
-        <v>18.45025796663667</v>
+        <v>18.45025796663668</v>
       </c>
       <c r="F2" t="n">
-        <v>13.19607365975642</v>
+        <v>13.19607365975641</v>
       </c>
       <c r="G2" t="n">
         <v>20.75536692088559</v>
@@ -7667,10 +7667,10 @@
         <v>20.54733306260797</v>
       </c>
       <c r="J2" t="n">
-        <v>26.08307690433346</v>
+        <v>26.08307690433348</v>
       </c>
       <c r="K2" t="n">
-        <v>26.71234000711039</v>
+        <v>26.71234000711041</v>
       </c>
       <c r="L2" t="n">
         <v>21.25338360568872</v>
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.69827692679628</v>
+        <v>20.69827692679629</v>
       </c>
       <c r="C3" t="n">
-        <v>13.87197768723887</v>
+        <v>13.87197768723888</v>
       </c>
       <c r="D3" t="n">
-        <v>25.67457089042729</v>
+        <v>25.6745708904273</v>
       </c>
       <c r="E3" t="n">
         <v>16.95292200863025</v>
       </c>
       <c r="F3" t="n">
-        <v>8.278189508461443</v>
+        <v>8.278189508461445</v>
       </c>
       <c r="G3" t="n">
-        <v>21.80440568336622</v>
+        <v>21.80440568336623</v>
       </c>
       <c r="H3" t="n">
-        <v>21.04401045411336</v>
+        <v>21.04401045411339</v>
       </c>
       <c r="I3" t="n">
         <v>20.32681431546153</v>
       </c>
       <c r="J3" t="n">
-        <v>30.3419732858064</v>
+        <v>30.34197328580644</v>
       </c>
       <c r="K3" t="n">
         <v>30.51234877698178</v>
       </c>
       <c r="L3" t="n">
-        <v>25.37190234644115</v>
+        <v>25.37190234644116</v>
       </c>
     </row>
     <row r="4">
@@ -7723,34 +7723,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.43329499121022</v>
+        <v>12.43329499121023</v>
       </c>
       <c r="C4" t="n">
         <v>11.53928174599518</v>
       </c>
       <c r="D4" t="n">
-        <v>20.36743673788075</v>
+        <v>20.36743673788074</v>
       </c>
       <c r="E4" t="n">
-        <v>11.55888948956255</v>
+        <v>11.55888948956256</v>
       </c>
       <c r="F4" t="n">
         <v>11.55888948956255</v>
       </c>
       <c r="G4" t="n">
-        <v>14.16085201572669</v>
+        <v>14.16085201572666</v>
       </c>
       <c r="H4" t="n">
-        <v>13.19180954222724</v>
+        <v>13.19180954222725</v>
       </c>
       <c r="I4" t="n">
         <v>11.65271215721782</v>
       </c>
       <c r="J4" t="n">
-        <v>13.64316044032881</v>
+        <v>13.64316044032882</v>
       </c>
       <c r="K4" t="n">
-        <v>11.8631841886333</v>
+        <v>11.86318418863332</v>
       </c>
       <c r="L4" t="n">
         <v>19.7756839477247</v>
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.30069352828991</v>
+        <v>53.30069352828983</v>
       </c>
       <c r="C5" t="n">
-        <v>44.24287216067499</v>
+        <v>44.24287216067503</v>
       </c>
       <c r="D5" t="n">
-        <v>174.5050699860957</v>
+        <v>174.5050699860956</v>
       </c>
       <c r="E5" t="n">
-        <v>44.24288016377557</v>
+        <v>44.24288016377558</v>
       </c>
       <c r="F5" t="n">
-        <v>44.24288016377557</v>
+        <v>44.24288016377558</v>
       </c>
       <c r="G5" t="n">
-        <v>82.25234450167642</v>
+        <v>82.25234450167594</v>
       </c>
       <c r="H5" t="n">
-        <v>70.63443072790849</v>
+        <v>70.63443072790852</v>
       </c>
       <c r="I5" t="n">
-        <v>44.24203032853533</v>
+        <v>44.24203032853534</v>
       </c>
       <c r="J5" t="n">
-        <v>77.25006110077267</v>
+        <v>77.25006110077258</v>
       </c>
       <c r="K5" t="n">
-        <v>43.8101376406909</v>
+        <v>43.81013764069089</v>
       </c>
       <c r="L5" t="n">
-        <v>199.1197644140229</v>
+        <v>199.1197644140224</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.20559325478584</v>
+        <v>42.20559325478585</v>
       </c>
       <c r="C6" t="n">
-        <v>28.9575321964364</v>
+        <v>28.95753219643636</v>
       </c>
       <c r="D6" t="n">
-        <v>37.97784700187407</v>
+        <v>37.97784700187405</v>
       </c>
       <c r="E6" t="n">
-        <v>27.27406400684027</v>
+        <v>27.27406400684026</v>
       </c>
       <c r="F6" t="n">
         <v>29.04454022456637</v>
       </c>
       <c r="G6" t="n">
-        <v>43.93315027930235</v>
+        <v>43.9331502793023</v>
       </c>
       <c r="H6" t="n">
-        <v>42.69629721098856</v>
+        <v>42.69629721098858</v>
       </c>
       <c r="I6" t="n">
-        <v>41.42501042079347</v>
+        <v>41.42501042079346</v>
       </c>
       <c r="J6" t="n">
-        <v>31.96256200096348</v>
+        <v>31.96256200096347</v>
       </c>
       <c r="K6" t="n">
-        <v>29.20387270129698</v>
+        <v>29.20387270129697</v>
       </c>
       <c r="L6" t="n">
-        <v>37.21809504375395</v>
+        <v>37.21809504375393</v>
       </c>
     </row>
     <row r="7">
@@ -7846,34 +7846,34 @@
         <v>16.53160775460648</v>
       </c>
       <c r="C7" t="n">
-        <v>15.75186675275375</v>
+        <v>15.75186675275374</v>
       </c>
       <c r="D7" t="n">
-        <v>24.46566756818546</v>
+        <v>24.46566756818547</v>
       </c>
       <c r="E7" t="n">
-        <v>15.74936990608937</v>
+        <v>15.74936990608938</v>
       </c>
       <c r="F7" t="n">
-        <v>15.74936990608937</v>
+        <v>15.74936990608938</v>
       </c>
       <c r="G7" t="n">
-        <v>18.25916477912297</v>
+        <v>18.2591647791229</v>
       </c>
       <c r="H7" t="n">
-        <v>17.29012230562349</v>
+        <v>17.2901223056235</v>
       </c>
       <c r="I7" t="n">
-        <v>15.75102492061409</v>
+        <v>15.7510249206141</v>
       </c>
       <c r="J7" t="n">
-        <v>17.74147320372507</v>
+        <v>17.74147320372508</v>
       </c>
       <c r="K7" t="n">
-        <v>15.96149695202957</v>
+        <v>15.96149695202956</v>
       </c>
       <c r="L7" t="n">
-        <v>23.87399671112097</v>
+        <v>23.87399671112096</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.53309907372887</v>
+        <v>28.53309907372894</v>
       </c>
       <c r="C8" t="n">
-        <v>38.34389415469671</v>
+        <v>38.34389415469682</v>
       </c>
       <c r="D8" t="n">
-        <v>49.25405367854916</v>
+        <v>49.25405367854927</v>
       </c>
       <c r="E8" t="n">
-        <v>35.44743447755601</v>
+        <v>35.4474344775561</v>
       </c>
       <c r="F8" t="n">
-        <v>28.08763115752007</v>
+        <v>28.08763115752015</v>
       </c>
       <c r="G8" t="n">
-        <v>40.85140763322239</v>
+        <v>40.85140763322249</v>
       </c>
       <c r="H8" t="n">
-        <v>39.88236515972287</v>
+        <v>39.882365159723</v>
       </c>
       <c r="I8" t="n">
-        <v>38.34326777471352</v>
+        <v>38.34326777471366</v>
       </c>
       <c r="J8" t="n">
-        <v>40.33579744481564</v>
+        <v>40.33579744481577</v>
       </c>
       <c r="K8" t="n">
-        <v>27.766259624016</v>
+        <v>27.76625962401608</v>
       </c>
       <c r="L8" t="n">
-        <v>57.52916512854227</v>
+        <v>57.52916512854245</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.4599388813469</v>
+        <v>25.45993888134689</v>
       </c>
       <c r="C9" t="n">
         <v>28.43996019883996</v>
       </c>
       <c r="D9" t="n">
-        <v>37.15384485513816</v>
+        <v>37.15384485513815</v>
       </c>
       <c r="E9" t="n">
-        <v>32.77865435143035</v>
+        <v>32.77865435143033</v>
       </c>
       <c r="F9" t="n">
-        <v>28.43996694450928</v>
+        <v>28.43996694450927</v>
       </c>
       <c r="G9" t="n">
-        <v>30.94725822520918</v>
+        <v>30.94725822520913</v>
       </c>
       <c r="H9" t="n">
-        <v>29.97821575170972</v>
+        <v>29.9782157517097</v>
       </c>
       <c r="I9" t="n">
-        <v>28.43911836670032</v>
+        <v>28.43911836670033</v>
       </c>
       <c r="J9" t="n">
-        <v>30.42956664981128</v>
+        <v>30.42956664981126</v>
       </c>
       <c r="K9" t="n">
-        <v>26.471170146965</v>
+        <v>26.47117014696496</v>
       </c>
       <c r="L9" t="n">
-        <v>36.56209015720719</v>
+        <v>36.56209015720717</v>
       </c>
     </row>
   </sheetData>
